--- a/output/BBC6 Music Log.xlsx
+++ b/output/BBC6 Music Log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F295"/>
+  <dimension ref="A1:F320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9878,6 +9878,806 @@
       <c r="F295" s="2" t="inlineStr">
         <is>
           <t>https://www.deezer.com/track/3956957011</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Richard Dawson</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Jogging</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/711704202</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Dubstar</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Stars</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1217625382</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Field Music</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Disappointed</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/133755428</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Prefab Sprout</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>The King of Rock 'N' Roll</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1130916</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>The Golden Virgins</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Renaissance Kid</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/935304</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Maxïmo Park</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Books from Boxes</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3616010452</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Frankie &amp; the Heartstrings</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Hunger</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/30252211</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Sneaker Pimps</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Spin Spin Sugar</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/752086972</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>The Futureheads</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Decent Days And Nights</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/727001</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Sam Fender</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Seventeen Going Under</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1420205872</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Koudlam</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>See You All</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1265558302</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Phil Lynott</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Old Town</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2256801247</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Joy Division</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Disorder</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/741235352</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Mac DeMarco</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>20191009 I Like Her</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2238193697</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>A$AP Rocky</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Praise The Lord (Da Shine) (feat. Skepta)</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/503169162</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>The Reels</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>This Guy's In Love (With You...)</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1879867277</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>The Voidz</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>7 Horses</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2878320772</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>The Voidz</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Square Wave</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2878320752</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Al Green</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>For the Good Times</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/136370908</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>The Doors</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Universal Mind (Live in Pittsburgh, May 2, 1970)</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/66769932</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Cornershop</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Natch</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/9834047</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Oasis</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Live Forever</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/987064552</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Prince Buster</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Al Capone</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/8596564</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Crack Cloud</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Marathon of Hope</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3756791092</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Joni Mitchell</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>This Flight Tonight</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2607673</t>
         </is>
       </c>
     </row>
@@ -10177,6 +10977,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F293" r:id="rId292"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F294" r:id="rId293"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F320" r:id="rId319"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/BBC6 Music Log.xlsx
+++ b/output/BBC6 Music Log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F320"/>
+  <dimension ref="A1:F474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10678,6 +10678,4934 @@
       <c r="F320" s="2" t="inlineStr">
         <is>
           <t>https://www.deezer.com/track/2607673</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Mug</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Brace Yourself</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1391821392</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Leslie Winer</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>When I Was Walt Whitman</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3185324791</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Mega Bog</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Obsidian Lizard</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1357895612</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Buffalo Daughter</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Socks, Drugs And Rock'n'roll</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2201084047</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Sneaks</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Down in the Woods</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3550775091</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Juana Molina</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Al oeste</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/142471797</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>WORLD BRAIN</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Minute papillon</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2764687591</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Prewn</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3447260691</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Bernthøler</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Pardon Up Here</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/142713316</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>molto morbidi</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>So Perfect the Loose Ends</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3899269671</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Alex Cameron</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Real Bad Lookin'</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/128855338</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Tame Impala</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Why Won't They Talk To Me?</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/60765506</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Bryan Ferry</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Slave To Love</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3152105</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Julee Cruise</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Movin' in on You</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/5620017</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Don Williams</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Some Broken Hearts Never Mend</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/594866492</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Frankie Newton</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Minor Jive</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/519536532</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Grimes</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Zoal, Face Dancer</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2725724751</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>El Wali</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Long Live the Sahrawi Army</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/765569992</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Strawberry Switchblade</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Since Yesterday</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/376010071</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>The Voidz</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Prophecy of The Dragon</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2878320762</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Kate Bush</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Why Should I Love You?</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2175439087</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Bix Beiderbecke</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>I'm Coming Virginia</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13398723</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>black midi</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>John L</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1259986392</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Crack Cloud</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Ouster Stew</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1865889797</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Crack Cloud</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Favour Your Fortune</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1865889787</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Crack Cloud</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Swish Swash</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/567894312</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Eva Petersen</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Melody</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/60852805</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>The Who</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>I Can't Explain</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/136341588</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Jesca Hoop</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Playground</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3788310712</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Ween</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Blue Balloon</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3833949881</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Kris Kristofferson</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Sunday Morning Coming Down</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/125000498</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Neu!</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Isi</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2693567972</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Wonky Alice</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Caterpillars</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1030389662</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Personal Trainer</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Punch Drunk Love</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3919908481</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Atomic Rooster</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Devil's Answer</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3808825292</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Immersion</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>We Don't Need Your Validation</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3993213531</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Wild Billy Childish &amp; CTMF</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Have You Seen the Devil?</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3840121541</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Gichard</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Your Private Hell</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3864481661</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Lime Garden</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>All Bad Parts</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3681569202</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Lowertown</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Worst Friend</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3855304791</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Rostam</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Back of a Truck</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3911628971</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>ZEP</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>TRYNA DO</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3993168661</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Miracle</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>PVC Vest</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3913381561</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>MADMADMAD</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Overload</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3957452531</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>media puzzle</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Knowledge</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3883541861</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Melter</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>I Think I Like It Here</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3964615011</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Warpaint</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Undertow</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2780210141</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>shortstraw.</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>pattern up</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3878855981</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>duendita</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>beach</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3892186741</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Adrenaline</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3959427051</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Ebbb</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Now You Know</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3946826981</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Jawdropped</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3958358491</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>RIP Magic</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Screwdark</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3941392001</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>BODEGA</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Pick up the Check</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3916680001</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Iceage</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>The Weak</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3870048731</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Dirty Projectors</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Stillness Is The Move</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4315630</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Cate Le Bon</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Sisters</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1925140357</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>The Knife</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>We Share Our Mothers Health</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1895198707</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>The All Seeing I</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Walk Like a Panther (feat. Tony Christie)</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/432048962</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Cabaret Voltaire</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Spies In The Wires (Remastered)</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/75373252</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Pulp</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Wickerman</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/66539172</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Big Truck</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Central Reservation Blues</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3912842831</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Nas</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>It Ain't Hard To Tell</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/77096696</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Sharon Van Etten</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Comeback Kid</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/603343352</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Underworld</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Dark &amp; Long</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/82265246</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Jockstrap</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>50/50</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1533769232</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>The Human League</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Love Action (I Believe In Love)</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3090431</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Yeah Yeah Yeahs</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Sacrilege</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/436622442</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>The Dandy Warhols</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>We Used To Be Friends</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2126030287</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Blur</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Tracy Jacks</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/44134611</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>CeCe Rogers</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Someday</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2809969392</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>The Smiths</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>The Boy With The Thorn In His Side</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13785971</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Wet Leg</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>catch these fists</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3285890721</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Spanky Wilson</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Sunshine Of Your Love</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1851803517</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>TV on the Radio</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Wolf Like Me</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/558606542</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>O.T. Quartet</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Hold That Sucker Down</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/115715810</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Visage</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Fade To Grey</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2285082</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Lip Critic</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Talon</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3652968042</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Goldfrapp</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Ride A White Horse</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F399" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3801397272</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>The Shins</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>New Slang</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1137208172</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>One Way System</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Give Us A Future</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/59152341</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>The Exploited</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Jimmy Boyle</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1526371482</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Love</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>7 and 7 Is</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1919926027</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Mykki Blanco</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Free Ride</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F404" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1278096022</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>The Specials</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Too Much Too Young</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2112694557</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>New Young Pony Club</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Ice Cream</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F406" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1139907</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Transit Kings</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Japanese Cars</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F407" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/10579263</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Pixies</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Monkey Gone to Heaven</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F408" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/936906</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Stevie Wonder</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Another Star</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F409" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/676011732</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Bonobo</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Rosewood</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F410" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1514341902</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Cubic 22</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Night In Motion</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F411" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/10352775</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Friends</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>I'm His Girl</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/139955057</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Vampire Weekend</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>A-Punk</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F413" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/66537484</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>07:46</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Broadcast</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Come On Let's Go</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F414" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/29374671</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Lauryn Hill</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Doo Wop (That Thing)</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F415" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/15586242</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>07:27</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>The Four Seasons</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Beggin'</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F416" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/80206740</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>07:13</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Wolf Alice</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Bros</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F417" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/101901861</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>07:08</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Jamie xx</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Gosh</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F418" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1036734852</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>S’Express</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Theme From S-Express</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F419" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2206502417</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>06:57</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>A Tribe Called Quest</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Buggin' Out</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2465904</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>New Young Pony Club</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>We Want To</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F421" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1674206107</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Fat Dog</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Running</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F422" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2724694691</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>06:27</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Panda Bear</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Boys Latin</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F423" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/92174070</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Primal Scream</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Loaded</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F424" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1912736557</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Arctic Monkeys</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Opening Night</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F425" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3783510512</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Solange</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Cranes In The Sky</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F426" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/133103636</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Ashaye</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Dreaming (Jungle Mix)</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F427" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1178174122</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>05:53</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Sun Kil Moon</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>New Orleans Morning</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3959115721</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>05:45</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>TOKiMONSTA &amp; PARTYOF2</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Feel It</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F429" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3422904981</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>05:41</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Aluna &amp; SIDEPIECE</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Misbehave</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3702217912</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>05:34</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Hole</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Violet</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F431" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/6604067</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>05:20</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Young Fathers</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Toy</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/450956922</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>05:11</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>S.G. Goodman</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Pepper</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F433" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3926107411</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Freeez</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>I.O.U.</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F434" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/936925</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>04:56</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Eurythmics</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Sweet Dreams (Are Made Of This)</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F435" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/561836</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>04:53</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Depeche Mode</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Everything Counts</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F436" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/68513660</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>04:44</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Gary Numan</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>M.E.</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F437" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/938543</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>04:39</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Bronski Beat</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Smalltown Boy</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F438" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/428735732</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>04:23</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>James Blake</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Death Of Love</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F439" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3842356261</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Fiona Apple</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Sleep To Dream</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F440" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/82292998</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>04:16</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Future Utopia</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Queen L</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F441" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1935679427</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>04:12</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Nation of Language</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Tougher Than The Rest</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F442" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3899510021</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>04:01</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Neil Young &amp; Crazy Horse</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Like A Hurricane</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F443" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/135377002</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>03:56</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Joy Division</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Atmosphere</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F444" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/797409</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>03:34</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Shygirl</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Cleo</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F445" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1515510842</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>03:25</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>J Dilla</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Workinonit</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F446" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/445960822</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>03:02</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>SBTRKT</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Wildfire</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F447" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/12292186</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>02:51</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Aretha Franklin</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>See Saw</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F448" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/144993836</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>02:47</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Squeeze</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Cool For Cats</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F449" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/524135482</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>02:46</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Garbage</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Milk</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F450" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1761472037</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>02:34</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Fleet Foxes</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>He Doesn't Know Why</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F451" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/75624088</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>02:27</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Robyn</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Sexistential</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F452" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3882885821</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>02:24</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Viagra Boys</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>The Bog Body</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F453" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3315433351</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>02:21</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Camera Obscura</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>French Navy</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F454" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/66537207</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>02:17</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Liquid</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Sweet Harmony</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F455" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2264408737</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>02:14</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Todd Rundgren</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>I Saw The Light</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F456" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/672389</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Tame Impala</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Elephant</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F457" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/60765509</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>02:07</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Jurassic 5</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>What's Golden</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F458" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2125122</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>02:02</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>LCD Soundsystem</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>All My Friends</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F459" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3110852</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>01:53</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Longpigs</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>She Said</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F460" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2526103</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>The Bucketheads</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>The Bomb! (These Sounds Fall Into My Mind)</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F461" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/85318128</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Amerie</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>1 Thing</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2553109</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>01:37</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Curtis Harding</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Need Your Love</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F463" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/412184692</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>01:35</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Elastica</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Waking Up</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F464" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/97089134</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>01:28</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>King Krule</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Easy Easy</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F465" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/69044614</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>01:21</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>D’Angelo</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Brown Sugar</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/139103999</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>01:13</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>The Crusaders</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Street Life</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F467" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1142755</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>01:01</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>PJ Harvey</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>This Is Love</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1172886</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>00:47</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Regina Spektor</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Us</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F469" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/787905</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>00:34</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Talking Heads</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>And She Was</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/747622</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>00:27</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>NewDad</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Nightmares</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F471" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2605449522</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>00:17</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Cindy</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Procession</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F472" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3765422862</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>00:12</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Television</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Marquee Moon</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F473" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/718312</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>00:02</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Childish Gambino</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Redbone</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F474" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/435821782</t>
         </is>
       </c>
     </row>
@@ -11002,6 +15930,160 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F318" r:id="rId317"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F319" r:id="rId318"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F410" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F411" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F412" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F413" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F414" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F415" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F416" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F417" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F418" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F419" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F420" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F421" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F422" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F423" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F424" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F425" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F426" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F427" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F428" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F429" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F430" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F431" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F432" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F433" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F434" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F435" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F436" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F437" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F438" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F439" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F440" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F441" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F442" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F443" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F444" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F445" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F446" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F447" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F448" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F449" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F450" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F451" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F452" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F453" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F454" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F455" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F456" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F457" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F458" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F459" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F460" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F461" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F462" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F463" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F464" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F465" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F466" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F467" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F468" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F469" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F470" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F471" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F472" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F473" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F474" r:id="rId473"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/BBC6 Music Log.xlsx
+++ b/output/BBC6 Music Log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F474"/>
+  <dimension ref="A1:F611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15606,6 +15606,4390 @@
       <c r="F474" s="2" t="inlineStr">
         <is>
           <t>https://www.deezer.com/track/435821782</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Tommy Barlow</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Earth Killer</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F475" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3959425471</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Boards of Canada</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Prophecy At 1420 MHz</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F476" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4007330451</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Yard Act</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Redeemer</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F477" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3994993521</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Benny Goodman</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Good-Bye</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/15780626</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Brian Eno</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Golden Hours</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F479" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3093674</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Brian Eno</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Another Green World</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F480" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3093671</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Altered Images</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Don't Talk to Me About Love</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F481" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2484903</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Leonard Cohen</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Hey, That's No Way To Say Goodbye</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F482" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/15218940</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>English Chamber Orchestra</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Variations on a theme of Frank Bridge, Op. 10 - IX. Funeral March</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F483" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/65727976</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>The Growlers</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Night Ride</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F484" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/745918212</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Eric Clapton</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Promises</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F485" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2178235</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>The Voidz</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Flexorcist</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F486" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2878320792</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Weyes Blood</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Everyday</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F487" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1137130782</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>The Human League</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Don't You Want Me</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F488" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3092940</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>British Birds</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Christian</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F489" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3916327141</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>RAYE</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>WHERE IS MY HUSBAND!</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F490" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3548216281</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>The Nightingales</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Paraffin Brain</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F491" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1685899077</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Pond</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Two Hands</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F492" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3906893951</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Four Tet</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Two Thousand And Seventeen</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F493" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/410613892</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Beth Orton</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F494" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3698719192</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Johnny Clarke</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Peace in the Ghetto</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F495" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3785934502</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Johnny Cash</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Hurt</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F496" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/128846783</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Office Dog</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Gold Things</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F497" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3945724921</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Irked</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Settle Down</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F498" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3918136621</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Amon Düül II</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Explode Like a Star</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F499" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/85956919</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Modern Woman</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Johnny's Dreamworld</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F500" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3718048642</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>The Chemical Brothers</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Setting Sun</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F501" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3252246</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Crying Loser</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Eat the Evidence</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F502" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3849661451</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Propaganda</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Duel</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F503" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1483921922</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>The Claypool Lennon Delirium</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Meat Machines</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F504" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3810805342</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Damaged Bug</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Junk Food</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F505" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3834637741</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>New York Dolls</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Pills</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F506" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2598234</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>IZCO</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Somebody Jump (feat. Reek0)</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F507" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3761624602</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Moonstarr</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Greed (Moonstarr Remix)</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F508" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1755734437</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>IZCO</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Longest Road (feat. PK)</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F509" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3761624582</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>The Streets</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Has It Come To This?</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F510" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/6112946</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>IZCO</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Dinero (feat. P Wavey)</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F511" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3761624552</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Peaches</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Whatcha Gonna Do About It</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F512" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3678869202</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Bathing Suits</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Swan Princess</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F513" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3898671711</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Steady Weather</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Walk Into The Light</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F514" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3968350871</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Gout</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Junk Sick</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F515" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3919006691</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>total tommy</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Pretty Little Mouth</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F516" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3936195111</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Kulku</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Dive In (Live at Stereo Club Glasgow)</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F517" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3960125921</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Ketan Jandoo</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Shaolin Lingerie</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F518" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3960126001</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Sylvie's Head</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Frankie</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F519" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3860930501</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>La Roux</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Cabin Fever</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F520" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3979223421</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Truthpaste</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Never Gonna Give</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F521" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3861843791</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Karen Nyame KG</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>In My Room</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F522" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3922585441</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Pigs Pigs Pigs Pigs Pigs Pigs Pigs</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Stitches</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F523" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3140406511</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Toots &amp; The Maytals</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Pressure Drop</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F524" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/549291992</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Idlewild</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>When I Argue I See Shapes</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F525" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3104761</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Alison Limerick</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Where Love Lives</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F526" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1057873</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Moonchild Sanelly</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Big Booty</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F527" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2871824642</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Doechii</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Nosebleeds</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F528" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3214315851</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>shame</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>One Rizla</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F529" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/440367672</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Squeeze</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Pulling Mussels (From The Shell)</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F530" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/932571</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Hole</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Celebrity Skin</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F531" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2229884</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Arctic Monkeys</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Mardy Bum</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F532" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4315317</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Dick Dale</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Misirlou</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F533" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1582164192</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Super Furry Animals</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Northern Lites</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F534" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3816549882</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Lykke Li</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Sadness Is A Blessing</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F535" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/9962978</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>MJ Lenderman</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Wristwatch</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F536" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2823026282</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Cardinals</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>She Makes Me Real</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F537" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3550260141</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Cassius</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Feeling For You</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F538" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/120536274</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>The Futureheads</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Hounds Of Love</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F539" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/746946</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>New Order</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Bizarre Love Triangle</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F540" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2481156</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Anna Erhard</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Botanical Garden</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F541" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2684522742</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>George Kranz</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Din daa daa</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F542" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/11563563</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Eyre Llew</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Bloom</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F543" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3825600381</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Yazmin Lacey</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Two Steps</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F544" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3606667862</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Ozric Tentacles</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Vita Voom</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F545" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1677332</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Frank Zappa</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>I'm The Slime</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F546" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/53946491</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Guthrie Govan</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Sevens</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F547" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3009235541</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Angie Stone</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Life Story</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F548" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/57859921</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>High Vis</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Guided Tour</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F549" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3039770701</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Siouxsie and the Banshees</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Love In A Void</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F550" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1148087</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>The Breeders</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>I Just Wanna Get Along</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F551" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/378817771</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Placebo</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Lady of the Flowers (RE:CREATED VERSION)</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F552" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3962751721</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Water Underground</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F553" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2515514491</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Lava La Rue</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Push N Shuv</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F554" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2630856452</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>07:17</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Sade</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Smooth Operator</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F555" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/10686127</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>07:13</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>The Style Council</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Shout To The Top</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F556" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2303034</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>07:09</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Steve Monite</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Only You</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F557" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1685313627</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Röyksopp</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>The Girl and the Robot (feat. Robyn)</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F558" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3307073641</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>06:59</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>J Dilla</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>U-Love</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F559" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/445961072</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Tame Impala</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Let It Happen</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F560" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/103052650</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Katie Alice Greer</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Come and Let Me Know</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F561" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3856124871</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>06:34</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Dinosaur Jr.</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Freak Scene</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F562" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/764758202</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Beastie Boys</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Intergalactic</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F563" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4013664</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Dr. Octagon</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Earth People</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F564" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1762695737</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>The RAH Band</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Clouds Across The Moon</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F565" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/12540257</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>06:14</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Air</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Kelly Watch The Stars</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F566" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/41296711</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Ian Brown</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>My Star</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F567" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/655843322</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Spiritualized</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Ladies and gentlemen we are floating in space</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F568" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/901455242</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>05:59</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Baba Stiltz &amp; Okay Kaya</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Gloria</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F569" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3680029262</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>05:54</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Todd Rundgren</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Hello It's Me</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F570" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1428566</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Pigeon</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Black James Dean</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F571" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3718400302</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>05:15</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Tiga</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>HIGH ROLLERS</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F572" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3582194171</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>05:11</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>808 State</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>In Yer Face</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F573" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1878241817</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>05:05</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Peaches</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Boys Wanna Be Her</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F574" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/937449</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>04:56</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>KH</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Looking At Your Pager</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F575" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1733196237</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>04:53</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>M.I.A.</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Bamboo Banga</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F576" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/943350</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>04:47</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Nitin Sawhney</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Homelands</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F577" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/398323442</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>04:43</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Nabihah Iqbal</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Sunflower</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F578" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2184030387</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>04:40</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Jai Paul</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>BTSTU</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F579" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/32936141</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>04:21</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Tinariwen</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Toumast Tincha</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F580" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3419532911</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>04:18</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Mount Palomar</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Little Fractures (feat. Pip Blom)</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F581" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3899859001</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>04:12</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>TOMORA</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>A BOY LIKE YOU</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F582" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3952507701</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>04:07</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Shell Of Light</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F583" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/80546742</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>04:01</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Yves Tumor</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Gospel For A New Century</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F584" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/880406332</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>03:58</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>H31R</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Backwards</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F585" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2421807955</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>03:33</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Barrington Levy</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Black Roses</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F586" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/403535212</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>03:27</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Teenage Fanclub</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Sparky's Dream</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F587" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/98008594</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>03:01</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Nick Drake</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Northern Sky</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F588" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2435239275</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>02:47</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>TEED</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Garden</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F589" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/14113473</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Pink Floyd</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>See Emily Play</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F590" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/116914280</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>02:25</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>The Smashing Pumpkins</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Today</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F591" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/15715634</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>02:21</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Khruangbin</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Time (You And I)</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F592" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/897339462</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>02:17</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Wu-Tang Clan</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Method Man</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F593" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/865480</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>02:14</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Superorganism</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Everybody Wants To Be Famous</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F594" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/432213132</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>02:08</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Hyperballad</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F595" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/14611474</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>02:05</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Jon Hopkins</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Luminous Beings</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F596" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/463054902</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>02:02</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Missy Elliott</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>We Run This</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F597" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/662596</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>01:47</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Japanese Breakfast</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Be Sweet</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F598" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1257797152</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>01:41</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>William Onyeabor</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Fantastic Man</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F599" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/70769616</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>01:38</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Warpaint</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>New Song</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F600" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/138547683</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>01:34</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>MGMT</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Kids</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F601" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/536485</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>01:28</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>France Gall</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Laisse Tomber Les Filles</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F602" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/110873534</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>01:21</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>The Horrors</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>I Can See Through You</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F603" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/62650906</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>01:16</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Finn Wolfhard</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>I'll Let You Finish</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F604" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3950073701</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>01:13</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>The Clash</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>The Guns Of Brixton</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F605" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/69924608</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>00:54</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>The Beta Band</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Dry The Rain</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F606" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/453207752</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>00:48</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Bogle</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Lost</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F607" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1637451162</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>00:43</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Kate Bush</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Babooshka</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F608" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2173947627</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>00:34</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>The Cribs</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Come On, Be A No-One</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F609" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/30781481</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>00:26</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Anna Smyrk</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Crying in an Internet Cafe</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F610" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3770500962</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Girl From Mars</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F611" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3773634912</t>
         </is>
       </c>
     </row>
@@ -16084,6 +20468,143 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F472" r:id="rId471"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F473" r:id="rId472"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F474" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F475" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F476" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F477" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F478" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F479" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F480" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F481" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F482" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F483" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F484" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F485" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F486" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F487" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F488" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F489" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F490" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F491" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F492" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F493" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F494" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F495" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F496" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F497" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F498" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F499" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F500" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F501" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F502" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F503" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F504" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F505" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F506" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F507" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F508" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F509" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F510" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F511" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F512" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F513" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F514" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F515" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F516" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F517" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F518" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F519" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F520" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F521" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F522" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F523" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F524" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F525" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F526" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F527" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F528" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F529" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F530" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F531" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F532" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F533" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F534" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F535" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F536" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F537" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F538" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F539" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F540" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F541" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F542" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F543" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F544" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F545" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F546" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F547" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F548" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F549" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F550" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F551" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F552" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F553" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F554" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F555" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F556" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F557" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F558" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F559" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F560" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F561" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F562" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F563" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F564" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F565" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F566" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F567" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F568" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F569" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F570" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F571" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F572" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F573" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F574" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F575" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F576" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F577" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F578" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F579" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F580" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F581" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F582" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F583" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F584" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F585" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F586" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F587" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F588" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F589" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F590" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F591" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F592" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F593" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F594" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F595" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F596" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F597" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F598" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F599" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F600" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F601" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F602" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F603" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F604" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F605" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F606" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F607" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F608" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F609" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F610" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F611" r:id="rId610"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/BBC6 Music Log.xlsx
+++ b/output/BBC6 Music Log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F611"/>
+  <dimension ref="A1:F760"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19990,6 +19990,4774 @@
       <c r="F611" s="2" t="inlineStr">
         <is>
           <t>https://www.deezer.com/track/3773634912</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>james K</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Ultra Facial!</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F612" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1489722222</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>19:37</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Daphni</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Sad Piano House</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F613" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3631235012</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Nabihah Iqbal</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Gentle Heart</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F614" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2171912797</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>System Olympia</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>BABE</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F615" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3818195061</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Crazy P</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Like A Fool</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F616" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/98845938</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Four Tet</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F617" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3936228341</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Floating Points</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Sea-Watch</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F618" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/763460262</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Bicep</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Atlas</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F619" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1101165382</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Laurence Guy</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Saw You for the First Time</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F620" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3575504231</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Joy Orbison &amp; Léa Sen</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Better</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F621" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1441790122</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Kelly Lee Owens</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Time To</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F622" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2883993252</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Orbital</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Halcyon and On and On</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F623" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1724869067</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Michael James</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Caffeine</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F624" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2334574635</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>King Kooba</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>You're (So Fine)</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F625" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/12263166</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>DJ Split</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>The Flower (Basement of Love Mix)</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F626" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3733152012</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Dav</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Messmaker</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F627" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/65250543</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>The White Stripes</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Jolene (live Under Blackpool Lights)</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F628" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1164738362</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Silver Jews</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Random Rules</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F629" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/479827782</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Mac DeMarco</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Out Of My Head</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F630" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1097261652</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Japanese Breakfast</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Kokomo, IN</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F631" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1257797162</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Big Thief</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Vampire Empire</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F632" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2421606815</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Lambchop</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Up With People</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F633" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3551281991</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Meat Puppets</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Up on the Sun</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F634" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/12516354</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>CMAT</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>I Wanna Be a Cowboy, Baby!</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F635" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1875454887</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Wilco &amp; Billy Bragg</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>California Stars</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F636" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2217004687</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>The Shins</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Gone For Good</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F637" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2459695005</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Alabama Shakes</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Hold On</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F638" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1981014397</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Pavement</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Father To A Sister Of Thought</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F639" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/105280968</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Elderberry Wine</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F640" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3319539481</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Beck</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Sissyneck</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F641" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/971422922</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Kings of Leon</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>California Waiting</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F642" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/552795612</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Super Furry Animals</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Ohio Heat</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F643" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3805799772</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Goat Girl</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Sad Cowboy</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F644" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1080089122</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>The Charlatans</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>North Country Boy</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F645" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/620486542</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Styrofoam Winos</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Next Thing</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F646" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3871545731</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Westside Cowboy</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Alright Alright Alright</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F647" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3418388371</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Divorce</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Antarctica</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F648" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3515450571</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Jagwar Ma</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Come Save Me</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F649" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3877003401</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Beck</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F650" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/422033092</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>JJerome87</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Brush Me Like A Horse</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F651" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3787881062</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>The War on Drugs</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Holding On</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F652" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/395723742</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>CMAT</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Stay for Something</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F653" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2401014305</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Tame Impala</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Solitude Is Bliss</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F654" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/572099612</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Stevie Wonder</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>All Day Sucker (Album Version)</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F655" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/608696412</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Stevie Wonder</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>All I Do</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F656" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2314443</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Stevie Wonder</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Love's In Need Of Love Today</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F657" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/676011572</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Black Uhuru</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Shine Eye Gal</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F658" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/822651332</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Harvey Mason</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>On And On</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F659" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/493135942</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Voilaaa &amp; Pat Kalla</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Le Disco Des Capitales</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F660" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/509752962</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Annahstasia</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Satisfy Me</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F661" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3245221851</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Say She She</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>C'est Si Bon</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F662" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2353834365</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Gorillaz</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Strobelite (feat. Peven Everett)</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F663" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/354195891</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Laid Back</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>White Horse</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F664" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3528855</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Nina Simone</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Funkier Than A Mosquito's Tweeter</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F665" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/66789278</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Commodores</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Brick House (12\" Mix)</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F666" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2179876</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Khruangbin</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Evan Finds the Third Room</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F667" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/445086962</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Frankie Knuckles</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Your Love</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F668" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1600906202</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Musique</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Keep On Jumpin'</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F669" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/68075779</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>M-Beat, Nazlyn</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Sweet Love</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F670" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4481742</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Basement Jaxx</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Where's Your Head At</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F671" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2661882</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Sampa the Great</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Final Form</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F672" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/680997892</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Gwen Guthrie</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Peanut Butter (Larry Levan Mix)</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F673" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/97925716</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>The Coral</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Dreaming Of You</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F674" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/119871084</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>808 State</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Pacific 707</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F675" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/478179352</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Funkadelic</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>One Nation Under A Groove</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F676" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/100492764</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>KNEECAP</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Liars Tale</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F677" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3722704482</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>KNEECAP</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Irish Goodbye (feat. Kae Tempest)</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F678" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3722704572</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>KNEECAP</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Smugglers &amp; Scholars</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F679" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3722704452</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Best Coast</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Boyfriend</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F680" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3945005191</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Mike D</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Switch Up</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F681" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4001466011</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>EELS</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>I Like Birds</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F682" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2075697017</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Jungle</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Back On 74</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F683" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2181330357</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Fat Dog</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>King of the Slugs</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F684" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2724694661</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Human Behaviour</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F685" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/14611450</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Sigur Rós</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Hoppípolla</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F686" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/607726822</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>The Darling Buds</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Hit The Ground</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F687" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/5318731</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Night Swimming</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Poison Berry</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F688" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3776350942</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Los Campesinos!</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Romance Is Boring</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F689" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1550718792</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Aretha Franklin</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>The House That Jack Built</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F690" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2133625</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Trying To Be Cool</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F691" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3025925711</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>The Velvet Underground</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Rock &amp; Roll</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F692" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/109844090</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>A Tribe Called Quest</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Can I Kick It?</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F693" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3311319751</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>The Libertines</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Don't Look Back Into the Sun</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F694" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/945223</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Darwin Deez</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Constellations</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F695" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/771179202</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Jayda G</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Both Of Us</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F696" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/959942152</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>LEMONSUCKR</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Stain</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F697" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3960912221</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Tame Impala</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Apocalypse Dreams</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F698" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/60765503</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>The Prodigy</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Everybody in the Place</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F699" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1115341512</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Gloria Jones</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Tainted Love</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F700" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3475976</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Pulp</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Babies</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F701" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/909996</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Arctic Monkeys</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>I Bet You Look Good On The Dancefloor</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F702" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4315310</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Chaka Khan</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Like Sugar</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F703" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/630799822</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Death Cab for Cutie</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>The Sound Of Settling</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F704" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/71511140</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Patti Jo</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Make Me Believe In You</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F705" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/732842512</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Big Thief</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Shark Smile</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F706" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2840205812</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>The Cardigans</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Lovefool</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F707" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/910474</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Empire of the Sun</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Walking On A Dream</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F708" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4286051</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Dirty Projectors</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Overlord</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F709" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/900951542</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Mogwai</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Glasgow Mega-Snake</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F710" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3836806</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Yeah Yeah Yeahs</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Gold Lion</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F711" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/24218911</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>The Sugarcubes</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Hit</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F712" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/14639484</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Blackalicious</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Alphabet Aerobics</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F713" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/12191213</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Janelle Monáe</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Tightrope (feat. Big Boi)</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F714" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/6030261</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>New Order</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Age Of Consent</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F715" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/107907786</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>The Charlatans</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>The Only One I Know</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F716" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/5867013</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>07:17</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>The Smiths</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Hand In Glove</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F717" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13785961</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Le Tigre</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>TKO</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F718" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4681467</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Royel Otis</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>moody</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F719" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3349000671</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Bel Cobain</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Mind is a Dancer</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F720" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3698469492</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>06:34</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>TLC</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>No Scrubs</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F721" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1075781</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>06:19</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Say She She</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Cut &amp; Rewind</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F722" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3378108841</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>06:17</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>La Sécurité</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Snack City</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F723" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3862396131</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>06:03</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Fatboy Slim</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Sunset (Bird Of Prey)</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F724" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/15688542</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>05:59</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Francis Bebey</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Forest Nativity</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F725" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2543691661</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>05:54</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Animal Collective</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Amazonawana / Anaconda Opportunity</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F726" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/353110571</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>05:46</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Kate Bush</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Aerial</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F727" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2175447557</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>05:43</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>The Durutti Column</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Sketch for Summer</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F728" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/432145262</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>05:40</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Cosmo Sheldrake</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Cuckoo Song</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F729" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2111535827</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>05:27</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Lauren Auder</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>praxis</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F730" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3560182991</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>05:21</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Florence the Machine</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Kiss With A Fist</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F731" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/7561776</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>05:01</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Maurice Joshua</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>This Is Acid</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F732" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/12894123</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>04:34</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Tensnake</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Coma Cat</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F733" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3155507821</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Madelline</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Expiration Dating</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F734" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3334763751</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>04:01</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Angélica Garcia</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F735" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3124676711</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>03:26</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Étienne de Crécy</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Am I Wrong</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F736" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2553669</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>03:21</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>LFO</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Freak</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F737" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/29394021</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>03:18</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Carl Cox</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>I Want You (Forever)</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F738" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1505204712</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>03:12</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Charles B.</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Lack Of Love</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F739" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/536506682</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>03:08</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Afrikan Boy</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Hit 'Em Up</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F740" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2019646047</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>03:02</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>MJ Cole</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Sincere</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F741" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/579927262</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>02:54</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Gat Décor</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Passion</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F742" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/89381103</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>02:50</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Cornershop</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Brimful of Asha</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F743" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/15686804</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>02:47</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>The Supremes</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Stoned Love</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F744" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1834450237</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>02:42</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>The KLF</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>What Time Is Love?</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F745" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1181472092</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Hercules &amp; Love Affair</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Blind</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F746" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3164619</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Alan Braxe &amp; Fred Falke</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Intro</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F747" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1702170497</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>02:28</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>The Donnas</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Take It Off</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F748" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3822563</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>02:18</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Charli xcx</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Rock Music</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F749" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4005499231</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>02:12</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Public Enemy</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Brothers Gonna Work It Out</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F750" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2120883</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>02:01</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>M83</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Reunion</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F751" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/75572710</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>01:50</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Gossip</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Where The Girls Are</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F752" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/30511141</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>01:46</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>RY-GUY</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Push Me In The Water</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F753" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3890380241</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>01:41</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Eve’s Plum</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>I Want It All</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F754" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/131339658</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>01:36</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Foals</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>What Went Down</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F755" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1232931722</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>01:10</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Black Sabbath</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Paranoid</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F756" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/74062292</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>01:02</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Groove Armada</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>I See You Baby</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F757" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/82299576</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>00:53</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Elbow</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Grounds For Divorce</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F758" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/429945972</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>00:49</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Johnny Marr</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Easy Money</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F759" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3803538582</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>00:31</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Primal Scream</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Rocks</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F760" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/85530824</t>
         </is>
       </c>
     </row>
@@ -20605,6 +25373,155 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F609" r:id="rId608"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F610" r:id="rId609"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F611" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F612" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F613" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F614" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F615" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F616" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F617" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F618" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F619" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F620" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F621" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F622" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F623" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F624" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F625" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F626" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F627" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F628" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F629" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F630" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F631" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F632" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F633" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F634" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F635" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F636" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F637" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F638" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F639" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F640" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F641" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F642" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F643" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F644" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F645" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F646" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F647" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F648" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F649" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F650" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F651" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F652" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F653" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F654" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F655" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F656" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F657" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F658" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F659" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F660" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F661" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F662" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F663" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F664" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F665" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F666" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F667" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F668" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F669" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F670" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F671" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F672" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F673" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F674" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F675" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F676" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F677" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F678" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F679" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F680" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F681" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F682" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F683" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F684" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F685" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F686" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F687" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F688" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F689" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F690" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F691" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F692" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F693" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F694" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F695" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F696" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F697" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F698" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F699" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F700" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F701" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F702" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F703" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F704" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F705" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F706" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F707" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F708" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F709" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F710" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F711" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F712" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F713" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F714" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F715" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F716" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F717" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F718" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F719" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F720" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F721" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F722" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F723" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F724" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F725" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F726" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F727" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F728" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F729" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F730" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F731" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F732" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F733" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F734" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F735" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F736" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F737" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F738" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F739" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F740" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F741" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F742" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F743" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F744" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F745" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F746" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F747" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F748" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F749" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F750" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F751" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F752" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F753" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F754" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F755" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F756" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F757" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F758" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F759" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F760" r:id="rId759"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/BBC6 Music Log.xlsx
+++ b/output/BBC6 Music Log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F760"/>
+  <dimension ref="A1:F879"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24758,6 +24758,3814 @@
       <c r="F760" s="2" t="inlineStr">
         <is>
           <t>https://www.deezer.com/track/85530824</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Sully</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F761" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2527470731</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>DJ Babatr</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>In Groove</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F762" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2691789902</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Objekt</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Chicken Garaage</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F763" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3017712121</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Batu</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Zeal</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F764" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2804882022</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>TSVI</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Kataklisma</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F765" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3882817201</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>DJ SWISHA &amp; OSSX</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>HOW U FEELIN</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F766" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2879457672</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Theo Kottis</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>Dark At 3pm</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F767" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3282407551</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>TSVI &amp; DJ Plead</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>Triple It</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F768" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3036228181</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Breaka</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>The Startup</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F769" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1080361832</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Anunaku &amp; DJ Plead</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>Clap Clap</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F770" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1489722402</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>TSVI</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Music Is Moving</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F771" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3882817171</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>TSVI</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>Hossam</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F772" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/558587492</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Anz</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>Clearly Rushing</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F773" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2322984875</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Overmono</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>BMW Track</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F774" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2064824217</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Olof Dreijer</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>Rosa Rugosa</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F775" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3826975621</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Erika de Casier &amp; Nick León</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>Bikini</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F776" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3315652511</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Bob Marley &amp; The Wailers</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>Satisfy My Soul</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F777" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2293793</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Goose Down</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>Hot Bread</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F778" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3930858661</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Tableek</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>Friends (feat. Suadela)</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F779" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3328468911</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>deary</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>Alma</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F780" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3702747882</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Broken Social Scene</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>Hey Amanda</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F781" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3783871632</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Kyla Kilzer &amp; Max Noir</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Break Through</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F782" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3631900002</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>The Royals</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>Pick Up The Pieces</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F783" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1293643592</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>lavender</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>Wake Up:Arms Too Long</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F784" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3935797821</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>The Loving Paupers</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>And The Piano's Playing</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F785" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/639058682</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Hak Baker</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Venezuela Riddim</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F786" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1875169377</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>Alexander IV</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>Midnight</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F787" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2335507895</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>Taiwan MC</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>Diskodub</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F788" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/90216079</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>SIMMS</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>Orbit</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F789" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3890470781</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>Herbie Hancock</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>Rockit</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F790" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/623838</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Baalti &amp; Lapgan</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Romance</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F791" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3907570941</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>The Clash</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>Overpowered By Funk</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F792" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/69962768</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>George Benson</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Love X Love</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F793" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/5094393</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Odyssey</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>Going Back To My Roots (12" Version)</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F794" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/424948112</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>Leroy Hutson</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>Blackberry Jam</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F795" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3050804301</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>Average White Band</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>You Got It</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F796" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4292963</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>The Perigents</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>Better Keep Movin'</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F797" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/77521989</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>The Dramatics</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>Get Up And Get Down</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F798" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13622519</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Johnnie Taylor</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>I Could Be President</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F799" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2202548</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Troy Keyes</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>Love Explosion</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F800" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/77521973</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Alice Clark</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>Charms Of The Arms Of Love</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F801" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3974934</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Melvin Davis</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>This Ain't The Way</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F802" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/7529243</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Dyke &amp; the Blazers</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>Funky Walk Part 1</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F803" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/86615605</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Marcia Griffiths</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>Mark My Word</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F804" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3785957262</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Margie Joseph</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>To Know You Is To Love You</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F805" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/6637268</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Buddy Miles</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>Memphis Train</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F806" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2184798</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>Leroy Hutson</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>Don't It Make You Feel Good</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F807" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3050804321</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>The Gap Band</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>Burn Rubber On Me</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F808" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/539098452</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Mamas Gun</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>The Proof</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F809" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3710770062</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Sonic Soul Orchestra, Daniel Thomas</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>Feel It (Bobby &amp; Steve Salsoul Piano End)</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F810" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3918262731</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Alexander O’Neal</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>Fake (Extended Version)</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F811" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/716517092</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>The Breaks</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>Snowballers</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F812" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3861823821</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Leroy Hutson</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>I Think I'm Falling In Love</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F813" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3050804271</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Bobby Womack</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>California Dreamin'</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F814" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3403716</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>The Womack Sisters</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>Chauffeur</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F815" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3956506721</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Earth, Wind &amp; Fire</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Magic Mind</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F816" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/27532891</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Matahari Sons</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>Dale Papi</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F817" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3514938731</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>06:37</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Nuevos Rios</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Malvada</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F818" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3752547382</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>06:34</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Dengue Dengue Dengue</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>Como Bailar Cumbia</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F819" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/77531454</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Baalti &amp; Lapgan</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Ipa Ma</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F820" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3907570911</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>06:24</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>Stereoripe</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Loud &amp; Decisive</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F821" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3886489441</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>06:23</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>LA GATA</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>KUiDAO</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F822" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3929950441</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Runkus</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>SUPERNOVA</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F823" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3791356902</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>06:14</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>Hagan</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>Mfantsefo Dance</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F824" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3911262341</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>05:43</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>Pixvae</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>EL PLATO DE COMIDA</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F825" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3913561451</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>05:21</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>Nico Jean</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>Olá, Malta!</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F826" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3909263001</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>05:12</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>El Calefón</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Quando Lembro</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F827" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3824295531</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>05:08</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>Yaya Bey</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>The Great Migration</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F828" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3812125702</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>04:57</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>John Glacier</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>If Anything</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F829" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1452077032</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>04:52</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>Don Bruce</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>Watiyo</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F830" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3765315832</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>04:47</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>Digable Planets</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Pacifics</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F831" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3440370</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>04:40</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>EMF</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>Unbelievable</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F832" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/367782641</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>04:38</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>Tony Bontana</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>Recoup (feat. leo sierra)</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F833" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3765097672</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>04:27</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>Otis Redding &amp; Carla Thomas</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>Tramp</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F834" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/358681641</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>04:19</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>The Gap Band</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>Oops Up Side Your Head</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F835" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/539098502</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>04:16</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>Mon Rovîa</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>Heavy Foot</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F836" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3422991631</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>04:11</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>Os Mutantes</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>A Minha Menina</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F837" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1560122</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>04:08</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>The Pointer Sisters</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>Automatic</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F838" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/539064</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>04:04</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Kleenex</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Die Matrosen</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F839" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/64843839</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>04:01</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>U.S. Girls</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>You've Got Everything - But A Smile</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F840" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3868429601</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>03:57</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Johnny Cash</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>Get Rhythm</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F841" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4336251</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>03:48</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>Nas</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>If I Ruled the World (Imagine That) (feat. Lauryn Hill)</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F842" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1015332</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>03:44</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>The KLF</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>Last Train to Trancentral (Live from the Lost Continent)</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F843" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1181472112</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>03:38</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>Dog Faced Hermans</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>Jan 9</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F844" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1674660257</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>03:33</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Paul Simon</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>Graceland</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F845" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/32140151</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>03:25</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>Bill Withers</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>Use Me</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F846" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/70016820</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>03:21</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>Arii Lopez &amp; Navy</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F847" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1123053032</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>03:17</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>New York Dolls</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>Looking For A Kiss</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F848" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2598227</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>03:14</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>David Bowie</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>Lady Grinning Soul</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F849" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/107474576</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>03:10</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>Destiny’s Child</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>Jumpin', Jumpin'</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F850" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/580931</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>03:06</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>Caroline Loeb</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>Narcissique</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F851" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/75105809</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>03:03</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>Nova Twins</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>Cleopatra</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F852" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1655445062</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>02:59</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>Nate Dogg</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>I Got Love</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F853" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/671270</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>02:56</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>Depeche Mode</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>Personal Jesus</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F854" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/68513563</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>02:53</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>Sudan Archives</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>Selfish Soul</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F855" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1719842667</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>02:46</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>Neneh Cherry</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>Buffalo Stance</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F856" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3324536</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>02:40</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>Mariah Carey</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>Obsessed</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F857" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4109366</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>02:37</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>Gary Clark Jr.</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>Cold Blooded</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F858" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/106586502</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>02:33</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>The Clash</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>The Magnificent Seven</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F859" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/69924718</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>02:27</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>Dance</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F860" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2121291437</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>02:24</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>Hank Williams</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>Settin' the Woods on Fire</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F861" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/548861222</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>02:21</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>The Selecter</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>On My Radio</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F862" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1787674107</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Girl Scout</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>Simple Life</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F863" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3684639682</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>02:03</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>T. Rex</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>Get It On</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F864" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/14619142</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>01:50</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>Samara Cyn</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>Sinner</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F865" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3023916801</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>01:43</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Simphiwe Dana</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>Ndiredi</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F866" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3774361092</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>01:33</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Moonchild Sanelly</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>Scrambled Eggs</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F867" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2992341011</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>01:27</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>The Rezillos</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>I Can't Stand My Baby</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F868" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/6635692</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>01:18</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Ultravox</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>Dancing With Tears in My Eyes</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F869" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1787621717</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>01:11</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Angel Olsen</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>Shut Up Kiss Me</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F870" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/129511556</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Arthur Russell</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>That's Us/Wild Combination</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F871" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/66687287</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>00:48</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Manic Street Preachers</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>Faster</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F872" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2244034</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>00:44</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>MORN</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>The Standard Model</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F873" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3925334191</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>00:33</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Yeasayer</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>O.N.E.</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F874" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/73919151</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>00:27</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Khruangbin</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>May Ninth</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F875" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2582328572</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>00:23</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Paper Crown</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>Letters</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F876" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3760293492</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>00:17</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Clio</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>Faces</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F877" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1061470462</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>00:08</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Grace Jones</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>Williams' Blood</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F878" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3964626</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>00:01</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>The Jesus and Mary Chain</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>Far Gone And Out</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F879" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3526274341</t>
         </is>
       </c>
     </row>
@@ -25522,6 +29330,125 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F758" r:id="rId757"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F759" r:id="rId758"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F760" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F761" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F762" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F763" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F764" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F765" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F766" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F767" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F768" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F769" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F770" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F771" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F772" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F773" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F774" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F775" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F776" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F777" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F778" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F779" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F780" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F781" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F782" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F783" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F784" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F785" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F786" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F787" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F788" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F789" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F790" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F791" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F792" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F793" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F794" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F795" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F796" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F797" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F798" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F799" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F800" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F801" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F802" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F803" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F804" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F805" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F806" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F807" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F808" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F809" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F810" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F811" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F812" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F813" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F814" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F815" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F816" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F817" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F818" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F819" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F820" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F821" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F822" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F823" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F824" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F825" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F826" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F827" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F828" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F829" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F830" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F831" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F832" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F833" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F834" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F835" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F836" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F837" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F838" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F839" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F840" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F841" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F842" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F843" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F844" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F845" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F846" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F847" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F848" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F849" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F850" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F851" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F852" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F853" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F854" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F855" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F856" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F857" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F858" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F859" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F860" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F861" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F862" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F863" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F864" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F865" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F866" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F867" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F868" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F869" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F870" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F871" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F872" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F873" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F874" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F875" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F876" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F877" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F878" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F879" r:id="rId878"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/BBC6 Music Log.xlsx
+++ b/output/BBC6 Music Log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F879"/>
+  <dimension ref="A1:F1048"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28566,6 +28566,5414 @@
       <c r="F879" s="2" t="inlineStr">
         <is>
           <t>https://www.deezer.com/track/3526274341</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Ren Harvieu</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>Revel In The Drama</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F880" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/968233372</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Cymande</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>Bra</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F881" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3124621941</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Luke James Williams</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>Full Moon</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F882" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3629483722</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>Big Mama Thornton</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>Hound Dog</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F883" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/427259512</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>Ron Sexsmith</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>Secret Heart</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F884" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1162007</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>David Attenborough</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>Hallelujah Chant</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F885" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1872105097</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>Glenn Gould</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>Goldberg Variations, BWV 988: Aria</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F886" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/106708496</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>Hiroshi Yoshimura</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>FEEL</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F887" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3185163841</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>Miles Davis</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>In A Silent Way</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F888" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/854007</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>Luiz Bonfá</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>Concerto for Guitar</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F889" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/602782582</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>Harold Budd</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>Butterfly Sunday</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F890" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3482028</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>Blue Eyed Soul</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>Burn</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F891" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/658948432</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>Naima Adams</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>How Long Till I Know?</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F892" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3915158791</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>Cocteau Twins</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>Pandora</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F893" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/105292196</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>Juana Molina</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>caravanas</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F894" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3571530761</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>Sam Gendel &amp; Sam Wilkes</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>RAPMAN</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F895" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3941715531</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>David Attenborough</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>Panambi Vera</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F896" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1872105387</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>Resavoir</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>Tea</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F897" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3791496692</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>Resavoir</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>Far Cry</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F898" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3791496662</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>Resavoir &amp; Matt Gold</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>Zero Gravity</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F899" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3231652071</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>Resavoir</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>Clouds</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F900" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/671263332</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>Raymond Scott</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>Sleepy Time</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F901" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/11893697</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>Laura Nyro</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>Brown Earth</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F902" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1067193</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>Clear Path Ensemble</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>Tongue Rhythm</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F903" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3980617611</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>Grouper</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>Kelso (Blue Sky)</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F904" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1442499182</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>Terry Callier</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>Spin, Spin, Spin</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F905" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/575923022</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>Greg Foat</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>Blob #1</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F906" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3990661341</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>Roy Montgomery</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>Above the Canopy</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F907" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/62304523</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>Charlie Haden &amp; Pat Metheny</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>Message To A Friend</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F908" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/921394</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>Eluvium</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>Prelude For Time Feelers</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F909" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/62743415</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>Alice Coltrane</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>Blue Nile</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F910" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/62347589</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>Harold Budd</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>Let Us Go Into The House Of The Lord/Butterfly Sunday</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F911" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3482028</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>Brooklyn Youth Chorus &amp; Dianne Berkun Menaker</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>So Quietly</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F912" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3497305201</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>Julianna Barwick</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>Look Into Your Own Mind</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F913" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/73913799</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Jon Hassell</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>Last Night The Moon Came</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F914" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/552584882</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>Lewis</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>Things Just Happen That Way</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F915" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3184997711</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>David Shea</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>A Sutra</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F916" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3646812072</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Talk Talk</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>New Grass</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F917" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/639788992</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>Soon</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F918" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/765719</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Can</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>Future Days</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F919" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/75457539</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>Margaret Hermant</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>Timeless - Pt.2</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F920" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3790137022</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>Hiroshi Yoshimura</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>Blink</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F921" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3047305501</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>Cocteau Twins</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>Frou-Frou Foxes in Midsummer Fires</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F922" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/942518</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>Richie Culver</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>Slow Car</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F923" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2768355141</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>Tracy Chapman</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>Fast Car</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F924" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2271563</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>Orits Williki</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>Fight The Fire</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F925" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3765315852</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>Night Bus</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F926" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/697321892</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>Y0GA</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>You Can't Have Everything</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F927" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3910348501</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>Joy Division</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>Love Will Tear Us Apart</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F928" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/797434</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>J Hus</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>Must Be</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F929" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/791085212</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>David Sylvian &amp; Ryuichi Sakamoto</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>Forbidden Colours</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F930" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/422234642</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>Ryuichi Sakamoto</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>20220304</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F931" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2019257067</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>Baka Forest People of South East Cameroon</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>Liquindi 2</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F932" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/487749732</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>Alva Noto</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>Xerrox Néant</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F933" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/958012372</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>Nils Frahm</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>My Friend the Forest</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F934" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/625967412</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>insomniac hotel</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>Reishi Forest Stream</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F935" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2402275435</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Masayoshi Fujita</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>As Dusk Falls (feat. NATURE)</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F936" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3310838651</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>Baka Forest People Of Southeast Cameroon</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>Eden Yelli 1</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F937" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1875142257</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>Skee Mask</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>Lil DB Tool</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F938" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/483124162</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>Rat Heart</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>Not 2Nite (feat. Cansu Kandemir)</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F939" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3607903552</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>Miles Davis</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>Miles Runs the Voodoo Down</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F940" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/7011529</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>Damaged Bug</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>In My Heart</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F941" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/899720542</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>Krisma</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>Black Silk Stocking</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F942" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/9157162</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>Perrey &amp; Kingsley</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>E.V.A.</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F943" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3128799</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>The Monochrome Set</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>The Monochrome Set (I Presume)</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F944" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/737059142</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>The Fall</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>Big New Prinz</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F945" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/105428502</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>Bhairavi Raman &amp; Nanthesh Sivarajah</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>Awakening</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F946" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3580852531</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>Earth</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>The Rakehell</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F947" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/16176233</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Bee Gees</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>Stayin' Alive</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F948" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/139138743</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>Meredith Monk</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>Candy Bullets And Moon</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F949" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2560666872</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>Laraaji</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>Om Namah Shivaya</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F950" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/440368642</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>Kali Malone</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>Passage Through The Spheres</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F951" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2474632941</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>DJ Screw</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>My Mind Went Blank (Screwed)</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F952" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/6224834</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>The Gentle People</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>Journey (Aphex Twin Care Mix)</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F953" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3388103561</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>10cc</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>I'm Not In Love</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F954" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1581601</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>Bill Callahan</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>AMERICA!</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F955" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/477791092</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>Donovan</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>Hey Gyp (Dig the Slowness)</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F956" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3786483152</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>Rondò Veneziano</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>La Serenissima</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F957" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/993272</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>Sandy Denny</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>Who Knows Where The Time Goes? (BBC Session - John Peel 11/9/73)</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F958" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/24943581</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>Normal Ltd</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>The Drowning Smile</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F959" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3944899951</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>M. Ward</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>Let's Dance</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F960" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3552187851</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>Unknown Mortal Orchestra</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>So Good At Being In Trouble</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F961" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2524364311</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>White Magic for Lovers</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>The Boy From The Bookshop</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F962" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2979811611</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>J.J. Cale</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>Crying Eyes</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F963" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2447241</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>Art of Noise</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>Island</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F964" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/100061350</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>Art of Noise</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>Crusoe</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F965" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/732877</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>Here We Go Magic</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>Over The Ocean</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F966" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/73919898</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>Doves</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>Firesuite</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F967" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3103136</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>Booker T. &amp; The M.G.'s</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>Tic Tac Toe</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F968" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/689596</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>Savourna Stevenson</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>An Buachaille</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F969" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/134913886</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>Roddy Frame</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>Surf</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F970" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1842687927</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>The Isley Brothers</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>Work To Do</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F971" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/106026608</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>Laura Groves</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F972" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2258556517</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>Sterling Holloway</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>Trust In Me</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F973" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/130320350</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>Bob Marley &amp; The Wailers</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>Three Little Birds</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F974" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/530300641</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>Yazmin Lacey</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>Wallpaper</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F975" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3606667902</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>It’s a Beautiful Day</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>White Bird</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F976" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3471083641</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>Tom Tom Club</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>Wordy Rappinghood</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F977" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/14618034</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>Bill Withers</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>Harlem</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F978" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2312056</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>Martha Wainwright</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>Factory</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F979" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/73221565</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>06:58</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>The Bobby Fuller Four</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>I Fought The Law</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F980" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3864322</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>Souad Massi &amp; Gaël Faye</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>D'ici, De là-bas (feat. Gaël Faye)</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F981" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3842910621</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>Manna Dey &amp; Lata Mangeshkar</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>Pyar Hua Iqrar Hua</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F982" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/468437902</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>Arlindo Cruz</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>Meu Lugar</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F983" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/96008310</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>Samba di Minas</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>Isto Aqui, O Que E</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F984" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2289467885</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>06:34</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>Parlor Greens</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>Eat Your Greens</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F985" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3706051372</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>06:29</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>The Incredible String Band</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>Cousin Caterpillar</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F986" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/118281246</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>John Williams &amp; London Symphony Orchestra</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>Main Title (From "Superman")</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F987" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/8146536</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>06:09</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>Kate Bush</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>Flower Of The Mountain</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F988" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2175439217</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>Lionel Hampton and His Orchestra</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>Flying Home</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F989" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1962439</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>05:58</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>Kate Carr</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>Under Wires</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F990" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/130030212</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>05:44</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>Jacques Loussier Trio</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>Boléro</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F991" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1263061992</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>05:07</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>John Lee Hooker</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>Shake It Baby</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F992" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/96199538</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>05:03</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>Van Morrison</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>Into The Mystic</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F993" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/71433041</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>04:59</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>J.J. Cale</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>Don't Go To Strangers</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F994" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2447232</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>04:53</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>Clannad</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>Chuaigh Me na Rosann</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F995" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1649373132</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>04:49</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>Clannad</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>Rince Philib a Cheoil</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F996" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1649373062</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>04:43</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>Miles Davis</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>Petit Bac (Take 2 - Bande originale du film \"Ascenseur pour l'échafaud\")</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F997" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/508354922</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>04:34</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>Demônios da Garoa &amp; Seu Jorge</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>Despejo na Favela - Ao Vivo</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F998" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3951917231</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>04:28</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>Lou Rawls</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>Bring It On Home</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F999" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/649788852</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>04:25</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>Big Thief</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>Certainty</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1000" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1627955032</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>04:18</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>Pentangle</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>Hunting Song</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1001" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3786480502</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>04:14</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>Flaer</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>Starling Descends</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1002" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3428702121</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>04:11</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>George Jones</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>Just One More</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1003" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/732399802</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>04:04</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>Father John Misty</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>I Guess Time Just Makes Fools Of Us All</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1004" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2967452091</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>Ibrahim Maalouf</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>Las Trompetas De Nael</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1005" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3989655151</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>03:57</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>The Coral</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>Dream River</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1006" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2435113675</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>03:54</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>Frank Ocean</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>Moon River</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1007" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/462898792</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>03:52</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>John Martyn</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>The River</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1008" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2000632547</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>03:33</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>Nick Drake</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>River Man</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1009" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2282995</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>03:28</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>Augustus Pablo</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>East Of The River Nile</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1010" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3558656141</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>03:24</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>Prince &amp; The Revolution</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>Purple Rain</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1011" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1767888867</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>03:22</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>Fleet Foxes</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>Wading In Waist-High Water</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1012" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1075897112</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>03:16</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>Tindersticks</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>Tiny Tears</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1013" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/487068332</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>03:10</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>Linda Perhacs</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>River of God</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1014" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/75227940</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>03:05</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>Ibeyi</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>River</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1015" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/81670608</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>03:01</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>Dennis Wilson</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>River Song</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1016" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13378297</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>02:57</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>Elis Regina</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>Aguas De Marco</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1017" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/565340102</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>02:53</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>Paul McCartney</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>Waterfalls</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1018" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/583770682</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>02:50</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>Jimmy Cliff</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>Many Rivers To Cross</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1019" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1106498992</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>02:48</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>Fennesz</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>Rivers of Sand</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1020" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/7636417</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>02:45</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>Jóhann Jóhannsson</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>The Drowned World</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1021" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3702998232</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>02:41</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>Agnes Obel</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>Riverside</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1022" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/10458911</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>02:33</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>Doves</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>Caught By The River</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1023" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3087987</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>02:27</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>Lael Neale</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>I Am The River</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1024" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2094356647</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>02:25</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>Steve Hackett</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>Tales Of The Riverbank</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1025" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/110147536</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>02:20</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>Terry Reid</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>River</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1026" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/729092</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>02:17</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>Brian Eno</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>By This River</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1027" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3093662</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>Al Green</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>Take Me to the River</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1028" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/577942252</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>02:04</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>The Jam</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>Tales From The Riverbank</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1029" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/932451</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>02:01</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>Lykke Li</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>I Follow Rivers</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1030" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/14235829</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>01:57</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>Fatoumata Diawara</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>Nterini</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1031" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3200166881</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>01:54</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>Mk.gee</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>Are You Looking Up</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1032" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3882658031</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>01:49</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>The Head and the Heart</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>Rivers and Roads</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1033" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3025976131</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>Ann Peebles</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>I Can't Stand The Rain</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1034" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/136371188</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>01:36</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>Pigeon</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1035" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3718400312</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>01:33</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Talking Heads</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>I Zimbra</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1036" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/6587028</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>01:24</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>Jalen Ngonda</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>Doctrine of Love</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1037" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3801750252</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>01:17</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Jai Paul</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>Str8 Outta Mumbai</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1038" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/689384972</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>01:14</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>Sister Nancy</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>Bam Bam</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1039" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3658608</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>01:05</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>Tony Allen &amp; Hugh Masekela</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>Never (Lagos Never Gonna Be The Same)</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1040" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3803488272</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Paul McCartney</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>Secret Friend (7" )</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1041" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2035210367</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>00:47</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>Steve Lacy</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>Dark Red</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1042" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1860754817</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>00:43</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Aswad</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>Warrior Charge</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1043" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1760979767</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>00:33</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>Hiatus Kaiyote</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>Get Sun (feat. Arthur Verocai)</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1044" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1391828852</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>00:26</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>Kokoroko</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>Sweetie</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1045" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3299231271</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>00:18</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>Isao Tomita</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>Suite Bergamasque: Clair de Lune, No. 3</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1046" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/71937319</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>00:14</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>Gloria Ann Taylor</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>How Can You Say It</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1047" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3850625261</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>00:10</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>Lauryn Hill</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>Ex-Factor</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1048" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/400418882</t>
         </is>
       </c>
     </row>
@@ -29449,6 +34857,175 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F877" r:id="rId876"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F878" r:id="rId877"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F879" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F880" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F881" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F882" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F883" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F884" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F885" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F886" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F887" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F888" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F889" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F890" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F891" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F892" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F893" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F894" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F895" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F896" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F897" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F898" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F899" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F900" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F901" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F902" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F903" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F904" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F905" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F906" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F907" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F908" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F909" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F910" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F911" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F912" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F913" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F914" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F915" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F916" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F917" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F918" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F919" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F920" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F921" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F922" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F923" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F924" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F925" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F926" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F927" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F928" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F929" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F930" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F931" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F932" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F933" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F934" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F935" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F936" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F937" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F938" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F939" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F940" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F941" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F942" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F943" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F944" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F945" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F946" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F947" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F948" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F949" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F950" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F951" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F952" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F953" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F954" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F955" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F956" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F957" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F958" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F959" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F960" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F961" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F962" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F963" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F964" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F965" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F966" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F967" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F968" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F969" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F970" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F971" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F972" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F973" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F974" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F975" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F976" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F977" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F978" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F979" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F980" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F981" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F982" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F983" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F984" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F985" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F986" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F987" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F988" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F989" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F990" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F991" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F992" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F993" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F994" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F995" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F996" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F997" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F998" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F999" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1000" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1001" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1002" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1003" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1004" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1005" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1006" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1007" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1008" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1009" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1010" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1011" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1012" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1013" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1014" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1015" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1016" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1017" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1018" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1019" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1020" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1021" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1022" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1023" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1024" r:id="rId1023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1025" r:id="rId1024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1026" r:id="rId1025"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1027" r:id="rId1026"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1028" r:id="rId1027"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1029" r:id="rId1028"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1030" r:id="rId1029"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1031" r:id="rId1030"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1032" r:id="rId1031"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1033" r:id="rId1032"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1034" r:id="rId1033"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1035" r:id="rId1034"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1036" r:id="rId1035"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1037" r:id="rId1036"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1038" r:id="rId1037"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1039" r:id="rId1038"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1040" r:id="rId1039"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1041" r:id="rId1040"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1042" r:id="rId1041"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1043" r:id="rId1042"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1044" r:id="rId1043"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1045" r:id="rId1044"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1046" r:id="rId1045"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1047" r:id="rId1046"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1048" r:id="rId1047"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/BBC6 Music Log.xlsx
+++ b/output/BBC6 Music Log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1048"/>
+  <dimension ref="A1:F1150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -33974,6 +33974,3270 @@
       <c r="F1048" s="2" t="inlineStr">
         <is>
           <t>https://www.deezer.com/track/400418882</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>Ganavya</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>draw something beautiful</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1049" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2852821522</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>Madonna</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>Don't Tell Me</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1050" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/781635</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>Hüsker Dü</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>It's Not Funny Anymore</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1051" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3491762371</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>The Fall</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>An Older Lover Etc</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1052" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3803084912</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>The Everly Brothers</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>Cathy's Clown</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1053" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/846293</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>Leonard Cohen</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>Paper Thin Hotel</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1054" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/80869670</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>My Precious Bunny</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>KookieCannibal</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1055" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3771323472</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>The Doors</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>Love Her Madly</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1056" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/65445458</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>Buzzcocks</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>Noise Annoys</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1057" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/376014641</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>Faust</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>The Sad Skinhead</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1058" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3459173</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>Edwin R. Stevens</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>Criminal</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1059" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3782281622</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>Television</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>Elevation</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1060" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/718319</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>The Bug Club</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>A Good Day For Dying</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1061" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3786754952</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>Elvis Costello</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>Pump It Up</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1062" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1110982</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>Smerz</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>Spring summer</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1063" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3935274651</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Dumama</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>No Abiding City</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1064" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3817588292</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>Any Young Mechanic</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>Captain And Compass</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1065" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3954483551</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>Theatre</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>You Are</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1066" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4000891971</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>ear</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>Ne Plus Ultra</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1067" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4001324831</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>supermodel*</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>cherry garcia</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1068" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3899789031</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>ZEP</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>FIGURE IT OUT</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1069" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3898109601</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>Knats</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>Never Gonna Be A Boxer</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1070" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3966837341</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>Heart Attack-Acks</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>Weird Guys</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1071" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4007180971</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>Metronomy</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>You Could Easily Have Me (Adiel and Pat Alvarez Rework)</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1072" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3936298841</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>1-800 GIRLS</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1073" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3971497431</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>Rostam</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>Hardy (feat. Clairo)</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1074" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3965388431</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>The Last Dinner Party</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>Big Dog</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1075" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3996037711</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>Little Simz</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>GAME ON</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1076" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3980007721</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>Mystery Jets</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>Black Sage</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1077" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3995717061</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>Swimmers Jackson</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>Every Time I...</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1078" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3897025501</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>Tooth</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>Restless in Bloom</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1079" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3913232271</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>The Itch</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>No More Sprechgesang</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1080" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3692982612</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>jo from school</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>Chicken</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1081" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3940381641</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>R. Dean Taylor</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>There's A Ghost In My House</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1082" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/960257732</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>Blondie</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>Picture This</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1083" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/418231442</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>Monie Love</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>Monie In The Middle</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1084" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1787681117</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>Beats International</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>Dub Be Good To Me</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1085" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1084256542</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>The Pipettes</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>Pull Shapes</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1086" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/7432815</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>Timo Maas</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>To Get Down</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1087" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/680610</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>Half Man Half Biscuit</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>Bad Losers On Yahoo! Chess</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1088" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1699527527</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>Sade</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>Your Love Is King</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1089" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1030651902</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>Muse</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>Knights Of Cydonia</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1090" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3590194</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>Kerala Dust</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>FEVER</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1091" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3909116061</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>Freestyle Fellowship</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>Sunshine Men</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1092" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2086703</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>The Pogues</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>Dirty Old Town</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1093" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4094365</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>Lawn Chair</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>The New Low</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1094" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3934897371</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>M.O.T.H.E.R</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>My Love</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1095" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1970022797</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>The Orb</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>Toxygene</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1096" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/933322</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>Brooke Combe</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>Tears Won't Lie</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1097" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3935623211</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>Ramones</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>Howling at the Moon (Sha-La-La)</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1098" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/14635549</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>Petula Clark</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>Downtown</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1099" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/95435018</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>Simian Mobile Disco</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>Hustler</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1763163857</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>07:16</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>Nookie</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>Love is the Message</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1856632267</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>Blame</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>Music Takes You</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2238722537</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>07:07</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>Wink</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>Higher State Of Consciousness</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3786806602</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>07:03</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>Brother Wallace</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>You're The Man</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3716706222</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>Joan As Police Woman</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>Out of Time</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/873172492</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>The Lemon Twigs</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>Look For Your Mind</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3840589201</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>06:33</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>Nine Inch Nails</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>Every Day Is Exactly the Same</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/139876083</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>06:27</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>Inspiral Carpets</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>This Is How It Feels</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3786222092</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>Inner City</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>Good Life</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2933511391</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>05:47</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>Millie Jackson</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>If Loving You Is Wrong I Don't Want To Be Right</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/65703923</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>05:33</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>The Chemical Brothers</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>Star Guitar</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3088130</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>05:25</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>The Beat</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>Save It For Later</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2522682601</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>05:16</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>Stereolab</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>Wow and Flutter</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/674115792</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>05:14</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>Pavement</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>Gold Soundz</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/105281818</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>05:09</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>Conquering Lion</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>Code Red</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3763401682</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>MJ Cole</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>Crazy Love</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3293134091</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>04:57</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>Moodymann</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>Don't You Want My Love</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/12756238</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>04:52</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>The Cure</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>Just Like Heaven</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/409670332</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>04:41</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>Father John Misty</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>The Payoff</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3947333931</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>04:33</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>The Stone Roses</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>I Am the Resurrection</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3960801</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>04:26</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>Deerhunter</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>Helicopter</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/7149045</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>Metronomy</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>The Bay</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/10240182</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>Chaka Khan</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>I Know You, I Live You</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/80149326</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>04:12</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>tUnE-yArDs</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>Look At Your Hands</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/447973612</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>04:10</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>Daniela Lalita &amp; Mura Masa</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>Tiroteo</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3962419631</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>03:46</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>Steve Spacek &amp; Shy One</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>Driving on Sand</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3808671332</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>03:34</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>Flying Lotus</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>Garmonbozia</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3272154061</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>03:21</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>The Jellies</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>Jive Baby On A Saturday Night</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/9876035</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>03:10</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>Sébastien Tellier</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>La Ritournelle</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2751407851</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>03:03</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>One Dove</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>White Love</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/685799</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>02:59</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>Olive</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>You’re Not Alone</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2900096</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>02:50</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>Massive Attack</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>Paradise Circus</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/5317037</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>02:44</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>Fluke</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>Setback</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3134006</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>The Beta Band</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>B A</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/453207772</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>02:27</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>Little Dragon</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>Ritual Union</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/12756253</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>02:16</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>SOAK</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>Sea Creatures</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/100656672</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>Kaeto</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>No Body</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2483109261</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>01:58</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>Mac DeMarco</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>Holy</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3442201291</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>01:55</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>My Love For You</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2121438327</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>01:24</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>Pulp</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>Begging for Change</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3839499261</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>01:19</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>The Knife</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>Silent Shout</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1895198677</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>01:02</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>Curtis Mayfield</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>Future Shock</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/721351</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>00:47</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>David Bowie</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>Suffragette City</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/107471938</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>00:33</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>Tom Browne</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>Funkin' For Jamaica</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13200806</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>00:25</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>White Denim</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>Small Talk (Feeling Control)</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2582849852</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>00:21</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>Spoon</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>The Underdog</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/415183932</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>00:16</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>Arrested Development</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>People Everyday</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3100807</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>00:13</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>Steely Dan</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>Peg</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2466017615</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>00:08</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>Xpansions</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>Move Your Body</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4007870631</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>00:02</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>Fontaines D.C.</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>Boys In The Better Land</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/731723442</t>
         </is>
       </c>
     </row>
@@ -35026,6 +38290,108 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1046" r:id="rId1045"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1047" r:id="rId1046"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1048" r:id="rId1047"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1049" r:id="rId1048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1050" r:id="rId1049"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1051" r:id="rId1050"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1052" r:id="rId1051"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1053" r:id="rId1052"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1054" r:id="rId1053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1055" r:id="rId1054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1056" r:id="rId1055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1057" r:id="rId1056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1058" r:id="rId1057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1059" r:id="rId1058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1060" r:id="rId1059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1061" r:id="rId1060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1062" r:id="rId1061"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1063" r:id="rId1062"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1064" r:id="rId1063"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1065" r:id="rId1064"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1066" r:id="rId1065"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1067" r:id="rId1066"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1068" r:id="rId1067"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1069" r:id="rId1068"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1070" r:id="rId1069"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1071" r:id="rId1070"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1072" r:id="rId1071"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1073" r:id="rId1072"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1074" r:id="rId1073"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1075" r:id="rId1074"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1076" r:id="rId1075"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1077" r:id="rId1076"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1078" r:id="rId1077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1079" r:id="rId1078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1080" r:id="rId1079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1081" r:id="rId1080"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1082" r:id="rId1081"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1083" r:id="rId1082"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1084" r:id="rId1083"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1085" r:id="rId1084"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1086" r:id="rId1085"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1087" r:id="rId1086"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1088" r:id="rId1087"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1089" r:id="rId1088"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1090" r:id="rId1089"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1091" r:id="rId1090"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1092" r:id="rId1091"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1093" r:id="rId1092"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1094" r:id="rId1093"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1095" r:id="rId1094"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1096" r:id="rId1095"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1097" r:id="rId1096"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1098" r:id="rId1097"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1099" r:id="rId1098"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1100" r:id="rId1099"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1101" r:id="rId1100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1102" r:id="rId1101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1103" r:id="rId1102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1104" r:id="rId1103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1105" r:id="rId1104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1106" r:id="rId1105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1107" r:id="rId1106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1108" r:id="rId1107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1109" r:id="rId1108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1110" r:id="rId1109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1111" r:id="rId1110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1112" r:id="rId1111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1113" r:id="rId1112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1114" r:id="rId1113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1115" r:id="rId1114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1116" r:id="rId1115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1117" r:id="rId1116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1118" r:id="rId1117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1119" r:id="rId1118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1120" r:id="rId1119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1121" r:id="rId1120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1122" r:id="rId1121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1123" r:id="rId1122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1124" r:id="rId1123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1125" r:id="rId1124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1126" r:id="rId1125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1127" r:id="rId1126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1128" r:id="rId1127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1129" r:id="rId1128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1130" r:id="rId1129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1131" r:id="rId1130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1132" r:id="rId1131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1133" r:id="rId1132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1134" r:id="rId1133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1135" r:id="rId1134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1136" r:id="rId1135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1137" r:id="rId1136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1138" r:id="rId1137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1139" r:id="rId1138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1140" r:id="rId1139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1141" r:id="rId1140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1142" r:id="rId1141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1143" r:id="rId1142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1144" r:id="rId1143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1145" r:id="rId1144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1146" r:id="rId1145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1147" r:id="rId1146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1148" r:id="rId1147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1149" r:id="rId1148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1150" r:id="rId1149"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/BBC6 Music Log.xlsx
+++ b/output/BBC6 Music Log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1150"/>
+  <dimension ref="A1:F1297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -37238,6 +37238,4710 @@
       <c r="F1150" s="2" t="inlineStr">
         <is>
           <t>https://www.deezer.com/track/731723442</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>Flowered Up</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>Weekender</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1209925252</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>The Mock Turtles</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>Can You Dig It?</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3247199</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>The Soup Dragons</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>I'm Free</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/95854720</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>Soho</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>Hippychick</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2551663</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>Paris Angels</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>All On You (Perfume)</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2367606515</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>The Stone Roses</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>Made Of Stone</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3960798</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>The Charlatans</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>Weirdo</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/935920</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>Happy Mondays</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>W.F.L.</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/428805682</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>Shy One</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>Full Circle</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3808671322</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>Shy One</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>Black Widow</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1925156847</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>Private Joy &amp; Shy One</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>Moonlight</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3808671312</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>Wiley</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>Igloo</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/620495542</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>Xtatik</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>Soca</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2412311605</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>Leviticus</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3623137412</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>Dwele</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>Find A Way</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3092680</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>Erykah Badu</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>On &amp; On</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1123844</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>A Tribe Called Quest</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>Like It Like That</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13163047</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>Miles Davis</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>Tutu</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/664205</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>Queen</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>Keep Yourself Alive</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/705326832</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>This Is the Kit</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>Moonshine Freeze</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/375846701</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>Lunge &amp; Neil Halstead</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>Milky Pinks</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3865432121</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>The Beach Boys</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>Darlin'</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3091990</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>LYR</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>Guernica Jigsaw</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3720345272</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>The Pop Group</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>She Is Beyond Good And Evil</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/723143052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>Midlake</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>Head Home</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/82746824</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>Pina Palau</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>All I Want Is Her</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3660169742</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>PJ Harvey</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>Down By the Water</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1169910</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>Faces</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>Ooh La La</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3858835</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>Crack Cloud</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>Reunion</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3756791122</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>Ian Dury &amp; the Blockheads</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>Sex &amp; Drugs &amp; Rock &amp; Roll</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3209917961</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>Yottie</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>miracle</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3849048751</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>Ojerime</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>4ME</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3983309251</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>LEAO</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>LALELEI</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3972529711</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Ista</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>Crusher</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3899952321</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>Pond</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>Through The Heather</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3949242071</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>Akusmi &amp; Daniel Brandt</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>Anima</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3911616061</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>Chinese American Bear</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>I Wanna Go Home (我想回家)</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3791903322</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>Loukeman</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>Pink Bape Lighter</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3839959941</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>Altrice</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>goodbye! later on!</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3950292751</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>Overmono</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>Lockup</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3974123351</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>corto.alto</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>THIEF</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3968016931</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>Show Me the Body</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>No God</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4002885601</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>Sofia Cordoba</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>Symptom of Love</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3976458231</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>Yves Tumor</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>Romanticist</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/916811392</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>The Jesus and Mary Chain</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>Just Like Honey</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2186999827</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>Prince &amp; The Revolution</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>Kiss</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1183586102</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>The Slits</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>I Heard It Through The Grapevine</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1140839</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>Magi Merlin</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>So Smart</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3960602051</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>Kate Peaches</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>Bored</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3931432931</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>Brodie Milner</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>Throw Away Your Medicine</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3960205251</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>The Gnomes</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>Magic Man</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3928357881</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>Riton &amp; Kah-Lo</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>Fake ID</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/440115402</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>The Divine Comedy</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>The Pop Singer's Fear of the Pollen Count</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3837322</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>Sleaford Mods</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>TCR</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/887229652</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>Sleigh Bells</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>Kids</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1563313612</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>Hot Chip</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>Boy from School</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/376014071</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>Busta Rhymes</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>Woo Hah!</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3589948</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>Modest Mouse</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>Third Side of the Moon</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3928951101</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>jasmine.4.t</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>Tall Girl</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2856903942</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>Brakes</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>All Night Disco Party</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/946124</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>Talking Heads</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>Once In A Lifetime</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/5093672</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>Walt Disco</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>Coup de foudre</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4004878251</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>Justice</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>We Are Your Friends</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2100102627</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>clipping.</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>Change The Channel</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3431408651</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>Unknown Mortal Orchestra</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>Can't Keep Checking My Phone</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/99241568</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>Veruca Salt</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>Seether</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1761076427</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>The Teardrop Explodes</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1580242</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>Sigue Sigue Sputnik</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>Love Missile F1-11</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3786405842</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>Quantic, Alice Russell &amp; Combo Bárbaro</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>Look Around The Corner</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3685620482</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>Gorillaz</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>Orange County (feat. Bizarrap, Kara Jackson &amp; Anoushka Shankar)</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3857373121</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>Downtown Boys</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>You're A Ghost</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3863066851</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>Mylo</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>In My Arms</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1895191447</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>dead prez</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>Hip Hop</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/15220137</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>The Roots</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>Distortion To Static</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1408782132</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>ALT BLK ERA</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>Silhouettes In the Mirror</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3921515341</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>Arrested Development</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3100809</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>Morcheeba</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>World Looking In</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/784904</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>Joy Division</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>Decades</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1021197562</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>Billy Nomates</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>Heels</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3186680991</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>MC Lyte</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>Cha Cha Cha</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/103134758</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>Adam F</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>Circles</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2909632151</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>Parlor Greens</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>Queen Of My Heart</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3706051472</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>case/lang/veirs</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>Atomic Number</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/378388181</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>Anderson .Paak</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>Jet Black (feat. Brandy)</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/662437282</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>Basement</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>Satisfy</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3824588841</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>Massive Attack</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>Teardrop</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3129748</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>Everything but the Girl</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>Each and Every One</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3908914041</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>Anna Calvi</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>Suzanne And I</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/9817298</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>Katy B</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>Lights On (feat. Ms. Dynamite)</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1239" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/10047068</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>Arctic Monkeys</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>Don't Sit Down 'Cause I've Moved Your Chair</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/12713707</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>Roxy Music</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>Re-Make/Re-Model</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3134797</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>Yo Majesty</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>Club Action</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4315542</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>Gwenno</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>N.Y.C.A.W.</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1243" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1665200832</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>Sharon Van Etten</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>Leonard</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/73915554</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>07:38</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>Truthpaste</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>Swill to the Swine</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3861843801</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>Led Zeppelin</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>Ramble On</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1246" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/78671033</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>Nadine Shah</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>Stealing Cars</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/123817762</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>TV on the Radio</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>Mercy</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1248" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1763100267</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>SebastiAn</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>Love In Motion (feat. Mayer Hawthorne)</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/445864702</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>Robyn</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>Talk To Me</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3882885811</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>06:59</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>Money Mark</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>Hand In Your Head</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1762822147</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>06:56</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>Love Spells</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>Crutch</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3981069391</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>Midlake</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>Young Bride</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1253" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/406118982</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>06:34</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>Caroline Polachek</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>Bunny Is A Rider</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1254" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2142188377</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>06:28</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>Lykke Li</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>Happy Now</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1255" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3691704592</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>06:19</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>Seren Saraç</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>YEKTE</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1256" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3746250972</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>06:16</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>Broken Social Scene</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>Cause = Time</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1257" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/425553902</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>06:04</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>Battles</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>Atlas</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/5785866</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>toe</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>Commit Ballad</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/364982331</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>05:53</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>Slint</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>Washer</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/125953475</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>05:42</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>Foals</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>Two Steps, Twice</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1261" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/14678697</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>05:28</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>Mandy, Indiana</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>try saying</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3604345102</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>05:21</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>Goat</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>Let It Burn</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/465835362</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>Cut Copy</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>Hearts On Fire</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1264" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/8238367</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>04:57</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>Fun Boy Three</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>Our Lips Are Sealed</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1787604047</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>04:34</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>The Notorious B.I.G.</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>Juicy</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2793753</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>04:16</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>Beastie Boys</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>Ch-Check It Out</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3091457</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>04:02</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>The La’s</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>There She Goes</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2518361</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>03:43</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>The Rolling Stones</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>Sympathy For The Devil</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/9956063</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>03:33</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>Alicia Myers</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>I Want To Thank You</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/630821712</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>03:22</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>Death From Above 1979</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>Romantic Rights</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/84855515</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>03:18</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>Squid</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>Houseplants</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1855404707</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>03:15</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>Prince</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>New Power Generation</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/775479</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>03:09</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>The Four Seasons</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>The Night</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1761660867</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>03:02</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>Goldfrapp</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>Rocket</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3785948782</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>02:50</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>4am Kru &amp; McDonald &amp; Jannetta</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>Pianos Raining Down</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2945454111</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>02:46</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>Teleman</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>Dusseldorf</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2478093631</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>02:40</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>Queen Latifah &amp; Monie Love</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>Ladies First</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1584428682</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>02:37</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>The Juan MacLean</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>Happy House</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1279" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/92181082</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>02:19</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>Angine de Poitrine</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>Fabienk</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3836051501</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>02:12</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>Mala</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>Changes</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1281" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1516824602</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>02:02</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>HAIM</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>Summer Girl</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1282" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1247979112</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>01:58</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>The Boo Radleys</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>Wake Up Boo</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1283" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13157572</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>01:56</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>Corinne Bailey Rae</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>New York Transit Queen</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2959397131</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>01:43</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>Skunk Anansie</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>All I Want</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2629609402</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>01:35</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>Happy Mondays</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>Loose Fit</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/428849972</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>01:23</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>Joy Division</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>Transmission</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/797403</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>01:13</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>Fiat Lux</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>Secrets</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/693399232</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>01:08</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>Santigold</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>Lights Out</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1289" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/85440828</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>00:56</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>XTC</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>Senses Working Overtime</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3135780</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>00:50</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>Kwes.</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/71287620</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>00:47</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>Lime Garden</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3681569172</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>00:36</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>The Verve</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>Bitter Sweet Symphony</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/398570642</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>Oasis</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>Slide Away</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/985979472</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>00:23</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>Sleeper</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>What Do I Do Now?</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13148358</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>00:10</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>DJ Food</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>Dark Lady</t>
+        </is>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/524889412</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>00:02</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>R.E.M.</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>The One I Love</t>
+        </is>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3154047</t>
         </is>
       </c>
     </row>
@@ -38392,6 +43096,153 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1148" r:id="rId1147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1149" r:id="rId1148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1150" r:id="rId1149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1151" r:id="rId1150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1152" r:id="rId1151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1153" r:id="rId1152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1154" r:id="rId1153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1155" r:id="rId1154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1156" r:id="rId1155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1157" r:id="rId1156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1158" r:id="rId1157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1159" r:id="rId1158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1160" r:id="rId1159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1161" r:id="rId1160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1162" r:id="rId1161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1163" r:id="rId1162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1164" r:id="rId1163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1165" r:id="rId1164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1166" r:id="rId1165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1167" r:id="rId1166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1168" r:id="rId1167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1169" r:id="rId1168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1170" r:id="rId1169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1171" r:id="rId1170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1172" r:id="rId1171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1173" r:id="rId1172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1174" r:id="rId1173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1175" r:id="rId1174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1176" r:id="rId1175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1177" r:id="rId1176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1178" r:id="rId1177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1179" r:id="rId1178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1180" r:id="rId1179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1181" r:id="rId1180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1182" r:id="rId1181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1183" r:id="rId1182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1184" r:id="rId1183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1185" r:id="rId1184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1186" r:id="rId1185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1187" r:id="rId1186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1188" r:id="rId1187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1189" r:id="rId1188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1190" r:id="rId1189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1191" r:id="rId1190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1192" r:id="rId1191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1193" r:id="rId1192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1194" r:id="rId1193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1195" r:id="rId1194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1196" r:id="rId1195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1197" r:id="rId1196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1198" r:id="rId1197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1199" r:id="rId1198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1200" r:id="rId1199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1201" r:id="rId1200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1202" r:id="rId1201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1203" r:id="rId1202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1204" r:id="rId1203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1205" r:id="rId1204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1206" r:id="rId1205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1207" r:id="rId1206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1208" r:id="rId1207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1209" r:id="rId1208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1210" r:id="rId1209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1211" r:id="rId1210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1212" r:id="rId1211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1213" r:id="rId1212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1214" r:id="rId1213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1215" r:id="rId1214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1216" r:id="rId1215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1217" r:id="rId1216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1218" r:id="rId1217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1219" r:id="rId1218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1220" r:id="rId1219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1221" r:id="rId1220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1222" r:id="rId1221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1223" r:id="rId1222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1224" r:id="rId1223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1225" r:id="rId1224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1226" r:id="rId1225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1227" r:id="rId1226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1228" r:id="rId1227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1229" r:id="rId1228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1230" r:id="rId1229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1231" r:id="rId1230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1232" r:id="rId1231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1233" r:id="rId1232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1234" r:id="rId1233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1235" r:id="rId1234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1236" r:id="rId1235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1237" r:id="rId1236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1238" r:id="rId1237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1239" r:id="rId1238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1240" r:id="rId1239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1241" r:id="rId1240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1242" r:id="rId1241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1243" r:id="rId1242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1244" r:id="rId1243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1245" r:id="rId1244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1246" r:id="rId1245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1247" r:id="rId1246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1248" r:id="rId1247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1249" r:id="rId1248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1250" r:id="rId1249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1251" r:id="rId1250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1252" r:id="rId1251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1253" r:id="rId1252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1254" r:id="rId1253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1255" r:id="rId1254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1256" r:id="rId1255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1257" r:id="rId1256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1258" r:id="rId1257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1259" r:id="rId1258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1260" r:id="rId1259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1261" r:id="rId1260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1262" r:id="rId1261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1263" r:id="rId1262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1264" r:id="rId1263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1265" r:id="rId1264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1266" r:id="rId1265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1267" r:id="rId1266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1268" r:id="rId1267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1269" r:id="rId1268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1270" r:id="rId1269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1271" r:id="rId1270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1272" r:id="rId1271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1273" r:id="rId1272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1274" r:id="rId1273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1275" r:id="rId1274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1276" r:id="rId1275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1277" r:id="rId1276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1278" r:id="rId1277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1279" r:id="rId1278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1280" r:id="rId1279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1281" r:id="rId1280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1282" r:id="rId1281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1283" r:id="rId1282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1284" r:id="rId1283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1285" r:id="rId1284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1286" r:id="rId1285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1287" r:id="rId1286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1288" r:id="rId1287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1289" r:id="rId1288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1290" r:id="rId1289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1291" r:id="rId1290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1292" r:id="rId1291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1293" r:id="rId1292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1294" r:id="rId1293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1295" r:id="rId1294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1296" r:id="rId1295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1297" r:id="rId1296"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/BBC6 Music Log.xlsx
+++ b/output/BBC6 Music Log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1297"/>
+  <dimension ref="A1:F1419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -41942,6 +41942,3910 @@
       <c r="F1297" s="2" t="inlineStr">
         <is>
           <t>https://www.deezer.com/track/3154047</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>Foreign Beggars &amp; Skrillex</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>Still Getting It</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/480456012</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>Betty Carter</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>Sounds (Movin On) (Live At Bradshaw's Great American Music Hall, San Francisco)</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/397178482</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>Hermeto Pascoal &amp; Aline Morena</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>Xote Cavaco</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/63870283</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>Gal Costa</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>Bem-Bom</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/70365390</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>Actores Alidos</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>Tzia Mariola</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1781779617</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>Skip &amp; Die</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>La Cumbia Dictadura</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/60748859</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>Micachu &amp; The Shapes</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>Eat Your Heart</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2802898</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>Jerskin Fendrix</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>Onigiri</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3728348372</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>KOGG</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>Doing Things</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3968342391</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>Ben Lukas Boysen</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>Only In The Dark</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/625628942</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>Max Cooper</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>Obsessive Compulsive Order</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3829281521</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>Max Cooper</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>Spectrum</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1597804392</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>Max Cooper</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>Order From Chaos</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/131246790</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>Max Cooper</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>Harmonisch Serie</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1311" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/493075892</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>Vaetxh</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>List Of Lists</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1312" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/12735406</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>Wink</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>Sprung Minimism</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/531885101</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>CJ Bolland</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>The Prophet</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/68724361</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>Three Drives</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>Greece 2000</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1315" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3719364722</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>Philip Glass</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>Koyaanisqatsi</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2329149</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>Enya</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>Boadicea</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/903448502</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>Michael Nyman</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>The Heart Asks Pleasure First</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3358382</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>Max Cooper</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>The Shape Of Memory</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1319" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3829281501</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>The Who</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>Boris The Spider</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/65414417</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>Ora Cogan</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>Limits</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3669038792</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>Courtney Marie Andrews</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>Cons and Clowns</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3571434881</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>Damaged Bug</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>Over-Exposed</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3834637761</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>Richard Harris</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>MacArthur Park</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/25029621</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>The Sensational Alex Harvey Band</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>The Boston Tea Party</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/121128024</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>Flanagan and Allen</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>Run Rabbit Run</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/6847922</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>Hannah Hu</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>Heartache Made Me A Killer</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3834999661</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>White Fence</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>Evaporating Love</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3773129462</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>Eric Matthews</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>Fanfare</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1137209522</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>54 Ultra</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>Turnaround</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3930077371</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>The Specials</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>A Message to You Rudy</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1787605117</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>Little Simz</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>Gorilla</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2057222967</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>Slow Cooked</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>Half Tesla</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3920566781</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>Will Hofbauer</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>Stair Car</t>
+        </is>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3864375121</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>Spacemoth</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>Internet Fantasy</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3923417661</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>ZEP</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>NO ENEMIES</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3995959361</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>Nia Archives</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>Headz Gone West</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1273514092</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>P!nk</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>So What</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/15597825</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>Red Hot Chili Peppers</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>Scar Tissue</t>
+        </is>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/725254</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>The Prodigy</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>Breathe</t>
+        </is>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/62126185</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>lots of hands</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>grapevine</t>
+        </is>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3912972311</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>Natacha Atlas &amp; Samy Bishai</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>Wana Leih</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3912928461</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>The Healing Power of Horses</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>i wait, i sink</t>
+        </is>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3938555271</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>School Fair</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>Gussied Up</t>
+        </is>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3997555371</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>Dua Saleh</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>Firestorm</t>
+        </is>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4014506601</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>Touching Ice</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>Praise Kink (Mandy, Indiana Remix)</t>
+        </is>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3941268491</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>Telehealth</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>Donor Country (A gOoD cAuSe)</t>
+        </is>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3807145002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>The Strokes</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>Falling Out Of Love</t>
+        </is>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4015084771</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>Mobb Deep</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>Survival Of The Fittest</t>
+        </is>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1044131</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>1000 Rabbits</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>Rubik's Cube</t>
+        </is>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3961858211</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>Big Thief</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>Masterpiece</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2544953471</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>Dermot Henry</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>Dead Man's Dog</t>
+        </is>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4013759721</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>Foals</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>In Degrees</t>
+        </is>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/643760802</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>M.I.A.</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>Boyz</t>
+        </is>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1354" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/943356</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>Gorillaz</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>Dirty Harry</t>
+        </is>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3129406</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>The Jam</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>That's Entertainment</t>
+        </is>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1356" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/984214</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>Lauryn Hill</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>Everything is Everything</t>
+        </is>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1357" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/400418982</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>Sylvester</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>You Make Me Feel (Mighty Real)</t>
+        </is>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/891619</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>The Dead Weather</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>Treat Me Like Your Mother</t>
+        </is>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3783640</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>Jamie T</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>Salvador</t>
+        </is>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1628901832</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>Bikini Kill</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>New Radio</t>
+        </is>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/550171292</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>Super Furry Animals</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>Juxtapozed With U</t>
+        </is>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3750970632</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>The Selecter</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>Three Minute Hero</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2112694727</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>Fontaines D.C.</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>Chequeless Reckless</t>
+        </is>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/627197952</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>Anz &amp; George Riley</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>You Could Be</t>
+        </is>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1455411482</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>The Chemical Brothers</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>Block Rockin' Beats</t>
+        </is>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1366" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3252242</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>Sweet</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>The Ballroom Blitz</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2269589547</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>Chubby and the Gang</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>All Along The Uxbridge Road</t>
+        </is>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1087475262</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>Lykke Li</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>Knife In The Heart</t>
+        </is>
+      </c>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3691704652</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>Cat Power</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>The Greatest</t>
+        </is>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/945521</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>The Clash</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>Armagideon Time</t>
+        </is>
+      </c>
+      <c r="E1371" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/69505562</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>07:17</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>The Stranglers</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>Hanging Around</t>
+        </is>
+      </c>
+      <c r="E1372" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3152613</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>07:14</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>New York Dolls</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>Who Are The Mystery Girls?</t>
+        </is>
+      </c>
+      <c r="E1373" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1169454</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>07:09</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>James Emmanuel</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>Good Man</t>
+        </is>
+      </c>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3983288391</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>Goldie</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>Angel</t>
+        </is>
+      </c>
+      <c r="E1375" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2824124772</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>06:49</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>Amy Taylor</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>Nobody's Son</t>
+        </is>
+      </c>
+      <c r="E1376" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3852363911</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>Sandii &amp; The Sunsetz</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>THE MIRRORS OF EYES</t>
+        </is>
+      </c>
+      <c r="E1377" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1054105902</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>06:33</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>The National</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>Bloodbuzz Ohio</t>
+        </is>
+      </c>
+      <c r="E1378" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/7536434</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>06:23</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>Dusty Springfield</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>Spooky</t>
+        </is>
+      </c>
+      <c r="E1379" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/849998842</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>The Jam</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>Down In The Tube Station At Midnight</t>
+        </is>
+      </c>
+      <c r="E1380" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/932429</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>05:46</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>PJ Harvey</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>Long Snake Moan</t>
+        </is>
+      </c>
+      <c r="E1381" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1169909</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>05:42</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>Jungle</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>Carry On</t>
+        </is>
+      </c>
+      <c r="E1382" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3912744561</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>05:26</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>Sports Team</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>The Drop</t>
+        </is>
+      </c>
+      <c r="E1383" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1901318637</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>05:21</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>Simple Minds</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>Promised You A Miracle</t>
+        </is>
+      </c>
+      <c r="E1384" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/129310928</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>05:17</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>Grandmaster Flash &amp; Grandmaster Melle Mel &amp; The Furious Five</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>The Message</t>
+        </is>
+      </c>
+      <c r="E1385" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3824620</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>05:14</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>Stevie Nicks</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>Edge Of Seventeen</t>
+        </is>
+      </c>
+      <c r="E1386" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/680601</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>Ride</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>Twisterella</t>
+        </is>
+      </c>
+      <c r="E1387" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/65091317</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>04:57</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>The Paragons</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>The Tide Is High</t>
+        </is>
+      </c>
+      <c r="E1388" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/12074401</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>04:54</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>The Bug Club</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>Marriage</t>
+        </is>
+      </c>
+      <c r="E1389" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1389" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2410865895</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>04:42</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>Blur</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>She's So High</t>
+        </is>
+      </c>
+      <c r="E1390" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/44134071</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>04:34</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>Tirzah</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>No Limit</t>
+        </is>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2380761695</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>04:26</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>Iceage</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>Star</t>
+        </is>
+      </c>
+      <c r="E1392" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3838080001</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>04:18</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>Nadia Rose</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>Skwod</t>
+        </is>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/129632980</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>04:01</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>Richie Havens</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>Going Back To My Roots</t>
+        </is>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/727743</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>03:52</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>runo plum</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>monarch</t>
+        </is>
+      </c>
+      <c r="E1395" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3852651071</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>03:17</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>Max Cooper</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>Phi</t>
+        </is>
+      </c>
+      <c r="E1396" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/508738122</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>03:02</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>The Prodigy</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>Firestarter</t>
+        </is>
+      </c>
+      <c r="E1397" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/62126191</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>02:59</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>CJ Bolland</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>Sugar Is Sweeter</t>
+        </is>
+      </c>
+      <c r="E1398" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/437463102</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>02:55</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>Sneaker Pimps</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>Spin Spin Sugar (Armand's Dark Garage Mix)</t>
+        </is>
+      </c>
+      <c r="E1399" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1399" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2978182651</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>02:44</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>DJ Shadow</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>The Number Song</t>
+        </is>
+      </c>
+      <c r="E1400" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1400" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2075765177</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>02:40</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>Underworld</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>Pearl's Girl</t>
+        </is>
+      </c>
+      <c r="E1401" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3992156741</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>02:27</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>Grizzly Bear</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>Two Weeks</t>
+        </is>
+      </c>
+      <c r="E1402" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/5959430</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>02:20</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>Broadcast</t>
+        </is>
+      </c>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>The Book Lovers</t>
+        </is>
+      </c>
+      <c r="E1403" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/547829922</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>02:13</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>lau.ra</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>Blow (feat. Eliza Legzdina)</t>
+        </is>
+      </c>
+      <c r="E1404" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1404" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1584525142</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>02:07</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>Moonchild Sanelly</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>Undumpable</t>
+        </is>
+      </c>
+      <c r="E1405" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1472416922</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>01:56</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>N.O.R.E.</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>Nothin'</t>
+        </is>
+      </c>
+      <c r="E1406" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1406" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2301256</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>01:33</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>Super Furry Animals</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>If You Don't Want Me To Destroy You</t>
+        </is>
+      </c>
+      <c r="E1407" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1407" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3750704352</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>01:17</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>Cass Elliot</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>Dream A Little Dream Of Me</t>
+        </is>
+      </c>
+      <c r="E1408" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1408" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/124990190</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>01:03</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>Double 99</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>Rip Groove</t>
+        </is>
+      </c>
+      <c r="E1409" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1409" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3808858922</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>00:47</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>The Cranberries</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>Dreams</t>
+        </is>
+      </c>
+      <c r="E1410" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1410" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1176439</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>00:47</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>Mitski</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>Nobody</t>
+        </is>
+      </c>
+      <c r="E1411" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1411" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/526540822</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>00:46</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>Modest Mouse</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>Float On</t>
+        </is>
+      </c>
+      <c r="E1412" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/581923</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>00:46</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>Radiohead</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>High And Dry</t>
+        </is>
+      </c>
+      <c r="E1413" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1413" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/138544261</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>00:34</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>The xx</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>Dangerous</t>
+        </is>
+      </c>
+      <c r="E1414" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1414" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/139787505</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>00:23</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>Orange Lemon</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>Dreams Of Santa Anna</t>
+        </is>
+      </c>
+      <c r="E1415" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1415" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/60844265</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>00:19</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>The Stills</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>Lola Stars And Stripes</t>
+        </is>
+      </c>
+      <c r="E1416" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1416" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/662033</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>00:15</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>Pet Shop Boys</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>Paninaro</t>
+        </is>
+      </c>
+      <c r="E1417" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1417" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/462775492</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>00:10</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>Kelis</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>Milkshake</t>
+        </is>
+      </c>
+      <c r="E1418" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1418" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/573288552</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>00:06</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>Kindness</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>That's Alright</t>
+        </is>
+      </c>
+      <c r="E1419" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1419" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1816877887</t>
         </is>
       </c>
     </row>
@@ -43243,6 +47147,128 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1295" r:id="rId1294"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1296" r:id="rId1295"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1297" r:id="rId1296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1298" r:id="rId1297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1299" r:id="rId1298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1300" r:id="rId1299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1301" r:id="rId1300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1302" r:id="rId1301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1303" r:id="rId1302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1304" r:id="rId1303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1305" r:id="rId1304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1306" r:id="rId1305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1307" r:id="rId1306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1308" r:id="rId1307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1309" r:id="rId1308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1310" r:id="rId1309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1311" r:id="rId1310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1312" r:id="rId1311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1313" r:id="rId1312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1314" r:id="rId1313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1315" r:id="rId1314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1316" r:id="rId1315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1317" r:id="rId1316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1318" r:id="rId1317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1319" r:id="rId1318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1320" r:id="rId1319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1321" r:id="rId1320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1322" r:id="rId1321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1323" r:id="rId1322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1324" r:id="rId1323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1325" r:id="rId1324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1326" r:id="rId1325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1327" r:id="rId1326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1328" r:id="rId1327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1329" r:id="rId1328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1330" r:id="rId1329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1331" r:id="rId1330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1332" r:id="rId1331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1333" r:id="rId1332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1334" r:id="rId1333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1335" r:id="rId1334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1336" r:id="rId1335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1337" r:id="rId1336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1338" r:id="rId1337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1339" r:id="rId1338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1340" r:id="rId1339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1341" r:id="rId1340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1342" r:id="rId1341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1343" r:id="rId1342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1344" r:id="rId1343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1345" r:id="rId1344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1346" r:id="rId1345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1347" r:id="rId1346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1348" r:id="rId1347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1349" r:id="rId1348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1350" r:id="rId1349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1351" r:id="rId1350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1352" r:id="rId1351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1353" r:id="rId1352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1354" r:id="rId1353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1355" r:id="rId1354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1356" r:id="rId1355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1357" r:id="rId1356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1358" r:id="rId1357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1359" r:id="rId1358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1360" r:id="rId1359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1361" r:id="rId1360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1362" r:id="rId1361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1363" r:id="rId1362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1364" r:id="rId1363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1365" r:id="rId1364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1366" r:id="rId1365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1367" r:id="rId1366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1368" r:id="rId1367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1369" r:id="rId1368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1370" r:id="rId1369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1371" r:id="rId1370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1372" r:id="rId1371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1373" r:id="rId1372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1374" r:id="rId1373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1375" r:id="rId1374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1376" r:id="rId1375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1377" r:id="rId1376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1378" r:id="rId1377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1379" r:id="rId1378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1380" r:id="rId1379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1381" r:id="rId1380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1382" r:id="rId1381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1383" r:id="rId1382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1384" r:id="rId1383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1385" r:id="rId1384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1386" r:id="rId1385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1387" r:id="rId1386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1388" r:id="rId1387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1389" r:id="rId1388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1390" r:id="rId1389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1391" r:id="rId1390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1392" r:id="rId1391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1393" r:id="rId1392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1394" r:id="rId1393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1395" r:id="rId1394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1396" r:id="rId1395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1397" r:id="rId1396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1398" r:id="rId1397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1399" r:id="rId1398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1400" r:id="rId1399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1401" r:id="rId1400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1402" r:id="rId1401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1403" r:id="rId1402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1404" r:id="rId1403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1405" r:id="rId1404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1406" r:id="rId1405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1407" r:id="rId1406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1408" r:id="rId1407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1409" r:id="rId1408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1410" r:id="rId1409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1411" r:id="rId1410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1412" r:id="rId1411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1413" r:id="rId1412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1414" r:id="rId1413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1415" r:id="rId1414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1416" r:id="rId1415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1417" r:id="rId1416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1418" r:id="rId1417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1419" r:id="rId1418"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/BBC6 Music Log.xlsx
+++ b/output/BBC6 Music Log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1419"/>
+  <dimension ref="A1:F1547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -45846,6 +45846,4102 @@
       <c r="F1419" s="2" t="inlineStr">
         <is>
           <t>https://www.deezer.com/track/1816877887</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>Elis Regina &amp; Antônio Carlos Jobim</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>Águas De Março</t>
+        </is>
+      </c>
+      <c r="E1420" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/565340102</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>Radiohead</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>Let Down</t>
+        </is>
+      </c>
+      <c r="E1421" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1421" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/138539979</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>Radiohead</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>Planet Telex</t>
+        </is>
+      </c>
+      <c r="E1422" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1422" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/138544257</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>Swervedriver</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>The Other Jesus</t>
+        </is>
+      </c>
+      <c r="E1423" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1423" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/670997122</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>18:39</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>Marvin Gaye</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>Inner City Blues (Make Me Wanna Holler)</t>
+        </is>
+      </c>
+      <c r="E1424" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1424" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1133408932</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>Ed O’Brien</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>Sail On</t>
+        </is>
+      </c>
+      <c r="E1425" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1425" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/928226772</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>Bauhaus</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>She's In Parties</t>
+        </is>
+      </c>
+      <c r="E1426" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1426" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/620499372</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>The Beatles</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>Paperback Writer</t>
+        </is>
+      </c>
+      <c r="E1427" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1427" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/116348618</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>The Beatles</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>Roll Over Beethoven</t>
+        </is>
+      </c>
+      <c r="E1428" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1428" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/116348710</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>Simon &amp; Garfunkel</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>Bridge Over Troubled Water</t>
+        </is>
+      </c>
+      <c r="E1429" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1429" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13174764</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>Ed O’Brien</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>Blue Morpho</t>
+        </is>
+      </c>
+      <c r="E1430" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1430" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3817519472</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>Pink Floyd</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="E1431" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1431" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/116914022</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>Damaged Bug</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>SIKE WITCH</t>
+        </is>
+      </c>
+      <c r="E1432" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3834637731</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>Mick Ronson</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>Billy Porter</t>
+        </is>
+      </c>
+      <c r="E1433" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1433" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/59246621</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>The Claypool Lennon Delirium</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>Troll Bait</t>
+        </is>
+      </c>
+      <c r="E1434" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1434" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3810805352</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>Winston Groovy</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>Funky Chicken</t>
+        </is>
+      </c>
+      <c r="E1435" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1435" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3387308681</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>Tai Haf Heb Drigolyn</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>Arafcore</t>
+        </is>
+      </c>
+      <c r="E1436" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1436" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3102331931</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>Anna B Savage</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>A Common Tern</t>
+        </is>
+      </c>
+      <c r="E1437" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1437" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2583123702</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>Grandaddy</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>He's Simple, He's Dumb, He's The Pilot</t>
+        </is>
+      </c>
+      <c r="E1438" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1438" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/74601854</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>The Psychedelic Furs</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>Sister Europe</t>
+        </is>
+      </c>
+      <c r="E1439" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1439" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1030489</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>Season 2</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>Abundance of Power</t>
+        </is>
+      </c>
+      <c r="E1440" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1440" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3778683442</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>First Aid Kit</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>Emmylou</t>
+        </is>
+      </c>
+      <c r="E1441" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1441" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/30250761</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>Bright Eyes</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>We Are Nowhere And It's Now</t>
+        </is>
+      </c>
+      <c r="E1442" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1442" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1357792732</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>Radiohead</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>No Surprises</t>
+        </is>
+      </c>
+      <c r="E1443" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1443" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/138539157</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>Serge Gainsbourg</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>Elisa (Bande originale du film \"L'horizon\")</t>
+        </is>
+      </c>
+      <c r="E1444" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1444" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1249402462</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>DEVO</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>Come Back Jonee</t>
+        </is>
+      </c>
+      <c r="E1445" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1445" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/14631337</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>Em Oshan</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>Spiders On The Roof</t>
+        </is>
+      </c>
+      <c r="E1446" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1446" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2543989801</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>Suzi Analogue</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>Wild Blend</t>
+        </is>
+      </c>
+      <c r="E1447" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1447" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2705691292</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>Ciel &amp; Kilig</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>Hearing Voices (Club Mix)</t>
+        </is>
+      </c>
+      <c r="E1448" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1448" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1454606072</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>Charlotte Day Wilson</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>Selfish</t>
+        </is>
+      </c>
+      <c r="E1449" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1449" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3607979392</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>DORIS</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>Party 2</t>
+        </is>
+      </c>
+      <c r="E1450" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1450" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2880025372</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>Vayda</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>mutable signs</t>
+        </is>
+      </c>
+      <c r="E1451" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1451" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2188294267</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>Lucía Beyond</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>Releasing the Pride of Ownership</t>
+        </is>
+      </c>
+      <c r="E1452" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1452" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2153490857</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>Tosca</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>Suzuki</t>
+        </is>
+      </c>
+      <c r="E1453" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1453" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/136932186</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>Murex</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>Massacre</t>
+        </is>
+      </c>
+      <c r="E1454" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1454" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3976481711</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>Anastasia Kristensen</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>Black-Footed Ferret</t>
+        </is>
+      </c>
+      <c r="E1455" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1455" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3866483311</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>Tigerbalm</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>Coco Makako</t>
+        </is>
+      </c>
+      <c r="E1456" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1456" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3765750432</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>Duval Timothy &amp; Carlos Niño</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>loopy</t>
+        </is>
+      </c>
+      <c r="E1457" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1457" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4010690781</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>Chanpan</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>confessions part iii</t>
+        </is>
+      </c>
+      <c r="E1458" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1458" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3951969811</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>Madra Salach</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>Blue &amp; Gold</t>
+        </is>
+      </c>
+      <c r="E1459" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1459" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3668156722</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>Cocteau Twins</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>Heaven Or Las Vegas</t>
+        </is>
+      </c>
+      <c r="E1460" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1460" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/942505</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>Lambrini Girls</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>Love</t>
+        </is>
+      </c>
+      <c r="E1461" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1461" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3026886261</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>Westside Cowboy</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>Don't Throw Rocks</t>
+        </is>
+      </c>
+      <c r="E1462" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3763862372</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>The Vines</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>Get Free</t>
+        </is>
+      </c>
+      <c r="E1463" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1463" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3099711</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>Kellan Christopher Cragg</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>I Remember When I Woke Up</t>
+        </is>
+      </c>
+      <c r="E1464" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1464" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3223050831</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>The Go! Team</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>Ladyflash</t>
+        </is>
+      </c>
+      <c r="E1465" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1465" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/29681161</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>PVA</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>Boyface</t>
+        </is>
+      </c>
+      <c r="E1466" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1466" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3507083821</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>Adjua</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>Forest Wild</t>
+        </is>
+      </c>
+      <c r="E1467" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1467" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3976771551</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>Brakes</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>Comma Comma Comma Full Stop</t>
+        </is>
+      </c>
+      <c r="E1468" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/858234092</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>Adele</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>Hometown Glory</t>
+        </is>
+      </c>
+      <c r="E1469" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1469" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/512575642</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>Rizzle Kicks</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>Down With The Trumpets</t>
+        </is>
+      </c>
+      <c r="E1470" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13982003</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>Fatboy Slim</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>Praise You</t>
+        </is>
+      </c>
+      <c r="E1471" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1471" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/15686777</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>Confidence Man</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>Boyfriend</t>
+        </is>
+      </c>
+      <c r="E1472" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1472" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/483390132</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>DEADLETTER</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>To The Brim</t>
+        </is>
+      </c>
+      <c r="E1473" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1473" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3611471032</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>Sassy 009</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>Someone</t>
+        </is>
+      </c>
+      <c r="E1474" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1474" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3681798812</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>Chicks on Speed &amp; Peaches</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>We Don't Play Guitars</t>
+        </is>
+      </c>
+      <c r="E1475" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1475" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3839729261</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>Killing Joke</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>Eighties</t>
+        </is>
+      </c>
+      <c r="E1476" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1476" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2374844195</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>Porno for Pyros</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>Pets</t>
+        </is>
+      </c>
+      <c r="E1477" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1477" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/6631801</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>Sparklehorse</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>Someday I Will treat You Good</t>
+        </is>
+      </c>
+      <c r="E1478" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3265682</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>The Alex Opal Outfit &amp; Cherrykim</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>Yellow Sky</t>
+        </is>
+      </c>
+      <c r="E1479" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1479" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3919315761</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>The Police</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>Synchronicity II</t>
+        </is>
+      </c>
+      <c r="E1480" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1480" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/665714252</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>Hüsker Dü</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>Sorry Somehow</t>
+        </is>
+      </c>
+      <c r="E1481" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1481" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/866395</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>XTC</t>
+        </is>
+      </c>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>Sgt. Rock (Is Going to Help Me)</t>
+        </is>
+      </c>
+      <c r="E1482" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1482" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3135744</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>Thee Marloes</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>Through the Changes</t>
+        </is>
+      </c>
+      <c r="E1483" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1483" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3930482381</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>The Light</t>
+        </is>
+      </c>
+      <c r="E1484" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1484" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/6106509</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>The Orielles</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>Tears Are</t>
+        </is>
+      </c>
+      <c r="E1485" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1485" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3579814761</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>Faith Evans</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>Love Like This</t>
+        </is>
+      </c>
+      <c r="E1486" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1486" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/6917807</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>Mac DeMarco</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>Salad Days</t>
+        </is>
+      </c>
+      <c r="E1487" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1487" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/76008440</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>Dire Straits</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>Private Investigations</t>
+        </is>
+      </c>
+      <c r="E1488" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1488" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/85047174</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>Shocking Blue</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>Send Me A Postcard</t>
+        </is>
+      </c>
+      <c r="E1489" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1489" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/60703429</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>Athletes Of God</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>Don't Wanna Be Normal (feat. Lady Blackbird)</t>
+        </is>
+      </c>
+      <c r="E1490" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1490" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1791189147</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>Depeche Mode</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>Boys Say Go</t>
+        </is>
+      </c>
+      <c r="E1491" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1491" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/68511314</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>Young Fathers</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>Border Girl</t>
+        </is>
+      </c>
+      <c r="E1492" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1492" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/450956892</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>Lime Garden</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>Maybe Not Tonight</t>
+        </is>
+      </c>
+      <c r="E1493" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1493" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3612961312</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>The Streets</t>
+        </is>
+      </c>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>Weak Become Heroes</t>
+        </is>
+      </c>
+      <c r="E1494" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1494" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/6112956</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>Ashanti</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>Foolish</t>
+        </is>
+      </c>
+      <c r="E1495" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1495" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1125953</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>Biig Piig</t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>Sunny</t>
+        </is>
+      </c>
+      <c r="E1496" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1496" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/710449412</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>Lil Mama</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>Lip Gloss</t>
+        </is>
+      </c>
+      <c r="E1497" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1497" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13160880</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>Yello</t>
+        </is>
+      </c>
+      <c r="D1498" t="inlineStr">
+        <is>
+          <t>The Race</t>
+        </is>
+      </c>
+      <c r="E1498" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1498" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/131741252</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>07:23</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>Primal Scream</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>Accelerator</t>
+        </is>
+      </c>
+      <c r="E1499" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1499" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/857716012</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>The Beatles</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>Drive My Car</t>
+        </is>
+      </c>
+      <c r="E1500" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1500" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/116348252</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>Fleetwood Mac</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>The Chain</t>
+        </is>
+      </c>
+      <c r="E1501" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1501" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/63480992</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>Pulp</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>Razzmatazz</t>
+        </is>
+      </c>
+      <c r="E1502" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1502" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1761182157</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>Laura Cahen &amp; Hand Habits</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>Un lieu</t>
+        </is>
+      </c>
+      <c r="E1503" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1503" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3958682581</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>06:49</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>Beach House</t>
+        </is>
+      </c>
+      <c r="D1504" t="inlineStr">
+        <is>
+          <t>Wild</t>
+        </is>
+      </c>
+      <c r="E1504" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1504" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1137090292</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>Fontaines D.C.</t>
+        </is>
+      </c>
+      <c r="D1505" t="inlineStr">
+        <is>
+          <t>Cello Song</t>
+        </is>
+      </c>
+      <c r="E1505" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1505" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3837043811</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>Bobbie Gentry</t>
+        </is>
+      </c>
+      <c r="D1506" t="inlineStr">
+        <is>
+          <t>Seasons Come, Seasons Go</t>
+        </is>
+      </c>
+      <c r="E1506" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1506" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3162356</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>05:51</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>Brian Eno &amp; David Byrne</t>
+        </is>
+      </c>
+      <c r="D1507" t="inlineStr">
+        <is>
+          <t>Strange Overtones</t>
+        </is>
+      </c>
+      <c r="E1507" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1507" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2301076435</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>05:47</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>St. Vincent &amp; David Byrne</t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>Who</t>
+        </is>
+      </c>
+      <c r="E1508" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1508" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/59054111</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>05:37</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>Talking Heads</t>
+        </is>
+      </c>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>Born Under Punches (The Heat Goes On)</t>
+        </is>
+      </c>
+      <c r="E1509" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1509" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/5093669</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>05:27</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>Orchestral Manoeuvres in the Dark</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="E1510" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1510" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3156220</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>05:23</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>Adult DVD</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>Real Tree Lee</t>
+        </is>
+      </c>
+      <c r="E1511" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1511" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3705735652</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>05:15</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>The Smile</t>
+        </is>
+      </c>
+      <c r="D1512" t="inlineStr">
+        <is>
+          <t>Friend Of A Friend</t>
+        </is>
+      </c>
+      <c r="E1512" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1512" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2607903472</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>04:53</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>The Pains of Being Pure at Heart</t>
+        </is>
+      </c>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>Until The Sun Explodes</t>
+        </is>
+      </c>
+      <c r="E1513" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1513" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/138732625</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>04:33</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>Pixies</t>
+        </is>
+      </c>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>Gigantic</t>
+        </is>
+      </c>
+      <c r="E1514" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1514" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/936897</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>The Brian Jonestown Massacre</t>
+        </is>
+      </c>
+      <c r="D1515" t="inlineStr">
+        <is>
+          <t>Anemone</t>
+        </is>
+      </c>
+      <c r="E1515" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1515" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13127187</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>04:11</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>Arlo Parks</t>
+        </is>
+      </c>
+      <c r="D1516" t="inlineStr">
+        <is>
+          <t>2SIDED</t>
+        </is>
+      </c>
+      <c r="E1516" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1516" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3708374722</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>03:57</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>Loraine James &amp; Miho Hatori</t>
+        </is>
+      </c>
+      <c r="D1517" t="inlineStr">
+        <is>
+          <t>Flatline</t>
+        </is>
+      </c>
+      <c r="E1517" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1517" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3860930311</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>03:50</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>Mitski</t>
+        </is>
+      </c>
+      <c r="D1518" t="inlineStr">
+        <is>
+          <t>Washing Machine Heart</t>
+        </is>
+      </c>
+      <c r="E1518" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1518" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/526540852</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>03:34</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>DJ Shadow &amp; Run The Jewels</t>
+        </is>
+      </c>
+      <c r="D1519" t="inlineStr">
+        <is>
+          <t>Nobody Speak</t>
+        </is>
+      </c>
+      <c r="E1519" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1519" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1391399512</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>03:22</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>Nine Inch Nails</t>
+        </is>
+      </c>
+      <c r="D1520" t="inlineStr">
+        <is>
+          <t>Head Like A Hole</t>
+        </is>
+      </c>
+      <c r="E1520" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1520" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/384093711</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>03:18</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>The Shamen</t>
+        </is>
+      </c>
+      <c r="D1521" t="inlineStr">
+        <is>
+          <t>Move Any Mountain</t>
+        </is>
+      </c>
+      <c r="E1521" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1521" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/16317002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>03:14</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>Janelle Monáe</t>
+        </is>
+      </c>
+      <c r="D1522" t="inlineStr">
+        <is>
+          <t>Make Me Feel</t>
+        </is>
+      </c>
+      <c r="E1522" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1522" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/464228502</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>03:09</t>
+        </is>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>Basement Jaxx</t>
+        </is>
+      </c>
+      <c r="D1523" t="inlineStr">
+        <is>
+          <t>Bingo Bango</t>
+        </is>
+      </c>
+      <c r="E1523" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1523" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2195369127</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>03:07</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>The Fall</t>
+        </is>
+      </c>
+      <c r="D1524" t="inlineStr">
+        <is>
+          <t>Mr. Pharmacist</t>
+        </is>
+      </c>
+      <c r="E1524" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1524" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/638264812</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>03:05</t>
+        </is>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>Michael Kiwanuka</t>
+        </is>
+      </c>
+      <c r="D1525" t="inlineStr">
+        <is>
+          <t>You Ain't The Problem</t>
+        </is>
+      </c>
+      <c r="E1525" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1525" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/788563602</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>03:02</t>
+        </is>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>Wet Leg</t>
+        </is>
+      </c>
+      <c r="D1526" t="inlineStr">
+        <is>
+          <t>Wet Dream</t>
+        </is>
+      </c>
+      <c r="E1526" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1526" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1549197792</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>02:57</t>
+        </is>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>Fcukers</t>
+        </is>
+      </c>
+      <c r="D1527" t="inlineStr">
+        <is>
+          <t>L.U.C.K.Y</t>
+        </is>
+      </c>
+      <c r="E1527" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1527" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3772064442</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>02:54</t>
+        </is>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>Alabama 3</t>
+        </is>
+      </c>
+      <c r="D1528" t="inlineStr">
+        <is>
+          <t>Ain't Goin' To Goa</t>
+        </is>
+      </c>
+      <c r="E1528" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1528" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1763184987</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>02:51</t>
+        </is>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>The Smiths</t>
+        </is>
+      </c>
+      <c r="D1529" t="inlineStr">
+        <is>
+          <t>William, It Was Really Nothing</t>
+        </is>
+      </c>
+      <c r="E1529" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1529" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13786032</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>02:49</t>
+        </is>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>T. Rex</t>
+        </is>
+      </c>
+      <c r="D1530" t="inlineStr">
+        <is>
+          <t>Metal Guru</t>
+        </is>
+      </c>
+      <c r="E1530" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1530" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1762966407</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>02:46</t>
+        </is>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>Marika Hackman</t>
+        </is>
+      </c>
+      <c r="D1531" t="inlineStr">
+        <is>
+          <t>Boyfriend</t>
+        </is>
+      </c>
+      <c r="E1531" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1531" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1137139742</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>02:37</t>
+        </is>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>Young MC</t>
+        </is>
+      </c>
+      <c r="D1532" t="inlineStr">
+        <is>
+          <t>Know How</t>
+        </is>
+      </c>
+      <c r="E1532" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1532" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/83971949</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>02:34</t>
+        </is>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>Badly Drawn Boy</t>
+        </is>
+      </c>
+      <c r="D1533" t="inlineStr">
+        <is>
+          <t>All Possibilities</t>
+        </is>
+      </c>
+      <c r="E1533" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1533" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/128973452</t>
+        </is>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>02:26</t>
+        </is>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>Gilberto Gil</t>
+        </is>
+      </c>
+      <c r="D1534" t="inlineStr">
+        <is>
+          <t>Palco</t>
+        </is>
+      </c>
+      <c r="E1534" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1534" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/709002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>02:19</t>
+        </is>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>Savages</t>
+        </is>
+      </c>
+      <c r="D1535" t="inlineStr">
+        <is>
+          <t>Husbands</t>
+        </is>
+      </c>
+      <c r="E1535" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1535" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1138986192</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>Sounds of Blackness</t>
+        </is>
+      </c>
+      <c r="D1536" t="inlineStr">
+        <is>
+          <t>The Pressure</t>
+        </is>
+      </c>
+      <c r="E1536" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1536" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2525836</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>02:01</t>
+        </is>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>English Teacher</t>
+        </is>
+      </c>
+      <c r="D1537" t="inlineStr">
+        <is>
+          <t>Nearly Daffodils</t>
+        </is>
+      </c>
+      <c r="E1537" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1537" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2477146031</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>01:48</t>
+        </is>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="D1538" t="inlineStr">
+        <is>
+          <t>Wild Grasses</t>
+        </is>
+      </c>
+      <c r="E1538" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1538" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3761434972</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>01:44</t>
+        </is>
+      </c>
+      <c r="C1539" t="inlineStr">
+        <is>
+          <t>The Shins</t>
+        </is>
+      </c>
+      <c r="D1539" t="inlineStr">
+        <is>
+          <t>Fighting In A Sack</t>
+        </is>
+      </c>
+      <c r="E1539" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1539" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2459694975</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>01:35</t>
+        </is>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>HAIM</t>
+        </is>
+      </c>
+      <c r="D1540" t="inlineStr">
+        <is>
+          <t>Forever</t>
+        </is>
+      </c>
+      <c r="E1540" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1540" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/70807168</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>01:18</t>
+        </is>
+      </c>
+      <c r="C1541" t="inlineStr">
+        <is>
+          <t>JJerome87</t>
+        </is>
+      </c>
+      <c r="D1541" t="inlineStr">
+        <is>
+          <t>Track and Field</t>
+        </is>
+      </c>
+      <c r="E1541" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1541" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3879791861</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>01:02</t>
+        </is>
+      </c>
+      <c r="C1542" t="inlineStr">
+        <is>
+          <t>Pavement</t>
+        </is>
+      </c>
+      <c r="D1542" t="inlineStr">
+        <is>
+          <t>Stereo</t>
+        </is>
+      </c>
+      <c r="E1542" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1542" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/105280990</t>
+        </is>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>00:59</t>
+        </is>
+      </c>
+      <c r="C1543" t="inlineStr">
+        <is>
+          <t>The Go! Team</t>
+        </is>
+      </c>
+      <c r="D1543" t="inlineStr">
+        <is>
+          <t>The Power Is On</t>
+        </is>
+      </c>
+      <c r="E1543" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1543" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/29681181</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>00:44</t>
+        </is>
+      </c>
+      <c r="C1544" t="inlineStr">
+        <is>
+          <t>Chanel Beads</t>
+        </is>
+      </c>
+      <c r="D1544" t="inlineStr">
+        <is>
+          <t>The Coward Forgets His Nightmare</t>
+        </is>
+      </c>
+      <c r="E1544" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1544" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3947078031</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>00:34</t>
+        </is>
+      </c>
+      <c r="C1545" t="inlineStr">
+        <is>
+          <t>Kendrick Lamar</t>
+        </is>
+      </c>
+      <c r="D1545" t="inlineStr">
+        <is>
+          <t>These Walls</t>
+        </is>
+      </c>
+      <c r="E1545" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1545" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/97206064</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>00:08</t>
+        </is>
+      </c>
+      <c r="C1546" t="inlineStr">
+        <is>
+          <t>Wu-Tang Clan</t>
+        </is>
+      </c>
+      <c r="D1546" t="inlineStr">
+        <is>
+          <t>Protect Ya Neck</t>
+        </is>
+      </c>
+      <c r="E1546" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1546" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/541327</t>
+        </is>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>00:01</t>
+        </is>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>St. Vincent</t>
+        </is>
+      </c>
+      <c r="D1547" t="inlineStr">
+        <is>
+          <t>Digital Witness</t>
+        </is>
+      </c>
+      <c r="E1547" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1547" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/94030966</t>
         </is>
       </c>
     </row>
@@ -47269,6 +51365,134 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1417" r:id="rId1416"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1418" r:id="rId1417"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1419" r:id="rId1418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1420" r:id="rId1419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1421" r:id="rId1420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1422" r:id="rId1421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1423" r:id="rId1422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1424" r:id="rId1423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1425" r:id="rId1424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1426" r:id="rId1425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1427" r:id="rId1426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1428" r:id="rId1427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1429" r:id="rId1428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1430" r:id="rId1429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1431" r:id="rId1430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1432" r:id="rId1431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1433" r:id="rId1432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1434" r:id="rId1433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1435" r:id="rId1434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1436" r:id="rId1435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1437" r:id="rId1436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1438" r:id="rId1437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1439" r:id="rId1438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1440" r:id="rId1439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1441" r:id="rId1440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1442" r:id="rId1441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1443" r:id="rId1442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1444" r:id="rId1443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1445" r:id="rId1444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1446" r:id="rId1445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1447" r:id="rId1446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1448" r:id="rId1447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1449" r:id="rId1448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1450" r:id="rId1449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1451" r:id="rId1450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1452" r:id="rId1451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1453" r:id="rId1452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1454" r:id="rId1453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1455" r:id="rId1454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1456" r:id="rId1455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1457" r:id="rId1456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1458" r:id="rId1457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1459" r:id="rId1458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1460" r:id="rId1459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1461" r:id="rId1460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1462" r:id="rId1461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1463" r:id="rId1462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1464" r:id="rId1463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1465" r:id="rId1464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1466" r:id="rId1465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1467" r:id="rId1466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1468" r:id="rId1467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1469" r:id="rId1468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1470" r:id="rId1469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1471" r:id="rId1470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1472" r:id="rId1471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1473" r:id="rId1472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1474" r:id="rId1473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1475" r:id="rId1474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1476" r:id="rId1475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1477" r:id="rId1476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1478" r:id="rId1477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1479" r:id="rId1478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1480" r:id="rId1479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1481" r:id="rId1480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1482" r:id="rId1481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1483" r:id="rId1482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1484" r:id="rId1483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1485" r:id="rId1484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1486" r:id="rId1485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1487" r:id="rId1486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1488" r:id="rId1487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1489" r:id="rId1488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1490" r:id="rId1489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1491" r:id="rId1490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1492" r:id="rId1491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1493" r:id="rId1492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1494" r:id="rId1493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1495" r:id="rId1494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1496" r:id="rId1495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1497" r:id="rId1496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1498" r:id="rId1497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1499" r:id="rId1498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1500" r:id="rId1499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1501" r:id="rId1500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1502" r:id="rId1501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1503" r:id="rId1502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1504" r:id="rId1503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1505" r:id="rId1504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1506" r:id="rId1505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1507" r:id="rId1506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1508" r:id="rId1507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1509" r:id="rId1508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1510" r:id="rId1509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1511" r:id="rId1510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1512" r:id="rId1511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1513" r:id="rId1512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1514" r:id="rId1513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1515" r:id="rId1514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1516" r:id="rId1515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1517" r:id="rId1516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1518" r:id="rId1517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1519" r:id="rId1518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1520" r:id="rId1519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1521" r:id="rId1520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1522" r:id="rId1521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1523" r:id="rId1522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1524" r:id="rId1523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1525" r:id="rId1524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1526" r:id="rId1525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1527" r:id="rId1526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1528" r:id="rId1527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1529" r:id="rId1528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1530" r:id="rId1529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1531" r:id="rId1530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1532" r:id="rId1531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1533" r:id="rId1532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1534" r:id="rId1533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1535" r:id="rId1534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1536" r:id="rId1535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1537" r:id="rId1536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1538" r:id="rId1537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1539" r:id="rId1538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1540" r:id="rId1539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1541" r:id="rId1540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1542" r:id="rId1541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1543" r:id="rId1542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1544" r:id="rId1543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1545" r:id="rId1544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1546" r:id="rId1545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1547" r:id="rId1546"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/BBC6 Music Log.xlsx
+++ b/output/BBC6 Music Log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1547"/>
+  <dimension ref="A1:F1695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -49942,6 +49942,4742 @@
       <c r="F1547" s="2" t="inlineStr">
         <is>
           <t>https://www.deezer.com/track/94030966</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>Bianca Oblivion</t>
+        </is>
+      </c>
+      <c r="D1548" t="inlineStr">
+        <is>
+          <t>Sinais (The Glitch Mob Remix)</t>
+        </is>
+      </c>
+      <c r="E1548" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1548" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2628551322</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>BASHKKA</t>
+        </is>
+      </c>
+      <c r="D1549" t="inlineStr">
+        <is>
+          <t>Act Bad</t>
+        </is>
+      </c>
+      <c r="E1549" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1549" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2098767517</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="C1550" t="inlineStr">
+        <is>
+          <t>Future FreQz</t>
+        </is>
+      </c>
+      <c r="D1550" t="inlineStr">
+        <is>
+          <t>Put Em Up</t>
+        </is>
+      </c>
+      <c r="E1550" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1550" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3356980441</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>Klubbheads</t>
+        </is>
+      </c>
+      <c r="D1551" t="inlineStr">
+        <is>
+          <t>Hard House</t>
+        </is>
+      </c>
+      <c r="E1551" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1551" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3297817611</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>Tronikhouse</t>
+        </is>
+      </c>
+      <c r="D1552" t="inlineStr">
+        <is>
+          <t>Uptempo</t>
+        </is>
+      </c>
+      <c r="E1552" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1552" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2351921825</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>Sam Alfred</t>
+        </is>
+      </c>
+      <c r="D1553" t="inlineStr">
+        <is>
+          <t>Feel The Friction</t>
+        </is>
+      </c>
+      <c r="E1553" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1553" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3232437241</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>Tony De Vit</t>
+        </is>
+      </c>
+      <c r="D1554" t="inlineStr">
+        <is>
+          <t>The Dawn</t>
+        </is>
+      </c>
+      <c r="E1554" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1554" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/770839912</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>Silva Bumpa</t>
+        </is>
+      </c>
+      <c r="D1555" t="inlineStr">
+        <is>
+          <t>Rush On Me</t>
+        </is>
+      </c>
+      <c r="E1555" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1555" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3205440581</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>Andre Zimmer &amp; Chloé Caillet</t>
+        </is>
+      </c>
+      <c r="D1556" t="inlineStr">
+        <is>
+          <t>Come Back 2 Me</t>
+        </is>
+      </c>
+      <c r="E1556" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1556" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3708842592</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>Manix</t>
+        </is>
+      </c>
+      <c r="D1557" t="inlineStr">
+        <is>
+          <t>Oblivion (Head in the Clouds)</t>
+        </is>
+      </c>
+      <c r="E1557" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1557" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2373249935</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>DJ Seduction</t>
+        </is>
+      </c>
+      <c r="D1558" t="inlineStr">
+        <is>
+          <t>Hardcore Heaven</t>
+        </is>
+      </c>
+      <c r="E1558" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1558" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/100887034</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>Syberian98</t>
+        </is>
+      </c>
+      <c r="D1559" t="inlineStr">
+        <is>
+          <t>Arcagal</t>
+        </is>
+      </c>
+      <c r="E1559" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1559" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3643724032</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>Binary Finary</t>
+        </is>
+      </c>
+      <c r="D1560" t="inlineStr">
+        <is>
+          <t>1998 (Anfisa Letyago Extended Remix)</t>
+        </is>
+      </c>
+      <c r="E1560" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1560" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2875981402</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>1morning</t>
+        </is>
+      </c>
+      <c r="D1561" t="inlineStr">
+        <is>
+          <t>The Circuit</t>
+        </is>
+      </c>
+      <c r="E1561" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1561" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3465080851</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="D1562" t="inlineStr">
+        <is>
+          <t>Dignity</t>
+        </is>
+      </c>
+      <c r="E1562" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1562" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3601376602</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>Pulp</t>
+        </is>
+      </c>
+      <c r="D1563" t="inlineStr">
+        <is>
+          <t>Spike Island</t>
+        </is>
+      </c>
+      <c r="E1563" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1563" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3929129601</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>Franz Ferdinand</t>
+        </is>
+      </c>
+      <c r="D1564" t="inlineStr">
+        <is>
+          <t>Do You Want To</t>
+        </is>
+      </c>
+      <c r="E1564" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1564" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4315297</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>The 1975</t>
+        </is>
+      </c>
+      <c r="D1565" t="inlineStr">
+        <is>
+          <t>Settle Down</t>
+        </is>
+      </c>
+      <c r="E1565" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1565" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1250701122</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>PJ Harvey</t>
+        </is>
+      </c>
+      <c r="D1566" t="inlineStr">
+        <is>
+          <t>The Community Of Hope</t>
+        </is>
+      </c>
+      <c r="E1566" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1566" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/122885560</t>
+        </is>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>The Smiths</t>
+        </is>
+      </c>
+      <c r="D1567" t="inlineStr">
+        <is>
+          <t>The Headmaster Ritual</t>
+        </is>
+      </c>
+      <c r="E1567" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1567" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13785999</t>
+        </is>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>Wolf Alice</t>
+        </is>
+      </c>
+      <c r="D1568" t="inlineStr">
+        <is>
+          <t>Bloom Baby Bloom</t>
+        </is>
+      </c>
+      <c r="E1568" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1568" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3508653201</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>Kaiser Chiefs</t>
+        </is>
+      </c>
+      <c r="D1569" t="inlineStr">
+        <is>
+          <t>Ruby</t>
+        </is>
+      </c>
+      <c r="E1569" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1569" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/93915710</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>The Vaccines</t>
+        </is>
+      </c>
+      <c r="D1570" t="inlineStr">
+        <is>
+          <t>I Always Knew</t>
+        </is>
+      </c>
+      <c r="E1570" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1570" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/941087892</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>Mogwai</t>
+        </is>
+      </c>
+      <c r="D1571" t="inlineStr">
+        <is>
+          <t>Ritchie Sacramento</t>
+        </is>
+      </c>
+      <c r="E1571" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1571" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1103079652</t>
+        </is>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>The Last Shadow Puppets</t>
+        </is>
+      </c>
+      <c r="D1572" t="inlineStr">
+        <is>
+          <t>Standing Next To Me</t>
+        </is>
+      </c>
+      <c r="E1572" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1572" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4315519</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>The Killers</t>
+        </is>
+      </c>
+      <c r="D1573" t="inlineStr">
+        <is>
+          <t>All These Things That I've Done</t>
+        </is>
+      </c>
+      <c r="E1573" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1573" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/71955241</t>
+        </is>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>The Wombats</t>
+        </is>
+      </c>
+      <c r="D1574" t="inlineStr">
+        <is>
+          <t>If You Ever Leave, I'm Coming with You</t>
+        </is>
+      </c>
+      <c r="E1574" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1574" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1898968737</t>
+        </is>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>The View</t>
+        </is>
+      </c>
+      <c r="D1575" t="inlineStr">
+        <is>
+          <t>Superstar Tradesman</t>
+        </is>
+      </c>
+      <c r="E1575" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1575" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/550531</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>Wet Leg</t>
+        </is>
+      </c>
+      <c r="D1576" t="inlineStr">
+        <is>
+          <t>mangetout</t>
+        </is>
+      </c>
+      <c r="E1576" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1576" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3285890751</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>The Libertines</t>
+        </is>
+      </c>
+      <c r="D1577" t="inlineStr">
+        <is>
+          <t>Can't Stand Me Now</t>
+        </is>
+      </c>
+      <c r="E1577" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1577" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/946297</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>Blur</t>
+        </is>
+      </c>
+      <c r="D1578" t="inlineStr">
+        <is>
+          <t>Song 2</t>
+        </is>
+      </c>
+      <c r="E1578" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1578" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3102130</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>Foals</t>
+        </is>
+      </c>
+      <c r="D1579" t="inlineStr">
+        <is>
+          <t>Olympic Airways</t>
+        </is>
+      </c>
+      <c r="E1579" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1579" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1230340012</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>DEADLETTER</t>
+        </is>
+      </c>
+      <c r="D1580" t="inlineStr">
+        <is>
+          <t>Binge</t>
+        </is>
+      </c>
+      <c r="E1580" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1580" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1843023607</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>Warmduscher</t>
+        </is>
+      </c>
+      <c r="D1581" t="inlineStr">
+        <is>
+          <t>I Got Friends</t>
+        </is>
+      </c>
+      <c r="E1581" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1581" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/489635002</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>The Smashing Pumpkins</t>
+        </is>
+      </c>
+      <c r="D1582" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="E1582" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1582" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/68976286</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>Martial Arts</t>
+        </is>
+      </c>
+      <c r="D1583" t="inlineStr">
+        <is>
+          <t>Before The Fire</t>
+        </is>
+      </c>
+      <c r="E1583" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1583" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3926335611</t>
+        </is>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="D1584" t="inlineStr">
+        <is>
+          <t>Pretend We're Dead</t>
+        </is>
+      </c>
+      <c r="E1584" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1584" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/5195706</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>Gurriers</t>
+        </is>
+      </c>
+      <c r="D1585" t="inlineStr">
+        <is>
+          <t>Top Of The Bill</t>
+        </is>
+      </c>
+      <c r="E1585" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1585" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2755099761</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>Arctic Monkeys</t>
+        </is>
+      </c>
+      <c r="D1586" t="inlineStr">
+        <is>
+          <t>Old Yellow Bricks</t>
+        </is>
+      </c>
+      <c r="E1586" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1586" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/14633828</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>Dodgy</t>
+        </is>
+      </c>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>Good Enough</t>
+        </is>
+      </c>
+      <c r="E1587" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1587" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2162563</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>Artificial Go</t>
+        </is>
+      </c>
+      <c r="D1588" t="inlineStr">
+        <is>
+          <t>Triple Ones</t>
+        </is>
+      </c>
+      <c r="E1588" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1588" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3923437011</t>
+        </is>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>Lambrini Girls</t>
+        </is>
+      </c>
+      <c r="D1589" t="inlineStr">
+        <is>
+          <t>Body Of Mine</t>
+        </is>
+      </c>
+      <c r="E1589" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1589" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2702133352</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>Super Furry Animals</t>
+        </is>
+      </c>
+      <c r="D1590" t="inlineStr">
+        <is>
+          <t>(Drawing) Rings Around the World</t>
+        </is>
+      </c>
+      <c r="E1590" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1590" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3786037892</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>Blur</t>
+        </is>
+      </c>
+      <c r="D1591" t="inlineStr">
+        <is>
+          <t>Parklife</t>
+        </is>
+      </c>
+      <c r="E1591" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1591" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/44134631</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t>Parquet Courts</t>
+        </is>
+      </c>
+      <c r="D1592" t="inlineStr">
+        <is>
+          <t>Total Football</t>
+        </is>
+      </c>
+      <c r="E1592" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1592" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/496911742</t>
+        </is>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>The Kills</t>
+        </is>
+      </c>
+      <c r="D1593" t="inlineStr">
+        <is>
+          <t>Cheap and Cheerful</t>
+        </is>
+      </c>
+      <c r="E1593" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1593" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/71990978</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>Gorillaz</t>
+        </is>
+      </c>
+      <c r="D1594" t="inlineStr">
+        <is>
+          <t>Dare</t>
+        </is>
+      </c>
+      <c r="E1594" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1594" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3129413</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>Dam Swindle &amp; Haile Supreme</t>
+        </is>
+      </c>
+      <c r="D1595" t="inlineStr">
+        <is>
+          <t>Not Enough (Two Soul Fusion Organ House Remix)</t>
+        </is>
+      </c>
+      <c r="E1595" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1595" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3965494701</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>Lack of Afro</t>
+        </is>
+      </c>
+      <c r="D1596" t="inlineStr">
+        <is>
+          <t>Where's Your Soul At?</t>
+        </is>
+      </c>
+      <c r="E1596" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1596" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3482363481</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t>Burna Boy</t>
+        </is>
+      </c>
+      <c r="D1597" t="inlineStr">
+        <is>
+          <t>Kilometre</t>
+        </is>
+      </c>
+      <c r="E1597" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1597" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1353162152</t>
+        </is>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>Obongjayar</t>
+        </is>
+      </c>
+      <c r="D1598" t="inlineStr">
+        <is>
+          <t>Just Cool</t>
+        </is>
+      </c>
+      <c r="E1598" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1598" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2245005307</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>Mica Paris</t>
+        </is>
+      </c>
+      <c r="D1599" t="inlineStr">
+        <is>
+          <t>I Should've Known Better</t>
+        </is>
+      </c>
+      <c r="E1599" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1599" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1377753842</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>Nelly</t>
+        </is>
+      </c>
+      <c r="D1600" t="inlineStr">
+        <is>
+          <t>Hot In Herre</t>
+        </is>
+      </c>
+      <c r="E1600" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1600" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2447436</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>Donald Byrd</t>
+        </is>
+      </c>
+      <c r="D1601" t="inlineStr">
+        <is>
+          <t>Wind Parade</t>
+        </is>
+      </c>
+      <c r="E1601" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1601" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3105500</t>
+        </is>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>Unknown Mortal Orchestra</t>
+        </is>
+      </c>
+      <c r="D1602" t="inlineStr">
+        <is>
+          <t>Hunnybee</t>
+        </is>
+      </c>
+      <c r="E1602" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1602" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/468638852</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t>Submotion Orchestra</t>
+        </is>
+      </c>
+      <c r="D1603" t="inlineStr">
+        <is>
+          <t>Passed Me By</t>
+        </is>
+      </c>
+      <c r="E1603" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1603" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3810695882</t>
+        </is>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>Omar</t>
+        </is>
+      </c>
+      <c r="D1604" t="inlineStr">
+        <is>
+          <t>It's So</t>
+        </is>
+      </c>
+      <c r="E1604" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1604" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1502653162</t>
+        </is>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>Chaka Khan</t>
+        </is>
+      </c>
+      <c r="D1605" t="inlineStr">
+        <is>
+          <t>Fate</t>
+        </is>
+      </c>
+      <c r="E1605" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1605" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3906250</t>
+        </is>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>Patrice Rushen</t>
+        </is>
+      </c>
+      <c r="D1606" t="inlineStr">
+        <is>
+          <t>I Was Tired of Being Alone</t>
+        </is>
+      </c>
+      <c r="E1606" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1606" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/434614232</t>
+        </is>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>Ty</t>
+        </is>
+      </c>
+      <c r="D1607" t="inlineStr">
+        <is>
+          <t>Wait A Minute</t>
+        </is>
+      </c>
+      <c r="E1607" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1607" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/10237086</t>
+        </is>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>Mulatu Astatke</t>
+        </is>
+      </c>
+      <c r="D1608" t="inlineStr">
+        <is>
+          <t>Mascaram Setaba</t>
+        </is>
+      </c>
+      <c r="E1608" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1608" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/349369701</t>
+        </is>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>Bobbi Humphrey</t>
+        </is>
+      </c>
+      <c r="D1609" t="inlineStr">
+        <is>
+          <t>Jasper Country Man</t>
+        </is>
+      </c>
+      <c r="E1609" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1609" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3104614</t>
+        </is>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>Bunny Mack</t>
+        </is>
+      </c>
+      <c r="D1610" t="inlineStr">
+        <is>
+          <t>Let Me Love You</t>
+        </is>
+      </c>
+      <c r="E1610" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1610" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3155459171</t>
+        </is>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>Lily Allen</t>
+        </is>
+      </c>
+      <c r="D1611" t="inlineStr">
+        <is>
+          <t>Knock 'Em Out</t>
+        </is>
+      </c>
+      <c r="E1611" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1611" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/41541931</t>
+        </is>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>N’Klabe</t>
+        </is>
+      </c>
+      <c r="D1612" t="inlineStr">
+        <is>
+          <t>I Love Salsa (Album Version)</t>
+        </is>
+      </c>
+      <c r="E1612" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1612" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13210497</t>
+        </is>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>Frankie Goes to Hollywood</t>
+        </is>
+      </c>
+      <c r="D1613" t="inlineStr">
+        <is>
+          <t>Welcome To The Pleasuredome</t>
+        </is>
+      </c>
+      <c r="E1613" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1613" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/479846902</t>
+        </is>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="C1614" t="inlineStr">
+        <is>
+          <t>Thin Lizzy</t>
+        </is>
+      </c>
+      <c r="D1614" t="inlineStr">
+        <is>
+          <t>Dancing in the Moonlight (It's Caught Me In Its Spotlight)</t>
+        </is>
+      </c>
+      <c r="E1614" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1614" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/12452380</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>SL2</t>
+        </is>
+      </c>
+      <c r="D1615" t="inlineStr">
+        <is>
+          <t>On A Ragga Tip</t>
+        </is>
+      </c>
+      <c r="E1615" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1615" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/950467</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="C1616" t="inlineStr">
+        <is>
+          <t>CAKE</t>
+        </is>
+      </c>
+      <c r="D1616" t="inlineStr">
+        <is>
+          <t>The Distance</t>
+        </is>
+      </c>
+      <c r="E1616" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1616" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/959356</t>
+        </is>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="C1617" t="inlineStr">
+        <is>
+          <t>Skunk Anansie</t>
+        </is>
+      </c>
+      <c r="D1617" t="inlineStr">
+        <is>
+          <t>An Artist Is An Artist</t>
+        </is>
+      </c>
+      <c r="E1617" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1617" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3202366331</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="C1618" t="inlineStr">
+        <is>
+          <t>Sonz of a Loop da Loop Era</t>
+        </is>
+      </c>
+      <c r="D1618" t="inlineStr">
+        <is>
+          <t>Far out</t>
+        </is>
+      </c>
+      <c r="E1618" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1618" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2206966927</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="C1619" t="inlineStr">
+        <is>
+          <t>Fugazi</t>
+        </is>
+      </c>
+      <c r="D1619" t="inlineStr">
+        <is>
+          <t>Waiting Room</t>
+        </is>
+      </c>
+      <c r="E1619" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1619" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1717942497</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="C1620" t="inlineStr">
+        <is>
+          <t>Panic Shack</t>
+        </is>
+      </c>
+      <c r="D1620" t="inlineStr">
+        <is>
+          <t>Girl Band Starter Pack</t>
+        </is>
+      </c>
+      <c r="E1620" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1620" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3292900931</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="C1621" t="inlineStr">
+        <is>
+          <t>Red Hot Chili Peppers</t>
+        </is>
+      </c>
+      <c r="D1621" t="inlineStr">
+        <is>
+          <t>Californication</t>
+        </is>
+      </c>
+      <c r="E1621" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1621" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/725274</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>Naughty by Nature</t>
+        </is>
+      </c>
+      <c r="D1622" t="inlineStr">
+        <is>
+          <t>Feel Me Flow</t>
+        </is>
+      </c>
+      <c r="E1622" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1622" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1586966932</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="D1623" t="inlineStr">
+        <is>
+          <t>Let's Make Love And Listen To Death From Above</t>
+        </is>
+      </c>
+      <c r="E1623" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1623" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1137185532</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>Gossip</t>
+        </is>
+      </c>
+      <c r="D1624" t="inlineStr">
+        <is>
+          <t>Heavy Cross</t>
+        </is>
+      </c>
+      <c r="E1624" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1624" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3732049</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>Suzanne Vega</t>
+        </is>
+      </c>
+      <c r="D1625" t="inlineStr">
+        <is>
+          <t>Marlene On The Wall</t>
+        </is>
+      </c>
+      <c r="E1625" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1625" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/542467382</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="C1626" t="inlineStr">
+        <is>
+          <t>Queen Latifah</t>
+        </is>
+      </c>
+      <c r="D1626" t="inlineStr">
+        <is>
+          <t>Come Into My House</t>
+        </is>
+      </c>
+      <c r="E1626" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1626" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1584428642</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="C1627" t="inlineStr">
+        <is>
+          <t>The Cure</t>
+        </is>
+      </c>
+      <c r="D1627" t="inlineStr">
+        <is>
+          <t>Friday I'm In Love</t>
+        </is>
+      </c>
+      <c r="E1627" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1627" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/409670382</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="C1628" t="inlineStr">
+        <is>
+          <t>Robyn</t>
+        </is>
+      </c>
+      <c r="D1628" t="inlineStr">
+        <is>
+          <t>Dancing On My Own</t>
+        </is>
+      </c>
+      <c r="E1628" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1628" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/821100262</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="C1629" t="inlineStr">
+        <is>
+          <t>LuxJury</t>
+        </is>
+      </c>
+      <c r="D1629" t="inlineStr">
+        <is>
+          <t>Both Teams</t>
+        </is>
+      </c>
+      <c r="E1629" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1629" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3680180902</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="C1630" t="inlineStr">
+        <is>
+          <t>Ramones</t>
+        </is>
+      </c>
+      <c r="D1630" t="inlineStr">
+        <is>
+          <t>Sheena Is A Punk Rocker</t>
+        </is>
+      </c>
+      <c r="E1630" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1630" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/426704712</t>
+        </is>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="C1631" t="inlineStr">
+        <is>
+          <t>Queens of the Stone Age</t>
+        </is>
+      </c>
+      <c r="D1631" t="inlineStr">
+        <is>
+          <t>The Lost Art Of Keeping A Secret</t>
+        </is>
+      </c>
+      <c r="E1631" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1631" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/6820130</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="C1632" t="inlineStr">
+        <is>
+          <t>Planningtorock</t>
+        </is>
+      </c>
+      <c r="D1632" t="inlineStr">
+        <is>
+          <t>Jam Fam</t>
+        </is>
+      </c>
+      <c r="E1632" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1632" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/992658332</t>
+        </is>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="C1633" t="inlineStr">
+        <is>
+          <t>Cameo</t>
+        </is>
+      </c>
+      <c r="D1633" t="inlineStr">
+        <is>
+          <t>Word Up</t>
+        </is>
+      </c>
+      <c r="E1633" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1633" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2600934</t>
+        </is>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="C1634" t="inlineStr">
+        <is>
+          <t>Eric B. &amp; Rakim</t>
+        </is>
+      </c>
+      <c r="D1634" t="inlineStr">
+        <is>
+          <t>Paid In Full</t>
+        </is>
+      </c>
+      <c r="E1634" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1634" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2508443</t>
+        </is>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="C1635" t="inlineStr">
+        <is>
+          <t>The Vaccines</t>
+        </is>
+      </c>
+      <c r="D1635" t="inlineStr">
+        <is>
+          <t>Wreckin' Bar (Ra Ra Ra)</t>
+        </is>
+      </c>
+      <c r="E1635" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1635" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/941197992</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="C1636" t="inlineStr">
+        <is>
+          <t>Aretha Franklin</t>
+        </is>
+      </c>
+      <c r="D1636" t="inlineStr">
+        <is>
+          <t>Think</t>
+        </is>
+      </c>
+      <c r="E1636" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1636" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/904784</t>
+        </is>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="C1637" t="inlineStr">
+        <is>
+          <t>Swindle</t>
+        </is>
+      </c>
+      <c r="D1637" t="inlineStr">
+        <is>
+          <t>Coming Home (feat. Kojey Radical)</t>
+        </is>
+      </c>
+      <c r="E1637" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1637" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1302730842</t>
+        </is>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="C1638" t="inlineStr">
+        <is>
+          <t>Donna Summer</t>
+        </is>
+      </c>
+      <c r="D1638" t="inlineStr">
+        <is>
+          <t>I Feel Love</t>
+        </is>
+      </c>
+      <c r="E1638" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1638" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1560033</t>
+        </is>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="C1639" t="inlineStr">
+        <is>
+          <t>The Raconteurs</t>
+        </is>
+      </c>
+      <c r="D1639" t="inlineStr">
+        <is>
+          <t>Steady As She Goes</t>
+        </is>
+      </c>
+      <c r="E1639" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1639" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1238177942</t>
+        </is>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="C1640" t="inlineStr">
+        <is>
+          <t>The Stone Roses</t>
+        </is>
+      </c>
+      <c r="D1640" t="inlineStr">
+        <is>
+          <t>She Bangs The Drums</t>
+        </is>
+      </c>
+      <c r="E1640" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1640" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3960792</t>
+        </is>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="C1641" t="inlineStr">
+        <is>
+          <t>Underworld</t>
+        </is>
+      </c>
+      <c r="D1641" t="inlineStr">
+        <is>
+          <t>Born Slippy</t>
+        </is>
+      </c>
+      <c r="E1641" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1641" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/82265248</t>
+        </is>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="C1642" t="inlineStr">
+        <is>
+          <t>Mexican Institute of Sound &amp; Meridian Brothers</t>
+        </is>
+      </c>
+      <c r="D1642" t="inlineStr">
+        <is>
+          <t>Cumbia fantasia</t>
+        </is>
+      </c>
+      <c r="E1642" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1642" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3807209082</t>
+        </is>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>Kate Bush</t>
+        </is>
+      </c>
+      <c r="D1643" t="inlineStr">
+        <is>
+          <t>Hounds Of Love</t>
+        </is>
+      </c>
+      <c r="E1643" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1643" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2173954697</t>
+        </is>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>beabadoobee</t>
+        </is>
+      </c>
+      <c r="D1644" t="inlineStr">
+        <is>
+          <t>Take A Bite</t>
+        </is>
+      </c>
+      <c r="E1644" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1644" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2758747991</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>Bobby Womack</t>
+        </is>
+      </c>
+      <c r="D1645" t="inlineStr">
+        <is>
+          <t>Woman's Gotta Have It</t>
+        </is>
+      </c>
+      <c r="E1645" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1645" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3355915</t>
+        </is>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>Sly &amp; the Family Stone</t>
+        </is>
+      </c>
+      <c r="D1646" t="inlineStr">
+        <is>
+          <t>Dance To The Music</t>
+        </is>
+      </c>
+      <c r="E1646" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1646" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/534574</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t>Roots Manuva</t>
+        </is>
+      </c>
+      <c r="D1647" t="inlineStr">
+        <is>
+          <t>Again &amp; Again</t>
+        </is>
+      </c>
+      <c r="E1647" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1647" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/10234666</t>
+        </is>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>Edie Brickell &amp; Edie Brickell &amp; New Bohemians</t>
+        </is>
+      </c>
+      <c r="D1648" t="inlineStr">
+        <is>
+          <t>What I Am</t>
+        </is>
+      </c>
+      <c r="E1648" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1648" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2498905</t>
+        </is>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>Turnstile</t>
+        </is>
+      </c>
+      <c r="D1649" t="inlineStr">
+        <is>
+          <t>DREAMING</t>
+        </is>
+      </c>
+      <c r="E1649" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1649" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3402267071</t>
+        </is>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="C1650" t="inlineStr">
+        <is>
+          <t>Michael Stipe &amp; Andrew Watt</t>
+        </is>
+      </c>
+      <c r="D1650" t="inlineStr">
+        <is>
+          <t>I Played the Fool (Main Title Theme from "Rooster")</t>
+        </is>
+      </c>
+      <c r="E1650" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1650" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3882310971</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>07:14</t>
+        </is>
+      </c>
+      <c r="C1651" t="inlineStr">
+        <is>
+          <t>Delta 5</t>
+        </is>
+      </c>
+      <c r="D1651" t="inlineStr">
+        <is>
+          <t>Mind Your Own Business</t>
+        </is>
+      </c>
+      <c r="E1651" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1651" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/30516301</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="C1652" t="inlineStr">
+        <is>
+          <t>Prince</t>
+        </is>
+      </c>
+      <c r="D1652" t="inlineStr">
+        <is>
+          <t>I Feel For You</t>
+        </is>
+      </c>
+      <c r="E1652" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1652" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3612793</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>07:07</t>
+        </is>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>Gary Numan</t>
+        </is>
+      </c>
+      <c r="D1653" t="inlineStr">
+        <is>
+          <t>Cars</t>
+        </is>
+      </c>
+      <c r="E1653" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1653" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/938553</t>
+        </is>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t>Denzel Curry</t>
+        </is>
+      </c>
+      <c r="D1654" t="inlineStr">
+        <is>
+          <t>Black Balloons</t>
+        </is>
+      </c>
+      <c r="E1654" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1654" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/531222571</t>
+        </is>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="C1655" t="inlineStr">
+        <is>
+          <t>Fcukers</t>
+        </is>
+      </c>
+      <c r="D1655" t="inlineStr">
+        <is>
+          <t>Play Me</t>
+        </is>
+      </c>
+      <c r="E1655" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1655" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3772064472</t>
+        </is>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>06:33</t>
+        </is>
+      </c>
+      <c r="C1656" t="inlineStr">
+        <is>
+          <t>Mazzy Star</t>
+        </is>
+      </c>
+      <c r="D1656" t="inlineStr">
+        <is>
+          <t>Ride It On</t>
+        </is>
+      </c>
+      <c r="E1656" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1656" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3123224</t>
+        </is>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="C1657" t="inlineStr">
+        <is>
+          <t>Bee Gees</t>
+        </is>
+      </c>
+      <c r="D1657" t="inlineStr">
+        <is>
+          <t>You Should Be Dancing</t>
+        </is>
+      </c>
+      <c r="E1657" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1657" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/350027741</t>
+        </is>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="C1658" t="inlineStr">
+        <is>
+          <t>The Hues Corporation</t>
+        </is>
+      </c>
+      <c r="D1658" t="inlineStr">
+        <is>
+          <t>Rock The Boat</t>
+        </is>
+      </c>
+      <c r="E1658" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1658" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/106115758</t>
+        </is>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="C1659" t="inlineStr">
+        <is>
+          <t>Cheryl Lynn</t>
+        </is>
+      </c>
+      <c r="D1659" t="inlineStr">
+        <is>
+          <t>Got To Be Real</t>
+        </is>
+      </c>
+      <c r="E1659" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1659" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/8014760</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>The Tams</t>
+        </is>
+      </c>
+      <c r="D1660" t="inlineStr">
+        <is>
+          <t>Be Young, Be Foolish, Be Happy</t>
+        </is>
+      </c>
+      <c r="E1660" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1660" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/123339068</t>
+        </is>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>05:50</t>
+        </is>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>Photay</t>
+        </is>
+      </c>
+      <c r="D1661" t="inlineStr">
+        <is>
+          <t>Always Cosmic</t>
+        </is>
+      </c>
+      <c r="E1661" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1661" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3900197821</t>
+        </is>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>05:46</t>
+        </is>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>Caribou</t>
+        </is>
+      </c>
+      <c r="D1662" t="inlineStr">
+        <is>
+          <t>Our Love</t>
+        </is>
+      </c>
+      <c r="E1662" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1662" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3550841951</t>
+        </is>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>05:34</t>
+        </is>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>Garbage</t>
+        </is>
+      </c>
+      <c r="D1663" t="inlineStr">
+        <is>
+          <t>Queer</t>
+        </is>
+      </c>
+      <c r="E1663" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1663" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1761472007</t>
+        </is>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>05:27</t>
+        </is>
+      </c>
+      <c r="C1664" t="inlineStr">
+        <is>
+          <t>Digitalism</t>
+        </is>
+      </c>
+      <c r="D1664" t="inlineStr">
+        <is>
+          <t>Achtung! Optimism</t>
+        </is>
+      </c>
+      <c r="E1664" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1664" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3950910601</t>
+        </is>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="C1665" t="inlineStr">
+        <is>
+          <t>U2</t>
+        </is>
+      </c>
+      <c r="D1665" t="inlineStr">
+        <is>
+          <t>Where The Streets Have No Name</t>
+        </is>
+      </c>
+      <c r="E1665" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1665" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/366440291</t>
+        </is>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>04:55</t>
+        </is>
+      </c>
+      <c r="C1666" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="D1666" t="inlineStr">
+        <is>
+          <t>Sometimes</t>
+        </is>
+      </c>
+      <c r="E1666" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1666" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1147569</t>
+        </is>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>04:47</t>
+        </is>
+      </c>
+      <c r="C1667" t="inlineStr">
+        <is>
+          <t>DEVO</t>
+        </is>
+      </c>
+      <c r="D1667" t="inlineStr">
+        <is>
+          <t>Jocko Homo</t>
+        </is>
+      </c>
+      <c r="E1667" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1667" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/14618362</t>
+        </is>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>04:44</t>
+        </is>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>David Bowie</t>
+        </is>
+      </c>
+      <c r="D1668" t="inlineStr">
+        <is>
+          <t>Boys Keep Swinging</t>
+        </is>
+      </c>
+      <c r="E1668" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1668" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/461045332</t>
+        </is>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>04:39</t>
+        </is>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>Talking Heads</t>
+        </is>
+      </c>
+      <c r="D1669" t="inlineStr">
+        <is>
+          <t>Take Me To The River</t>
+        </is>
+      </c>
+      <c r="E1669" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1669" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/77386189</t>
+        </is>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>04:23</t>
+        </is>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>Althea &amp; Donna</t>
+        </is>
+      </c>
+      <c r="D1670" t="inlineStr">
+        <is>
+          <t>Uptown Top Ranking</t>
+        </is>
+      </c>
+      <c r="E1670" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1670" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3376045</t>
+        </is>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>04:17</t>
+        </is>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>Hot Chip</t>
+        </is>
+      </c>
+      <c r="D1671" t="inlineStr">
+        <is>
+          <t>Huarache Lights</t>
+        </is>
+      </c>
+      <c r="E1671" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1671" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/99689634</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>LCD Soundsystem</t>
+        </is>
+      </c>
+      <c r="D1672" t="inlineStr">
+        <is>
+          <t>Tribulations</t>
+        </is>
+      </c>
+      <c r="E1672" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1672" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3095120</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>03:58</t>
+        </is>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>Vashti Bunyan</t>
+        </is>
+      </c>
+      <c r="D1673" t="inlineStr">
+        <is>
+          <t>Diamond Day</t>
+        </is>
+      </c>
+      <c r="E1673" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1673" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/16313620</t>
+        </is>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>03:42</t>
+        </is>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>Rostam</t>
+        </is>
+      </c>
+      <c r="D1674" t="inlineStr">
+        <is>
+          <t>Different Light</t>
+        </is>
+      </c>
+      <c r="E1674" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1674" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3840886961</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>03:33</t>
+        </is>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>The Black Keys</t>
+        </is>
+      </c>
+      <c r="D1675" t="inlineStr">
+        <is>
+          <t>Gold on the Ceiling</t>
+        </is>
+      </c>
+      <c r="E1675" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1675" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/14932100</t>
+        </is>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>03:17</t>
+        </is>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>Adonis</t>
+        </is>
+      </c>
+      <c r="D1676" t="inlineStr">
+        <is>
+          <t>No Way Back</t>
+        </is>
+      </c>
+      <c r="E1676" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1676" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/573132612</t>
+        </is>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>03:13</t>
+        </is>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>Rufus &amp; Chaka Khan</t>
+        </is>
+      </c>
+      <c r="D1677" t="inlineStr">
+        <is>
+          <t>Tell Me Something Good</t>
+        </is>
+      </c>
+      <c r="E1677" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1677" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/10202440</t>
+        </is>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>Joan As Police Woman</t>
+        </is>
+      </c>
+      <c r="D1678" t="inlineStr">
+        <is>
+          <t>Holy City</t>
+        </is>
+      </c>
+      <c r="E1678" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1678" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/75827666</t>
+        </is>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>02:18</t>
+        </is>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>The Style Council</t>
+        </is>
+      </c>
+      <c r="D1679" t="inlineStr">
+        <is>
+          <t>Walls Come Tumbling Down</t>
+        </is>
+      </c>
+      <c r="E1679" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1679" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1118027612</t>
+        </is>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>02:14</t>
+        </is>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>Franz Ferdinand</t>
+        </is>
+      </c>
+      <c r="D1680" t="inlineStr">
+        <is>
+          <t>The Dark Of The Matinée</t>
+        </is>
+      </c>
+      <c r="E1680" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1680" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4315685</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>01:54</t>
+        </is>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>KH</t>
+        </is>
+      </c>
+      <c r="D1681" t="inlineStr">
+        <is>
+          <t>Only Human</t>
+        </is>
+      </c>
+      <c r="E1681" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1681" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3727612072</t>
+        </is>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>01:50</t>
+        </is>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>The Walkmen</t>
+        </is>
+      </c>
+      <c r="D1682" t="inlineStr">
+        <is>
+          <t>The Rat</t>
+        </is>
+      </c>
+      <c r="E1682" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1682" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3859024</t>
+        </is>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>01:46</t>
+        </is>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>Geese</t>
+        </is>
+      </c>
+      <c r="D1683" t="inlineStr">
+        <is>
+          <t>Cobra</t>
+        </is>
+      </c>
+      <c r="E1683" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1683" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3399059211</t>
+        </is>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>01:42</t>
+        </is>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>The Prodigy</t>
+        </is>
+      </c>
+      <c r="D1684" t="inlineStr">
+        <is>
+          <t>Out of Space</t>
+        </is>
+      </c>
+      <c r="E1684" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1684" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/128973850</t>
+        </is>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>01:38</t>
+        </is>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>Justice</t>
+        </is>
+      </c>
+      <c r="D1685" t="inlineStr">
+        <is>
+          <t>Civilization</t>
+        </is>
+      </c>
+      <c r="E1685" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1685" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/445849502</t>
+        </is>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>01:34</t>
+        </is>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>Blondie</t>
+        </is>
+      </c>
+      <c r="D1686" t="inlineStr">
+        <is>
+          <t>Atomic</t>
+        </is>
+      </c>
+      <c r="E1686" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1686" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3151381</t>
+        </is>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>01:18</t>
+        </is>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>Smerz</t>
+        </is>
+      </c>
+      <c r="D1687" t="inlineStr">
+        <is>
+          <t>Roll the dice</t>
+        </is>
+      </c>
+      <c r="E1687" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1687" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3282634601</t>
+        </is>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>01:14</t>
+        </is>
+      </c>
+      <c r="C1688" t="inlineStr">
+        <is>
+          <t>O’Flynn &amp; Swordman Kitala</t>
+        </is>
+      </c>
+      <c r="D1688" t="inlineStr">
+        <is>
+          <t>Sekete</t>
+        </is>
+      </c>
+      <c r="E1688" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1688" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3960102241</t>
+        </is>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>01:12</t>
+        </is>
+      </c>
+      <c r="C1689" t="inlineStr">
+        <is>
+          <t>Broadcast</t>
+        </is>
+      </c>
+      <c r="D1689" t="inlineStr">
+        <is>
+          <t>I Found The F</t>
+        </is>
+      </c>
+      <c r="E1689" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1689" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/5785696</t>
+        </is>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>01:02</t>
+        </is>
+      </c>
+      <c r="C1690" t="inlineStr">
+        <is>
+          <t>The Beatles</t>
+        </is>
+      </c>
+      <c r="D1690" t="inlineStr">
+        <is>
+          <t>Hey Bulldog</t>
+        </is>
+      </c>
+      <c r="E1690" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1690" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/116348730</t>
+        </is>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>00:58</t>
+        </is>
+      </c>
+      <c r="C1691" t="inlineStr">
+        <is>
+          <t>The Clash</t>
+        </is>
+      </c>
+      <c r="D1691" t="inlineStr">
+        <is>
+          <t>Capital Radio</t>
+        </is>
+      </c>
+      <c r="E1691" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1691" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1628173832</t>
+        </is>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>00:34</t>
+        </is>
+      </c>
+      <c r="C1692" t="inlineStr">
+        <is>
+          <t>Stereolab</t>
+        </is>
+      </c>
+      <c r="D1692" t="inlineStr">
+        <is>
+          <t>French Disko</t>
+        </is>
+      </c>
+      <c r="E1692" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1692" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/355426501</t>
+        </is>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>00:12</t>
+        </is>
+      </c>
+      <c r="C1693" t="inlineStr">
+        <is>
+          <t>Pareidolls</t>
+        </is>
+      </c>
+      <c r="D1693" t="inlineStr">
+        <is>
+          <t>Jessie</t>
+        </is>
+      </c>
+      <c r="E1693" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1693" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3917122801</t>
+        </is>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>00:08</t>
+        </is>
+      </c>
+      <c r="C1694" t="inlineStr">
+        <is>
+          <t>Sharon Van Etten</t>
+        </is>
+      </c>
+      <c r="D1694" t="inlineStr">
+        <is>
+          <t>Give Out</t>
+        </is>
+      </c>
+      <c r="E1694" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1694" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/73915551</t>
+        </is>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>00:01</t>
+        </is>
+      </c>
+      <c r="C1695" t="inlineStr">
+        <is>
+          <t>Mantronix</t>
+        </is>
+      </c>
+      <c r="D1695" t="inlineStr">
+        <is>
+          <t>King Of The Beats</t>
+        </is>
+      </c>
+      <c r="E1695" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1695" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/6283574</t>
         </is>
       </c>
     </row>
@@ -51493,6 +56229,154 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1545" r:id="rId1544"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1546" r:id="rId1545"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1547" r:id="rId1546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1548" r:id="rId1547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1549" r:id="rId1548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1550" r:id="rId1549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1551" r:id="rId1550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1552" r:id="rId1551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1553" r:id="rId1552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1554" r:id="rId1553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1555" r:id="rId1554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1556" r:id="rId1555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1557" r:id="rId1556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1558" r:id="rId1557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1559" r:id="rId1558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1560" r:id="rId1559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1561" r:id="rId1560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1562" r:id="rId1561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1563" r:id="rId1562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1564" r:id="rId1563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1565" r:id="rId1564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1566" r:id="rId1565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1567" r:id="rId1566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1568" r:id="rId1567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1569" r:id="rId1568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1570" r:id="rId1569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1571" r:id="rId1570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1572" r:id="rId1571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1573" r:id="rId1572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1574" r:id="rId1573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1575" r:id="rId1574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1576" r:id="rId1575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1577" r:id="rId1576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1578" r:id="rId1577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1579" r:id="rId1578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1580" r:id="rId1579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1581" r:id="rId1580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1582" r:id="rId1581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1583" r:id="rId1582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1584" r:id="rId1583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1585" r:id="rId1584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1586" r:id="rId1585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1587" r:id="rId1586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1588" r:id="rId1587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1589" r:id="rId1588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1590" r:id="rId1589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1591" r:id="rId1590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1592" r:id="rId1591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1593" r:id="rId1592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1594" r:id="rId1593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1595" r:id="rId1594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1596" r:id="rId1595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1597" r:id="rId1596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1598" r:id="rId1597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1599" r:id="rId1598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1600" r:id="rId1599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1601" r:id="rId1600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1602" r:id="rId1601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1603" r:id="rId1602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1604" r:id="rId1603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1605" r:id="rId1604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1606" r:id="rId1605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1607" r:id="rId1606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1608" r:id="rId1607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1609" r:id="rId1608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1610" r:id="rId1609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1611" r:id="rId1610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1612" r:id="rId1611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1613" r:id="rId1612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1614" r:id="rId1613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1615" r:id="rId1614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1616" r:id="rId1615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1617" r:id="rId1616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1618" r:id="rId1617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1619" r:id="rId1618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1620" r:id="rId1619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1621" r:id="rId1620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1622" r:id="rId1621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1623" r:id="rId1622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1624" r:id="rId1623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1625" r:id="rId1624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1626" r:id="rId1625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1627" r:id="rId1626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1628" r:id="rId1627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1629" r:id="rId1628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1630" r:id="rId1629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1631" r:id="rId1630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1632" r:id="rId1631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1633" r:id="rId1632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1634" r:id="rId1633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1635" r:id="rId1634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1636" r:id="rId1635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1637" r:id="rId1636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1638" r:id="rId1637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1639" r:id="rId1638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1640" r:id="rId1639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1641" r:id="rId1640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1642" r:id="rId1641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1643" r:id="rId1642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1644" r:id="rId1643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1645" r:id="rId1644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1646" r:id="rId1645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1647" r:id="rId1646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1648" r:id="rId1647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1649" r:id="rId1648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1650" r:id="rId1649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1651" r:id="rId1650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1652" r:id="rId1651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1653" r:id="rId1652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1654" r:id="rId1653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1655" r:id="rId1654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1656" r:id="rId1655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1657" r:id="rId1656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1658" r:id="rId1657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1659" r:id="rId1658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1660" r:id="rId1659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1661" r:id="rId1660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1662" r:id="rId1661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1663" r:id="rId1662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1664" r:id="rId1663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1665" r:id="rId1664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1666" r:id="rId1665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1667" r:id="rId1666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1668" r:id="rId1667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1669" r:id="rId1668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1670" r:id="rId1669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1671" r:id="rId1670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1672" r:id="rId1671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1673" r:id="rId1672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1674" r:id="rId1673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1675" r:id="rId1674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1676" r:id="rId1675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1677" r:id="rId1676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1678" r:id="rId1677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1679" r:id="rId1678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1680" r:id="rId1679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1681" r:id="rId1680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1682" r:id="rId1681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1683" r:id="rId1682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1684" r:id="rId1683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1685" r:id="rId1684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1686" r:id="rId1685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1687" r:id="rId1686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1688" r:id="rId1687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1689" r:id="rId1688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1690" r:id="rId1689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1691" r:id="rId1690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1692" r:id="rId1691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1693" r:id="rId1692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1694" r:id="rId1693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1695" r:id="rId1694"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/BBC6 Music Log.xlsx
+++ b/output/BBC6 Music Log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1695"/>
+  <dimension ref="A1:F1791"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -54678,6 +54678,3078 @@
       <c r="F1695" s="2" t="inlineStr">
         <is>
           <t>https://www.deezer.com/track/6283574</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="C1696" t="inlineStr">
+        <is>
+          <t>Linodnb</t>
+        </is>
+      </c>
+      <c r="D1696" t="inlineStr">
+        <is>
+          <t>Nada Como Você</t>
+        </is>
+      </c>
+      <c r="E1696" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1696" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3796267262</t>
+        </is>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="C1697" t="inlineStr">
+        <is>
+          <t>Jam Thieves</t>
+        </is>
+      </c>
+      <c r="D1697" t="inlineStr">
+        <is>
+          <t>Brasilandia</t>
+        </is>
+      </c>
+      <c r="E1697" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1697" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1867218257</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C1698" t="inlineStr">
+        <is>
+          <t>DJ Marky &amp; Bungle</t>
+        </is>
+      </c>
+      <c r="D1698" t="inlineStr">
+        <is>
+          <t>Codename: A.1</t>
+        </is>
+      </c>
+      <c r="E1698" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1698" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2338117925</t>
+        </is>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="C1699" t="inlineStr">
+        <is>
+          <t>Total Science &amp; S.P.Y</t>
+        </is>
+      </c>
+      <c r="D1699" t="inlineStr">
+        <is>
+          <t>Double Trouble</t>
+        </is>
+      </c>
+      <c r="E1699" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1699" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2259875117</t>
+        </is>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="C1700" t="inlineStr">
+        <is>
+          <t>Calibre &amp; ST Files</t>
+        </is>
+      </c>
+      <c r="D1700" t="inlineStr">
+        <is>
+          <t>STCal Roller</t>
+        </is>
+      </c>
+      <c r="E1700" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1700" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/82177886</t>
+        </is>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="C1701" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="D1701" t="inlineStr">
+        <is>
+          <t>The Big Picture</t>
+        </is>
+      </c>
+      <c r="E1701" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1701" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1006992892</t>
+        </is>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="C1702" t="inlineStr">
+        <is>
+          <t>Seu Jorge</t>
+        </is>
+      </c>
+      <c r="D1702" t="inlineStr">
+        <is>
+          <t>Chega No Suingue</t>
+        </is>
+      </c>
+      <c r="E1702" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1702" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/73525853</t>
+        </is>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="C1703" t="inlineStr">
+        <is>
+          <t>Drumagick</t>
+        </is>
+      </c>
+      <c r="D1703" t="inlineStr">
+        <is>
+          <t>Easy Boom</t>
+        </is>
+      </c>
+      <c r="E1703" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1703" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/385661161</t>
+        </is>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="C1704" t="inlineStr">
+        <is>
+          <t>Trüby Trio</t>
+        </is>
+      </c>
+      <c r="D1704" t="inlineStr">
+        <is>
+          <t>A Go Go (DJ Patife Remix)</t>
+        </is>
+      </c>
+      <c r="E1704" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1704" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/138296249</t>
+        </is>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="C1705" t="inlineStr">
+        <is>
+          <t>DJ Patife</t>
+        </is>
+      </c>
+      <c r="D1705" t="inlineStr">
+        <is>
+          <t>Enigma</t>
+        </is>
+      </c>
+      <c r="E1705" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1705" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/135016854</t>
+        </is>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="C1706" t="inlineStr">
+        <is>
+          <t>DJ Patife</t>
+        </is>
+      </c>
+      <c r="D1706" t="inlineStr">
+        <is>
+          <t>Lovin U</t>
+        </is>
+      </c>
+      <c r="E1706" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1706" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/135016856</t>
+        </is>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>Shy FX</t>
+        </is>
+      </c>
+      <c r="D1707" t="inlineStr">
+        <is>
+          <t>Roll The Dice (feat. Stamina MC &amp; Lily Allen)</t>
+        </is>
+      </c>
+      <c r="E1707" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1707" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/592352742</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>Drumagick</t>
+        </is>
+      </c>
+      <c r="D1708" t="inlineStr">
+        <is>
+          <t>Malandragem</t>
+        </is>
+      </c>
+      <c r="E1708" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1708" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/775681462</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>Marcelinho da Lua &amp; Seu Jorge</t>
+        </is>
+      </c>
+      <c r="D1709" t="inlineStr">
+        <is>
+          <t>Cotidiano</t>
+        </is>
+      </c>
+      <c r="E1709" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1709" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/96004096</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>Azymuth</t>
+        </is>
+      </c>
+      <c r="D1710" t="inlineStr">
+        <is>
+          <t>Laranjeiras (Flytronix's Drum 'n' Bass Mix)</t>
+        </is>
+      </c>
+      <c r="E1710" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1710" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/107813988</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>Goldie</t>
+        </is>
+      </c>
+      <c r="D1711" t="inlineStr">
+        <is>
+          <t>Single Petal of a Rose</t>
+        </is>
+      </c>
+      <c r="E1711" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1711" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/511684342</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>Protoje</t>
+        </is>
+      </c>
+      <c r="D1712" t="inlineStr">
+        <is>
+          <t>Big 45</t>
+        </is>
+      </c>
+      <c r="E1712" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1712" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3828031251</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>Yumi and the Weather</t>
+        </is>
+      </c>
+      <c r="D1713" t="inlineStr">
+        <is>
+          <t>Rip Tide</t>
+        </is>
+      </c>
+      <c r="E1713" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1713" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3898213741</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>WHATMORE</t>
+        </is>
+      </c>
+      <c r="D1714" t="inlineStr">
+        <is>
+          <t>Still Loiteringgg</t>
+        </is>
+      </c>
+      <c r="E1714" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1714" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3858226151</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>Love Maximum</t>
+        </is>
+      </c>
+      <c r="D1715" t="inlineStr">
+        <is>
+          <t>I've Been Trying</t>
+        </is>
+      </c>
+      <c r="E1715" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1715" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/79601886</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>Kae Tempest</t>
+        </is>
+      </c>
+      <c r="D1716" t="inlineStr">
+        <is>
+          <t>Don't You Ever</t>
+        </is>
+      </c>
+      <c r="E1716" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1716" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1705403797</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="C1717" t="inlineStr">
+        <is>
+          <t>Marvin Gaye</t>
+        </is>
+      </c>
+      <c r="D1717" t="inlineStr">
+        <is>
+          <t>What's Happening Brother</t>
+        </is>
+      </c>
+      <c r="E1717" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1717" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1133408862</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>Massive Attack &amp; Tom Waits</t>
+        </is>
+      </c>
+      <c r="D1718" t="inlineStr">
+        <is>
+          <t>Boots On The Ground</t>
+        </is>
+      </c>
+      <c r="E1718" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1718" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3908387001</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>Hugh Mundell</t>
+        </is>
+      </c>
+      <c r="D1719" t="inlineStr">
+        <is>
+          <t>Run Revolution a Come</t>
+        </is>
+      </c>
+      <c r="E1719" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1719" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/391088651</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>Cornelius</t>
+        </is>
+      </c>
+      <c r="D1720" t="inlineStr">
+        <is>
+          <t>Yumenemi</t>
+        </is>
+      </c>
+      <c r="E1720" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1720" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3983604151</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>Mr. Williamz &amp; Reggae Roast</t>
+        </is>
+      </c>
+      <c r="D1721" t="inlineStr">
+        <is>
+          <t>Dubplate Daddy</t>
+        </is>
+      </c>
+      <c r="E1721" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1721" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3732864852</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>Papa Michigan</t>
+        </is>
+      </c>
+      <c r="D1722" t="inlineStr">
+        <is>
+          <t>Style</t>
+        </is>
+      </c>
+      <c r="E1722" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1722" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/121413864</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>Felipe Gordon</t>
+        </is>
+      </c>
+      <c r="D1723" t="inlineStr">
+        <is>
+          <t>Tezeta</t>
+        </is>
+      </c>
+      <c r="E1723" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1723" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3940645411</t>
+        </is>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="C1724" t="inlineStr">
+        <is>
+          <t>Naughty by Nature</t>
+        </is>
+      </c>
+      <c r="D1724" t="inlineStr">
+        <is>
+          <t>O.P.P.</t>
+        </is>
+      </c>
+      <c r="E1724" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1724" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1584432772</t>
+        </is>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="C1725" t="inlineStr">
+        <is>
+          <t>Moloko</t>
+        </is>
+      </c>
+      <c r="D1725" t="inlineStr">
+        <is>
+          <t>Pure Pleasure Seeker</t>
+        </is>
+      </c>
+      <c r="E1725" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1725" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3803017122</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="C1726" t="inlineStr">
+        <is>
+          <t>Disgusting Sisters</t>
+        </is>
+      </c>
+      <c r="D1726" t="inlineStr">
+        <is>
+          <t>Weirdo Magnet</t>
+        </is>
+      </c>
+      <c r="E1726" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1726" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3908387121</t>
+        </is>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="C1727" t="inlineStr">
+        <is>
+          <t>TOMORA</t>
+        </is>
+      </c>
+      <c r="D1727" t="inlineStr">
+        <is>
+          <t>I Drink The Light</t>
+        </is>
+      </c>
+      <c r="E1727" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1727" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3996037401</t>
+        </is>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="C1728" t="inlineStr">
+        <is>
+          <t>Martyn</t>
+        </is>
+      </c>
+      <c r="D1728" t="inlineStr">
+        <is>
+          <t>These Words</t>
+        </is>
+      </c>
+      <c r="E1728" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1728" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2512024531</t>
+        </is>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="C1729" t="inlineStr">
+        <is>
+          <t>Buju Banton</t>
+        </is>
+      </c>
+      <c r="D1729" t="inlineStr">
+        <is>
+          <t>Butterflies</t>
+        </is>
+      </c>
+      <c r="E1729" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1729" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3945276991</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="C1730" t="inlineStr">
+        <is>
+          <t>David Bowie</t>
+        </is>
+      </c>
+      <c r="D1730" t="inlineStr">
+        <is>
+          <t>Let's Dance</t>
+        </is>
+      </c>
+      <c r="E1730" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1730" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/565656032</t>
+        </is>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="C1731" t="inlineStr">
+        <is>
+          <t>Asian Dub Foundation</t>
+        </is>
+      </c>
+      <c r="D1731" t="inlineStr">
+        <is>
+          <t>Buzzing</t>
+        </is>
+      </c>
+      <c r="E1731" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1731" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1763140237</t>
+        </is>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="C1732" t="inlineStr">
+        <is>
+          <t>Yuji Ohno</t>
+        </is>
+      </c>
+      <c r="D1732" t="inlineStr">
+        <is>
+          <t>The Chase</t>
+        </is>
+      </c>
+      <c r="E1732" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1732" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2665311132</t>
+        </is>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="C1733" t="inlineStr">
+        <is>
+          <t>Yuji Ohno</t>
+        </is>
+      </c>
+      <c r="D1733" t="inlineStr">
+        <is>
+          <t>Lupin III '78</t>
+        </is>
+      </c>
+      <c r="E1733" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1733" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2524738241</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="C1734" t="inlineStr">
+        <is>
+          <t>Yuji Ohno</t>
+        </is>
+      </c>
+      <c r="D1734" t="inlineStr">
+        <is>
+          <t>Love Ballade</t>
+        </is>
+      </c>
+      <c r="E1734" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1734" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1591210572</t>
+        </is>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="C1735" t="inlineStr">
+        <is>
+          <t>Solange</t>
+        </is>
+      </c>
+      <c r="D1735" t="inlineStr">
+        <is>
+          <t>Things I Imagined</t>
+        </is>
+      </c>
+      <c r="E1735" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1735" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/641647262</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>06:59</t>
+        </is>
+      </c>
+      <c r="C1736" t="inlineStr">
+        <is>
+          <t>Ossie</t>
+        </is>
+      </c>
+      <c r="D1736" t="inlineStr">
+        <is>
+          <t>Hidden Forest</t>
+        </is>
+      </c>
+      <c r="E1736" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1736" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3083055891</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>06:57</t>
+        </is>
+      </c>
+      <c r="C1737" t="inlineStr">
+        <is>
+          <t>ZJ</t>
+        </is>
+      </c>
+      <c r="D1737" t="inlineStr">
+        <is>
+          <t>Body Action</t>
+        </is>
+      </c>
+      <c r="E1737" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1737" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4000616261</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>06:55</t>
+        </is>
+      </c>
+      <c r="C1738" t="inlineStr">
+        <is>
+          <t>DJ Gregory</t>
+        </is>
+      </c>
+      <c r="D1738" t="inlineStr">
+        <is>
+          <t>Attend 1</t>
+        </is>
+      </c>
+      <c r="E1738" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1738" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3155489561</t>
+        </is>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>06:49</t>
+        </is>
+      </c>
+      <c r="C1739" t="inlineStr">
+        <is>
+          <t>Blck Mamba</t>
+        </is>
+      </c>
+      <c r="D1739" t="inlineStr">
+        <is>
+          <t>TAKE ME WITH YOU</t>
+        </is>
+      </c>
+      <c r="E1739" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1739" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3459637361</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="C1740" t="inlineStr">
+        <is>
+          <t>Sam One</t>
+        </is>
+      </c>
+      <c r="D1740" t="inlineStr">
+        <is>
+          <t>Kitale</t>
+        </is>
+      </c>
+      <c r="E1740" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1740" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/501979462</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>06:35</t>
+        </is>
+      </c>
+      <c r="C1741" t="inlineStr">
+        <is>
+          <t>Doug Gomez</t>
+        </is>
+      </c>
+      <c r="D1741" t="inlineStr">
+        <is>
+          <t>This Rhythm Is Me And You</t>
+        </is>
+      </c>
+      <c r="E1741" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1741" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3472390291</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>06:29</t>
+        </is>
+      </c>
+      <c r="C1742" t="inlineStr">
+        <is>
+          <t>Esa Williams</t>
+        </is>
+      </c>
+      <c r="D1742" t="inlineStr">
+        <is>
+          <t>Vanguard Drive</t>
+        </is>
+      </c>
+      <c r="E1742" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1742" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3605910512</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>06:08</t>
+        </is>
+      </c>
+      <c r="C1743" t="inlineStr">
+        <is>
+          <t>Esa Williams</t>
+        </is>
+      </c>
+      <c r="D1743" t="inlineStr">
+        <is>
+          <t>Kwanini</t>
+        </is>
+      </c>
+      <c r="E1743" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1743" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3605938442</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>05:54</t>
+        </is>
+      </c>
+      <c r="C1744" t="inlineStr">
+        <is>
+          <t>Runkus</t>
+        </is>
+      </c>
+      <c r="D1744" t="inlineStr">
+        <is>
+          <t>3310</t>
+        </is>
+      </c>
+      <c r="E1744" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1744" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3348841051</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>05:29</t>
+        </is>
+      </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>Charlie Chimi</t>
+        </is>
+      </c>
+      <c r="D1745" t="inlineStr">
+        <is>
+          <t>Échale Candela</t>
+        </is>
+      </c>
+      <c r="E1745" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1745" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3389335031</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>05:26</t>
+        </is>
+      </c>
+      <c r="C1746" t="inlineStr">
+        <is>
+          <t>LOOPCINICO</t>
+        </is>
+      </c>
+      <c r="D1746" t="inlineStr">
+        <is>
+          <t>Curimbóbata</t>
+        </is>
+      </c>
+      <c r="E1746" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1746" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/104472960</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>05:03</t>
+        </is>
+      </c>
+      <c r="C1747" t="inlineStr">
+        <is>
+          <t>Buraka Som Sistema</t>
+        </is>
+      </c>
+      <c r="D1747" t="inlineStr">
+        <is>
+          <t>Puro Mambo</t>
+        </is>
+      </c>
+      <c r="E1747" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1747" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3864827451</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1748" t="inlineStr">
+        <is>
+          <t>04:56</t>
+        </is>
+      </c>
+      <c r="C1748" t="inlineStr">
+        <is>
+          <t>Kelela</t>
+        </is>
+      </c>
+      <c r="D1748" t="inlineStr">
+        <is>
+          <t>All The Way Down</t>
+        </is>
+      </c>
+      <c r="E1748" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1748" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/366699281</t>
+        </is>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1749" t="inlineStr">
+        <is>
+          <t>04:50</t>
+        </is>
+      </c>
+      <c r="C1749" t="inlineStr">
+        <is>
+          <t>The Isley Brothers</t>
+        </is>
+      </c>
+      <c r="D1749" t="inlineStr">
+        <is>
+          <t>Summer Breeze</t>
+        </is>
+      </c>
+      <c r="E1749" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1749" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/855995</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1750" t="inlineStr">
+        <is>
+          <t>04:47</t>
+        </is>
+      </c>
+      <c r="C1750" t="inlineStr">
+        <is>
+          <t>Skull Snaps</t>
+        </is>
+      </c>
+      <c r="D1750" t="inlineStr">
+        <is>
+          <t>It's A New Day</t>
+        </is>
+      </c>
+      <c r="E1750" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1750" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/111247622</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1751" t="inlineStr">
+        <is>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="C1751" t="inlineStr">
+        <is>
+          <t>The Donays</t>
+        </is>
+      </c>
+      <c r="D1751" t="inlineStr">
+        <is>
+          <t>Devil in His Heart</t>
+        </is>
+      </c>
+      <c r="E1751" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1751" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4198597</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1752" t="inlineStr">
+        <is>
+          <t>04:36</t>
+        </is>
+      </c>
+      <c r="C1752" t="inlineStr">
+        <is>
+          <t>Teddy Pendergrass</t>
+        </is>
+      </c>
+      <c r="D1752" t="inlineStr">
+        <is>
+          <t>Love T.K.O.</t>
+        </is>
+      </c>
+      <c r="E1752" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1752" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/711115672</t>
+        </is>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1753" t="inlineStr">
+        <is>
+          <t>04:33</t>
+        </is>
+      </c>
+      <c r="C1753" t="inlineStr">
+        <is>
+          <t>Jamie xx</t>
+        </is>
+      </c>
+      <c r="D1753" t="inlineStr">
+        <is>
+          <t>KILL DEM</t>
+        </is>
+      </c>
+      <c r="E1753" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1753" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1892750597</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1754" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="C1754" t="inlineStr">
+        <is>
+          <t>Alicia Keys</t>
+        </is>
+      </c>
+      <c r="D1754" t="inlineStr">
+        <is>
+          <t>You Don't Know My Name</t>
+        </is>
+      </c>
+      <c r="E1754" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1754" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/629463</t>
+        </is>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1755" t="inlineStr">
+        <is>
+          <t>04:10</t>
+        </is>
+      </c>
+      <c r="C1755" t="inlineStr">
+        <is>
+          <t>Magazine</t>
+        </is>
+      </c>
+      <c r="D1755" t="inlineStr">
+        <is>
+          <t>Shot By Both Sides</t>
+        </is>
+      </c>
+      <c r="E1755" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1755" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3110837</t>
+        </is>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1756" t="inlineStr">
+        <is>
+          <t>04:05</t>
+        </is>
+      </c>
+      <c r="C1756" t="inlineStr">
+        <is>
+          <t>Martha and the Muffins</t>
+        </is>
+      </c>
+      <c r="D1756" t="inlineStr">
+        <is>
+          <t>Echo Beach</t>
+        </is>
+      </c>
+      <c r="E1756" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1756" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3345167571</t>
+        </is>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>03:59</t>
+        </is>
+      </c>
+      <c r="C1757" t="inlineStr">
+        <is>
+          <t>Sinéad O’Connor</t>
+        </is>
+      </c>
+      <c r="D1757" t="inlineStr">
+        <is>
+          <t>The Emperor's New Clothes</t>
+        </is>
+      </c>
+      <c r="E1757" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1757" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1798617777</t>
+        </is>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1758" t="inlineStr">
+        <is>
+          <t>03:56</t>
+        </is>
+      </c>
+      <c r="C1758" t="inlineStr">
+        <is>
+          <t>Nina Simone</t>
+        </is>
+      </c>
+      <c r="D1758" t="inlineStr">
+        <is>
+          <t>Rich Girl</t>
+        </is>
+      </c>
+      <c r="E1758" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1758" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1028876</t>
+        </is>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1759" t="inlineStr">
+        <is>
+          <t>03:52</t>
+        </is>
+      </c>
+      <c r="C1759" t="inlineStr">
+        <is>
+          <t>Zapp</t>
+        </is>
+      </c>
+      <c r="D1759" t="inlineStr">
+        <is>
+          <t>Computer Love</t>
+        </is>
+      </c>
+      <c r="E1759" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1759" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4288322</t>
+        </is>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1760" t="inlineStr">
+        <is>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="C1760" t="inlineStr">
+        <is>
+          <t>Edwin Hawkins Singers</t>
+        </is>
+      </c>
+      <c r="D1760" t="inlineStr">
+        <is>
+          <t>Oh Happy Day</t>
+        </is>
+      </c>
+      <c r="E1760" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1760" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13176492</t>
+        </is>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>03:41</t>
+        </is>
+      </c>
+      <c r="C1761" t="inlineStr">
+        <is>
+          <t>The Cardigans</t>
+        </is>
+      </c>
+      <c r="D1761" t="inlineStr">
+        <is>
+          <t>Iron Man</t>
+        </is>
+      </c>
+      <c r="E1761" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1761" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/623737262</t>
+        </is>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>03:39</t>
+        </is>
+      </c>
+      <c r="C1762" t="inlineStr">
+        <is>
+          <t>The Two Lips</t>
+        </is>
+      </c>
+      <c r="D1762" t="inlineStr">
+        <is>
+          <t>kiss goodbye</t>
+        </is>
+      </c>
+      <c r="E1762" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1762" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3939708651</t>
+        </is>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>03:33</t>
+        </is>
+      </c>
+      <c r="C1763" t="inlineStr">
+        <is>
+          <t>SAULT</t>
+        </is>
+      </c>
+      <c r="D1763" t="inlineStr">
+        <is>
+          <t>Up All Night</t>
+        </is>
+      </c>
+      <c r="E1763" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1763" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/670509692</t>
+        </is>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1764" t="inlineStr">
+        <is>
+          <t>03:27</t>
+        </is>
+      </c>
+      <c r="C1764" t="inlineStr">
+        <is>
+          <t>Kelis</t>
+        </is>
+      </c>
+      <c r="D1764" t="inlineStr">
+        <is>
+          <t>Young Fresh N'New</t>
+        </is>
+      </c>
+      <c r="E1764" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1764" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/948444852</t>
+        </is>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1765" t="inlineStr">
+        <is>
+          <t>03:22</t>
+        </is>
+      </c>
+      <c r="C1765" t="inlineStr">
+        <is>
+          <t>Talking Heads</t>
+        </is>
+      </c>
+      <c r="D1765" t="inlineStr">
+        <is>
+          <t>Girlfriend Is Better</t>
+        </is>
+      </c>
+      <c r="E1765" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1765" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3614311</t>
+        </is>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>03:19</t>
+        </is>
+      </c>
+      <c r="C1766" t="inlineStr">
+        <is>
+          <t>Gang of Four</t>
+        </is>
+      </c>
+      <c r="D1766" t="inlineStr">
+        <is>
+          <t>To Hell With Poverty</t>
+        </is>
+      </c>
+      <c r="E1766" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1766" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/880653342</t>
+        </is>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>03:13</t>
+        </is>
+      </c>
+      <c r="C1767" t="inlineStr">
+        <is>
+          <t>Violent Femmes</t>
+        </is>
+      </c>
+      <c r="D1767" t="inlineStr">
+        <is>
+          <t>Add It Up</t>
+        </is>
+      </c>
+      <c r="E1767" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1767" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1372756832</t>
+        </is>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>03:11</t>
+        </is>
+      </c>
+      <c r="C1768" t="inlineStr">
+        <is>
+          <t>Leikeli47</t>
+        </is>
+      </c>
+      <c r="D1768" t="inlineStr">
+        <is>
+          <t>Bad Guy</t>
+        </is>
+      </c>
+      <c r="E1768" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1768" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3915944521</t>
+        </is>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1769" t="inlineStr">
+        <is>
+          <t>03:04</t>
+        </is>
+      </c>
+      <c r="C1769" t="inlineStr">
+        <is>
+          <t>Coati Mundi</t>
+        </is>
+      </c>
+      <c r="D1769" t="inlineStr">
+        <is>
+          <t>Que Pasa / Me No Pop I</t>
+        </is>
+      </c>
+      <c r="E1769" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1769" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/75332453</t>
+        </is>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>03:02</t>
+        </is>
+      </c>
+      <c r="C1770" t="inlineStr">
+        <is>
+          <t>MC5</t>
+        </is>
+      </c>
+      <c r="D1770" t="inlineStr">
+        <is>
+          <t>Kick Out The Jams</t>
+        </is>
+      </c>
+      <c r="E1770" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1770" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/670838</t>
+        </is>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1771" t="inlineStr">
+        <is>
+          <t>02:51</t>
+        </is>
+      </c>
+      <c r="C1771" t="inlineStr">
+        <is>
+          <t>Kehlani</t>
+        </is>
+      </c>
+      <c r="D1771" t="inlineStr">
+        <is>
+          <t>Back and Forth (feat. Missy Elliott)</t>
+        </is>
+      </c>
+      <c r="E1771" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1771" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3897501831</t>
+        </is>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1772" t="inlineStr">
+        <is>
+          <t>02:48</t>
+        </is>
+      </c>
+      <c r="C1772" t="inlineStr">
+        <is>
+          <t>Venus &amp; the Flytraps</t>
+        </is>
+      </c>
+      <c r="D1772" t="inlineStr">
+        <is>
+          <t>Worse Together</t>
+        </is>
+      </c>
+      <c r="E1772" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1772" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2129206387</t>
+        </is>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1773" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="C1773" t="inlineStr">
+        <is>
+          <t>TV Girl</t>
+        </is>
+      </c>
+      <c r="D1773" t="inlineStr">
+        <is>
+          <t>Lovers Rock</t>
+        </is>
+      </c>
+      <c r="E1773" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1773" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1751426027</t>
+        </is>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1774" t="inlineStr">
+        <is>
+          <t>02:33</t>
+        </is>
+      </c>
+      <c r="C1774" t="inlineStr">
+        <is>
+          <t>OutKast</t>
+        </is>
+      </c>
+      <c r="D1774" t="inlineStr">
+        <is>
+          <t>Prototype</t>
+        </is>
+      </c>
+      <c r="E1774" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1774" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/628265</t>
+        </is>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1775" t="inlineStr">
+        <is>
+          <t>02:27</t>
+        </is>
+      </c>
+      <c r="C1775" t="inlineStr">
+        <is>
+          <t>Buzzcocks</t>
+        </is>
+      </c>
+      <c r="D1775" t="inlineStr">
+        <is>
+          <t>What Do I Get?</t>
+        </is>
+      </c>
+      <c r="E1775" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1775" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/376010561</t>
+        </is>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1776" t="inlineStr">
+        <is>
+          <t>02:20</t>
+        </is>
+      </c>
+      <c r="C1776" t="inlineStr">
+        <is>
+          <t>Patti Smith</t>
+        </is>
+      </c>
+      <c r="D1776" t="inlineStr">
+        <is>
+          <t>Redondo Beach</t>
+        </is>
+      </c>
+      <c r="E1776" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1776" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/107278736</t>
+        </is>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1777" t="inlineStr">
+        <is>
+          <t>02:08</t>
+        </is>
+      </c>
+      <c r="C1777" t="inlineStr">
+        <is>
+          <t>Go‐Go’s</t>
+        </is>
+      </c>
+      <c r="D1777" t="inlineStr">
+        <is>
+          <t>This Town</t>
+        </is>
+      </c>
+      <c r="E1777" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1777" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1412741422</t>
+        </is>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1778" t="inlineStr">
+        <is>
+          <t>02:04</t>
+        </is>
+      </c>
+      <c r="C1778" t="inlineStr">
+        <is>
+          <t>Romeo Void</t>
+        </is>
+      </c>
+      <c r="D1778" t="inlineStr">
+        <is>
+          <t>Never Say Never</t>
+        </is>
+      </c>
+      <c r="E1778" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1778" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/8146658</t>
+        </is>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1779" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="C1779" t="inlineStr">
+        <is>
+          <t>Norman Greenbaum</t>
+        </is>
+      </c>
+      <c r="D1779" t="inlineStr">
+        <is>
+          <t>Spirit In The Sky</t>
+        </is>
+      </c>
+      <c r="E1779" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1779" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/673832662</t>
+        </is>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1780" t="inlineStr">
+        <is>
+          <t>01:57</t>
+        </is>
+      </c>
+      <c r="C1780" t="inlineStr">
+        <is>
+          <t>Dream Wife</t>
+        </is>
+      </c>
+      <c r="D1780" t="inlineStr">
+        <is>
+          <t>Hey Heartbreaker</t>
+        </is>
+      </c>
+      <c r="E1780" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1780" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/799241842</t>
+        </is>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1781" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="C1781" t="inlineStr">
+        <is>
+          <t>Laufey</t>
+        </is>
+      </c>
+      <c r="D1781" t="inlineStr">
+        <is>
+          <t>Lover Girl</t>
+        </is>
+      </c>
+      <c r="E1781" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1781" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3401301081</t>
+        </is>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1782" t="inlineStr">
+        <is>
+          <t>01:38</t>
+        </is>
+      </c>
+      <c r="C1782" t="inlineStr">
+        <is>
+          <t>Erroll Garner</t>
+        </is>
+      </c>
+      <c r="D1782" t="inlineStr">
+        <is>
+          <t>Teach Me Tonight</t>
+        </is>
+      </c>
+      <c r="E1782" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1782" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/7225474</t>
+        </is>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1783" t="inlineStr">
+        <is>
+          <t>01:14</t>
+        </is>
+      </c>
+      <c r="C1783" t="inlineStr">
+        <is>
+          <t>Santigold</t>
+        </is>
+      </c>
+      <c r="D1783" t="inlineStr">
+        <is>
+          <t>Say Aha</t>
+        </is>
+      </c>
+      <c r="E1783" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1783" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/85440822</t>
+        </is>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1784" t="inlineStr">
+        <is>
+          <t>01:01</t>
+        </is>
+      </c>
+      <c r="C1784" t="inlineStr">
+        <is>
+          <t>New Order</t>
+        </is>
+      </c>
+      <c r="D1784" t="inlineStr">
+        <is>
+          <t>The Perfect Kiss</t>
+        </is>
+      </c>
+      <c r="E1784" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1784" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/107750190</t>
+        </is>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1785" t="inlineStr">
+        <is>
+          <t>00:52</t>
+        </is>
+      </c>
+      <c r="C1785" t="inlineStr">
+        <is>
+          <t>The Beach Boys</t>
+        </is>
+      </c>
+      <c r="D1785" t="inlineStr">
+        <is>
+          <t>I Just Wasn't Made For These Times</t>
+        </is>
+      </c>
+      <c r="E1785" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1785" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2263082747</t>
+        </is>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1786" t="inlineStr">
+        <is>
+          <t>00:49</t>
+        </is>
+      </c>
+      <c r="C1786" t="inlineStr">
+        <is>
+          <t>The Beach Boys</t>
+        </is>
+      </c>
+      <c r="D1786" t="inlineStr">
+        <is>
+          <t>You Still Believe In Me</t>
+        </is>
+      </c>
+      <c r="E1786" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1786" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2263082637</t>
+        </is>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1787" t="inlineStr">
+        <is>
+          <t>00:28</t>
+        </is>
+      </c>
+      <c r="C1787" t="inlineStr">
+        <is>
+          <t>The Cure</t>
+        </is>
+      </c>
+      <c r="D1787" t="inlineStr">
+        <is>
+          <t>In Between Days</t>
+        </is>
+      </c>
+      <c r="E1787" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1787" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/409670302</t>
+        </is>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1788" t="inlineStr">
+        <is>
+          <t>00:24</t>
+        </is>
+      </c>
+      <c r="C1788" t="inlineStr">
+        <is>
+          <t>Marine Store Dealer</t>
+        </is>
+      </c>
+      <c r="D1788" t="inlineStr">
+        <is>
+          <t>High Flyers</t>
+        </is>
+      </c>
+      <c r="E1788" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1788" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3655835872</t>
+        </is>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1789" t="inlineStr">
+        <is>
+          <t>00:20</t>
+        </is>
+      </c>
+      <c r="C1789" t="inlineStr">
+        <is>
+          <t>Foreal People</t>
+        </is>
+      </c>
+      <c r="D1789" t="inlineStr">
+        <is>
+          <t>Tango Hustle (Dave Lee Latican Hustle Edit)</t>
+        </is>
+      </c>
+      <c r="E1789" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1789" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3919327441</t>
+        </is>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1790" t="inlineStr">
+        <is>
+          <t>00:12</t>
+        </is>
+      </c>
+      <c r="C1790" t="inlineStr">
+        <is>
+          <t>The Knife</t>
+        </is>
+      </c>
+      <c r="D1790" t="inlineStr">
+        <is>
+          <t>Pass This On</t>
+        </is>
+      </c>
+      <c r="E1790" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1790" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1856374127</t>
+        </is>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B1791" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="C1791" t="inlineStr">
+        <is>
+          <t>Wire</t>
+        </is>
+      </c>
+      <c r="D1791" t="inlineStr">
+        <is>
+          <t>I Am The Fly</t>
+        </is>
+      </c>
+      <c r="E1791" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1791" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/444231552</t>
         </is>
       </c>
     </row>
@@ -56377,6 +59449,102 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1693" r:id="rId1692"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1694" r:id="rId1693"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1695" r:id="rId1694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1696" r:id="rId1695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1697" r:id="rId1696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1698" r:id="rId1697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1699" r:id="rId1698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1700" r:id="rId1699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1701" r:id="rId1700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1702" r:id="rId1701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1703" r:id="rId1702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1704" r:id="rId1703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1705" r:id="rId1704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1706" r:id="rId1705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1707" r:id="rId1706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1708" r:id="rId1707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1709" r:id="rId1708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1710" r:id="rId1709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1711" r:id="rId1710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1712" r:id="rId1711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1713" r:id="rId1712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1714" r:id="rId1713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1715" r:id="rId1714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1716" r:id="rId1715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1717" r:id="rId1716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1718" r:id="rId1717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1719" r:id="rId1718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1720" r:id="rId1719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1721" r:id="rId1720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1722" r:id="rId1721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1723" r:id="rId1722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1724" r:id="rId1723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1725" r:id="rId1724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1726" r:id="rId1725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1727" r:id="rId1726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1728" r:id="rId1727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1729" r:id="rId1728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1730" r:id="rId1729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1731" r:id="rId1730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1732" r:id="rId1731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1733" r:id="rId1732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1734" r:id="rId1733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1735" r:id="rId1734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1736" r:id="rId1735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1737" r:id="rId1736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1738" r:id="rId1737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1739" r:id="rId1738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1740" r:id="rId1739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1741" r:id="rId1740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1742" r:id="rId1741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1743" r:id="rId1742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1744" r:id="rId1743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1745" r:id="rId1744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1746" r:id="rId1745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1747" r:id="rId1746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1748" r:id="rId1747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1749" r:id="rId1748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1750" r:id="rId1749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1751" r:id="rId1750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1752" r:id="rId1751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1753" r:id="rId1752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1754" r:id="rId1753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1755" r:id="rId1754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1756" r:id="rId1755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1757" r:id="rId1756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1758" r:id="rId1757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1759" r:id="rId1758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1760" r:id="rId1759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1761" r:id="rId1760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1762" r:id="rId1761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1763" r:id="rId1762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1764" r:id="rId1763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1765" r:id="rId1764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1766" r:id="rId1765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1767" r:id="rId1766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1768" r:id="rId1767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1769" r:id="rId1768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1770" r:id="rId1769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1771" r:id="rId1770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1772" r:id="rId1771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1773" r:id="rId1772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1774" r:id="rId1773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1775" r:id="rId1774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1776" r:id="rId1775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1777" r:id="rId1776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1778" r:id="rId1777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1779" r:id="rId1778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1780" r:id="rId1779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1781" r:id="rId1780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1782" r:id="rId1781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1783" r:id="rId1782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1784" r:id="rId1783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1785" r:id="rId1784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1786" r:id="rId1785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1787" r:id="rId1786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1788" r:id="rId1787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1789" r:id="rId1788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1790" r:id="rId1789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1791" r:id="rId1790"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/BBC6 Music Log.xlsx
+++ b/output/BBC6 Music Log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1791"/>
+  <dimension ref="A1:F1906"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -57750,6 +57750,3686 @@
       <c r="F1791" s="2" t="inlineStr">
         <is>
           <t>https://www.deezer.com/track/444231552</t>
+        </is>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1792" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="C1792" t="inlineStr">
+        <is>
+          <t>Luke Temple</t>
+        </is>
+      </c>
+      <c r="D1792" t="inlineStr">
+        <is>
+          <t>The Birds Of Late December</t>
+        </is>
+      </c>
+      <c r="E1792" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1792" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/131711358</t>
+        </is>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1793" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="C1793" t="inlineStr">
+        <is>
+          <t>Kings of Convenience</t>
+        </is>
+      </c>
+      <c r="D1793" t="inlineStr">
+        <is>
+          <t>Riot On An Empty Street</t>
+        </is>
+      </c>
+      <c r="E1793" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1793" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2100017487</t>
+        </is>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1794" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="C1794" t="inlineStr">
+        <is>
+          <t>Carole King</t>
+        </is>
+      </c>
+      <c r="D1794" t="inlineStr">
+        <is>
+          <t>So Far Away</t>
+        </is>
+      </c>
+      <c r="E1794" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1794" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/119819700</t>
+        </is>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1795" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="C1795" t="inlineStr">
+        <is>
+          <t>Ian Dury &amp; Blockheads</t>
+        </is>
+      </c>
+      <c r="D1795" t="inlineStr">
+        <is>
+          <t>Wake Up And Make Love With Me</t>
+        </is>
+      </c>
+      <c r="E1795" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1795" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3207251871</t>
+        </is>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1796" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="C1796" t="inlineStr">
+        <is>
+          <t>The Sixth Great Lake</t>
+        </is>
+      </c>
+      <c r="D1796" t="inlineStr">
+        <is>
+          <t>Duck Pond</t>
+        </is>
+      </c>
+      <c r="E1796" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1796" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/467679272</t>
+        </is>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1797" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="C1797" t="inlineStr">
+        <is>
+          <t>Wilco</t>
+        </is>
+      </c>
+      <c r="D1797" t="inlineStr">
+        <is>
+          <t>Jesus, Etc.</t>
+        </is>
+      </c>
+      <c r="E1797" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1797" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2794330</t>
+        </is>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1798" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="C1798" t="inlineStr">
+        <is>
+          <t>Dave Grusin</t>
+        </is>
+      </c>
+      <c r="D1798" t="inlineStr">
+        <is>
+          <t>On Golden Pond (Main Theme)</t>
+        </is>
+      </c>
+      <c r="E1798" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1798" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/505540442</t>
+        </is>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1799" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="C1799" t="inlineStr">
+        <is>
+          <t>øjeRum</t>
+        </is>
+      </c>
+      <c r="D1799" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E1799" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1799" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3938506341</t>
+        </is>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1800" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="C1800" t="inlineStr">
+        <is>
+          <t>Ana Roxanne</t>
+        </is>
+      </c>
+      <c r="D1800" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E1800" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1800" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3841311551</t>
+        </is>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1801" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="C1801" t="inlineStr">
+        <is>
+          <t>Stephen Star</t>
+        </is>
+      </c>
+      <c r="D1801" t="inlineStr">
+        <is>
+          <t>Tragic Figure</t>
+        </is>
+      </c>
+      <c r="E1801" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1801" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3918568491</t>
+        </is>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1802" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="C1802" t="inlineStr">
+        <is>
+          <t>Joan Baez</t>
+        </is>
+      </c>
+      <c r="D1802" t="inlineStr">
+        <is>
+          <t>Geordie</t>
+        </is>
+      </c>
+      <c r="E1802" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1802" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/6103824</t>
+        </is>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1803" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="C1803" t="inlineStr">
+        <is>
+          <t>Enya</t>
+        </is>
+      </c>
+      <c r="D1803" t="inlineStr">
+        <is>
+          <t>Orinoco Flow</t>
+        </is>
+      </c>
+      <c r="E1803" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1803" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/917594892</t>
+        </is>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1804" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="C1804" t="inlineStr">
+        <is>
+          <t>Pau Riba</t>
+        </is>
+      </c>
+      <c r="D1804" t="inlineStr">
+        <is>
+          <t>HELENA, DESENGANYA'T</t>
+        </is>
+      </c>
+      <c r="E1804" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1804" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/644959112</t>
+        </is>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="A1805" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1805" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="C1805" t="inlineStr">
+        <is>
+          <t>X-Cetra</t>
+        </is>
+      </c>
+      <c r="D1805" t="inlineStr">
+        <is>
+          <t>Wasn't There</t>
+        </is>
+      </c>
+      <c r="E1805" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1805" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2309817335</t>
+        </is>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1806" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="C1806" t="inlineStr">
+        <is>
+          <t>Emily A. Sprague</t>
+        </is>
+      </c>
+      <c r="D1806" t="inlineStr">
+        <is>
+          <t>Double Moon</t>
+        </is>
+      </c>
+      <c r="E1806" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1806" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3871839431</t>
+        </is>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1807" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="C1807" t="inlineStr">
+        <is>
+          <t>Tom Waits</t>
+        </is>
+      </c>
+      <c r="D1807" t="inlineStr">
+        <is>
+          <t>Martha</t>
+        </is>
+      </c>
+      <c r="E1807" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1807" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/447698212</t>
+        </is>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1808" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="C1808" t="inlineStr">
+        <is>
+          <t>Tom Waits</t>
+        </is>
+      </c>
+      <c r="D1808" t="inlineStr">
+        <is>
+          <t>Closing Time</t>
+        </is>
+      </c>
+      <c r="E1808" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1808" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/447698272</t>
+        </is>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="A1809" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1809" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="C1809" t="inlineStr">
+        <is>
+          <t>Sibylle Baier</t>
+        </is>
+      </c>
+      <c r="D1809" t="inlineStr">
+        <is>
+          <t>Tonight</t>
+        </is>
+      </c>
+      <c r="E1809" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1809" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/112979012</t>
+        </is>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="A1810" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1810" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="C1810" t="inlineStr">
+        <is>
+          <t>Sibylle Baier</t>
+        </is>
+      </c>
+      <c r="D1810" t="inlineStr">
+        <is>
+          <t>Give me a smile</t>
+        </is>
+      </c>
+      <c r="E1810" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1810" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/112979038</t>
+        </is>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="A1811" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1811" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="C1811" t="inlineStr">
+        <is>
+          <t>Eliana Glass</t>
+        </is>
+      </c>
+      <c r="D1811" t="inlineStr">
+        <is>
+          <t>Dawn to May</t>
+        </is>
+      </c>
+      <c r="E1811" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1811" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3904421611</t>
+        </is>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1812" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="C1812" t="inlineStr">
+        <is>
+          <t>Resavoir</t>
+        </is>
+      </c>
+      <c r="D1812" t="inlineStr">
+        <is>
+          <t>Alone With Guitar</t>
+        </is>
+      </c>
+      <c r="E1812" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1812" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3791496742</t>
+        </is>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1813" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C1813" t="inlineStr">
+        <is>
+          <t>Broadcast</t>
+        </is>
+      </c>
+      <c r="D1813" t="inlineStr">
+        <is>
+          <t>Come Back to Me</t>
+        </is>
+      </c>
+      <c r="E1813" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1813" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2680713742</t>
+        </is>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1814" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="C1814" t="inlineStr">
+        <is>
+          <t>Duval Timothy &amp; Carlos Nino</t>
+        </is>
+      </c>
+      <c r="D1814" t="inlineStr">
+        <is>
+          <t>Loopy</t>
+        </is>
+      </c>
+      <c r="E1814" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1814" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4010690781</t>
+        </is>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1815" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="C1815" t="inlineStr">
+        <is>
+          <t>Matt Gold &amp; Dustin Laurenzi</t>
+        </is>
+      </c>
+      <c r="D1815" t="inlineStr">
+        <is>
+          <t>End of the Horn</t>
+        </is>
+      </c>
+      <c r="E1815" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1815" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3849476511</t>
+        </is>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1816" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="C1816" t="inlineStr">
+        <is>
+          <t>Amaria Hamadalher</t>
+        </is>
+      </c>
+      <c r="D1816" t="inlineStr">
+        <is>
+          <t>Tarhanine</t>
+        </is>
+      </c>
+      <c r="E1816" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1816" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1702112037</t>
+        </is>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1817" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="C1817" t="inlineStr">
+        <is>
+          <t>Donnie &amp; Joe Emerson</t>
+        </is>
+      </c>
+      <c r="D1817" t="inlineStr">
+        <is>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="E1817" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1817" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3184950481</t>
+        </is>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1818" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="C1818" t="inlineStr">
+        <is>
+          <t>Pete La Roca</t>
+        </is>
+      </c>
+      <c r="D1818" t="inlineStr">
+        <is>
+          <t>Bliss</t>
+        </is>
+      </c>
+      <c r="E1818" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1818" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/12179971</t>
+        </is>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1819" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="C1819" t="inlineStr">
+        <is>
+          <t>Eliana Glass</t>
+        </is>
+      </c>
+      <c r="D1819" t="inlineStr">
+        <is>
+          <t>Good Friends Call Me E</t>
+        </is>
+      </c>
+      <c r="E1819" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1819" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3188403081</t>
+        </is>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1820" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="C1820" t="inlineStr">
+        <is>
+          <t>Jonas Cambien</t>
+        </is>
+      </c>
+      <c r="D1820" t="inlineStr">
+        <is>
+          <t>Árbol</t>
+        </is>
+      </c>
+      <c r="E1820" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1820" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3725334332</t>
+        </is>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="A1821" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1821" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="C1821" t="inlineStr">
+        <is>
+          <t>Bill Orcutt</t>
+        </is>
+      </c>
+      <c r="D1821" t="inlineStr">
+        <is>
+          <t>Giving unknown origin</t>
+        </is>
+      </c>
+      <c r="E1821" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1821" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3776710942</t>
+        </is>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1822" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="C1822" t="inlineStr">
+        <is>
+          <t>Camel</t>
+        </is>
+      </c>
+      <c r="D1822" t="inlineStr">
+        <is>
+          <t>Rhayader</t>
+        </is>
+      </c>
+      <c r="E1822" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1822" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/525012322</t>
+        </is>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1823" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="C1823" t="inlineStr">
+        <is>
+          <t>Oneohtrix Point Never</t>
+        </is>
+      </c>
+      <c r="D1823" t="inlineStr">
+        <is>
+          <t>Dim Stars</t>
+        </is>
+      </c>
+      <c r="E1823" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1823" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3921896841</t>
+        </is>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1824" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="C1824" t="inlineStr">
+        <is>
+          <t>Martin Carr</t>
+        </is>
+      </c>
+      <c r="D1824" t="inlineStr">
+        <is>
+          <t>Connie Converse Is Playing At My House</t>
+        </is>
+      </c>
+      <c r="E1824" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1824" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3826135171</t>
+        </is>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="A1825" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1825" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="C1825" t="inlineStr">
+        <is>
+          <t>Natalie Wildgoose</t>
+        </is>
+      </c>
+      <c r="D1825" t="inlineStr">
+        <is>
+          <t>In The North</t>
+        </is>
+      </c>
+      <c r="E1825" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1825" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3837804831</t>
+        </is>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="A1826" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1826" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="C1826" t="inlineStr">
+        <is>
+          <t>Brainticket</t>
+        </is>
+      </c>
+      <c r="D1826" t="inlineStr">
+        <is>
+          <t>Black Sand</t>
+        </is>
+      </c>
+      <c r="E1826" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1826" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/115927718</t>
+        </is>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1827" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="C1827" t="inlineStr">
+        <is>
+          <t>Robert Stillman</t>
+        </is>
+      </c>
+      <c r="D1827" t="inlineStr">
+        <is>
+          <t>10,000 Rivers (Jobs)</t>
+        </is>
+      </c>
+      <c r="E1827" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1827" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3628801202</t>
+        </is>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1828" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="C1828" t="inlineStr">
+        <is>
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="D1828" t="inlineStr">
+        <is>
+          <t>Always Calling</t>
+        </is>
+      </c>
+      <c r="E1828" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1828" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3389500571</t>
+        </is>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1829" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="C1829" t="inlineStr">
+        <is>
+          <t>My New Band Believe</t>
+        </is>
+      </c>
+      <c r="D1829" t="inlineStr">
+        <is>
+          <t>In the Blink of an Eye</t>
+        </is>
+      </c>
+      <c r="E1829" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1829" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3910139781</t>
+        </is>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1830" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="C1830" t="inlineStr">
+        <is>
+          <t>Lip Critic</t>
+        </is>
+      </c>
+      <c r="D1830" t="inlineStr">
+        <is>
+          <t>Debt Forest</t>
+        </is>
+      </c>
+      <c r="E1830" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1830" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3652968032</t>
+        </is>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1831" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="C1831" t="inlineStr">
+        <is>
+          <t>alys(alys)alys</t>
+        </is>
+      </c>
+      <c r="D1831" t="inlineStr">
+        <is>
+          <t>effervescence</t>
+        </is>
+      </c>
+      <c r="E1831" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1831" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3994363811</t>
+        </is>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1832" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="C1832" t="inlineStr">
+        <is>
+          <t>Cinna Peyghamy</t>
+        </is>
+      </c>
+      <c r="D1832" t="inlineStr">
+        <is>
+          <t>Zur زور</t>
+        </is>
+      </c>
+      <c r="E1832" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1832" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3953661911</t>
+        </is>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1833" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="C1833" t="inlineStr">
+        <is>
+          <t>Purelink &amp; Rainy Miller</t>
+        </is>
+      </c>
+      <c r="D1833" t="inlineStr">
+        <is>
+          <t>Barrons Hotel (I, To, Thee)</t>
+        </is>
+      </c>
+      <c r="E1833" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1833" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3929807041</t>
+        </is>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1834" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="C1834" t="inlineStr">
+        <is>
+          <t>Ryuichi Sakamoto</t>
+        </is>
+      </c>
+      <c r="D1834" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="E1834" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1834" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2903524451</t>
+        </is>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1835" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="C1835" t="inlineStr">
+        <is>
+          <t>Trois-Quarts Taxi System</t>
+        </is>
+      </c>
+      <c r="D1835" t="inlineStr">
+        <is>
+          <t>Metamorphism</t>
+        </is>
+      </c>
+      <c r="E1835" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1835" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3200151001</t>
+        </is>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1836" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="C1836" t="inlineStr">
+        <is>
+          <t>Kode9</t>
+        </is>
+      </c>
+      <c r="D1836" t="inlineStr">
+        <is>
+          <t>UH</t>
+        </is>
+      </c>
+      <c r="E1836" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1836" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2253362817</t>
+        </is>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1837" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="C1837" t="inlineStr">
+        <is>
+          <t>LCN</t>
+        </is>
+      </c>
+      <c r="D1837" t="inlineStr">
+        <is>
+          <t>PLAY</t>
+        </is>
+      </c>
+      <c r="E1837" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1837" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3939035921</t>
+        </is>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1838" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="C1838" t="inlineStr">
+        <is>
+          <t>Joy Orbison</t>
+        </is>
+      </c>
+      <c r="D1838" t="inlineStr">
+        <is>
+          <t>Hyph Mngo</t>
+        </is>
+      </c>
+      <c r="E1838" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1838" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/740240082</t>
+        </is>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1839" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="C1839" t="inlineStr">
+        <is>
+          <t>Gui &amp; Adhi</t>
+        </is>
+      </c>
+      <c r="D1839" t="inlineStr">
+        <is>
+          <t>Turiya</t>
+        </is>
+      </c>
+      <c r="E1839" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1839" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3265274661</t>
+        </is>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1840" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="C1840" t="inlineStr">
+        <is>
+          <t>Paul St. Hilaire</t>
+        </is>
+      </c>
+      <c r="D1840" t="inlineStr">
+        <is>
+          <t>Little Way</t>
+        </is>
+      </c>
+      <c r="E1840" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1840" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2078019277</t>
+        </is>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1841" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="C1841" t="inlineStr">
+        <is>
+          <t>Grace Jones</t>
+        </is>
+      </c>
+      <c r="D1841" t="inlineStr">
+        <is>
+          <t>Private Life</t>
+        </is>
+      </c>
+      <c r="E1841" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1841" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3950036261</t>
+        </is>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1842" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="C1842" t="inlineStr">
+        <is>
+          <t>Himba</t>
+        </is>
+      </c>
+      <c r="D1842" t="inlineStr">
+        <is>
+          <t>The Boers Do Not Have Mercy (They Kill! They Kill! They Kill!)</t>
+        </is>
+      </c>
+      <c r="E1842" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1842" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3988199521</t>
+        </is>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1843" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="C1843" t="inlineStr">
+        <is>
+          <t>Karen Nyame KG</t>
+        </is>
+      </c>
+      <c r="D1843" t="inlineStr">
+        <is>
+          <t>Allure</t>
+        </is>
+      </c>
+      <c r="E1843" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1843" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3922585451</t>
+        </is>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1844" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="C1844" t="inlineStr">
+        <is>
+          <t>Fela Kuti</t>
+        </is>
+      </c>
+      <c r="D1844" t="inlineStr">
+        <is>
+          <t>Ako</t>
+        </is>
+      </c>
+      <c r="E1844" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1844" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3125255371</t>
+        </is>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1845" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="C1845" t="inlineStr">
+        <is>
+          <t>Don Randi Trio</t>
+        </is>
+      </c>
+      <c r="D1845" t="inlineStr">
+        <is>
+          <t>Love You To</t>
+        </is>
+      </c>
+      <c r="E1845" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1845" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/666209912</t>
+        </is>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1846" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="C1846" t="inlineStr">
+        <is>
+          <t>Little Simz</t>
+        </is>
+      </c>
+      <c r="D1846" t="inlineStr">
+        <is>
+          <t>Offence</t>
+        </is>
+      </c>
+      <c r="E1846" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1846" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1952541167</t>
+        </is>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1847" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="C1847" t="inlineStr">
+        <is>
+          <t>Tinariwen</t>
+        </is>
+      </c>
+      <c r="D1847" t="inlineStr">
+        <is>
+          <t>Amalouna</t>
+        </is>
+      </c>
+      <c r="E1847" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1847" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3419532711</t>
+        </is>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1848" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="C1848" t="inlineStr">
+        <is>
+          <t>Depeche Mode</t>
+        </is>
+      </c>
+      <c r="D1848" t="inlineStr">
+        <is>
+          <t>Any Second Now (Voices)</t>
+        </is>
+      </c>
+      <c r="E1848" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1848" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/68511058</t>
+        </is>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1849" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="C1849" t="inlineStr">
+        <is>
+          <t>The Human League</t>
+        </is>
+      </c>
+      <c r="D1849" t="inlineStr">
+        <is>
+          <t>The Path of Least Resistance (Early Version)</t>
+        </is>
+      </c>
+      <c r="E1849" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1849" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/136339314</t>
+        </is>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1850" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="C1850" t="inlineStr">
+        <is>
+          <t>The Treorchy Male Voice Choir</t>
+        </is>
+      </c>
+      <c r="D1850" t="inlineStr">
+        <is>
+          <t>Radio Ga Ga</t>
+        </is>
+      </c>
+      <c r="E1850" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1850" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3144087</t>
+        </is>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1851" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="C1851" t="inlineStr">
+        <is>
+          <t>Iggy Pop</t>
+        </is>
+      </c>
+      <c r="D1851" t="inlineStr">
+        <is>
+          <t>Nightclubbing</t>
+        </is>
+      </c>
+      <c r="E1851" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1851" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/366456051</t>
+        </is>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1852" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="C1852" t="inlineStr">
+        <is>
+          <t>New Order</t>
+        </is>
+      </c>
+      <c r="D1852" t="inlineStr">
+        <is>
+          <t>Elegia</t>
+        </is>
+      </c>
+      <c r="E1852" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1852" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/107750196</t>
+        </is>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1853" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="C1853" t="inlineStr">
+        <is>
+          <t>Ennio Morricone</t>
+        </is>
+      </c>
+      <c r="D1853" t="inlineStr">
+        <is>
+          <t>A Fistful of Dollars (Main Theme)</t>
+        </is>
+      </c>
+      <c r="E1853" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1853" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3857396061</t>
+        </is>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1854" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="C1854" t="inlineStr">
+        <is>
+          <t>Lee Remick</t>
+        </is>
+      </c>
+      <c r="D1854" t="inlineStr">
+        <is>
+          <t>Anyone Can Whistle</t>
+        </is>
+      </c>
+      <c r="E1854" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1854" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1070835</t>
+        </is>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1855" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="C1855" t="inlineStr">
+        <is>
+          <t>Erik Satie</t>
+        </is>
+      </c>
+      <c r="D1855" t="inlineStr">
+        <is>
+          <t>Gnossienne: No. 2</t>
+        </is>
+      </c>
+      <c r="E1855" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1855" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1981337067</t>
+        </is>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1856" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="C1856" t="inlineStr">
+        <is>
+          <t>Roy Orbison</t>
+        </is>
+      </c>
+      <c r="D1856" t="inlineStr">
+        <is>
+          <t>In Dreams</t>
+        </is>
+      </c>
+      <c r="E1856" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1856" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3568036</t>
+        </is>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1857" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="C1857" t="inlineStr">
+        <is>
+          <t>John Martyn</t>
+        </is>
+      </c>
+      <c r="D1857" t="inlineStr">
+        <is>
+          <t>Lay It All Down</t>
+        </is>
+      </c>
+      <c r="E1857" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1857" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2500353</t>
+        </is>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1858" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="C1858" t="inlineStr">
+        <is>
+          <t>Headless Heroes</t>
+        </is>
+      </c>
+      <c r="D1858" t="inlineStr">
+        <is>
+          <t>Blues Run the Game</t>
+        </is>
+      </c>
+      <c r="E1858" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1858" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/347821261</t>
+        </is>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1859" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="C1859" t="inlineStr">
+        <is>
+          <t>Smog</t>
+        </is>
+      </c>
+      <c r="D1859" t="inlineStr">
+        <is>
+          <t>Drinking At The Dam</t>
+        </is>
+      </c>
+      <c r="E1859" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1859" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/479816562</t>
+        </is>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1860" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="C1860" t="inlineStr">
+        <is>
+          <t>Massive Attack</t>
+        </is>
+      </c>
+      <c r="D1860" t="inlineStr">
+        <is>
+          <t>Splitting the Atom</t>
+        </is>
+      </c>
+      <c r="E1860" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1860" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/5317033</t>
+        </is>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1861" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="C1861" t="inlineStr">
+        <is>
+          <t>Irma Thomas</t>
+        </is>
+      </c>
+      <c r="D1861" t="inlineStr">
+        <is>
+          <t>Ruler Of My heart</t>
+        </is>
+      </c>
+      <c r="E1861" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1861" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3076474221</t>
+        </is>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1862" t="inlineStr">
+        <is>
+          <t>07:17</t>
+        </is>
+      </c>
+      <c r="C1862" t="inlineStr">
+        <is>
+          <t>Mazzy Star</t>
+        </is>
+      </c>
+      <c r="D1862" t="inlineStr">
+        <is>
+          <t>Rhymes Of An Hour</t>
+        </is>
+      </c>
+      <c r="E1862" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1862" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3130621</t>
+        </is>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1863" t="inlineStr">
+        <is>
+          <t>07:14</t>
+        </is>
+      </c>
+      <c r="C1863" t="inlineStr">
+        <is>
+          <t>Calexico</t>
+        </is>
+      </c>
+      <c r="D1863" t="inlineStr">
+        <is>
+          <t>Woven Birds</t>
+        </is>
+      </c>
+      <c r="E1863" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1863" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/125953451</t>
+        </is>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1864" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="C1864" t="inlineStr">
+        <is>
+          <t>Joni Mitchell</t>
+        </is>
+      </c>
+      <c r="D1864" t="inlineStr">
+        <is>
+          <t>Hejira</t>
+        </is>
+      </c>
+      <c r="E1864" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1864" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/718253</t>
+        </is>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1865" t="inlineStr">
+        <is>
+          <t>07:04</t>
+        </is>
+      </c>
+      <c r="C1865" t="inlineStr">
+        <is>
+          <t>Roger Webb</t>
+        </is>
+      </c>
+      <c r="D1865" t="inlineStr">
+        <is>
+          <t>Moonbird</t>
+        </is>
+      </c>
+      <c r="E1865" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1865" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1862723317</t>
+        </is>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1866" t="inlineStr">
+        <is>
+          <t>06:59</t>
+        </is>
+      </c>
+      <c r="C1866" t="inlineStr">
+        <is>
+          <t>The Smiths</t>
+        </is>
+      </c>
+      <c r="D1866" t="inlineStr">
+        <is>
+          <t>Please, Please, Please Let Me Get What I Want</t>
+        </is>
+      </c>
+      <c r="E1866" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1866" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13786047</t>
+        </is>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1867" t="inlineStr">
+        <is>
+          <t>06:55</t>
+        </is>
+      </c>
+      <c r="C1867" t="inlineStr">
+        <is>
+          <t>10,000 Maniacs</t>
+        </is>
+      </c>
+      <c r="D1867" t="inlineStr">
+        <is>
+          <t>Hey Jack Kerouac</t>
+        </is>
+      </c>
+      <c r="E1867" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1867" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3922531</t>
+        </is>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1868" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="C1868" t="inlineStr">
+        <is>
+          <t>Bowerbirds</t>
+        </is>
+      </c>
+      <c r="D1868" t="inlineStr">
+        <is>
+          <t>In Our Talons</t>
+        </is>
+      </c>
+      <c r="E1868" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1868" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/73913416</t>
+        </is>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1869" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="C1869" t="inlineStr">
+        <is>
+          <t>Elton John</t>
+        </is>
+      </c>
+      <c r="D1869" t="inlineStr">
+        <is>
+          <t>Chameleon</t>
+        </is>
+      </c>
+      <c r="E1869" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1869" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3140277031</t>
+        </is>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1870" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="C1870" t="inlineStr">
+        <is>
+          <t>Link Wray &amp; Joey Welz</t>
+        </is>
+      </c>
+      <c r="D1870" t="inlineStr">
+        <is>
+          <t>Fire and Brimstone</t>
+        </is>
+      </c>
+      <c r="E1870" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1870" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1601632</t>
+        </is>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1871" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="C1871" t="inlineStr">
+        <is>
+          <t>Duke Ellington and His Orchestra</t>
+        </is>
+      </c>
+      <c r="D1871" t="inlineStr">
+        <is>
+          <t>Bluebird Of Delhi (Mynah)</t>
+        </is>
+      </c>
+      <c r="E1871" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1871" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/393647512</t>
+        </is>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1872" t="inlineStr">
+        <is>
+          <t>06:06</t>
+        </is>
+      </c>
+      <c r="C1872" t="inlineStr">
+        <is>
+          <t>The Monkees</t>
+        </is>
+      </c>
+      <c r="D1872" t="inlineStr">
+        <is>
+          <t>Me &amp; Magdalena</t>
+        </is>
+      </c>
+      <c r="E1872" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1872" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/124861476</t>
+        </is>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1873" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="C1873" t="inlineStr">
+        <is>
+          <t>Goldfrapp</t>
+        </is>
+      </c>
+      <c r="D1873" t="inlineStr">
+        <is>
+          <t>Felt Mountain</t>
+        </is>
+      </c>
+      <c r="E1873" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1873" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3786220872</t>
+        </is>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1874" t="inlineStr">
+        <is>
+          <t>05:56</t>
+        </is>
+      </c>
+      <c r="C1874" t="inlineStr">
+        <is>
+          <t>Talking Heads</t>
+        </is>
+      </c>
+      <c r="D1874" t="inlineStr">
+        <is>
+          <t>This Must Be The Place (Naive Melody)</t>
+        </is>
+      </c>
+      <c r="E1874" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1874" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3614317</t>
+        </is>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1875" t="inlineStr">
+        <is>
+          <t>05:49</t>
+        </is>
+      </c>
+      <c r="C1875" t="inlineStr">
+        <is>
+          <t>Tom Rush</t>
+        </is>
+      </c>
+      <c r="D1875" t="inlineStr">
+        <is>
+          <t>No Regrets (Album Version)</t>
+        </is>
+      </c>
+      <c r="E1875" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1875" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/855909</t>
+        </is>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1876" t="inlineStr">
+        <is>
+          <t>04:58</t>
+        </is>
+      </c>
+      <c r="C1876" t="inlineStr">
+        <is>
+          <t>Sister Rosetta Tharpe</t>
+        </is>
+      </c>
+      <c r="D1876" t="inlineStr">
+        <is>
+          <t>Rock Me</t>
+        </is>
+      </c>
+      <c r="E1876" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1876" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/805075132</t>
+        </is>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1877" t="inlineStr">
+        <is>
+          <t>04:56</t>
+        </is>
+      </c>
+      <c r="C1877" t="inlineStr">
+        <is>
+          <t>Michael Jackson</t>
+        </is>
+      </c>
+      <c r="D1877" t="inlineStr">
+        <is>
+          <t>Rock With You</t>
+        </is>
+      </c>
+      <c r="E1877" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1877" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/15586286</t>
+        </is>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1878" t="inlineStr">
+        <is>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="C1878" t="inlineStr">
+        <is>
+          <t>Cibo Matto</t>
+        </is>
+      </c>
+      <c r="D1878" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="E1878" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1878" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3919745</t>
+        </is>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1879" t="inlineStr">
+        <is>
+          <t>04:37</t>
+        </is>
+      </c>
+      <c r="C1879" t="inlineStr">
+        <is>
+          <t>Baby Rose &amp; Leon Thomas</t>
+        </is>
+      </c>
+      <c r="D1879" t="inlineStr">
+        <is>
+          <t>Friends Again</t>
+        </is>
+      </c>
+      <c r="E1879" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1879" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3791096622</t>
+        </is>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1880" t="inlineStr">
+        <is>
+          <t>04:34</t>
+        </is>
+      </c>
+      <c r="C1880" t="inlineStr">
+        <is>
+          <t>Alewya</t>
+        </is>
+      </c>
+      <c r="D1880" t="inlineStr">
+        <is>
+          <t>Selah</t>
+        </is>
+      </c>
+      <c r="E1880" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1880" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3871334561</t>
+        </is>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1881" t="inlineStr">
+        <is>
+          <t>04:18</t>
+        </is>
+      </c>
+      <c r="C1881" t="inlineStr">
+        <is>
+          <t>Noriel Vilela</t>
+        </is>
+      </c>
+      <c r="D1881" t="inlineStr">
+        <is>
+          <t>16 Toneladas</t>
+        </is>
+      </c>
+      <c r="E1881" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1881" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2597274</t>
+        </is>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1882" t="inlineStr">
+        <is>
+          <t>04:09</t>
+        </is>
+      </c>
+      <c r="C1882" t="inlineStr">
+        <is>
+          <t>Aaron Dolan</t>
+        </is>
+      </c>
+      <c r="D1882" t="inlineStr">
+        <is>
+          <t>Caoineadh Cú Chulainn</t>
+        </is>
+      </c>
+      <c r="E1882" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1882" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3959845981</t>
+        </is>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1883" t="inlineStr">
+        <is>
+          <t>03:58</t>
+        </is>
+      </c>
+      <c r="C1883" t="inlineStr">
+        <is>
+          <t>The Clash</t>
+        </is>
+      </c>
+      <c r="D1883" t="inlineStr">
+        <is>
+          <t>Rock The Casbah</t>
+        </is>
+      </c>
+      <c r="E1883" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1883" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/69962765</t>
+        </is>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1884" t="inlineStr">
+        <is>
+          <t>03:54</t>
+        </is>
+      </c>
+      <c r="C1884" t="inlineStr">
+        <is>
+          <t>Gorillaz</t>
+        </is>
+      </c>
+      <c r="D1884" t="inlineStr">
+        <is>
+          <t>Rock The House</t>
+        </is>
+      </c>
+      <c r="E1884" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1884" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/77528565</t>
+        </is>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1885" t="inlineStr">
+        <is>
+          <t>03:48</t>
+        </is>
+      </c>
+      <c r="C1885" t="inlineStr">
+        <is>
+          <t>Duo Ruut &amp; Erki Pärnoja</t>
+        </is>
+      </c>
+      <c r="D1885" t="inlineStr">
+        <is>
+          <t>Interlude</t>
+        </is>
+      </c>
+      <c r="E1885" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1885" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3394023481</t>
+        </is>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1886" t="inlineStr">
+        <is>
+          <t>03:43</t>
+        </is>
+      </c>
+      <c r="C1886" t="inlineStr">
+        <is>
+          <t>Lata Mangeshkar</t>
+        </is>
+      </c>
+      <c r="D1886" t="inlineStr">
+        <is>
+          <t>Ajib Dastan Hai Yeh</t>
+        </is>
+      </c>
+      <c r="E1886" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1886" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/468436712</t>
+        </is>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1887" t="inlineStr">
+        <is>
+          <t>03:41</t>
+        </is>
+      </c>
+      <c r="C1887" t="inlineStr">
+        <is>
+          <t>The Wombles</t>
+        </is>
+      </c>
+      <c r="D1887" t="inlineStr">
+        <is>
+          <t>The Wombling Song</t>
+        </is>
+      </c>
+      <c r="E1887" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1887" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/16540777</t>
+        </is>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1888" t="inlineStr">
+        <is>
+          <t>02:48</t>
+        </is>
+      </c>
+      <c r="C1888" t="inlineStr">
+        <is>
+          <t>Roy Ayers</t>
+        </is>
+      </c>
+      <c r="D1888" t="inlineStr">
+        <is>
+          <t>Papa Was A Rolling Stone</t>
+        </is>
+      </c>
+      <c r="E1888" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1888" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1162333</t>
+        </is>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1889" t="inlineStr">
+        <is>
+          <t>02:45</t>
+        </is>
+      </c>
+      <c r="C1889" t="inlineStr">
+        <is>
+          <t>The SteelDrivers</t>
+        </is>
+      </c>
+      <c r="D1889" t="inlineStr">
+        <is>
+          <t>Midnight On The Mountain</t>
+        </is>
+      </c>
+      <c r="E1889" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1889" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/6994077</t>
+        </is>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1890" t="inlineStr">
+        <is>
+          <t>02:41</t>
+        </is>
+      </c>
+      <c r="C1890" t="inlineStr">
+        <is>
+          <t>Alison Krauss &amp; Union Station</t>
+        </is>
+      </c>
+      <c r="D1890" t="inlineStr">
+        <is>
+          <t>I Am A Man Of Constant Sorrow (Live From The Louisville Palace, Kentucky / 2002)</t>
+        </is>
+      </c>
+      <c r="E1890" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1890" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/93182776</t>
+        </is>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1891" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C1891" t="inlineStr">
+        <is>
+          <t>The Rolling Stones</t>
+        </is>
+      </c>
+      <c r="D1891" t="inlineStr">
+        <is>
+          <t>It's Only Rock 'n' Roll (But I Like It)</t>
+        </is>
+      </c>
+      <c r="E1891" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1891" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4123087</t>
+        </is>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1892" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="C1892" t="inlineStr">
+        <is>
+          <t>Kate Carr</t>
+        </is>
+      </c>
+      <c r="D1892" t="inlineStr">
+        <is>
+          <t>Flicker Mooring Chains</t>
+        </is>
+      </c>
+      <c r="E1892" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1892" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/130030220</t>
+        </is>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1893" t="inlineStr">
+        <is>
+          <t>02:22</t>
+        </is>
+      </c>
+      <c r="C1893" t="inlineStr">
+        <is>
+          <t>Bob Dylan</t>
+        </is>
+      </c>
+      <c r="D1893" t="inlineStr">
+        <is>
+          <t>Rainy Day Women #12 &amp; 35</t>
+        </is>
+      </c>
+      <c r="E1893" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1893" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/15190485</t>
+        </is>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1894" t="inlineStr">
+        <is>
+          <t>02:16</t>
+        </is>
+      </c>
+      <c r="C1894" t="inlineStr">
+        <is>
+          <t>Sulaf</t>
+        </is>
+      </c>
+      <c r="D1894" t="inlineStr">
+        <is>
+          <t>Naada</t>
+        </is>
+      </c>
+      <c r="E1894" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1894" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3892487361</t>
+        </is>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1895" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C1895" t="inlineStr">
+        <is>
+          <t>Laura Misch</t>
+        </is>
+      </c>
+      <c r="D1895" t="inlineStr">
+        <is>
+          <t>Kairos</t>
+        </is>
+      </c>
+      <c r="E1895" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1895" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3788486202</t>
+        </is>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1896" t="inlineStr">
+        <is>
+          <t>02:06</t>
+        </is>
+      </c>
+      <c r="C1896" t="inlineStr">
+        <is>
+          <t>B.B. King</t>
+        </is>
+      </c>
+      <c r="D1896" t="inlineStr">
+        <is>
+          <t>Rock Me Baby</t>
+        </is>
+      </c>
+      <c r="E1896" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1896" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/538674272</t>
+        </is>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1897" t="inlineStr">
+        <is>
+          <t>02:01</t>
+        </is>
+      </c>
+      <c r="C1897" t="inlineStr">
+        <is>
+          <t>Spinal Tap</t>
+        </is>
+      </c>
+      <c r="D1897" t="inlineStr">
+        <is>
+          <t>Stonehenge</t>
+        </is>
+      </c>
+      <c r="E1897" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1897" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3531042491</t>
+        </is>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1898" t="inlineStr">
+        <is>
+          <t>01:58</t>
+        </is>
+      </c>
+      <c r="C1898" t="inlineStr">
+        <is>
+          <t>Goat</t>
+        </is>
+      </c>
+      <c r="D1898" t="inlineStr">
+        <is>
+          <t>Run To Your Mama</t>
+        </is>
+      </c>
+      <c r="E1898" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1898" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/34326081</t>
+        </is>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1899" t="inlineStr">
+        <is>
+          <t>01:27</t>
+        </is>
+      </c>
+      <c r="C1899" t="inlineStr">
+        <is>
+          <t>The National</t>
+        </is>
+      </c>
+      <c r="D1899" t="inlineStr">
+        <is>
+          <t>Anyone's Ghost</t>
+        </is>
+      </c>
+      <c r="E1899" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1899" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/7536431</t>
+        </is>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1900" t="inlineStr">
+        <is>
+          <t>01:02</t>
+        </is>
+      </c>
+      <c r="C1900" t="inlineStr">
+        <is>
+          <t>Blondie</t>
+        </is>
+      </c>
+      <c r="D1900" t="inlineStr">
+        <is>
+          <t>(I'm Always Touched By Your) Presence, Dear</t>
+        </is>
+      </c>
+      <c r="E1900" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1900" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3100616</t>
+        </is>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1901" t="inlineStr">
+        <is>
+          <t>00:58</t>
+        </is>
+      </c>
+      <c r="C1901" t="inlineStr">
+        <is>
+          <t>Frankie Archer</t>
+        </is>
+      </c>
+      <c r="D1901" t="inlineStr">
+        <is>
+          <t>The Unquiet Grave</t>
+        </is>
+      </c>
+      <c r="E1901" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1901" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3849930111</t>
+        </is>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1902" t="inlineStr">
+        <is>
+          <t>00:33</t>
+        </is>
+      </c>
+      <c r="C1902" t="inlineStr">
+        <is>
+          <t>David Holmes</t>
+        </is>
+      </c>
+      <c r="D1902" t="inlineStr">
+        <is>
+          <t>I Heard Wonders</t>
+        </is>
+      </c>
+      <c r="E1902" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1902" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2668905412</t>
+        </is>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1903" t="inlineStr">
+        <is>
+          <t>00:28</t>
+        </is>
+      </c>
+      <c r="C1903" t="inlineStr">
+        <is>
+          <t>Poliça</t>
+        </is>
+      </c>
+      <c r="D1903" t="inlineStr">
+        <is>
+          <t>Chain My Name</t>
+        </is>
+      </c>
+      <c r="E1903" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1903" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3877046021</t>
+        </is>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1904" t="inlineStr">
+        <is>
+          <t>00:19</t>
+        </is>
+      </c>
+      <c r="C1904" t="inlineStr">
+        <is>
+          <t>The Lemon Pipers</t>
+        </is>
+      </c>
+      <c r="D1904" t="inlineStr">
+        <is>
+          <t>Green Tambourine</t>
+        </is>
+      </c>
+      <c r="E1904" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1904" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/7398223</t>
+        </is>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1905" t="inlineStr">
+        <is>
+          <t>00:14</t>
+        </is>
+      </c>
+      <c r="C1905" t="inlineStr">
+        <is>
+          <t>Elastica</t>
+        </is>
+      </c>
+      <c r="D1905" t="inlineStr">
+        <is>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="E1905" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1905" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/97089136</t>
+        </is>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B1906" t="inlineStr">
+        <is>
+          <t>00:01</t>
+        </is>
+      </c>
+      <c r="C1906" t="inlineStr">
+        <is>
+          <t>Cerrone</t>
+        </is>
+      </c>
+      <c r="D1906" t="inlineStr">
+        <is>
+          <t>Supernature</t>
+        </is>
+      </c>
+      <c r="E1906" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1906" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1013210122</t>
         </is>
       </c>
     </row>
@@ -59545,6 +63225,121 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1789" r:id="rId1788"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1790" r:id="rId1789"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1791" r:id="rId1790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1792" r:id="rId1791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1793" r:id="rId1792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1794" r:id="rId1793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1795" r:id="rId1794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1796" r:id="rId1795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1797" r:id="rId1796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1798" r:id="rId1797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1799" r:id="rId1798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1800" r:id="rId1799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1801" r:id="rId1800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1802" r:id="rId1801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1803" r:id="rId1802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1804" r:id="rId1803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1805" r:id="rId1804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1806" r:id="rId1805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1807" r:id="rId1806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1808" r:id="rId1807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1809" r:id="rId1808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1810" r:id="rId1809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1811" r:id="rId1810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1812" r:id="rId1811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1813" r:id="rId1812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1814" r:id="rId1813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1815" r:id="rId1814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1816" r:id="rId1815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1817" r:id="rId1816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1818" r:id="rId1817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1819" r:id="rId1818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1820" r:id="rId1819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1821" r:id="rId1820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1822" r:id="rId1821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1823" r:id="rId1822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1824" r:id="rId1823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1825" r:id="rId1824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1826" r:id="rId1825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1827" r:id="rId1826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1828" r:id="rId1827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1829" r:id="rId1828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1830" r:id="rId1829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1831" r:id="rId1830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1832" r:id="rId1831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1833" r:id="rId1832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1834" r:id="rId1833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1835" r:id="rId1834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1836" r:id="rId1835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1837" r:id="rId1836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1838" r:id="rId1837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1839" r:id="rId1838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1840" r:id="rId1839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1841" r:id="rId1840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1842" r:id="rId1841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1843" r:id="rId1842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1844" r:id="rId1843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1845" r:id="rId1844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1846" r:id="rId1845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1847" r:id="rId1846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1848" r:id="rId1847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1849" r:id="rId1848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1850" r:id="rId1849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1851" r:id="rId1850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1852" r:id="rId1851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1853" r:id="rId1852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1854" r:id="rId1853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1855" r:id="rId1854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1856" r:id="rId1855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1857" r:id="rId1856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1858" r:id="rId1857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1859" r:id="rId1858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1860" r:id="rId1859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1861" r:id="rId1860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1862" r:id="rId1861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1863" r:id="rId1862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1864" r:id="rId1863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1865" r:id="rId1864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1866" r:id="rId1865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1867" r:id="rId1866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1868" r:id="rId1867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1869" r:id="rId1868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1870" r:id="rId1869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1871" r:id="rId1870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1872" r:id="rId1871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1873" r:id="rId1872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1874" r:id="rId1873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1875" r:id="rId1874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1876" r:id="rId1875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1877" r:id="rId1876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1878" r:id="rId1877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1879" r:id="rId1878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1880" r:id="rId1879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1881" r:id="rId1880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1882" r:id="rId1881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1883" r:id="rId1882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1884" r:id="rId1883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1885" r:id="rId1884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1886" r:id="rId1885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1887" r:id="rId1886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1888" r:id="rId1887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1889" r:id="rId1888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1890" r:id="rId1889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1891" r:id="rId1890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1892" r:id="rId1891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1893" r:id="rId1892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1894" r:id="rId1893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1895" r:id="rId1894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1896" r:id="rId1895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1897" r:id="rId1896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1898" r:id="rId1897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1899" r:id="rId1898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1900" r:id="rId1899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1901" r:id="rId1900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1902" r:id="rId1901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1903" r:id="rId1902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1904" r:id="rId1903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1905" r:id="rId1904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1906" r:id="rId1905"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/BBC6 Music Log.xlsx
+++ b/output/BBC6 Music Log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1906"/>
+  <dimension ref="A1:F2034"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -61430,6 +61430,4102 @@
       <c r="F1906" s="2" t="inlineStr">
         <is>
           <t>https://www.deezer.com/track/1013210122</t>
+        </is>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1907" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="C1907" t="inlineStr">
+        <is>
+          <t>Dusty Springfield</t>
+        </is>
+      </c>
+      <c r="D1907" t="inlineStr">
+        <is>
+          <t>Nothing Has Been Proved</t>
+        </is>
+      </c>
+      <c r="E1907" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1907" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3445109</t>
+        </is>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1908" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="C1908" t="inlineStr">
+        <is>
+          <t>Kylie Minogue</t>
+        </is>
+      </c>
+      <c r="D1908" t="inlineStr">
+        <is>
+          <t>Wouldn't Change A Thing</t>
+        </is>
+      </c>
+      <c r="E1908" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1908" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3786417612</t>
+        </is>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1909" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="C1909" t="inlineStr">
+        <is>
+          <t>Pet Shop Boys</t>
+        </is>
+      </c>
+      <c r="D1909" t="inlineStr">
+        <is>
+          <t>Groovy</t>
+        </is>
+      </c>
+      <c r="E1909" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1909" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2586825252</t>
+        </is>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1910" t="inlineStr">
+        <is>
+          <t>19:29</t>
+        </is>
+      </c>
+      <c r="C1910" t="inlineStr">
+        <is>
+          <t>Pet Shop Boys</t>
+        </is>
+      </c>
+      <c r="D1910" t="inlineStr">
+        <is>
+          <t>The Pop Kids</t>
+        </is>
+      </c>
+      <c r="E1910" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1910" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2586825202</t>
+        </is>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1911" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="C1911" t="inlineStr">
+        <is>
+          <t>Ozzy Osbourne</t>
+        </is>
+      </c>
+      <c r="D1911" t="inlineStr">
+        <is>
+          <t>Mr. Crowley</t>
+        </is>
+      </c>
+      <c r="E1911" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1911" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/83919191</t>
+        </is>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1912" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="C1912" t="inlineStr">
+        <is>
+          <t>Ozzy Osbourne</t>
+        </is>
+      </c>
+      <c r="D1912" t="inlineStr">
+        <is>
+          <t>Believer</t>
+        </is>
+      </c>
+      <c r="E1912" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1912" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/12000274</t>
+        </is>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1913" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="C1913" t="inlineStr">
+        <is>
+          <t>Ozzy Osbourne</t>
+        </is>
+      </c>
+      <c r="D1913" t="inlineStr">
+        <is>
+          <t>Mama, I'm Coming Home</t>
+        </is>
+      </c>
+      <c r="E1913" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1913" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/625945</t>
+        </is>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1914" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="C1914" t="inlineStr">
+        <is>
+          <t>Jazz Sabbath</t>
+        </is>
+      </c>
+      <c r="D1914" t="inlineStr">
+        <is>
+          <t>Iron Man</t>
+        </is>
+      </c>
+      <c r="E1914" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1914" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/879942582</t>
+        </is>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1915" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="C1915" t="inlineStr">
+        <is>
+          <t>Ozzy Osbourne</t>
+        </is>
+      </c>
+      <c r="D1915" t="inlineStr">
+        <is>
+          <t>Breakin' All the Rules</t>
+        </is>
+      </c>
+      <c r="E1915" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1915" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/829801</t>
+        </is>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1916" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="C1916" t="inlineStr">
+        <is>
+          <t>Kelly Osbourne &amp; Ozzy Osbourne, Kelly Osbourne &amp; Ozzy Osbourne</t>
+        </is>
+      </c>
+      <c r="D1916" t="inlineStr">
+        <is>
+          <t>Changes</t>
+        </is>
+      </c>
+      <c r="E1916" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1916" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/729113672</t>
+        </is>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1917" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="C1917" t="inlineStr">
+        <is>
+          <t>Ozzy Osbourne</t>
+        </is>
+      </c>
+      <c r="D1917" t="inlineStr">
+        <is>
+          <t>Bark at the Moon</t>
+        </is>
+      </c>
+      <c r="E1917" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1917" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/623616</t>
+        </is>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1918" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="C1918" t="inlineStr">
+        <is>
+          <t>Black Sabbath</t>
+        </is>
+      </c>
+      <c r="D1918" t="inlineStr">
+        <is>
+          <t>The Wizard</t>
+        </is>
+      </c>
+      <c r="E1918" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1918" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/74062598</t>
+        </is>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1919" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="C1919" t="inlineStr">
+        <is>
+          <t>Black Sabbath</t>
+        </is>
+      </c>
+      <c r="D1919" t="inlineStr">
+        <is>
+          <t>Black Sabbath</t>
+        </is>
+      </c>
+      <c r="E1919" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1919" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/74062597</t>
+        </is>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1920" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="C1920" t="inlineStr">
+        <is>
+          <t>Ozzy Osbourne</t>
+        </is>
+      </c>
+      <c r="D1920" t="inlineStr">
+        <is>
+          <t>Crazy Train</t>
+        </is>
+      </c>
+      <c r="E1920" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1920" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/83919189</t>
+        </is>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1921" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="C1921" t="inlineStr">
+        <is>
+          <t>Elvis Costello</t>
+        </is>
+      </c>
+      <c r="D1921" t="inlineStr">
+        <is>
+          <t>Shipbuilding</t>
+        </is>
+      </c>
+      <c r="E1921" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1921" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1111000</t>
+        </is>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1922" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="C1922" t="inlineStr">
+        <is>
+          <t>Aldous Harding</t>
+        </is>
+      </c>
+      <c r="D1922" t="inlineStr">
+        <is>
+          <t>One Stop</t>
+        </is>
+      </c>
+      <c r="E1922" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1922" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3964400781</t>
+        </is>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1923" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="C1923" t="inlineStr">
+        <is>
+          <t>Vic Godard</t>
+        </is>
+      </c>
+      <c r="D1923" t="inlineStr">
+        <is>
+          <t>Penny Drops</t>
+        </is>
+      </c>
+      <c r="E1923" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1923" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3950561791</t>
+        </is>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1924" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="C1924" t="inlineStr">
+        <is>
+          <t>John Lee Hooker</t>
+        </is>
+      </c>
+      <c r="D1924" t="inlineStr">
+        <is>
+          <t>Crawling King Snake</t>
+        </is>
+      </c>
+      <c r="E1924" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1924" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/12055102</t>
+        </is>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1925" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="C1925" t="inlineStr">
+        <is>
+          <t>Led Zeppelin</t>
+        </is>
+      </c>
+      <c r="D1925" t="inlineStr">
+        <is>
+          <t>Misty Mountain Hop</t>
+        </is>
+      </c>
+      <c r="E1925" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1925" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/111628788</t>
+        </is>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1926" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="C1926" t="inlineStr">
+        <is>
+          <t>Go-Kart Mozart</t>
+        </is>
+      </c>
+      <c r="D1926" t="inlineStr">
+        <is>
+          <t>We're Selfish, Lazy and Greedy</t>
+        </is>
+      </c>
+      <c r="E1926" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1926" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1551851552</t>
+        </is>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1927" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="C1927" t="inlineStr">
+        <is>
+          <t>The Boo Radleys</t>
+        </is>
+      </c>
+      <c r="D1927" t="inlineStr">
+        <is>
+          <t>Lazarus</t>
+        </is>
+      </c>
+      <c r="E1927" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1927" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/860507</t>
+        </is>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1928" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="C1928" t="inlineStr">
+        <is>
+          <t>Little Richard</t>
+        </is>
+      </c>
+      <c r="D1928" t="inlineStr">
+        <is>
+          <t>Lucille</t>
+        </is>
+      </c>
+      <c r="E1928" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1928" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2203637</t>
+        </is>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1929" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="C1929" t="inlineStr">
+        <is>
+          <t>Laura Veirs</t>
+        </is>
+      </c>
+      <c r="D1929" t="inlineStr">
+        <is>
+          <t>Flying Into Darkness</t>
+        </is>
+      </c>
+      <c r="E1929" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1929" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3962835091</t>
+        </is>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1930" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="C1930" t="inlineStr">
+        <is>
+          <t>Siouxsie and the Banshees</t>
+        </is>
+      </c>
+      <c r="D1930" t="inlineStr">
+        <is>
+          <t>Happy House</t>
+        </is>
+      </c>
+      <c r="E1930" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1930" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/704098772</t>
+        </is>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1931" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="C1931" t="inlineStr">
+        <is>
+          <t>Momoko Gill</t>
+        </is>
+      </c>
+      <c r="D1931" t="inlineStr">
+        <is>
+          <t>No Others</t>
+        </is>
+      </c>
+      <c r="E1931" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1931" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3561842641</t>
+        </is>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1932" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="C1932" t="inlineStr">
+        <is>
+          <t>Chiminyo</t>
+        </is>
+      </c>
+      <c r="D1932" t="inlineStr">
+        <is>
+          <t>Transference</t>
+        </is>
+      </c>
+      <c r="E1932" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1932" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3898894611</t>
+        </is>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1933" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="C1933" t="inlineStr">
+        <is>
+          <t>My New Band Believe</t>
+        </is>
+      </c>
+      <c r="D1933" t="inlineStr">
+        <is>
+          <t>Numerology</t>
+        </is>
+      </c>
+      <c r="E1933" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1933" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3768391142</t>
+        </is>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1934" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="C1934" t="inlineStr">
+        <is>
+          <t>Bleech 9:3</t>
+        </is>
+      </c>
+      <c r="D1934" t="inlineStr">
+        <is>
+          <t>No Surprise</t>
+        </is>
+      </c>
+      <c r="E1934" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1934" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4008636941</t>
+        </is>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1935" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="C1935" t="inlineStr">
+        <is>
+          <t>Qendresa</t>
+        </is>
+      </c>
+      <c r="D1935" t="inlineStr">
+        <is>
+          <t>Rain in July</t>
+        </is>
+      </c>
+      <c r="E1935" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1935" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3892785931</t>
+        </is>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1936" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="C1936" t="inlineStr">
+        <is>
+          <t>Ibeyi</t>
+        </is>
+      </c>
+      <c r="D1936" t="inlineStr">
+        <is>
+          <t>Aset</t>
+        </is>
+      </c>
+      <c r="E1936" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1936" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3995667501</t>
+        </is>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1937" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="C1937" t="inlineStr">
+        <is>
+          <t>Nomi</t>
+        </is>
+      </c>
+      <c r="D1937" t="inlineStr">
+        <is>
+          <t>sweet talk</t>
+        </is>
+      </c>
+      <c r="E1937" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1937" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3968872691</t>
+        </is>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1938" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="C1938" t="inlineStr">
+        <is>
+          <t>House Arrest</t>
+        </is>
+      </c>
+      <c r="D1938" t="inlineStr">
+        <is>
+          <t>No Shame At All</t>
+        </is>
+      </c>
+      <c r="E1938" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1938" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3986332111</t>
+        </is>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1939" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="C1939" t="inlineStr">
+        <is>
+          <t>Sadie</t>
+        </is>
+      </c>
+      <c r="D1939" t="inlineStr">
+        <is>
+          <t>Better Angels</t>
+        </is>
+      </c>
+      <c r="E1939" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1939" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3851091281</t>
+        </is>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1940" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="C1940" t="inlineStr">
+        <is>
+          <t>mary in the junkyard</t>
+        </is>
+      </c>
+      <c r="D1940" t="inlineStr">
+        <is>
+          <t>New Muscles</t>
+        </is>
+      </c>
+      <c r="E1940" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1940" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3953832701</t>
+        </is>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1941" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="C1941" t="inlineStr">
+        <is>
+          <t>Blondshell</t>
+        </is>
+      </c>
+      <c r="D1941" t="inlineStr">
+        <is>
+          <t>Heart Has To Work So Hard</t>
+        </is>
+      </c>
+      <c r="E1941" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1941" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3995881461</t>
+        </is>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1942" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="C1942" t="inlineStr">
+        <is>
+          <t>Irked</t>
+        </is>
+      </c>
+      <c r="D1942" t="inlineStr">
+        <is>
+          <t>Repeat Offender</t>
+        </is>
+      </c>
+      <c r="E1942" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1942" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3918136581</t>
+        </is>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1943" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="C1943" t="inlineStr">
+        <is>
+          <t>Really Good Time</t>
+        </is>
+      </c>
+      <c r="D1943" t="inlineStr">
+        <is>
+          <t>Do It</t>
+        </is>
+      </c>
+      <c r="E1943" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1943" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3945531391</t>
+        </is>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1944" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="C1944" t="inlineStr">
+        <is>
+          <t>Monobloc</t>
+        </is>
+      </c>
+      <c r="D1944" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="E1944" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1944" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3772574452</t>
+        </is>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1945" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="C1945" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D1945" t="inlineStr">
+        <is>
+          <t>Skipper</t>
+        </is>
+      </c>
+      <c r="E1945" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1945" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3812951712</t>
+        </is>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1946" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="C1946" t="inlineStr">
+        <is>
+          <t>Mr. Scruff</t>
+        </is>
+      </c>
+      <c r="D1946" t="inlineStr">
+        <is>
+          <t>Get A Move On</t>
+        </is>
+      </c>
+      <c r="E1946" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1946" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/513126452</t>
+        </is>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1947" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="C1947" t="inlineStr">
+        <is>
+          <t>MORN</t>
+        </is>
+      </c>
+      <c r="D1947" t="inlineStr">
+        <is>
+          <t>Modern Man</t>
+        </is>
+      </c>
+      <c r="E1947" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1947" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3358296901</t>
+        </is>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1948" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="C1948" t="inlineStr">
+        <is>
+          <t>Any Young Mechanic</t>
+        </is>
+      </c>
+      <c r="D1948" t="inlineStr">
+        <is>
+          <t>My House Divides</t>
+        </is>
+      </c>
+      <c r="E1948" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1948" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3872035791</t>
+        </is>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1949" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="C1949" t="inlineStr">
+        <is>
+          <t>Any Young Mechanic</t>
+        </is>
+      </c>
+      <c r="D1949" t="inlineStr">
+        <is>
+          <t>Pretty Strange World</t>
+        </is>
+      </c>
+      <c r="E1949" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1949" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3886868521</t>
+        </is>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1950" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="C1950" t="inlineStr">
+        <is>
+          <t>MUDRAT</t>
+        </is>
+      </c>
+      <c r="D1950" t="inlineStr">
+        <is>
+          <t>YOU DON'T CARE ABOUT POOR PEOPLE</t>
+        </is>
+      </c>
+      <c r="E1950" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1950" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3320357661</t>
+        </is>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1951" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="C1951" t="inlineStr">
+        <is>
+          <t>MORN</t>
+        </is>
+      </c>
+      <c r="D1951" t="inlineStr">
+        <is>
+          <t>Standard Model</t>
+        </is>
+      </c>
+      <c r="E1951" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1951" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3925334191</t>
+        </is>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1952" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="C1952" t="inlineStr">
+        <is>
+          <t>Wu-Tang Clan</t>
+        </is>
+      </c>
+      <c r="D1952" t="inlineStr">
+        <is>
+          <t>Gravel Pit</t>
+        </is>
+      </c>
+      <c r="E1952" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1952" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2466305</t>
+        </is>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1953" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="C1953" t="inlineStr">
+        <is>
+          <t>Faithless</t>
+        </is>
+      </c>
+      <c r="D1953" t="inlineStr">
+        <is>
+          <t>Salva Mea</t>
+        </is>
+      </c>
+      <c r="E1953" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1953" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/560274</t>
+        </is>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1954" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="C1954" t="inlineStr">
+        <is>
+          <t>Adam and the Ants</t>
+        </is>
+      </c>
+      <c r="D1954" t="inlineStr">
+        <is>
+          <t>Stand And Deliver</t>
+        </is>
+      </c>
+      <c r="E1954" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1954" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/564953</t>
+        </is>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1955" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="C1955" t="inlineStr">
+        <is>
+          <t>Lush</t>
+        </is>
+      </c>
+      <c r="D1955" t="inlineStr">
+        <is>
+          <t>For Love</t>
+        </is>
+      </c>
+      <c r="E1955" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1955" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/66539071</t>
+        </is>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1956" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="C1956" t="inlineStr">
+        <is>
+          <t>Saint Clair</t>
+        </is>
+      </c>
+      <c r="D1956" t="inlineStr">
+        <is>
+          <t>Too Young To Notice</t>
+        </is>
+      </c>
+      <c r="E1956" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1956" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3922113871</t>
+        </is>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1957" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="C1957" t="inlineStr">
+        <is>
+          <t>Lady G</t>
+        </is>
+      </c>
+      <c r="D1957" t="inlineStr">
+        <is>
+          <t>Nuff Respect</t>
+        </is>
+      </c>
+      <c r="E1957" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1957" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/7171640</t>
+        </is>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1958" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="C1958" t="inlineStr">
+        <is>
+          <t>Band Of Revelations</t>
+        </is>
+      </c>
+      <c r="D1958" t="inlineStr">
+        <is>
+          <t>All the way home</t>
+        </is>
+      </c>
+      <c r="E1958" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1958" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3907033781</t>
+        </is>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1959" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="C1959" t="inlineStr">
+        <is>
+          <t>Geneva</t>
+        </is>
+      </c>
+      <c r="D1959" t="inlineStr">
+        <is>
+          <t>Into The Blue</t>
+        </is>
+      </c>
+      <c r="E1959" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1959" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3221254191</t>
+        </is>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1960" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="C1960" t="inlineStr">
+        <is>
+          <t>Dorothy Moore</t>
+        </is>
+      </c>
+      <c r="D1960" t="inlineStr">
+        <is>
+          <t>Misty Blue</t>
+        </is>
+      </c>
+      <c r="E1960" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1960" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/404145992</t>
+        </is>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1961" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="C1961" t="inlineStr">
+        <is>
+          <t>The All Seeing I</t>
+        </is>
+      </c>
+      <c r="D1961" t="inlineStr">
+        <is>
+          <t>Beat Goes On</t>
+        </is>
+      </c>
+      <c r="E1961" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1961" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1951687507</t>
+        </is>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1962" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C1962" t="inlineStr">
+        <is>
+          <t>Dr. John</t>
+        </is>
+      </c>
+      <c r="D1962" t="inlineStr">
+        <is>
+          <t>Right Place Wrong Time</t>
+        </is>
+      </c>
+      <c r="E1962" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1962" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/724461</t>
+        </is>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1963" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="C1963" t="inlineStr">
+        <is>
+          <t>¡Forward, Russia!</t>
+        </is>
+      </c>
+      <c r="D1963" t="inlineStr">
+        <is>
+          <t>Twelve</t>
+        </is>
+      </c>
+      <c r="E1963" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1963" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/141106929</t>
+        </is>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1964" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="C1964" t="inlineStr">
+        <is>
+          <t>La Sécurité</t>
+        </is>
+      </c>
+      <c r="D1964" t="inlineStr">
+        <is>
+          <t>Deny</t>
+        </is>
+      </c>
+      <c r="E1964" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1964" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3862420681</t>
+        </is>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1965" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="C1965" t="inlineStr">
+        <is>
+          <t>Chloe Slater</t>
+        </is>
+      </c>
+      <c r="D1965" t="inlineStr">
+        <is>
+          <t>UGLY</t>
+        </is>
+      </c>
+      <c r="E1965" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1965" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3975362061</t>
+        </is>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1966" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C1966" t="inlineStr">
+        <is>
+          <t>Elastica</t>
+        </is>
+      </c>
+      <c r="D1966" t="inlineStr">
+        <is>
+          <t>Connection</t>
+        </is>
+      </c>
+      <c r="E1966" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1966" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/97089118</t>
+        </is>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1967" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="C1967" t="inlineStr">
+        <is>
+          <t>David Bowie</t>
+        </is>
+      </c>
+      <c r="D1967" t="inlineStr">
+        <is>
+          <t>Life On Mars?</t>
+        </is>
+      </c>
+      <c r="E1967" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1967" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/107474522</t>
+        </is>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1968" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="C1968" t="inlineStr">
+        <is>
+          <t>Caroline Rose</t>
+        </is>
+      </c>
+      <c r="D1968" t="inlineStr">
+        <is>
+          <t>Yip Yip Yow</t>
+        </is>
+      </c>
+      <c r="E1968" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1968" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3981571701</t>
+        </is>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1969" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="C1969" t="inlineStr">
+        <is>
+          <t>Fuzzbox</t>
+        </is>
+      </c>
+      <c r="D1969" t="inlineStr">
+        <is>
+          <t>Love Is The Slug</t>
+        </is>
+      </c>
+      <c r="E1969" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1969" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/14172620</t>
+        </is>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1970" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="C1970" t="inlineStr">
+        <is>
+          <t>Ivy Knight</t>
+        </is>
+      </c>
+      <c r="D1970" t="inlineStr">
+        <is>
+          <t>Red Rock</t>
+        </is>
+      </c>
+      <c r="E1970" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1970" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3812134742</t>
+        </is>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1971" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="C1971" t="inlineStr">
+        <is>
+          <t>Portishead</t>
+        </is>
+      </c>
+      <c r="D1971" t="inlineStr">
+        <is>
+          <t>Strangers</t>
+        </is>
+      </c>
+      <c r="E1971" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1971" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/982653</t>
+        </is>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1972" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="C1972" t="inlineStr">
+        <is>
+          <t>Delegation</t>
+        </is>
+      </c>
+      <c r="D1972" t="inlineStr">
+        <is>
+          <t>Oh Honey</t>
+        </is>
+      </c>
+      <c r="E1972" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1972" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/38026751</t>
+        </is>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1973" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="C1973" t="inlineStr">
+        <is>
+          <t>Stevie Wonder</t>
+        </is>
+      </c>
+      <c r="D1973" t="inlineStr">
+        <is>
+          <t>Too High</t>
+        </is>
+      </c>
+      <c r="E1973" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1973" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2319293</t>
+        </is>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1974" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="C1974" t="inlineStr">
+        <is>
+          <t>Rotary Connection</t>
+        </is>
+      </c>
+      <c r="D1974" t="inlineStr">
+        <is>
+          <t>I Am The Black Gold Of The Sun</t>
+        </is>
+      </c>
+      <c r="E1974" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1974" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1408771882</t>
+        </is>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1975" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="C1975" t="inlineStr">
+        <is>
+          <t>Fruit Bats</t>
+        </is>
+      </c>
+      <c r="D1975" t="inlineStr">
+        <is>
+          <t>That Goddamn Sun</t>
+        </is>
+      </c>
+      <c r="E1975" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1975" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3962928801</t>
+        </is>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1976" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="C1976" t="inlineStr">
+        <is>
+          <t>The Undertones</t>
+        </is>
+      </c>
+      <c r="D1976" t="inlineStr">
+        <is>
+          <t>Wednesday Week</t>
+        </is>
+      </c>
+      <c r="E1976" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1976" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3788176592</t>
+        </is>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1977" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="C1977" t="inlineStr">
+        <is>
+          <t>Grace Jones</t>
+        </is>
+      </c>
+      <c r="D1977" t="inlineStr">
+        <is>
+          <t>She's Lost Control</t>
+        </is>
+      </c>
+      <c r="E1977" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1977" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2960633</t>
+        </is>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1978" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="C1978" t="inlineStr">
+        <is>
+          <t>Buzzcocks</t>
+        </is>
+      </c>
+      <c r="D1978" t="inlineStr">
+        <is>
+          <t>Why Can't I Touch It?</t>
+        </is>
+      </c>
+      <c r="E1978" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1978" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/405629082</t>
+        </is>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1979" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="C1979" t="inlineStr">
+        <is>
+          <t>PJ Harvey</t>
+        </is>
+      </c>
+      <c r="D1979" t="inlineStr">
+        <is>
+          <t>You Said Something</t>
+        </is>
+      </c>
+      <c r="E1979" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1979" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1172884</t>
+        </is>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1980" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="C1980" t="inlineStr">
+        <is>
+          <t>MT Jones</t>
+        </is>
+      </c>
+      <c r="D1980" t="inlineStr">
+        <is>
+          <t>You Don't Love Me Now</t>
+        </is>
+      </c>
+      <c r="E1980" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1980" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3590293381</t>
+        </is>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1981" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="C1981" t="inlineStr">
+        <is>
+          <t>The Prodigy</t>
+        </is>
+      </c>
+      <c r="D1981" t="inlineStr">
+        <is>
+          <t>No Good (Start The Dance)</t>
+        </is>
+      </c>
+      <c r="E1981" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1981" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/128973862</t>
+        </is>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1982" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="C1982" t="inlineStr">
+        <is>
+          <t>Pete Heller</t>
+        </is>
+      </c>
+      <c r="D1982" t="inlineStr">
+        <is>
+          <t>Big Love</t>
+        </is>
+      </c>
+      <c r="E1982" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1982" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3232086521</t>
+        </is>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1983" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="C1983" t="inlineStr">
+        <is>
+          <t>Jennifer Lara</t>
+        </is>
+      </c>
+      <c r="D1983" t="inlineStr">
+        <is>
+          <t>A Change Is Gonna Come</t>
+        </is>
+      </c>
+      <c r="E1983" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1983" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/110011142</t>
+        </is>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1984" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="C1984" t="inlineStr">
+        <is>
+          <t>Danny Brown</t>
+        </is>
+      </c>
+      <c r="D1984" t="inlineStr">
+        <is>
+          <t>Grown Up</t>
+        </is>
+      </c>
+      <c r="E1984" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1984" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/619875272</t>
+        </is>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1985" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="C1985" t="inlineStr">
+        <is>
+          <t>Talking Heads</t>
+        </is>
+      </c>
+      <c r="D1985" t="inlineStr">
+        <is>
+          <t>Road To Nowhere</t>
+        </is>
+      </c>
+      <c r="E1985" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1985" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/747616</t>
+        </is>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1986" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="C1986" t="inlineStr">
+        <is>
+          <t>Sade</t>
+        </is>
+      </c>
+      <c r="D1986" t="inlineStr">
+        <is>
+          <t>The Sweetest Taboo</t>
+        </is>
+      </c>
+      <c r="E1986" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1986" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1030651942</t>
+        </is>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1987" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="C1987" t="inlineStr">
+        <is>
+          <t>Echo &amp; the Bunnymen</t>
+        </is>
+      </c>
+      <c r="D1987" t="inlineStr">
+        <is>
+          <t>Bring On The Dancing Horses</t>
+        </is>
+      </c>
+      <c r="E1987" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1987" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/751146</t>
+        </is>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1988" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="C1988" t="inlineStr">
+        <is>
+          <t>Boy Azooga</t>
+        </is>
+      </c>
+      <c r="D1988" t="inlineStr">
+        <is>
+          <t>Loner Boogie</t>
+        </is>
+      </c>
+      <c r="E1988" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1988" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/455600232</t>
+        </is>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1989" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="C1989" t="inlineStr">
+        <is>
+          <t>Pet Shop Boys</t>
+        </is>
+      </c>
+      <c r="D1989" t="inlineStr">
+        <is>
+          <t>Being Boring</t>
+        </is>
+      </c>
+      <c r="E1989" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1989" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2210634497</t>
+        </is>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1990" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="C1990" t="inlineStr">
+        <is>
+          <t>Regina Spektor</t>
+        </is>
+      </c>
+      <c r="D1990" t="inlineStr">
+        <is>
+          <t>Eet</t>
+        </is>
+      </c>
+      <c r="E1990" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1990" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/14611175</t>
+        </is>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1991" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="C1991" t="inlineStr">
+        <is>
+          <t>Baba Stiltz &amp; Okay Kaya</t>
+        </is>
+      </c>
+      <c r="D1991" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="E1991" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1991" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3680029252</t>
+        </is>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1992" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="C1992" t="inlineStr">
+        <is>
+          <t>Sleeper</t>
+        </is>
+      </c>
+      <c r="D1992" t="inlineStr">
+        <is>
+          <t>Sale Of The Century</t>
+        </is>
+      </c>
+      <c r="E1992" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1992" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13147889</t>
+        </is>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1993" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="C1993" t="inlineStr">
+        <is>
+          <t>RIP Magic</t>
+        </is>
+      </c>
+      <c r="D1993" t="inlineStr">
+        <is>
+          <t>5words</t>
+        </is>
+      </c>
+      <c r="E1993" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1993" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3736411112</t>
+        </is>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1994" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="C1994" t="inlineStr">
+        <is>
+          <t>Wunderhorse</t>
+        </is>
+      </c>
+      <c r="D1994" t="inlineStr">
+        <is>
+          <t>Midas</t>
+        </is>
+      </c>
+      <c r="E1994" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1994" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2670456992</t>
+        </is>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1995" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="C1995" t="inlineStr">
+        <is>
+          <t>Ritchie</t>
+        </is>
+      </c>
+      <c r="D1995" t="inlineStr">
+        <is>
+          <t>Menina Veneno</t>
+        </is>
+      </c>
+      <c r="E1995" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1995" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/14924893</t>
+        </is>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1996" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="C1996" t="inlineStr">
+        <is>
+          <t>Sylvester</t>
+        </is>
+      </c>
+      <c r="D1996" t="inlineStr">
+        <is>
+          <t>I Need You</t>
+        </is>
+      </c>
+      <c r="E1996" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1996" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/67800544</t>
+        </is>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1997" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="C1997" t="inlineStr">
+        <is>
+          <t>Planningtorock</t>
+        </is>
+      </c>
+      <c r="D1997" t="inlineStr">
+        <is>
+          <t>Beulah Loves Dancing</t>
+        </is>
+      </c>
+      <c r="E1997" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1997" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/546885162</t>
+        </is>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1998" t="inlineStr">
+        <is>
+          <t>06:34</t>
+        </is>
+      </c>
+      <c r="C1998" t="inlineStr">
+        <is>
+          <t>George Harrison</t>
+        </is>
+      </c>
+      <c r="D1998" t="inlineStr">
+        <is>
+          <t>What Is Life</t>
+        </is>
+      </c>
+      <c r="E1998" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1998" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/84791533</t>
+        </is>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B1999" t="inlineStr">
+        <is>
+          <t>06:24</t>
+        </is>
+      </c>
+      <c r="C1999" t="inlineStr">
+        <is>
+          <t>Cheetah &amp; Nia Archives</t>
+        </is>
+      </c>
+      <c r="D1999" t="inlineStr">
+        <is>
+          <t>Get Loose</t>
+        </is>
+      </c>
+      <c r="E1999" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F1999" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3299497571</t>
+        </is>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2000" t="inlineStr">
+        <is>
+          <t>06:13</t>
+        </is>
+      </c>
+      <c r="C2000" t="inlineStr">
+        <is>
+          <t>Sofia Kourtesis</t>
+        </is>
+      </c>
+      <c r="D2000" t="inlineStr">
+        <is>
+          <t>La Perla</t>
+        </is>
+      </c>
+      <c r="E2000" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2000" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1208367042</t>
+        </is>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2001" t="inlineStr">
+        <is>
+          <t>06:04</t>
+        </is>
+      </c>
+      <c r="C2001" t="inlineStr">
+        <is>
+          <t>Prince &amp; The Revolution</t>
+        </is>
+      </c>
+      <c r="D2001" t="inlineStr">
+        <is>
+          <t>I Would Die 4 U</t>
+        </is>
+      </c>
+      <c r="E2001" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2001" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1767888847</t>
+        </is>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2002" t="inlineStr">
+        <is>
+          <t>05:54</t>
+        </is>
+      </c>
+      <c r="C2002" t="inlineStr">
+        <is>
+          <t>Jeru the Damaja</t>
+        </is>
+      </c>
+      <c r="D2002" t="inlineStr">
+        <is>
+          <t>My Mind Spray</t>
+        </is>
+      </c>
+      <c r="E2002" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2002" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/548844592</t>
+        </is>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2003" t="inlineStr">
+        <is>
+          <t>05:51</t>
+        </is>
+      </c>
+      <c r="C2003" t="inlineStr">
+        <is>
+          <t>Warren G &amp; Nate Dogg</t>
+        </is>
+      </c>
+      <c r="D2003" t="inlineStr">
+        <is>
+          <t>Regulate</t>
+        </is>
+      </c>
+      <c r="E2003" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2003" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/953902</t>
+        </is>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2004" t="inlineStr">
+        <is>
+          <t>05:46</t>
+        </is>
+      </c>
+      <c r="C2004" t="inlineStr">
+        <is>
+          <t>Röyksopp</t>
+        </is>
+      </c>
+      <c r="D2004" t="inlineStr">
+        <is>
+          <t>Eple</t>
+        </is>
+      </c>
+      <c r="E2004" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2004" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3286437</t>
+        </is>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2005" t="inlineStr">
+        <is>
+          <t>05:42</t>
+        </is>
+      </c>
+      <c r="C2005" t="inlineStr">
+        <is>
+          <t>Missy Elliott</t>
+        </is>
+      </c>
+      <c r="D2005" t="inlineStr">
+        <is>
+          <t>Work It</t>
+        </is>
+      </c>
+      <c r="E2005" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2005" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/663571</t>
+        </is>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2006" t="inlineStr">
+        <is>
+          <t>05:38</t>
+        </is>
+      </c>
+      <c r="C2006" t="inlineStr">
+        <is>
+          <t>Bob James</t>
+        </is>
+      </c>
+      <c r="D2006" t="inlineStr">
+        <is>
+          <t>Take Me To The Mardi Gras</t>
+        </is>
+      </c>
+      <c r="E2006" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2006" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/519874132</t>
+        </is>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2007" t="inlineStr">
+        <is>
+          <t>05:20</t>
+        </is>
+      </c>
+      <c r="C2007" t="inlineStr">
+        <is>
+          <t>Art of Noise</t>
+        </is>
+      </c>
+      <c r="D2007" t="inlineStr">
+        <is>
+          <t>Moments In Love</t>
+        </is>
+      </c>
+      <c r="E2007" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2007" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/482782582</t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2008" t="inlineStr">
+        <is>
+          <t>05:09</t>
+        </is>
+      </c>
+      <c r="C2008" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="D2008" t="inlineStr">
+        <is>
+          <t>Big Time Sensuality</t>
+        </is>
+      </c>
+      <c r="E2008" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2008" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/14611455</t>
+        </is>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2009" t="inlineStr">
+        <is>
+          <t>04:57</t>
+        </is>
+      </c>
+      <c r="C2009" t="inlineStr">
+        <is>
+          <t>Hüsker Dü</t>
+        </is>
+      </c>
+      <c r="D2009" t="inlineStr">
+        <is>
+          <t>Don't Want To Know If You Are Lonely</t>
+        </is>
+      </c>
+      <c r="E2009" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2009" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/866393</t>
+        </is>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2010" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="C2010" t="inlineStr">
+        <is>
+          <t>Candi Staton</t>
+        </is>
+      </c>
+      <c r="D2010" t="inlineStr">
+        <is>
+          <t>In The Ghetto</t>
+        </is>
+      </c>
+      <c r="E2010" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2010" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3794067732</t>
+        </is>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2011" t="inlineStr">
+        <is>
+          <t>04:02</t>
+        </is>
+      </c>
+      <c r="C2011" t="inlineStr">
+        <is>
+          <t>The Jesus and Mary Chain</t>
+        </is>
+      </c>
+      <c r="D2011" t="inlineStr">
+        <is>
+          <t>Some Candy Talking</t>
+        </is>
+      </c>
+      <c r="E2011" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2011" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1592022831</t>
+        </is>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2012" t="inlineStr">
+        <is>
+          <t>03:24</t>
+        </is>
+      </c>
+      <c r="C2012" t="inlineStr">
+        <is>
+          <t>DEVO</t>
+        </is>
+      </c>
+      <c r="D2012" t="inlineStr">
+        <is>
+          <t>Whip It</t>
+        </is>
+      </c>
+      <c r="E2012" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2012" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4382923</t>
+        </is>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2013" t="inlineStr">
+        <is>
+          <t>03:20</t>
+        </is>
+      </c>
+      <c r="C2013" t="inlineStr">
+        <is>
+          <t>Coldcut</t>
+        </is>
+      </c>
+      <c r="D2013" t="inlineStr">
+        <is>
+          <t>Timber</t>
+        </is>
+      </c>
+      <c r="E2013" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2013" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/524904842</t>
+        </is>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2014" t="inlineStr">
+        <is>
+          <t>03:16</t>
+        </is>
+      </c>
+      <c r="C2014" t="inlineStr">
+        <is>
+          <t>M83</t>
+        </is>
+      </c>
+      <c r="D2014" t="inlineStr">
+        <is>
+          <t>Do It, Try It</t>
+        </is>
+      </c>
+      <c r="E2014" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2014" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/121767336</t>
+        </is>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2015" t="inlineStr">
+        <is>
+          <t>03:11</t>
+        </is>
+      </c>
+      <c r="C2015" t="inlineStr">
+        <is>
+          <t>M.I.A.</t>
+        </is>
+      </c>
+      <c r="D2015" t="inlineStr">
+        <is>
+          <t>Galang '05</t>
+        </is>
+      </c>
+      <c r="E2015" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2015" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/620487052</t>
+        </is>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2016" t="inlineStr">
+        <is>
+          <t>03:08</t>
+        </is>
+      </c>
+      <c r="C2016" t="inlineStr">
+        <is>
+          <t>Jungle</t>
+        </is>
+      </c>
+      <c r="D2016" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="E2016" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2016" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1951189107</t>
+        </is>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2017" t="inlineStr">
+        <is>
+          <t>03:03</t>
+        </is>
+      </c>
+      <c r="C2017" t="inlineStr">
+        <is>
+          <t>The Beloved</t>
+        </is>
+      </c>
+      <c r="D2017" t="inlineStr">
+        <is>
+          <t>The Sun Rising</t>
+        </is>
+      </c>
+      <c r="E2017" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2017" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3404700041</t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2018" t="inlineStr">
+        <is>
+          <t>02:53</t>
+        </is>
+      </c>
+      <c r="C2018" t="inlineStr">
+        <is>
+          <t>Animal Collective</t>
+        </is>
+      </c>
+      <c r="D2018" t="inlineStr">
+        <is>
+          <t>Floridada</t>
+        </is>
+      </c>
+      <c r="E2018" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2018" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/119383520</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2019" t="inlineStr">
+        <is>
+          <t>02:49</t>
+        </is>
+      </c>
+      <c r="C2019" t="inlineStr">
+        <is>
+          <t>Disclosure</t>
+        </is>
+      </c>
+      <c r="D2019" t="inlineStr">
+        <is>
+          <t>She's Gone, Dance On</t>
+        </is>
+      </c>
+      <c r="E2019" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2019" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2813082002</t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2020" t="inlineStr">
+        <is>
+          <t>02:46</t>
+        </is>
+      </c>
+      <c r="C2020" t="inlineStr">
+        <is>
+          <t>Princess Nokia</t>
+        </is>
+      </c>
+      <c r="D2020" t="inlineStr">
+        <is>
+          <t>Drop Dead Gorgeous</t>
+        </is>
+      </c>
+      <c r="E2020" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2020" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3396663201</t>
+        </is>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2021" t="inlineStr">
+        <is>
+          <t>02:27</t>
+        </is>
+      </c>
+      <c r="C2021" t="inlineStr">
+        <is>
+          <t>Mystery Jets</t>
+        </is>
+      </c>
+      <c r="D2021" t="inlineStr">
+        <is>
+          <t>Young Love (feat. Laura Marling)</t>
+        </is>
+      </c>
+      <c r="E2021" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2021" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/794579</t>
+        </is>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2022" t="inlineStr">
+        <is>
+          <t>02:19</t>
+        </is>
+      </c>
+      <c r="C2022" t="inlineStr">
+        <is>
+          <t>Gilla Band</t>
+        </is>
+      </c>
+      <c r="D2022" t="inlineStr">
+        <is>
+          <t>Going Norway</t>
+        </is>
+      </c>
+      <c r="E2022" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2022" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/755427892</t>
+        </is>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2023" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C2023" t="inlineStr">
+        <is>
+          <t>E-Z Rollers</t>
+        </is>
+      </c>
+      <c r="D2023" t="inlineStr">
+        <is>
+          <t>Walk This Land</t>
+        </is>
+      </c>
+      <c r="E2023" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2023" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3912143</t>
+        </is>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2024" t="inlineStr">
+        <is>
+          <t>02:01</t>
+        </is>
+      </c>
+      <c r="C2024" t="inlineStr">
+        <is>
+          <t>Amy Winehouse</t>
+        </is>
+      </c>
+      <c r="D2024" t="inlineStr">
+        <is>
+          <t>In My Bed</t>
+        </is>
+      </c>
+      <c r="E2024" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2024" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1758856797</t>
+        </is>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2025" t="inlineStr">
+        <is>
+          <t>01:57</t>
+        </is>
+      </c>
+      <c r="C2025" t="inlineStr">
+        <is>
+          <t>Echobelly</t>
+        </is>
+      </c>
+      <c r="D2025" t="inlineStr">
+        <is>
+          <t>Great Things</t>
+        </is>
+      </c>
+      <c r="E2025" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2025" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13161934</t>
+        </is>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2026" t="inlineStr">
+        <is>
+          <t>01:49</t>
+        </is>
+      </c>
+      <c r="C2026" t="inlineStr">
+        <is>
+          <t>The Stranglers</t>
+        </is>
+      </c>
+      <c r="D2026" t="inlineStr">
+        <is>
+          <t>No More Heroes</t>
+        </is>
+      </c>
+      <c r="E2026" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2026" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3177037</t>
+        </is>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2027" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="C2027" t="inlineStr">
+        <is>
+          <t>Chinese American Bear</t>
+        </is>
+      </c>
+      <c r="D2027" t="inlineStr">
+        <is>
+          <t>Turn Up The Radio (把收音机开大点)</t>
+        </is>
+      </c>
+      <c r="E2027" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2027" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3791903332</t>
+        </is>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2028" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="C2028" t="inlineStr">
+        <is>
+          <t>The Orielles</t>
+        </is>
+      </c>
+      <c r="D2028" t="inlineStr">
+        <is>
+          <t>Bobbi's Second World</t>
+        </is>
+      </c>
+      <c r="E2028" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2028" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/576341922</t>
+        </is>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2029" t="inlineStr">
+        <is>
+          <t>01:33</t>
+        </is>
+      </c>
+      <c r="C2029" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="D2029" t="inlineStr">
+        <is>
+          <t>Everything Is Everything</t>
+        </is>
+      </c>
+      <c r="E2029" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2029" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3088930</t>
+        </is>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2030" t="inlineStr">
+        <is>
+          <t>01:20</t>
+        </is>
+      </c>
+      <c r="C2030" t="inlineStr">
+        <is>
+          <t>Nirvana</t>
+        </is>
+      </c>
+      <c r="D2030" t="inlineStr">
+        <is>
+          <t>Sliver</t>
+        </is>
+      </c>
+      <c r="E2030" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2030" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/529900461</t>
+        </is>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2031" t="inlineStr">
+        <is>
+          <t>00:59</t>
+        </is>
+      </c>
+      <c r="C2031" t="inlineStr">
+        <is>
+          <t>Madness</t>
+        </is>
+      </c>
+      <c r="D2031" t="inlineStr">
+        <is>
+          <t>One Step Beyond</t>
+        </is>
+      </c>
+      <c r="E2031" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2031" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3069857841</t>
+        </is>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2032" t="inlineStr">
+        <is>
+          <t>00:46</t>
+        </is>
+      </c>
+      <c r="C2032" t="inlineStr">
+        <is>
+          <t>The Mysterines</t>
+        </is>
+      </c>
+      <c r="D2032" t="inlineStr">
+        <is>
+          <t>Love's Not Enough</t>
+        </is>
+      </c>
+      <c r="E2032" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2032" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1800725527</t>
+        </is>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2033" t="inlineStr">
+        <is>
+          <t>00:13</t>
+        </is>
+      </c>
+      <c r="C2033" t="inlineStr">
+        <is>
+          <t>Sunstack Jones</t>
+        </is>
+      </c>
+      <c r="D2033" t="inlineStr">
+        <is>
+          <t>Make Your Own Way Out</t>
+        </is>
+      </c>
+      <c r="E2033" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2033" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3984051261</t>
+        </is>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B2034" t="inlineStr">
+        <is>
+          <t>00:01</t>
+        </is>
+      </c>
+      <c r="C2034" t="inlineStr">
+        <is>
+          <t>Buzzcocks</t>
+        </is>
+      </c>
+      <c r="D2034" t="inlineStr">
+        <is>
+          <t>Promises</t>
+        </is>
+      </c>
+      <c r="E2034" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2034" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/658922022</t>
         </is>
       </c>
     </row>
@@ -63340,6 +67436,134 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1904" r:id="rId1903"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1905" r:id="rId1904"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1906" r:id="rId1905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1907" r:id="rId1906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1908" r:id="rId1907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1909" r:id="rId1908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1910" r:id="rId1909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1911" r:id="rId1910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1912" r:id="rId1911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1913" r:id="rId1912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1914" r:id="rId1913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1915" r:id="rId1914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1916" r:id="rId1915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1917" r:id="rId1916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1918" r:id="rId1917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1919" r:id="rId1918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1920" r:id="rId1919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1921" r:id="rId1920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1922" r:id="rId1921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1923" r:id="rId1922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1924" r:id="rId1923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1925" r:id="rId1924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1926" r:id="rId1925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1927" r:id="rId1926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1928" r:id="rId1927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1929" r:id="rId1928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1930" r:id="rId1929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1931" r:id="rId1930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1932" r:id="rId1931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1933" r:id="rId1932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1934" r:id="rId1933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1935" r:id="rId1934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1936" r:id="rId1935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1937" r:id="rId1936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1938" r:id="rId1937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1939" r:id="rId1938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1940" r:id="rId1939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1941" r:id="rId1940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1942" r:id="rId1941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1943" r:id="rId1942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1944" r:id="rId1943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1945" r:id="rId1944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1946" r:id="rId1945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1947" r:id="rId1946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1948" r:id="rId1947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1949" r:id="rId1948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1950" r:id="rId1949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1951" r:id="rId1950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1952" r:id="rId1951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1953" r:id="rId1952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1954" r:id="rId1953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1955" r:id="rId1954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1956" r:id="rId1955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1957" r:id="rId1956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1958" r:id="rId1957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1959" r:id="rId1958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1960" r:id="rId1959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1961" r:id="rId1960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1962" r:id="rId1961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1963" r:id="rId1962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1964" r:id="rId1963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1965" r:id="rId1964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1966" r:id="rId1965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1967" r:id="rId1966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1968" r:id="rId1967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1969" r:id="rId1968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1970" r:id="rId1969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1971" r:id="rId1970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1972" r:id="rId1971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1973" r:id="rId1972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1974" r:id="rId1973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1975" r:id="rId1974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1976" r:id="rId1975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1977" r:id="rId1976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1978" r:id="rId1977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1979" r:id="rId1978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1980" r:id="rId1979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1981" r:id="rId1980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1982" r:id="rId1981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1983" r:id="rId1982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1984" r:id="rId1983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1985" r:id="rId1984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1986" r:id="rId1985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1987" r:id="rId1986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1988" r:id="rId1987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1989" r:id="rId1988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1990" r:id="rId1989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1991" r:id="rId1990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1992" r:id="rId1991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1993" r:id="rId1992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1994" r:id="rId1993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1995" r:id="rId1994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1996" r:id="rId1995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1997" r:id="rId1996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1998" r:id="rId1997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1999" r:id="rId1998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2000" r:id="rId1999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2001" r:id="rId2000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2002" r:id="rId2001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2003" r:id="rId2002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2004" r:id="rId2003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2005" r:id="rId2004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2006" r:id="rId2005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2007" r:id="rId2006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2008" r:id="rId2007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2009" r:id="rId2008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2010" r:id="rId2009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2011" r:id="rId2010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2012" r:id="rId2011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2013" r:id="rId2012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2014" r:id="rId2013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2015" r:id="rId2014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2016" r:id="rId2015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2017" r:id="rId2016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2018" r:id="rId2017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2019" r:id="rId2018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2020" r:id="rId2019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2021" r:id="rId2020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2022" r:id="rId2021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2023" r:id="rId2022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2024" r:id="rId2023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2025" r:id="rId2024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2026" r:id="rId2025"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2027" r:id="rId2026"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2028" r:id="rId2027"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2029" r:id="rId2028"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2030" r:id="rId2029"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2031" r:id="rId2030"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2032" r:id="rId2031"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2033" r:id="rId2032"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2034" r:id="rId2033"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/BBC6 Music Log.xlsx
+++ b/output/BBC6 Music Log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2034"/>
+  <dimension ref="A1:F2148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -65526,6 +65526,3654 @@
       <c r="F2034" s="2" t="inlineStr">
         <is>
           <t>https://www.deezer.com/track/658922022</t>
+        </is>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2035" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="C2035" t="inlineStr">
+        <is>
+          <t>Calendar Girls Original London Cast</t>
+        </is>
+      </c>
+      <c r="D2035" t="inlineStr">
+        <is>
+          <t>Dare</t>
+        </is>
+      </c>
+      <c r="E2035" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2035" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/468261602</t>
+        </is>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2036" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
+      <c r="C2036" t="inlineStr">
+        <is>
+          <t>Gorillaz</t>
+        </is>
+      </c>
+      <c r="D2036" t="inlineStr">
+        <is>
+          <t>Clint Eastwood</t>
+        </is>
+      </c>
+      <c r="E2036" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2036" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/77528562</t>
+        </is>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2037" t="inlineStr">
+        <is>
+          <t>19:37</t>
+        </is>
+      </c>
+      <c r="C2037" t="inlineStr">
+        <is>
+          <t>New Order</t>
+        </is>
+      </c>
+      <c r="D2037" t="inlineStr">
+        <is>
+          <t>Blue Monday 1988 (Michael Johnson 12'' Remix)</t>
+        </is>
+      </c>
+      <c r="E2037" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2037" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3092593051</t>
+        </is>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2038" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="C2038" t="inlineStr">
+        <is>
+          <t>Klaxons</t>
+        </is>
+      </c>
+      <c r="D2038" t="inlineStr">
+        <is>
+          <t>Gravity's Rainbow (Soulwax Remix)</t>
+        </is>
+      </c>
+      <c r="E2038" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2038" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2458812625</t>
+        </is>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2039" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="C2039" t="inlineStr">
+        <is>
+          <t>Yeah Yeah Yeahs</t>
+        </is>
+      </c>
+      <c r="D2039" t="inlineStr">
+        <is>
+          <t>Heads Will Roll (A-Trak Remix)</t>
+        </is>
+      </c>
+      <c r="E2039" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2039" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1117954742</t>
+        </is>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2040" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="C2040" t="inlineStr">
+        <is>
+          <t>Confidence Man</t>
+        </is>
+      </c>
+      <c r="D2040" t="inlineStr">
+        <is>
+          <t>I CAN'T LOSE YOU</t>
+        </is>
+      </c>
+      <c r="E2040" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2040" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2823518822</t>
+        </is>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2041" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="C2041" t="inlineStr">
+        <is>
+          <t>Fcukers</t>
+        </is>
+      </c>
+      <c r="D2041" t="inlineStr">
+        <is>
+          <t>if you wanna party, come over to my house</t>
+        </is>
+      </c>
+      <c r="E2041" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2041" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3772064462</t>
+        </is>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2042" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="C2042" t="inlineStr">
+        <is>
+          <t>Justice</t>
+        </is>
+      </c>
+      <c r="D2042" t="inlineStr">
+        <is>
+          <t>D.A.N.C.E.</t>
+        </is>
+      </c>
+      <c r="E2042" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2042" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/10284847</t>
+        </is>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2043" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="C2043" t="inlineStr">
+        <is>
+          <t>Mason &amp; Princess Superstar</t>
+        </is>
+      </c>
+      <c r="D2043" t="inlineStr">
+        <is>
+          <t>Perfect (Exceeder)</t>
+        </is>
+      </c>
+      <c r="E2043" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2043" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1041079192</t>
+        </is>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2044" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="C2044" t="inlineStr">
+        <is>
+          <t>Wet Leg</t>
+        </is>
+      </c>
+      <c r="D2044" t="inlineStr">
+        <is>
+          <t>Mangetout (The Dare Remix)</t>
+        </is>
+      </c>
+      <c r="E2044" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2044" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3813644832</t>
+        </is>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2045" t="inlineStr">
+        <is>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="C2045" t="inlineStr">
+        <is>
+          <t>Baxter Dury</t>
+        </is>
+      </c>
+      <c r="D2045" t="inlineStr">
+        <is>
+          <t>Allbarone</t>
+        </is>
+      </c>
+      <c r="E2045" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2045" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3951796961</t>
+        </is>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2046" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="C2046" t="inlineStr">
+        <is>
+          <t>LCD Soundsystem</t>
+        </is>
+      </c>
+      <c r="D2046" t="inlineStr">
+        <is>
+          <t>Home (Tom Sharkett Edit)</t>
+        </is>
+      </c>
+      <c r="E2046" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2046" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3413335541</t>
+        </is>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2047" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="C2047" t="inlineStr">
+        <is>
+          <t>Hot Chip</t>
+        </is>
+      </c>
+      <c r="D2047" t="inlineStr">
+        <is>
+          <t>Over and Over</t>
+        </is>
+      </c>
+      <c r="E2047" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2047" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/376022571</t>
+        </is>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2048" t="inlineStr">
+        <is>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="C2048" t="inlineStr">
+        <is>
+          <t>Dolly Parton</t>
+        </is>
+      </c>
+      <c r="D2048" t="inlineStr">
+        <is>
+          <t>Why'd You Come In Here Lookin' Like That</t>
+        </is>
+      </c>
+      <c r="E2048" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2048" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1056580</t>
+        </is>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2049" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="C2049" t="inlineStr">
+        <is>
+          <t>Dolly Parton</t>
+        </is>
+      </c>
+      <c r="D2049" t="inlineStr">
+        <is>
+          <t>9 to 5</t>
+        </is>
+      </c>
+      <c r="E2049" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2049" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/992937</t>
+        </is>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2050" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="C2050" t="inlineStr">
+        <is>
+          <t>Dolly Parton</t>
+        </is>
+      </c>
+      <c r="D2050" t="inlineStr">
+        <is>
+          <t>Love Is Like A Butterfly</t>
+        </is>
+      </c>
+      <c r="E2050" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2050" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/75388986</t>
+        </is>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2051" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="C2051" t="inlineStr">
+        <is>
+          <t>Dolly Parton</t>
+        </is>
+      </c>
+      <c r="D2051" t="inlineStr">
+        <is>
+          <t>Coat Of Many Colors</t>
+        </is>
+      </c>
+      <c r="E2051" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2051" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/15641218</t>
+        </is>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2052" t="inlineStr">
+        <is>
+          <t>18:23</t>
+        </is>
+      </c>
+      <c r="C2052" t="inlineStr">
+        <is>
+          <t>Dolly Parton</t>
+        </is>
+      </c>
+      <c r="D2052" t="inlineStr">
+        <is>
+          <t>Jolene</t>
+        </is>
+      </c>
+      <c r="E2052" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2052" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/114422238</t>
+        </is>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2053" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="C2053" t="inlineStr">
+        <is>
+          <t>Dolly Parton</t>
+        </is>
+      </c>
+      <c r="D2053" t="inlineStr">
+        <is>
+          <t>My Tennessee Mountain Home</t>
+        </is>
+      </c>
+      <c r="E2053" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2053" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/8035639</t>
+        </is>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2054" t="inlineStr">
+        <is>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="C2054" t="inlineStr">
+        <is>
+          <t>Dolly Parton</t>
+        </is>
+      </c>
+      <c r="D2054" t="inlineStr">
+        <is>
+          <t>I Will Always Love You</t>
+        </is>
+      </c>
+      <c r="E2054" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2054" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/567771</t>
+        </is>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2055" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="C2055" t="inlineStr">
+        <is>
+          <t>Dolly Parton</t>
+        </is>
+      </c>
+      <c r="D2055" t="inlineStr">
+        <is>
+          <t>Dumb Blonde</t>
+        </is>
+      </c>
+      <c r="E2055" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2055" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/587696062</t>
+        </is>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2056" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="C2056" t="inlineStr">
+        <is>
+          <t>Sir Richard Bishop</t>
+        </is>
+      </c>
+      <c r="D2056" t="inlineStr">
+        <is>
+          <t>Finger, Tennessee</t>
+        </is>
+      </c>
+      <c r="E2056" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2056" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3949817381</t>
+        </is>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2057" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="C2057" t="inlineStr">
+        <is>
+          <t>The Beatles &amp; Tony Sheridan</t>
+        </is>
+      </c>
+      <c r="D2057" t="inlineStr">
+        <is>
+          <t>My Bonnie</t>
+        </is>
+      </c>
+      <c r="E2057" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2057" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3668065912</t>
+        </is>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2058" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="C2058" t="inlineStr">
+        <is>
+          <t>SUEP</t>
+        </is>
+      </c>
+      <c r="D2058" t="inlineStr">
+        <is>
+          <t>Fornever</t>
+        </is>
+      </c>
+      <c r="E2058" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2058" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3610977492</t>
+        </is>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2059" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="C2059" t="inlineStr">
+        <is>
+          <t>The Puffs</t>
+        </is>
+      </c>
+      <c r="D2059" t="inlineStr">
+        <is>
+          <t>I Only Cry Once a Day Now</t>
+        </is>
+      </c>
+      <c r="E2059" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2059" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1734150467</t>
+        </is>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2060" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="C2060" t="inlineStr">
+        <is>
+          <t>Arab Strap</t>
+        </is>
+      </c>
+      <c r="D2060" t="inlineStr">
+        <is>
+          <t>You You You</t>
+        </is>
+      </c>
+      <c r="E2060" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2060" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2625857872</t>
+        </is>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2061" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C2061" t="inlineStr">
+        <is>
+          <t>Funkadelic</t>
+        </is>
+      </c>
+      <c r="D2061" t="inlineStr">
+        <is>
+          <t>Baby I Owe You Something Good</t>
+        </is>
+      </c>
+      <c r="E2061" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2061" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1551920552</t>
+        </is>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2062" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="C2062" t="inlineStr">
+        <is>
+          <t>Maximilian</t>
+        </is>
+      </c>
+      <c r="D2062" t="inlineStr">
+        <is>
+          <t>Rest Your Head</t>
+        </is>
+      </c>
+      <c r="E2062" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2062" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3808164622</t>
+        </is>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2063" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="C2063" t="inlineStr">
+        <is>
+          <t>Elliott Smith</t>
+        </is>
+      </c>
+      <c r="D2063" t="inlineStr">
+        <is>
+          <t>Pretty (Ugly Before)</t>
+        </is>
+      </c>
+      <c r="E2063" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2063" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3434924581</t>
+        </is>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2064" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="C2064" t="inlineStr">
+        <is>
+          <t>Andy Williams</t>
+        </is>
+      </c>
+      <c r="D2064" t="inlineStr">
+        <is>
+          <t>Moon River</t>
+        </is>
+      </c>
+      <c r="E2064" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2064" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1080849</t>
+        </is>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2065" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="C2065" t="inlineStr">
+        <is>
+          <t>Masal &amp; Emma Anderson</t>
+        </is>
+      </c>
+      <c r="D2065" t="inlineStr">
+        <is>
+          <t>Pause the Rain</t>
+        </is>
+      </c>
+      <c r="E2065" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2065" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3951449811</t>
+        </is>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2066" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="C2066" t="inlineStr">
+        <is>
+          <t>Pomelo</t>
+        </is>
+      </c>
+      <c r="D2066" t="inlineStr">
+        <is>
+          <t>Nasty Sauce</t>
+        </is>
+      </c>
+      <c r="E2066" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2066" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3899826251</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2067" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="C2067" t="inlineStr">
+        <is>
+          <t>Homer</t>
+        </is>
+      </c>
+      <c r="D2067" t="inlineStr">
+        <is>
+          <t>The Love and the Laughter</t>
+        </is>
+      </c>
+      <c r="E2067" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2067" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3988225791</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2068" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="C2068" t="inlineStr">
+        <is>
+          <t>Shaking Hand</t>
+        </is>
+      </c>
+      <c r="D2068" t="inlineStr">
+        <is>
+          <t>The Shining</t>
+        </is>
+      </c>
+      <c r="E2068" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2068" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3947964391</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2069" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="C2069" t="inlineStr">
+        <is>
+          <t>Swapmeet</t>
+        </is>
+      </c>
+      <c r="D2069" t="inlineStr">
+        <is>
+          <t>2 C U</t>
+        </is>
+      </c>
+      <c r="E2069" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2069" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3923146921</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2070" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="C2070" t="inlineStr">
+        <is>
+          <t>Gurriers</t>
+        </is>
+      </c>
+      <c r="D2070" t="inlineStr">
+        <is>
+          <t>Nobody's Coming to Save You</t>
+        </is>
+      </c>
+      <c r="E2070" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2070" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3964742221</t>
+        </is>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2071" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C2071" t="inlineStr">
+        <is>
+          <t>Panic Shack</t>
+        </is>
+      </c>
+      <c r="D2071" t="inlineStr">
+        <is>
+          <t>Grin &amp; Bear It</t>
+        </is>
+      </c>
+      <c r="E2071" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2071" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3996752811</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2072" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="C2072" t="inlineStr">
+        <is>
+          <t>The Auteurs</t>
+        </is>
+      </c>
+      <c r="D2072" t="inlineStr">
+        <is>
+          <t>Lenny Valentino</t>
+        </is>
+      </c>
+      <c r="E2072" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2072" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3132886</t>
+        </is>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2073" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="C2073" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="D2073" t="inlineStr">
+        <is>
+          <t>Twilight Galaxy</t>
+        </is>
+      </c>
+      <c r="E2073" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2073" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1758502957</t>
+        </is>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2074" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="C2074" t="inlineStr">
+        <is>
+          <t>Broken Social Scene</t>
+        </is>
+      </c>
+      <c r="D2074" t="inlineStr">
+        <is>
+          <t>Only The Good I Keep</t>
+        </is>
+      </c>
+      <c r="E2074" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2074" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3783871562</t>
+        </is>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2075" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="C2075" t="inlineStr">
+        <is>
+          <t>Broken Social Scene</t>
+        </is>
+      </c>
+      <c r="D2075" t="inlineStr">
+        <is>
+          <t>Anthems for a Seventeen Year-Old Girl</t>
+        </is>
+      </c>
+      <c r="E2075" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2075" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/425553892</t>
+        </is>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2076" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="C2076" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="D2076" t="inlineStr">
+        <is>
+          <t>Crush Forever</t>
+        </is>
+      </c>
+      <c r="E2076" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2076" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3720389782</t>
+        </is>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2077" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="C2077" t="inlineStr">
+        <is>
+          <t>MOULD</t>
+        </is>
+      </c>
+      <c r="D2077" t="inlineStr">
+        <is>
+          <t>Lucid</t>
+        </is>
+      </c>
+      <c r="E2077" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2077" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3966177251</t>
+        </is>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2078" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="C2078" t="inlineStr">
+        <is>
+          <t>Young Fathers</t>
+        </is>
+      </c>
+      <c r="D2078" t="inlineStr">
+        <is>
+          <t>Get Up</t>
+        </is>
+      </c>
+      <c r="E2078" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2078" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/71708102</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2079" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="C2079" t="inlineStr">
+        <is>
+          <t>Wet Leg</t>
+        </is>
+      </c>
+      <c r="D2079" t="inlineStr">
+        <is>
+          <t>Angelica</t>
+        </is>
+      </c>
+      <c r="E2079" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2079" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1549197772</t>
+        </is>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2080" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="C2080" t="inlineStr">
+        <is>
+          <t>Goldfrapp</t>
+        </is>
+      </c>
+      <c r="D2080" t="inlineStr">
+        <is>
+          <t>Strict Machine</t>
+        </is>
+      </c>
+      <c r="E2080" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2080" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3786218392</t>
+        </is>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2081" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="C2081" t="inlineStr">
+        <is>
+          <t>The Stone Roses</t>
+        </is>
+      </c>
+      <c r="D2081" t="inlineStr">
+        <is>
+          <t>Driving South</t>
+        </is>
+      </c>
+      <c r="E2081" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2081" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2457805</t>
+        </is>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2082" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="C2082" t="inlineStr">
+        <is>
+          <t>Perfume Genius</t>
+        </is>
+      </c>
+      <c r="D2082" t="inlineStr">
+        <is>
+          <t>Queen</t>
+        </is>
+      </c>
+      <c r="E2082" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2082" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/85496472</t>
+        </is>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2083" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="C2083" t="inlineStr">
+        <is>
+          <t>SAULT</t>
+        </is>
+      </c>
+      <c r="D2083" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="E2083" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2083" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1076612752</t>
+        </is>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2084" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="C2084" t="inlineStr">
+        <is>
+          <t>Roxy Music</t>
+        </is>
+      </c>
+      <c r="D2084" t="inlineStr">
+        <is>
+          <t>Virginia Plain</t>
+        </is>
+      </c>
+      <c r="E2084" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2084" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3134800</t>
+        </is>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2085" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="C2085" t="inlineStr">
+        <is>
+          <t>Klaxons</t>
+        </is>
+      </c>
+      <c r="D2085" t="inlineStr">
+        <is>
+          <t>Gravity's Rainbow</t>
+        </is>
+      </c>
+      <c r="E2085" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2085" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1157382</t>
+        </is>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2086" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="C2086" t="inlineStr">
+        <is>
+          <t>The Who</t>
+        </is>
+      </c>
+      <c r="D2086" t="inlineStr">
+        <is>
+          <t>Baba O'Riley</t>
+        </is>
+      </c>
+      <c r="E2086" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2086" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2121805</t>
+        </is>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2087" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="C2087" t="inlineStr">
+        <is>
+          <t>Unknown Mortal Orchestra</t>
+        </is>
+      </c>
+      <c r="D2087" t="inlineStr">
+        <is>
+          <t>Swim and Sleep (Like A Shark)</t>
+        </is>
+      </c>
+      <c r="E2087" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2087" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2524364301</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2088" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="C2088" t="inlineStr">
+        <is>
+          <t>Albert King &amp; Stevie Ray Vaughan</t>
+        </is>
+      </c>
+      <c r="D2088" t="inlineStr">
+        <is>
+          <t>Pride And Joy</t>
+        </is>
+      </c>
+      <c r="E2088" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2088" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4123156</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2089" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="C2089" t="inlineStr">
+        <is>
+          <t>B.B. King</t>
+        </is>
+      </c>
+      <c r="D2089" t="inlineStr">
+        <is>
+          <t>Blues Man</t>
+        </is>
+      </c>
+      <c r="E2089" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2089" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2181387</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2090" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="C2090" t="inlineStr">
+        <is>
+          <t>Muddy Waters</t>
+        </is>
+      </c>
+      <c r="D2090" t="inlineStr">
+        <is>
+          <t>The Blues Had A Baby And They Named It Rock And Roll</t>
+        </is>
+      </c>
+      <c r="E2090" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2090" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/595069</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2091" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="C2091" t="inlineStr">
+        <is>
+          <t>Beth Orton</t>
+        </is>
+      </c>
+      <c r="D2091" t="inlineStr">
+        <is>
+          <t>Concrete Sky</t>
+        </is>
+      </c>
+      <c r="E2091" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2091" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3099050</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2092" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="C2092" t="inlineStr">
+        <is>
+          <t>Melanie Baker</t>
+        </is>
+      </c>
+      <c r="D2092" t="inlineStr">
+        <is>
+          <t>Real Life</t>
+        </is>
+      </c>
+      <c r="E2092" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2092" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3866915021</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2093" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="C2093" t="inlineStr">
+        <is>
+          <t>Fleetwood Mac</t>
+        </is>
+      </c>
+      <c r="D2093" t="inlineStr">
+        <is>
+          <t>Albatross</t>
+        </is>
+      </c>
+      <c r="E2093" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2093" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/926674352</t>
+        </is>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2094" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="C2094" t="inlineStr">
+        <is>
+          <t>The Chemical Brothers</t>
+        </is>
+      </c>
+      <c r="D2094" t="inlineStr">
+        <is>
+          <t>Asleep From Day</t>
+        </is>
+      </c>
+      <c r="E2094" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2094" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3135032</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2095" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="C2095" t="inlineStr">
+        <is>
+          <t>The Concretes</t>
+        </is>
+      </c>
+      <c r="D2095" t="inlineStr">
+        <is>
+          <t>You Can't Hurry Love</t>
+        </is>
+      </c>
+      <c r="E2095" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2095" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/61530598</t>
+        </is>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2096" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="C2096" t="inlineStr">
+        <is>
+          <t>Joy Division</t>
+        </is>
+      </c>
+      <c r="D2096" t="inlineStr">
+        <is>
+          <t>Digital</t>
+        </is>
+      </c>
+      <c r="E2096" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2096" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/741235352</t>
+        </is>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2097" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="C2097" t="inlineStr">
+        <is>
+          <t>Bloc Party</t>
+        </is>
+      </c>
+      <c r="D2097" t="inlineStr">
+        <is>
+          <t>Coming On Strong</t>
+        </is>
+      </c>
+      <c r="E2097" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2097" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3997130921</t>
+        </is>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2098" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="C2098" t="inlineStr">
+        <is>
+          <t>Antony Szmierek</t>
+        </is>
+      </c>
+      <c r="D2098" t="inlineStr">
+        <is>
+          <t>Chalk</t>
+        </is>
+      </c>
+      <c r="E2098" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2098" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3964755521</t>
+        </is>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2099" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="C2099" t="inlineStr">
+        <is>
+          <t>Beach House</t>
+        </is>
+      </c>
+      <c r="D2099" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E2099" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2099" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1137161792</t>
+        </is>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2100" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="C2100" t="inlineStr">
+        <is>
+          <t>Caribou</t>
+        </is>
+      </c>
+      <c r="D2100" t="inlineStr">
+        <is>
+          <t>Can't Do Without You</t>
+        </is>
+      </c>
+      <c r="E2100" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/79033808</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2101" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="C2101" t="inlineStr">
+        <is>
+          <t>Kelis</t>
+        </is>
+      </c>
+      <c r="D2101" t="inlineStr">
+        <is>
+          <t>Rumble</t>
+        </is>
+      </c>
+      <c r="E2101" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/75077916</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2102" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="C2102" t="inlineStr">
+        <is>
+          <t>Future Islands</t>
+        </is>
+      </c>
+      <c r="D2102" t="inlineStr">
+        <is>
+          <t>Seasons (Waiting On You)</t>
+        </is>
+      </c>
+      <c r="E2102" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/75749474</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2103" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C2103" t="inlineStr">
+        <is>
+          <t>Yeah Yeah Yeahs</t>
+        </is>
+      </c>
+      <c r="D2103" t="inlineStr">
+        <is>
+          <t>Date With the Night</t>
+        </is>
+      </c>
+      <c r="E2103" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/417368922</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2104" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="C2104" t="inlineStr">
+        <is>
+          <t>Suede</t>
+        </is>
+      </c>
+      <c r="D2104" t="inlineStr">
+        <is>
+          <t>She's In Fashion</t>
+        </is>
+      </c>
+      <c r="E2104" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1207284612</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2105" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="C2105" t="inlineStr">
+        <is>
+          <t>Eaves Wilder</t>
+        </is>
+      </c>
+      <c r="D2105" t="inlineStr">
+        <is>
+          <t>The Great Plains</t>
+        </is>
+      </c>
+      <c r="E2105" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3722537652</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2106" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="C2106" t="inlineStr">
+        <is>
+          <t>Phyllis Dillon</t>
+        </is>
+      </c>
+      <c r="D2106" t="inlineStr">
+        <is>
+          <t>Woman Of The Ghetto</t>
+        </is>
+      </c>
+      <c r="E2106" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3786115522</t>
+        </is>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2107" t="inlineStr">
+        <is>
+          <t>07:16</t>
+        </is>
+      </c>
+      <c r="C2107" t="inlineStr">
+        <is>
+          <t>Small Faces</t>
+        </is>
+      </c>
+      <c r="D2107" t="inlineStr">
+        <is>
+          <t>Itchycoo Park</t>
+        </is>
+      </c>
+      <c r="E2107" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/75994742</t>
+        </is>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2108" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="C2108" t="inlineStr">
+        <is>
+          <t>Doves</t>
+        </is>
+      </c>
+      <c r="D2108" t="inlineStr">
+        <is>
+          <t>The Cedar Room</t>
+        </is>
+      </c>
+      <c r="E2108" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/5723510</t>
+        </is>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2109" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="C2109" t="inlineStr">
+        <is>
+          <t>Jane Weaver</t>
+        </is>
+      </c>
+      <c r="D2109" t="inlineStr">
+        <is>
+          <t>The Revolution Of Super Visions</t>
+        </is>
+      </c>
+      <c r="E2109" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2120069397</t>
+        </is>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2110" t="inlineStr">
+        <is>
+          <t>06:34</t>
+        </is>
+      </c>
+      <c r="C2110" t="inlineStr">
+        <is>
+          <t>The Rapture</t>
+        </is>
+      </c>
+      <c r="D2110" t="inlineStr">
+        <is>
+          <t>Get Myself Into It</t>
+        </is>
+      </c>
+      <c r="E2110" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/60723830</t>
+        </is>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2111" t="inlineStr">
+        <is>
+          <t>06:27</t>
+        </is>
+      </c>
+      <c r="C2111" t="inlineStr">
+        <is>
+          <t>Shannon Lay</t>
+        </is>
+      </c>
+      <c r="D2111" t="inlineStr">
+        <is>
+          <t>Past the Veil</t>
+        </is>
+      </c>
+      <c r="E2111" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3952256131</t>
+        </is>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2112" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="C2112" t="inlineStr">
+        <is>
+          <t>Sérgio Mendes</t>
+        </is>
+      </c>
+      <c r="D2112" t="inlineStr">
+        <is>
+          <t>Magalenha</t>
+        </is>
+      </c>
+      <c r="E2112" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1444380712</t>
+        </is>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2113" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="C2113" t="inlineStr">
+        <is>
+          <t>Grace Jones</t>
+        </is>
+      </c>
+      <c r="D2113" t="inlineStr">
+        <is>
+          <t>Slave To The Rhythm</t>
+        </is>
+      </c>
+      <c r="E2113" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1359248602</t>
+        </is>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2114" t="inlineStr">
+        <is>
+          <t>05:58</t>
+        </is>
+      </c>
+      <c r="C2114" t="inlineStr">
+        <is>
+          <t>Grace Jones</t>
+        </is>
+      </c>
+      <c r="D2114" t="inlineStr">
+        <is>
+          <t>Warm Leatherette</t>
+        </is>
+      </c>
+      <c r="E2114" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3551834</t>
+        </is>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2115" t="inlineStr">
+        <is>
+          <t>05:54</t>
+        </is>
+      </c>
+      <c r="C2115" t="inlineStr">
+        <is>
+          <t>Gorillaz</t>
+        </is>
+      </c>
+      <c r="D2115" t="inlineStr">
+        <is>
+          <t>Charger (feat. Grace Jones)</t>
+        </is>
+      </c>
+      <c r="E2115" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/354133271</t>
+        </is>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2116" t="inlineStr">
+        <is>
+          <t>05:48</t>
+        </is>
+      </c>
+      <c r="C2116" t="inlineStr">
+        <is>
+          <t>Grace Jones</t>
+        </is>
+      </c>
+      <c r="D2116" t="inlineStr">
+        <is>
+          <t>My Jamaican Guy</t>
+        </is>
+      </c>
+      <c r="E2116" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/541910412</t>
+        </is>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2117" t="inlineStr">
+        <is>
+          <t>05:38</t>
+        </is>
+      </c>
+      <c r="C2117" t="inlineStr">
+        <is>
+          <t>Grace Jones</t>
+        </is>
+      </c>
+      <c r="D2117" t="inlineStr">
+        <is>
+          <t>Nightclubbing</t>
+        </is>
+      </c>
+      <c r="E2117" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1359256422</t>
+        </is>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2118" t="inlineStr">
+        <is>
+          <t>05:27</t>
+        </is>
+      </c>
+      <c r="C2118" t="inlineStr">
+        <is>
+          <t>The Streets</t>
+        </is>
+      </c>
+      <c r="D2118" t="inlineStr">
+        <is>
+          <t>Same Old Thing</t>
+        </is>
+      </c>
+      <c r="E2118" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/6112949</t>
+        </is>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2119" t="inlineStr">
+        <is>
+          <t>05:09</t>
+        </is>
+      </c>
+      <c r="C2119" t="inlineStr">
+        <is>
+          <t>Neal Francis</t>
+        </is>
+      </c>
+      <c r="D2119" t="inlineStr">
+        <is>
+          <t>Hide</t>
+        </is>
+      </c>
+      <c r="E2119" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3938844621</t>
+        </is>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2120" t="inlineStr">
+        <is>
+          <t>05:01</t>
+        </is>
+      </c>
+      <c r="C2120" t="inlineStr">
+        <is>
+          <t>Phoebe Bridgers</t>
+        </is>
+      </c>
+      <c r="D2120" t="inlineStr">
+        <is>
+          <t>Motion Sickness</t>
+        </is>
+      </c>
+      <c r="E2120" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/397301582</t>
+        </is>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2121" t="inlineStr">
+        <is>
+          <t>04:56</t>
+        </is>
+      </c>
+      <c r="C2121" t="inlineStr">
+        <is>
+          <t>Geese</t>
+        </is>
+      </c>
+      <c r="D2121" t="inlineStr">
+        <is>
+          <t>2122</t>
+        </is>
+      </c>
+      <c r="E2121" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3428529501</t>
+        </is>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2122" t="inlineStr">
+        <is>
+          <t>04:33</t>
+        </is>
+      </c>
+      <c r="C2122" t="inlineStr">
+        <is>
+          <t>PJ Harvey</t>
+        </is>
+      </c>
+      <c r="D2122" t="inlineStr">
+        <is>
+          <t>The Letter</t>
+        </is>
+      </c>
+      <c r="E2122" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2541654</t>
+        </is>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2123" t="inlineStr">
+        <is>
+          <t>04:23</t>
+        </is>
+      </c>
+      <c r="C2123" t="inlineStr">
+        <is>
+          <t>Ibibio Sound Machine</t>
+        </is>
+      </c>
+      <c r="D2123" t="inlineStr">
+        <is>
+          <t>The Chant (Iquo Isang)</t>
+        </is>
+      </c>
+      <c r="E2123" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3550775671</t>
+        </is>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2124" t="inlineStr">
+        <is>
+          <t>04:16</t>
+        </is>
+      </c>
+      <c r="C2124" t="inlineStr">
+        <is>
+          <t>The Cure</t>
+        </is>
+      </c>
+      <c r="D2124" t="inlineStr">
+        <is>
+          <t>Close To Me</t>
+        </is>
+      </c>
+      <c r="E2124" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/409670312</t>
+        </is>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2125" t="inlineStr">
+        <is>
+          <t>03:48</t>
+        </is>
+      </c>
+      <c r="C2125" t="inlineStr">
+        <is>
+          <t>Brass Construction</t>
+        </is>
+      </c>
+      <c r="D2125" t="inlineStr">
+        <is>
+          <t>Movin'</t>
+        </is>
+      </c>
+      <c r="E2125" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3404394</t>
+        </is>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2126" t="inlineStr">
+        <is>
+          <t>03:43</t>
+        </is>
+      </c>
+      <c r="C2126" t="inlineStr">
+        <is>
+          <t>Grace Jones</t>
+        </is>
+      </c>
+      <c r="D2126" t="inlineStr">
+        <is>
+          <t>Pull Up To The Bumper</t>
+        </is>
+      </c>
+      <c r="E2126" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1359256402</t>
+        </is>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2127" t="inlineStr">
+        <is>
+          <t>03:23</t>
+        </is>
+      </c>
+      <c r="C2127" t="inlineStr">
+        <is>
+          <t>Sade</t>
+        </is>
+      </c>
+      <c r="D2127" t="inlineStr">
+        <is>
+          <t>Paradise</t>
+        </is>
+      </c>
+      <c r="E2127" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1030652012</t>
+        </is>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2128" t="inlineStr">
+        <is>
+          <t>03:18</t>
+        </is>
+      </c>
+      <c r="C2128" t="inlineStr">
+        <is>
+          <t>Rilo Kiley</t>
+        </is>
+      </c>
+      <c r="D2128" t="inlineStr">
+        <is>
+          <t>Portions For Foxes</t>
+        </is>
+      </c>
+      <c r="E2128" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/787972</t>
+        </is>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2129" t="inlineStr">
+        <is>
+          <t>03:14</t>
+        </is>
+      </c>
+      <c r="C2129" t="inlineStr">
+        <is>
+          <t>The Smashing Pumpkins</t>
+        </is>
+      </c>
+      <c r="D2129" t="inlineStr">
+        <is>
+          <t>Siva</t>
+        </is>
+      </c>
+      <c r="E2129" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/15715616</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2130" t="inlineStr">
+        <is>
+          <t>03:10</t>
+        </is>
+      </c>
+      <c r="C2130" t="inlineStr">
+        <is>
+          <t>Aretha Franklin</t>
+        </is>
+      </c>
+      <c r="D2130" t="inlineStr">
+        <is>
+          <t>Respect</t>
+        </is>
+      </c>
+      <c r="E2130" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/904732</t>
+        </is>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2131" t="inlineStr">
+        <is>
+          <t>03:06</t>
+        </is>
+      </c>
+      <c r="C2131" t="inlineStr">
+        <is>
+          <t>Confidence Man</t>
+        </is>
+      </c>
+      <c r="D2131" t="inlineStr">
+        <is>
+          <t>Holiday</t>
+        </is>
+      </c>
+      <c r="E2131" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1902456757</t>
+        </is>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2132" t="inlineStr">
+        <is>
+          <t>02:55</t>
+        </is>
+      </c>
+      <c r="C2132" t="inlineStr">
+        <is>
+          <t>Dave &amp; Ansel Collins</t>
+        </is>
+      </c>
+      <c r="D2132" t="inlineStr">
+        <is>
+          <t>Monkey Spanner</t>
+        </is>
+      </c>
+      <c r="E2132" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3808685352</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2133" t="inlineStr">
+        <is>
+          <t>02:48</t>
+        </is>
+      </c>
+      <c r="C2133" t="inlineStr">
+        <is>
+          <t>Maximum Balloon &amp; Theophilus London</t>
+        </is>
+      </c>
+      <c r="D2133" t="inlineStr">
+        <is>
+          <t>Groove Me</t>
+        </is>
+      </c>
+      <c r="E2133" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1761490807</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2134" t="inlineStr">
+        <is>
+          <t>02:41</t>
+        </is>
+      </c>
+      <c r="C2134" t="inlineStr">
+        <is>
+          <t>Marshall Jefferson</t>
+        </is>
+      </c>
+      <c r="D2134" t="inlineStr">
+        <is>
+          <t>Move Your Body (The House Music Anthem)</t>
+        </is>
+      </c>
+      <c r="E2134" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1811060157</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2135" t="inlineStr">
+        <is>
+          <t>02:18</t>
+        </is>
+      </c>
+      <c r="C2135" t="inlineStr">
+        <is>
+          <t>SOPHIE</t>
+        </is>
+      </c>
+      <c r="D2135" t="inlineStr">
+        <is>
+          <t>BIPP</t>
+        </is>
+      </c>
+      <c r="E2135" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1054951722</t>
+        </is>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2136" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C2136" t="inlineStr">
+        <is>
+          <t>Little Dragon</t>
+        </is>
+      </c>
+      <c r="D2136" t="inlineStr">
+        <is>
+          <t>Best Friends</t>
+        </is>
+      </c>
+      <c r="E2136" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1760968737</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2137" t="inlineStr">
+        <is>
+          <t>02:01</t>
+        </is>
+      </c>
+      <c r="C2137" t="inlineStr">
+        <is>
+          <t>Funkadelic</t>
+        </is>
+      </c>
+      <c r="D2137" t="inlineStr">
+        <is>
+          <t>Can You Get To That</t>
+        </is>
+      </c>
+      <c r="E2137" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1551922352</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2138" t="inlineStr">
+        <is>
+          <t>01:56</t>
+        </is>
+      </c>
+      <c r="C2138" t="inlineStr">
+        <is>
+          <t>Alabama 3</t>
+        </is>
+      </c>
+      <c r="D2138" t="inlineStr">
+        <is>
+          <t>Woke Up This Morning</t>
+        </is>
+      </c>
+      <c r="E2138" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1645567962</t>
+        </is>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2139" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="C2139" t="inlineStr">
+        <is>
+          <t>The Staves</t>
+        </is>
+      </c>
+      <c r="D2139" t="inlineStr">
+        <is>
+          <t>All Now</t>
+        </is>
+      </c>
+      <c r="E2139" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2585545992</t>
+        </is>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2140" t="inlineStr">
+        <is>
+          <t>01:34</t>
+        </is>
+      </c>
+      <c r="C2140" t="inlineStr">
+        <is>
+          <t>Midlake</t>
+        </is>
+      </c>
+      <c r="D2140" t="inlineStr">
+        <is>
+          <t>Roscoe</t>
+        </is>
+      </c>
+      <c r="E2140" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/82746820</t>
+        </is>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2141" t="inlineStr">
+        <is>
+          <t>01:14</t>
+        </is>
+      </c>
+      <c r="C2141" t="inlineStr">
+        <is>
+          <t>DAG</t>
+        </is>
+      </c>
+      <c r="D2141" t="inlineStr">
+        <is>
+          <t>Righteous (City Pain)</t>
+        </is>
+      </c>
+      <c r="E2141" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1633950242</t>
+        </is>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2142" t="inlineStr">
+        <is>
+          <t>01:10</t>
+        </is>
+      </c>
+      <c r="C2142" t="inlineStr">
+        <is>
+          <t>White Denim</t>
+        </is>
+      </c>
+      <c r="D2142" t="inlineStr">
+        <is>
+          <t>Shanalala</t>
+        </is>
+      </c>
+      <c r="E2142" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2582849872</t>
+        </is>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2143" t="inlineStr">
+        <is>
+          <t>01:01</t>
+        </is>
+      </c>
+      <c r="C2143" t="inlineStr">
+        <is>
+          <t>Zero 7</t>
+        </is>
+      </c>
+      <c r="D2143" t="inlineStr">
+        <is>
+          <t>In The Waiting Line</t>
+        </is>
+      </c>
+      <c r="E2143" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3366891221</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2144" t="inlineStr">
+        <is>
+          <t>00:57</t>
+        </is>
+      </c>
+      <c r="C2144" t="inlineStr">
+        <is>
+          <t>Dave Brubeck</t>
+        </is>
+      </c>
+      <c r="D2144" t="inlineStr">
+        <is>
+          <t>Take Five</t>
+        </is>
+      </c>
+      <c r="E2144" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1031007</t>
+        </is>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2145" t="inlineStr">
+        <is>
+          <t>00:48</t>
+        </is>
+      </c>
+      <c r="C2145" t="inlineStr">
+        <is>
+          <t>Blood Orange</t>
+        </is>
+      </c>
+      <c r="D2145" t="inlineStr">
+        <is>
+          <t>Mind Loaded (feat. Caroline Polachek, Mustafa &amp; Lorde)</t>
+        </is>
+      </c>
+      <c r="E2145" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3450350151</t>
+        </is>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2146" t="inlineStr">
+        <is>
+          <t>00:17</t>
+        </is>
+      </c>
+      <c r="C2146" t="inlineStr">
+        <is>
+          <t>Julia Jacklin</t>
+        </is>
+      </c>
+      <c r="D2146" t="inlineStr">
+        <is>
+          <t>Pressure To Party</t>
+        </is>
+      </c>
+      <c r="E2146" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1982252007</t>
+        </is>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2147" t="inlineStr">
+        <is>
+          <t>00:09</t>
+        </is>
+      </c>
+      <c r="C2147" t="inlineStr">
+        <is>
+          <t>Jimmy Eat World</t>
+        </is>
+      </c>
+      <c r="D2147" t="inlineStr">
+        <is>
+          <t>Sweetness</t>
+        </is>
+      </c>
+      <c r="E2147" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/623714232</t>
+        </is>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B2148" t="inlineStr">
+        <is>
+          <t>00:01</t>
+        </is>
+      </c>
+      <c r="C2148" t="inlineStr">
+        <is>
+          <t>Cocteau Twins</t>
+        </is>
+      </c>
+      <c r="D2148" t="inlineStr">
+        <is>
+          <t>Musette And Drums</t>
+        </is>
+      </c>
+      <c r="E2148" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/105291630</t>
         </is>
       </c>
     </row>
@@ -67564,6 +71212,120 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2032" r:id="rId2031"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2033" r:id="rId2032"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2034" r:id="rId2033"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2035" r:id="rId2034"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2036" r:id="rId2035"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2037" r:id="rId2036"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2038" r:id="rId2037"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2039" r:id="rId2038"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2040" r:id="rId2039"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2041" r:id="rId2040"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2042" r:id="rId2041"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2043" r:id="rId2042"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2044" r:id="rId2043"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2045" r:id="rId2044"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2046" r:id="rId2045"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2047" r:id="rId2046"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2048" r:id="rId2047"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2049" r:id="rId2048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2050" r:id="rId2049"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2051" r:id="rId2050"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2052" r:id="rId2051"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2053" r:id="rId2052"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2054" r:id="rId2053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2055" r:id="rId2054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2056" r:id="rId2055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2057" r:id="rId2056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2058" r:id="rId2057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2059" r:id="rId2058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2060" r:id="rId2059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2061" r:id="rId2060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2062" r:id="rId2061"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2063" r:id="rId2062"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2064" r:id="rId2063"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2065" r:id="rId2064"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2066" r:id="rId2065"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2067" r:id="rId2066"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2068" r:id="rId2067"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2069" r:id="rId2068"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2070" r:id="rId2069"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2071" r:id="rId2070"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2072" r:id="rId2071"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2073" r:id="rId2072"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2074" r:id="rId2073"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2075" r:id="rId2074"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2076" r:id="rId2075"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2077" r:id="rId2076"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2078" r:id="rId2077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2079" r:id="rId2078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2080" r:id="rId2079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2081" r:id="rId2080"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2082" r:id="rId2081"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2083" r:id="rId2082"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2084" r:id="rId2083"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2085" r:id="rId2084"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2086" r:id="rId2085"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2087" r:id="rId2086"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2088" r:id="rId2087"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2089" r:id="rId2088"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2090" r:id="rId2089"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2091" r:id="rId2090"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2092" r:id="rId2091"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2093" r:id="rId2092"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2094" r:id="rId2093"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2095" r:id="rId2094"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2096" r:id="rId2095"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2097" r:id="rId2096"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2098" r:id="rId2097"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2099" r:id="rId2098"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2100" r:id="rId2099"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2101" r:id="rId2100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2102" r:id="rId2101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2103" r:id="rId2102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2104" r:id="rId2103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2105" r:id="rId2104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2106" r:id="rId2105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2107" r:id="rId2106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2108" r:id="rId2107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2109" r:id="rId2108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2110" r:id="rId2109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2111" r:id="rId2110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2112" r:id="rId2111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2113" r:id="rId2112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2114" r:id="rId2113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2115" r:id="rId2114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2116" r:id="rId2115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2117" r:id="rId2116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2118" r:id="rId2117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2119" r:id="rId2118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2120" r:id="rId2119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2121" r:id="rId2120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2122" r:id="rId2121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2123" r:id="rId2122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2124" r:id="rId2123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2125" r:id="rId2124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2126" r:id="rId2125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2127" r:id="rId2126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2128" r:id="rId2127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2129" r:id="rId2128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2130" r:id="rId2129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2131" r:id="rId2130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2132" r:id="rId2131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2133" r:id="rId2132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2134" r:id="rId2133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2135" r:id="rId2134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2136" r:id="rId2135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2137" r:id="rId2136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2138" r:id="rId2137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2139" r:id="rId2138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2140" r:id="rId2139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2141" r:id="rId2140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2142" r:id="rId2141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2143" r:id="rId2142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2144" r:id="rId2143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2145" r:id="rId2144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2146" r:id="rId2145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2147" r:id="rId2146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2148" r:id="rId2147"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/BBC6 Music Log.xlsx
+++ b/output/BBC6 Music Log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2148"/>
+  <dimension ref="A1:F2273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -69174,6 +69174,4006 @@
       <c r="F2148" s="2" t="inlineStr">
         <is>
           <t>https://www.deezer.com/track/105291630</t>
+        </is>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2149" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="C2149" t="inlineStr">
+        <is>
+          <t>Dave Clarkson</t>
+        </is>
+      </c>
+      <c r="D2149" t="inlineStr">
+        <is>
+          <t>Coastal Ghost Towns</t>
+        </is>
+      </c>
+      <c r="E2149" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3928805571</t>
+        </is>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2150" t="inlineStr">
+        <is>
+          <t>19:51</t>
+        </is>
+      </c>
+      <c r="C2150" t="inlineStr">
+        <is>
+          <t>Philip Jeck &amp; Chris Watson</t>
+        </is>
+      </c>
+      <c r="D2150" t="inlineStr">
+        <is>
+          <t>Beetroot Train</t>
+        </is>
+      </c>
+      <c r="E2150" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2272823017</t>
+        </is>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2151" t="inlineStr">
+        <is>
+          <t>19:37</t>
+        </is>
+      </c>
+      <c r="C2151" t="inlineStr">
+        <is>
+          <t>Robin Rimbaud</t>
+        </is>
+      </c>
+      <c r="D2151" t="inlineStr">
+        <is>
+          <t>Waterbrush</t>
+        </is>
+      </c>
+      <c r="E2151" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2416987</t>
+        </is>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2152" t="inlineStr">
+        <is>
+          <t>19:29</t>
+        </is>
+      </c>
+      <c r="C2152" t="inlineStr">
+        <is>
+          <t>Kayla Painter</t>
+        </is>
+      </c>
+      <c r="D2152" t="inlineStr">
+        <is>
+          <t>Where the Hollow Tree Grows</t>
+        </is>
+      </c>
+      <c r="E2152" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3758722992</t>
+        </is>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2153" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="C2153" t="inlineStr">
+        <is>
+          <t>Audio Obscura</t>
+        </is>
+      </c>
+      <c r="D2153" t="inlineStr">
+        <is>
+          <t>Hollowlands</t>
+        </is>
+      </c>
+      <c r="E2153" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2668593772</t>
+        </is>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2154" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="C2154" t="inlineStr">
+        <is>
+          <t>Kate Bush</t>
+        </is>
+      </c>
+      <c r="D2154" t="inlineStr">
+        <is>
+          <t>Running Up That Hill</t>
+        </is>
+      </c>
+      <c r="E2154" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2173954687</t>
+        </is>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2155" t="inlineStr">
+        <is>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="C2155" t="inlineStr">
+        <is>
+          <t>Kate Bush</t>
+        </is>
+      </c>
+      <c r="D2155" t="inlineStr">
+        <is>
+          <t>This Woman's Work</t>
+        </is>
+      </c>
+      <c r="E2155" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2175439197</t>
+        </is>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2156" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="C2156" t="inlineStr">
+        <is>
+          <t>Kate Bush</t>
+        </is>
+      </c>
+      <c r="D2156" t="inlineStr">
+        <is>
+          <t>Hello Earth</t>
+        </is>
+      </c>
+      <c r="E2156" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2175438827</t>
+        </is>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2157" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="C2157" t="inlineStr">
+        <is>
+          <t>Kate Bush</t>
+        </is>
+      </c>
+      <c r="D2157" t="inlineStr">
+        <is>
+          <t>Mrs. Bartolozzi</t>
+        </is>
+      </c>
+      <c r="E2157" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2175447437</t>
+        </is>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2158" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="C2158" t="inlineStr">
+        <is>
+          <t>Kate Bush</t>
+        </is>
+      </c>
+      <c r="D2158" t="inlineStr">
+        <is>
+          <t>James and the Cold Gun</t>
+        </is>
+      </c>
+      <c r="E2158" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2173947557</t>
+        </is>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2159" t="inlineStr">
+        <is>
+          <t>18:39</t>
+        </is>
+      </c>
+      <c r="C2159" t="inlineStr">
+        <is>
+          <t>Kate Bush</t>
+        </is>
+      </c>
+      <c r="D2159" t="inlineStr">
+        <is>
+          <t>The Man With The Child In His Eyes</t>
+        </is>
+      </c>
+      <c r="E2159" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2173947537</t>
+        </is>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2160" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="C2160" t="inlineStr">
+        <is>
+          <t>Kate Bush</t>
+        </is>
+      </c>
+      <c r="D2160" t="inlineStr">
+        <is>
+          <t>Cloudbusting</t>
+        </is>
+      </c>
+      <c r="E2160" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2173954727</t>
+        </is>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2161" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="C2161" t="inlineStr">
+        <is>
+          <t>Kate Bush</t>
+        </is>
+      </c>
+      <c r="D2161" t="inlineStr">
+        <is>
+          <t>King Of The Mountain</t>
+        </is>
+      </c>
+      <c r="E2161" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2175447407</t>
+        </is>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2162" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="C2162" t="inlineStr">
+        <is>
+          <t>Kate Bush</t>
+        </is>
+      </c>
+      <c r="D2162" t="inlineStr">
+        <is>
+          <t>Waking The Witch</t>
+        </is>
+      </c>
+      <c r="E2162" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2173954757</t>
+        </is>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2163" t="inlineStr">
+        <is>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="C2163" t="inlineStr">
+        <is>
+          <t>Kate Bush</t>
+        </is>
+      </c>
+      <c r="D2163" t="inlineStr">
+        <is>
+          <t>Experiment IV</t>
+        </is>
+      </c>
+      <c r="E2163" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3572584791</t>
+        </is>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2164" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="C2164" t="inlineStr">
+        <is>
+          <t>Kate Bush</t>
+        </is>
+      </c>
+      <c r="D2164" t="inlineStr">
+        <is>
+          <t>Kashka from Baghdad</t>
+        </is>
+      </c>
+      <c r="E2164" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2173954517</t>
+        </is>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2165" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="C2165" t="inlineStr">
+        <is>
+          <t>Kate Bush</t>
+        </is>
+      </c>
+      <c r="D2165" t="inlineStr">
+        <is>
+          <t>Wuthering Heights</t>
+        </is>
+      </c>
+      <c r="E2165" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2173947547</t>
+        </is>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2166" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="C2166" t="inlineStr">
+        <is>
+          <t>Naima Bock</t>
+        </is>
+      </c>
+      <c r="D2166" t="inlineStr">
+        <is>
+          <t>Kaley</t>
+        </is>
+      </c>
+      <c r="E2166" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2816401592</t>
+        </is>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2167" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="C2167" t="inlineStr">
+        <is>
+          <t>Jah Wobble &amp; Jon Klein</t>
+        </is>
+      </c>
+      <c r="D2167" t="inlineStr">
+        <is>
+          <t>Make It Stop</t>
+        </is>
+      </c>
+      <c r="E2167" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3961005061</t>
+        </is>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2168" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="C2168" t="inlineStr">
+        <is>
+          <t>Bob Dylan</t>
+        </is>
+      </c>
+      <c r="D2168" t="inlineStr">
+        <is>
+          <t>Jokerman</t>
+        </is>
+      </c>
+      <c r="E2168" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/70310224</t>
+        </is>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2169" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="C2169" t="inlineStr">
+        <is>
+          <t>Sam &amp; Dave</t>
+        </is>
+      </c>
+      <c r="D2169" t="inlineStr">
+        <is>
+          <t>Soul Man</t>
+        </is>
+      </c>
+      <c r="E2169" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3923661</t>
+        </is>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2170" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="C2170" t="inlineStr">
+        <is>
+          <t>Pictish Trail</t>
+        </is>
+      </c>
+      <c r="D2170" t="inlineStr">
+        <is>
+          <t>Battery Pack</t>
+        </is>
+      </c>
+      <c r="E2170" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3721805662</t>
+        </is>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2171" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="C2171" t="inlineStr">
+        <is>
+          <t>The Seeds</t>
+        </is>
+      </c>
+      <c r="D2171" t="inlineStr">
+        <is>
+          <t>Evil Hoodoo</t>
+        </is>
+      </c>
+      <c r="E2171" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/7822197</t>
+        </is>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2172" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="C2172" t="inlineStr">
+        <is>
+          <t>Judee Sill</t>
+        </is>
+      </c>
+      <c r="D2172" t="inlineStr">
+        <is>
+          <t>Jesus Was A Cross Maker</t>
+        </is>
+      </c>
+      <c r="E2172" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/753447</t>
+        </is>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2173" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="C2173" t="inlineStr">
+        <is>
+          <t>David McWilliams</t>
+        </is>
+      </c>
+      <c r="D2173" t="inlineStr">
+        <is>
+          <t>The Days Of Pearly Spencer</t>
+        </is>
+      </c>
+      <c r="E2173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/123174968</t>
+        </is>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2174" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="C2174" t="inlineStr">
+        <is>
+          <t>BAG</t>
+        </is>
+      </c>
+      <c r="D2174" t="inlineStr">
+        <is>
+          <t>Vessel Diaspora</t>
+        </is>
+      </c>
+      <c r="E2174" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3861804281</t>
+        </is>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2175" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="C2175" t="inlineStr">
+        <is>
+          <t>Pollyfromthedirt</t>
+        </is>
+      </c>
+      <c r="D2175" t="inlineStr">
+        <is>
+          <t>Sounds like hell</t>
+        </is>
+      </c>
+      <c r="E2175" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3866651511</t>
+        </is>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2176" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="C2176" t="inlineStr">
+        <is>
+          <t>Eartheater</t>
+        </is>
+      </c>
+      <c r="D2176" t="inlineStr">
+        <is>
+          <t>Paradise Rains</t>
+        </is>
+      </c>
+      <c r="E2176" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3990292091</t>
+        </is>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2177" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="C2177" t="inlineStr">
+        <is>
+          <t>Tyondai Braxton</t>
+        </is>
+      </c>
+      <c r="D2177" t="inlineStr">
+        <is>
+          <t>UnFS</t>
+        </is>
+      </c>
+      <c r="E2177" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3983260461</t>
+        </is>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2178" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="C2178" t="inlineStr">
+        <is>
+          <t>Fatoumata Diawara</t>
+        </is>
+      </c>
+      <c r="D2178" t="inlineStr">
+        <is>
+          <t>Sigui</t>
+        </is>
+      </c>
+      <c r="E2178" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3938711381</t>
+        </is>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2179" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="C2179" t="inlineStr">
+        <is>
+          <t>Wings of Desire</t>
+        </is>
+      </c>
+      <c r="D2179" t="inlineStr">
+        <is>
+          <t>Your Twenties</t>
+        </is>
+      </c>
+      <c r="E2179" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3975568711</t>
+        </is>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2180" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="C2180" t="inlineStr">
+        <is>
+          <t>Namasenda</t>
+        </is>
+      </c>
+      <c r="D2180" t="inlineStr">
+        <is>
+          <t>Madonna</t>
+        </is>
+      </c>
+      <c r="E2180" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3722040372</t>
+        </is>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2181" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="C2181" t="inlineStr">
+        <is>
+          <t>Stevie Wonder</t>
+        </is>
+      </c>
+      <c r="D2181" t="inlineStr">
+        <is>
+          <t>Superstition</t>
+        </is>
+      </c>
+      <c r="E2181" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/596034702</t>
+        </is>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2182" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="C2182" t="inlineStr">
+        <is>
+          <t>Jorja Smith</t>
+        </is>
+      </c>
+      <c r="D2182" t="inlineStr">
+        <is>
+          <t>What's Done Is Done</t>
+        </is>
+      </c>
+      <c r="E2182" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3987716111</t>
+        </is>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2183" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="C2183" t="inlineStr">
+        <is>
+          <t>They Are Gutting a Body of Water &amp; Horse Jumper of Love</t>
+        </is>
+      </c>
+      <c r="D2183" t="inlineStr">
+        <is>
+          <t>charter spec</t>
+        </is>
+      </c>
+      <c r="E2183" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4002525411</t>
+        </is>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="A2184" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2184" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C2184" t="inlineStr">
+        <is>
+          <t>Westside Cowboy</t>
+        </is>
+      </c>
+      <c r="D2184" t="inlineStr">
+        <is>
+          <t>Kick Stones (The Boys)</t>
+        </is>
+      </c>
+      <c r="E2184" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4019806861</t>
+        </is>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="A2185" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2185" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="C2185" t="inlineStr">
+        <is>
+          <t>Marsy</t>
+        </is>
+      </c>
+      <c r="D2185" t="inlineStr">
+        <is>
+          <t>Magic</t>
+        </is>
+      </c>
+      <c r="E2185" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3972192271</t>
+        </is>
+      </c>
+    </row>
+    <row r="2186">
+      <c r="A2186" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2186" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="C2186" t="inlineStr">
+        <is>
+          <t>The Murder Capital</t>
+        </is>
+      </c>
+      <c r="D2186" t="inlineStr">
+        <is>
+          <t>Words Lost Meaning</t>
+        </is>
+      </c>
+      <c r="E2186" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3079937881</t>
+        </is>
+      </c>
+    </row>
+    <row r="2187">
+      <c r="A2187" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2187" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="C2187" t="inlineStr">
+        <is>
+          <t>Little Simz</t>
+        </is>
+      </c>
+      <c r="D2187" t="inlineStr">
+        <is>
+          <t>Game On (feat. JT)</t>
+        </is>
+      </c>
+      <c r="E2187" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3980007721</t>
+        </is>
+      </c>
+    </row>
+    <row r="2188">
+      <c r="A2188" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2188" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="C2188" t="inlineStr">
+        <is>
+          <t>Kevin Morby</t>
+        </is>
+      </c>
+      <c r="D2188" t="inlineStr">
+        <is>
+          <t>Javelin</t>
+        </is>
+      </c>
+      <c r="E2188" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3786696582</t>
+        </is>
+      </c>
+    </row>
+    <row r="2189">
+      <c r="A2189" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2189" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="C2189" t="inlineStr">
+        <is>
+          <t>Hrishikesh Hirway &amp; Uwade</t>
+        </is>
+      </c>
+      <c r="D2189" t="inlineStr">
+        <is>
+          <t>The Ocean</t>
+        </is>
+      </c>
+      <c r="E2189" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3765815452</t>
+        </is>
+      </c>
+    </row>
+    <row r="2190">
+      <c r="A2190" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B2190" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="C2190" t="inlineStr">
+        <is>
+          <t>Kevin Morby</t>
+        </is>
+      </c>
+      <c r="D2190" t="inlineStr">
+        <is>
+          <t>This Is A Photograph</t>
+        </is>
+      </c>
+      <c r="E2190" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1638155712</t>
+        </is>
+      </c>
+    </row>
+    <row r="2191">
+      <c r="A2191" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2191" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="C2191" t="inlineStr">
+        <is>
+          <t>Mac DeMarco</t>
+        </is>
+      </c>
+      <c r="D2191" t="inlineStr">
+        <is>
+          <t>Freaking Out The Neighborhood</t>
+        </is>
+      </c>
+      <c r="E2191" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/62744398</t>
+        </is>
+      </c>
+    </row>
+    <row r="2192">
+      <c r="A2192" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2192" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="C2192" t="inlineStr">
+        <is>
+          <t>Jorja Smith</t>
+        </is>
+      </c>
+      <c r="D2192" t="inlineStr">
+        <is>
+          <t>Little Things</t>
+        </is>
+      </c>
+      <c r="E2192" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2337181965</t>
+        </is>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="A2193" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2193" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="C2193" t="inlineStr">
+        <is>
+          <t>Patti Smith</t>
+        </is>
+      </c>
+      <c r="D2193" t="inlineStr">
+        <is>
+          <t>Frederick</t>
+        </is>
+      </c>
+      <c r="E2193" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1043238</t>
+        </is>
+      </c>
+    </row>
+    <row r="2194">
+      <c r="A2194" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2194" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="C2194" t="inlineStr">
+        <is>
+          <t>The Human League</t>
+        </is>
+      </c>
+      <c r="D2194" t="inlineStr">
+        <is>
+          <t>Open Your Heart</t>
+        </is>
+      </c>
+      <c r="E2194" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3092932</t>
+        </is>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="A2195" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2195" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="C2195" t="inlineStr">
+        <is>
+          <t>Friendly Fires</t>
+        </is>
+      </c>
+      <c r="D2195" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E2195" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4119478</t>
+        </is>
+      </c>
+    </row>
+    <row r="2196">
+      <c r="A2196" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2196" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="C2196" t="inlineStr">
+        <is>
+          <t>The Smiths</t>
+        </is>
+      </c>
+      <c r="D2196" t="inlineStr">
+        <is>
+          <t>How Soon Is Now?</t>
+        </is>
+      </c>
+      <c r="E2196" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/5093609</t>
+        </is>
+      </c>
+    </row>
+    <row r="2197">
+      <c r="A2197" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2197" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="C2197" t="inlineStr">
+        <is>
+          <t>Jackie Edwards</t>
+        </is>
+      </c>
+      <c r="D2197" t="inlineStr">
+        <is>
+          <t>Hear My Cry</t>
+        </is>
+      </c>
+      <c r="E2197" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/62953799</t>
+        </is>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="A2198" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2198" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="C2198" t="inlineStr">
+        <is>
+          <t>Jade</t>
+        </is>
+      </c>
+      <c r="D2198" t="inlineStr">
+        <is>
+          <t>Don't Walk Away</t>
+        </is>
+      </c>
+      <c r="E2198" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/5617992</t>
+        </is>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="A2199" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2199" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C2199" t="inlineStr">
+        <is>
+          <t>Anderson .Paak</t>
+        </is>
+      </c>
+      <c r="D2199" t="inlineStr">
+        <is>
+          <t>King James</t>
+        </is>
+      </c>
+      <c r="E2199" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/662437262</t>
+        </is>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="A2200" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2200" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C2200" t="inlineStr">
+        <is>
+          <t>Martha Reeves and the Vandellas</t>
+        </is>
+      </c>
+      <c r="D2200" t="inlineStr">
+        <is>
+          <t>Nowhere To Run</t>
+        </is>
+      </c>
+      <c r="E2200" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2288113</t>
+        </is>
+      </c>
+    </row>
+    <row r="2201">
+      <c r="A2201" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2201" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="C2201" t="inlineStr">
+        <is>
+          <t>Jurassic 5</t>
+        </is>
+      </c>
+      <c r="D2201" t="inlineStr">
+        <is>
+          <t>Jayou</t>
+        </is>
+      </c>
+      <c r="E2201" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3073020151</t>
+        </is>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="A2202" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2202" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="C2202" t="inlineStr">
+        <is>
+          <t>Jamie xx</t>
+        </is>
+      </c>
+      <c r="D2202" t="inlineStr">
+        <is>
+          <t>Let's Do It Again</t>
+        </is>
+      </c>
+      <c r="E2202" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1692342827</t>
+        </is>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2203" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="C2203" t="inlineStr">
+        <is>
+          <t>Dexys Midnight Runners</t>
+        </is>
+      </c>
+      <c r="D2203" t="inlineStr">
+        <is>
+          <t>My Life In England Pt. 1</t>
+        </is>
+      </c>
+      <c r="E2203" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3968477371</t>
+        </is>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2204" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="C2204" t="inlineStr">
+        <is>
+          <t>Sugar</t>
+        </is>
+      </c>
+      <c r="D2204" t="inlineStr">
+        <is>
+          <t>If I Can't Change Your Mind</t>
+        </is>
+      </c>
+      <c r="E2204" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3786250872</t>
+        </is>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2205" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="C2205" t="inlineStr">
+        <is>
+          <t>Kano</t>
+        </is>
+      </c>
+      <c r="D2205" t="inlineStr">
+        <is>
+          <t>P's &amp; Q's</t>
+        </is>
+      </c>
+      <c r="E2205" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/83770410</t>
+        </is>
+      </c>
+    </row>
+    <row r="2206">
+      <c r="A2206" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2206" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="C2206" t="inlineStr">
+        <is>
+          <t>Cults</t>
+        </is>
+      </c>
+      <c r="D2206" t="inlineStr">
+        <is>
+          <t>I Can Hardly Make You Mine</t>
+        </is>
+      </c>
+      <c r="E2206" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/71279686</t>
+        </is>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2207" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="C2207" t="inlineStr">
+        <is>
+          <t>Pixies</t>
+        </is>
+      </c>
+      <c r="D2207" t="inlineStr">
+        <is>
+          <t>Here Comes Your Man</t>
+        </is>
+      </c>
+      <c r="E2207" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/945389</t>
+        </is>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2208" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="C2208" t="inlineStr">
+        <is>
+          <t>Junior Murvin</t>
+        </is>
+      </c>
+      <c r="D2208" t="inlineStr">
+        <is>
+          <t>Police And Thieves</t>
+        </is>
+      </c>
+      <c r="E2208" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/118584972</t>
+        </is>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="A2209" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2209" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="C2209" t="inlineStr">
+        <is>
+          <t>Kevin Morby</t>
+        </is>
+      </c>
+      <c r="D2209" t="inlineStr">
+        <is>
+          <t>100,000</t>
+        </is>
+      </c>
+      <c r="E2209" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3786696612</t>
+        </is>
+      </c>
+    </row>
+    <row r="2210">
+      <c r="A2210" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2210" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="C2210" t="inlineStr">
+        <is>
+          <t>Wolf Alice</t>
+        </is>
+      </c>
+      <c r="D2210" t="inlineStr">
+        <is>
+          <t>White Horses</t>
+        </is>
+      </c>
+      <c r="E2210" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3508653281</t>
+        </is>
+      </c>
+    </row>
+    <row r="2211">
+      <c r="A2211" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2211" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="C2211" t="inlineStr">
+        <is>
+          <t>The Adverts</t>
+        </is>
+      </c>
+      <c r="D2211" t="inlineStr">
+        <is>
+          <t>Gary Gilmore's Eyes</t>
+        </is>
+      </c>
+      <c r="E2211" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2126591157</t>
+        </is>
+      </c>
+    </row>
+    <row r="2212">
+      <c r="A2212" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2212" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="C2212" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="D2212" t="inlineStr">
+        <is>
+          <t>I'm Alive</t>
+        </is>
+      </c>
+      <c r="E2212" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4760668</t>
+        </is>
+      </c>
+    </row>
+    <row r="2213">
+      <c r="A2213" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2213" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="C2213" t="inlineStr">
+        <is>
+          <t>Angelic Upstarts</t>
+        </is>
+      </c>
+      <c r="D2213" t="inlineStr">
+        <is>
+          <t>The Sun Never Shines</t>
+        </is>
+      </c>
+      <c r="E2213" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4588824</t>
+        </is>
+      </c>
+    </row>
+    <row r="2214">
+      <c r="A2214" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2214" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="C2214" t="inlineStr">
+        <is>
+          <t>Franz Ferdinand</t>
+        </is>
+      </c>
+      <c r="D2214" t="inlineStr">
+        <is>
+          <t>Darts Of Pleasure</t>
+        </is>
+      </c>
+      <c r="E2214" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4315689</t>
+        </is>
+      </c>
+    </row>
+    <row r="2215">
+      <c r="A2215" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2215" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="C2215" t="inlineStr">
+        <is>
+          <t>The Fall</t>
+        </is>
+      </c>
+      <c r="D2215" t="inlineStr">
+        <is>
+          <t>Hey! Luciani</t>
+        </is>
+      </c>
+      <c r="E2215" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/84787285</t>
+        </is>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="A2216" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2216" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="C2216" t="inlineStr">
+        <is>
+          <t>Charlotte Adigéry &amp; Bolis Pupul</t>
+        </is>
+      </c>
+      <c r="D2216" t="inlineStr">
+        <is>
+          <t>Ceci n'est pas un cliché</t>
+        </is>
+      </c>
+      <c r="E2216" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1503924352</t>
+        </is>
+      </c>
+    </row>
+    <row r="2217">
+      <c r="A2217" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2217" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="C2217" t="inlineStr">
+        <is>
+          <t>Mogwai</t>
+        </is>
+      </c>
+      <c r="D2217" t="inlineStr">
+        <is>
+          <t>Helicon 1</t>
+        </is>
+      </c>
+      <c r="E2217" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/565630772</t>
+        </is>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="A2218" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2218" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C2218" t="inlineStr">
+        <is>
+          <t>Wailing Souls</t>
+        </is>
+      </c>
+      <c r="D2218" t="inlineStr">
+        <is>
+          <t>Firehouse Rock</t>
+        </is>
+      </c>
+      <c r="E2218" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/123491784</t>
+        </is>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2219" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="C2219" t="inlineStr">
+        <is>
+          <t>Lou Reed</t>
+        </is>
+      </c>
+      <c r="D2219" t="inlineStr">
+        <is>
+          <t>I'm So Free</t>
+        </is>
+      </c>
+      <c r="E2219" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/97081754</t>
+        </is>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="A2220" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2220" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="C2220" t="inlineStr">
+        <is>
+          <t>English Teacher</t>
+        </is>
+      </c>
+      <c r="D2220" t="inlineStr">
+        <is>
+          <t>Song About Love</t>
+        </is>
+      </c>
+      <c r="E2220" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2041300517</t>
+        </is>
+      </c>
+    </row>
+    <row r="2221">
+      <c r="A2221" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2221" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="C2221" t="inlineStr">
+        <is>
+          <t>Ramones</t>
+        </is>
+      </c>
+      <c r="D2221" t="inlineStr">
+        <is>
+          <t>Blitzkrieg Bop</t>
+        </is>
+      </c>
+      <c r="E2221" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/131744724</t>
+        </is>
+      </c>
+    </row>
+    <row r="2222">
+      <c r="A2222" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2222" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="C2222" t="inlineStr">
+        <is>
+          <t>The Runaways</t>
+        </is>
+      </c>
+      <c r="D2222" t="inlineStr">
+        <is>
+          <t>Cherry Bomb</t>
+        </is>
+      </c>
+      <c r="E2222" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/5677465</t>
+        </is>
+      </c>
+    </row>
+    <row r="2223">
+      <c r="A2223" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2223" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="C2223" t="inlineStr">
+        <is>
+          <t>Toots &amp; The Maytals</t>
+        </is>
+      </c>
+      <c r="D2223" t="inlineStr">
+        <is>
+          <t>Reggae Got Soul</t>
+        </is>
+      </c>
+      <c r="E2223" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/24203581</t>
+        </is>
+      </c>
+    </row>
+    <row r="2224">
+      <c r="A2224" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2224" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="C2224" t="inlineStr">
+        <is>
+          <t>Pollyfromthedirt</t>
+        </is>
+      </c>
+      <c r="D2224" t="inlineStr">
+        <is>
+          <t>Dont Shoot Now</t>
+        </is>
+      </c>
+      <c r="E2224" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3866651521</t>
+        </is>
+      </c>
+    </row>
+    <row r="2225">
+      <c r="A2225" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2225" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="C2225" t="inlineStr">
+        <is>
+          <t>FKA twigs</t>
+        </is>
+      </c>
+      <c r="D2225" t="inlineStr">
+        <is>
+          <t>Predictable Girl</t>
+        </is>
+      </c>
+      <c r="E2225" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3632195222</t>
+        </is>
+      </c>
+    </row>
+    <row r="2226">
+      <c r="A2226" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2226" t="inlineStr">
+        <is>
+          <t>07:23</t>
+        </is>
+      </c>
+      <c r="C2226" t="inlineStr">
+        <is>
+          <t>Cameron Winter</t>
+        </is>
+      </c>
+      <c r="D2226" t="inlineStr">
+        <is>
+          <t>Love Takes Miles</t>
+        </is>
+      </c>
+      <c r="E2226" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2982937461</t>
+        </is>
+      </c>
+    </row>
+    <row r="2227">
+      <c r="A2227" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2227" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="C2227" t="inlineStr">
+        <is>
+          <t>Dr. Alimantado</t>
+        </is>
+      </c>
+      <c r="D2227" t="inlineStr">
+        <is>
+          <t>Born For A Purpose / Reason For Living</t>
+        </is>
+      </c>
+      <c r="E2227" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/375647711</t>
+        </is>
+      </c>
+    </row>
+    <row r="2228">
+      <c r="A2228" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2228" t="inlineStr">
+        <is>
+          <t>07:03</t>
+        </is>
+      </c>
+      <c r="C2228" t="inlineStr">
+        <is>
+          <t>Depeche Mode</t>
+        </is>
+      </c>
+      <c r="D2228" t="inlineStr">
+        <is>
+          <t>I Feel You</t>
+        </is>
+      </c>
+      <c r="E2228" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/68514212</t>
+        </is>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="A2229" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2229" t="inlineStr">
+        <is>
+          <t>06:58</t>
+        </is>
+      </c>
+      <c r="C2229" t="inlineStr">
+        <is>
+          <t>Mia Doi Todd</t>
+        </is>
+      </c>
+      <c r="D2229" t="inlineStr">
+        <is>
+          <t>Human Experience</t>
+        </is>
+      </c>
+      <c r="E2229" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3941394061</t>
+        </is>
+      </c>
+    </row>
+    <row r="2230">
+      <c r="A2230" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2230" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="C2230" t="inlineStr">
+        <is>
+          <t>Bert Jansch</t>
+        </is>
+      </c>
+      <c r="D2230" t="inlineStr">
+        <is>
+          <t>Oh How Your Love Is Strong</t>
+        </is>
+      </c>
+      <c r="E2230" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3788412612</t>
+        </is>
+      </c>
+    </row>
+    <row r="2231">
+      <c r="A2231" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2231" t="inlineStr">
+        <is>
+          <t>06:34</t>
+        </is>
+      </c>
+      <c r="C2231" t="inlineStr">
+        <is>
+          <t>Blood Orange</t>
+        </is>
+      </c>
+      <c r="D2231" t="inlineStr">
+        <is>
+          <t>Charcoal Baby</t>
+        </is>
+      </c>
+      <c r="E2231" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/539920562</t>
+        </is>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="A2232" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2232" t="inlineStr">
+        <is>
+          <t>06:13</t>
+        </is>
+      </c>
+      <c r="C2232" t="inlineStr">
+        <is>
+          <t>Quando Quango</t>
+        </is>
+      </c>
+      <c r="D2232" t="inlineStr">
+        <is>
+          <t>Love Tempo (Remix)</t>
+        </is>
+      </c>
+      <c r="E2232" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/10990075</t>
+        </is>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="A2233" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2233" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="C2233" t="inlineStr">
+        <is>
+          <t>Primal Scream</t>
+        </is>
+      </c>
+      <c r="D2233" t="inlineStr">
+        <is>
+          <t>Country Girl</t>
+        </is>
+      </c>
+      <c r="E2233" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13183482</t>
+        </is>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="A2234" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2234" t="inlineStr">
+        <is>
+          <t>05:45</t>
+        </is>
+      </c>
+      <c r="C2234" t="inlineStr">
+        <is>
+          <t>Megan Thee Stallion</t>
+        </is>
+      </c>
+      <c r="D2234" t="inlineStr">
+        <is>
+          <t>Like a Freak</t>
+        </is>
+      </c>
+      <c r="E2234" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3061373811</t>
+        </is>
+      </c>
+    </row>
+    <row r="2235">
+      <c r="A2235" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2235" t="inlineStr">
+        <is>
+          <t>05:38</t>
+        </is>
+      </c>
+      <c r="C2235" t="inlineStr">
+        <is>
+          <t>Busta Rhymes</t>
+        </is>
+      </c>
+      <c r="D2235" t="inlineStr">
+        <is>
+          <t>Gimme Some More</t>
+        </is>
+      </c>
+      <c r="E2235" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3822102</t>
+        </is>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="A2236" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2236" t="inlineStr">
+        <is>
+          <t>05:19</t>
+        </is>
+      </c>
+      <c r="C2236" t="inlineStr">
+        <is>
+          <t>Amyl and the Sniffers</t>
+        </is>
+      </c>
+      <c r="D2236" t="inlineStr">
+        <is>
+          <t>Balaclava Lover Boogie</t>
+        </is>
+      </c>
+      <c r="E2236" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1512581352</t>
+        </is>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2237" t="inlineStr">
+        <is>
+          <t>05:10</t>
+        </is>
+      </c>
+      <c r="C2237" t="inlineStr">
+        <is>
+          <t>Little Barrie</t>
+        </is>
+      </c>
+      <c r="D2237" t="inlineStr">
+        <is>
+          <t>Luggin' Hurt</t>
+        </is>
+      </c>
+      <c r="E2237" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3963805061</t>
+        </is>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2238" t="inlineStr">
+        <is>
+          <t>05:10</t>
+        </is>
+      </c>
+      <c r="C2238" t="inlineStr">
+        <is>
+          <t>Funkadelic</t>
+        </is>
+      </c>
+      <c r="D2238" t="inlineStr">
+        <is>
+          <t>Standing On The Verge Of Getting It On</t>
+        </is>
+      </c>
+      <c r="E2238" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1554708472</t>
+        </is>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="A2239" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2239" t="inlineStr">
+        <is>
+          <t>05:01</t>
+        </is>
+      </c>
+      <c r="C2239" t="inlineStr">
+        <is>
+          <t>Roni Size</t>
+        </is>
+      </c>
+      <c r="D2239" t="inlineStr">
+        <is>
+          <t>Heroes</t>
+        </is>
+      </c>
+      <c r="E2239" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2239" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2133889517</t>
+        </is>
+      </c>
+    </row>
+    <row r="2240">
+      <c r="A2240" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2240" t="inlineStr">
+        <is>
+          <t>04:57</t>
+        </is>
+      </c>
+      <c r="C2240" t="inlineStr">
+        <is>
+          <t>Kate Bush</t>
+        </is>
+      </c>
+      <c r="D2240" t="inlineStr">
+        <is>
+          <t>Army Dreamers</t>
+        </is>
+      </c>
+      <c r="E2240" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2173947717</t>
+        </is>
+      </c>
+    </row>
+    <row r="2241">
+      <c r="A2241" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2241" t="inlineStr">
+        <is>
+          <t>04:35</t>
+        </is>
+      </c>
+      <c r="C2241" t="inlineStr">
+        <is>
+          <t>Radiohead</t>
+        </is>
+      </c>
+      <c r="D2241" t="inlineStr">
+        <is>
+          <t>Just</t>
+        </is>
+      </c>
+      <c r="E2241" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/138544269</t>
+        </is>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="A2242" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2242" t="inlineStr">
+        <is>
+          <t>04:18</t>
+        </is>
+      </c>
+      <c r="C2242" t="inlineStr">
+        <is>
+          <t>The Shamen</t>
+        </is>
+      </c>
+      <c r="D2242" t="inlineStr">
+        <is>
+          <t>Ebeneezer Goode</t>
+        </is>
+      </c>
+      <c r="E2242" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/16317006</t>
+        </is>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="A2243" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2243" t="inlineStr">
+        <is>
+          <t>04:02</t>
+        </is>
+      </c>
+      <c r="C2243" t="inlineStr">
+        <is>
+          <t>Public Enemy</t>
+        </is>
+      </c>
+      <c r="D2243" t="inlineStr">
+        <is>
+          <t>Don't Believe The Hype</t>
+        </is>
+      </c>
+      <c r="E2243" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2243" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/89825261</t>
+        </is>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="A2244" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2244" t="inlineStr">
+        <is>
+          <t>03:59</t>
+        </is>
+      </c>
+      <c r="C2244" t="inlineStr">
+        <is>
+          <t>keiyaA</t>
+        </is>
+      </c>
+      <c r="D2244" t="inlineStr">
+        <is>
+          <t>k.i.s.s.</t>
+        </is>
+      </c>
+      <c r="E2244" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3593789332</t>
+        </is>
+      </c>
+    </row>
+    <row r="2245">
+      <c r="A2245" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2245" t="inlineStr">
+        <is>
+          <t>03:49</t>
+        </is>
+      </c>
+      <c r="C2245" t="inlineStr">
+        <is>
+          <t>Barbara Acklin</t>
+        </is>
+      </c>
+      <c r="D2245" t="inlineStr">
+        <is>
+          <t>Am I the Same Girl</t>
+        </is>
+      </c>
+      <c r="E2245" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/116857780</t>
+        </is>
+      </c>
+    </row>
+    <row r="2246">
+      <c r="A2246" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2246" t="inlineStr">
+        <is>
+          <t>03:46</t>
+        </is>
+      </c>
+      <c r="C2246" t="inlineStr">
+        <is>
+          <t>Nina Simone</t>
+        </is>
+      </c>
+      <c r="D2246" t="inlineStr">
+        <is>
+          <t>I Put A Spell On You</t>
+        </is>
+      </c>
+      <c r="E2246" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2246" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/593690882</t>
+        </is>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="A2247" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2247" t="inlineStr">
+        <is>
+          <t>03:34</t>
+        </is>
+      </c>
+      <c r="C2247" t="inlineStr">
+        <is>
+          <t>I. JORDAN</t>
+        </is>
+      </c>
+      <c r="D2247" t="inlineStr">
+        <is>
+          <t>Always Been</t>
+        </is>
+      </c>
+      <c r="E2247" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1771048887</t>
+        </is>
+      </c>
+    </row>
+    <row r="2248">
+      <c r="A2248" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2248" t="inlineStr">
+        <is>
+          <t>03:25</t>
+        </is>
+      </c>
+      <c r="C2248" t="inlineStr">
+        <is>
+          <t>Turnstile</t>
+        </is>
+      </c>
+      <c r="D2248" t="inlineStr">
+        <is>
+          <t>T.L.C. (TURNSTILE LOVE CONNECTION)</t>
+        </is>
+      </c>
+      <c r="E2248" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2248" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1461867152</t>
+        </is>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="A2249" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2249" t="inlineStr">
+        <is>
+          <t>03:22</t>
+        </is>
+      </c>
+      <c r="C2249" t="inlineStr">
+        <is>
+          <t>N.W.A</t>
+        </is>
+      </c>
+      <c r="D2249" t="inlineStr">
+        <is>
+          <t>If It Ain't Ruff</t>
+        </is>
+      </c>
+      <c r="E2249" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/105364506</t>
+        </is>
+      </c>
+    </row>
+    <row r="2250">
+      <c r="A2250" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2250" t="inlineStr">
+        <is>
+          <t>03:16</t>
+        </is>
+      </c>
+      <c r="C2250" t="inlineStr">
+        <is>
+          <t>Sleigh Bells</t>
+        </is>
+      </c>
+      <c r="D2250" t="inlineStr">
+        <is>
+          <t>Rill Rill</t>
+        </is>
+      </c>
+      <c r="E2250" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1563313672</t>
+        </is>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="A2251" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2251" t="inlineStr">
+        <is>
+          <t>03:10</t>
+        </is>
+      </c>
+      <c r="C2251" t="inlineStr">
+        <is>
+          <t>Chaka Khan</t>
+        </is>
+      </c>
+      <c r="D2251" t="inlineStr">
+        <is>
+          <t>Hello Happiness</t>
+        </is>
+      </c>
+      <c r="E2251" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/630799782</t>
+        </is>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2252" t="inlineStr">
+        <is>
+          <t>03:07</t>
+        </is>
+      </c>
+      <c r="C2252" t="inlineStr">
+        <is>
+          <t>Felix da Housecat</t>
+        </is>
+      </c>
+      <c r="D2252" t="inlineStr">
+        <is>
+          <t>Silver Screen Shower Scene</t>
+        </is>
+      </c>
+      <c r="E2252" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2200270597</t>
+        </is>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2253" t="inlineStr">
+        <is>
+          <t>02:53</t>
+        </is>
+      </c>
+      <c r="C2253" t="inlineStr">
+        <is>
+          <t>Bentley Rhythm Ace</t>
+        </is>
+      </c>
+      <c r="D2253" t="inlineStr">
+        <is>
+          <t>Bentley's Gonna Sort You Out</t>
+        </is>
+      </c>
+      <c r="E2253" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2253" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/5151797</t>
+        </is>
+      </c>
+    </row>
+    <row r="2254">
+      <c r="A2254" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2254" t="inlineStr">
+        <is>
+          <t>02:50</t>
+        </is>
+      </c>
+      <c r="C2254" t="inlineStr">
+        <is>
+          <t>St. Vincent</t>
+        </is>
+      </c>
+      <c r="D2254" t="inlineStr">
+        <is>
+          <t>Bad Believer</t>
+        </is>
+      </c>
+      <c r="E2254" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2254" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/94030980</t>
+        </is>
+      </c>
+    </row>
+    <row r="2255">
+      <c r="A2255" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2255" t="inlineStr">
+        <is>
+          <t>02:42</t>
+        </is>
+      </c>
+      <c r="C2255" t="inlineStr">
+        <is>
+          <t>Elastica</t>
+        </is>
+      </c>
+      <c r="D2255" t="inlineStr">
+        <is>
+          <t>Stutter</t>
+        </is>
+      </c>
+      <c r="E2255" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2255" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/97089140</t>
+        </is>
+      </c>
+    </row>
+    <row r="2256">
+      <c r="A2256" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2256" t="inlineStr">
+        <is>
+          <t>02:39</t>
+        </is>
+      </c>
+      <c r="C2256" t="inlineStr">
+        <is>
+          <t>Kendrick Lamar</t>
+        </is>
+      </c>
+      <c r="D2256" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="E2256" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2256" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/73196532</t>
+        </is>
+      </c>
+    </row>
+    <row r="2257">
+      <c r="A2257" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2257" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="C2257" t="inlineStr">
+        <is>
+          <t>Zed Bias</t>
+        </is>
+      </c>
+      <c r="D2257" t="inlineStr">
+        <is>
+          <t>Neighbourhood</t>
+        </is>
+      </c>
+      <c r="E2257" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2257" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1095168812</t>
+        </is>
+      </c>
+    </row>
+    <row r="2258">
+      <c r="A2258" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2258" t="inlineStr">
+        <is>
+          <t>02:29</t>
+        </is>
+      </c>
+      <c r="C2258" t="inlineStr">
+        <is>
+          <t>Dove Ellis</t>
+        </is>
+      </c>
+      <c r="D2258" t="inlineStr">
+        <is>
+          <t>Heaven Has No Wings</t>
+        </is>
+      </c>
+      <c r="E2258" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3606392022</t>
+        </is>
+      </c>
+    </row>
+    <row r="2259">
+      <c r="A2259" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2259" t="inlineStr">
+        <is>
+          <t>02:02</t>
+        </is>
+      </c>
+      <c r="C2259" t="inlineStr">
+        <is>
+          <t>Metronomy</t>
+        </is>
+      </c>
+      <c r="D2259" t="inlineStr">
+        <is>
+          <t>Love Letters</t>
+        </is>
+      </c>
+      <c r="E2259" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/75311311</t>
+        </is>
+      </c>
+    </row>
+    <row r="2260">
+      <c r="A2260" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2260" t="inlineStr">
+        <is>
+          <t>01:54</t>
+        </is>
+      </c>
+      <c r="C2260" t="inlineStr">
+        <is>
+          <t>Oasis</t>
+        </is>
+      </c>
+      <c r="D2260" t="inlineStr">
+        <is>
+          <t>Whatever</t>
+        </is>
+      </c>
+      <c r="E2260" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/985704102</t>
+        </is>
+      </c>
+    </row>
+    <row r="2261">
+      <c r="A2261" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2261" t="inlineStr">
+        <is>
+          <t>01:43</t>
+        </is>
+      </c>
+      <c r="C2261" t="inlineStr">
+        <is>
+          <t>The Streets</t>
+        </is>
+      </c>
+      <c r="D2261" t="inlineStr">
+        <is>
+          <t>Let's Push Things Forward</t>
+        </is>
+      </c>
+      <c r="E2261" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2261" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/6112947</t>
+        </is>
+      </c>
+    </row>
+    <row r="2262">
+      <c r="A2262" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2262" t="inlineStr">
+        <is>
+          <t>01:34</t>
+        </is>
+      </c>
+      <c r="C2262" t="inlineStr">
+        <is>
+          <t>Sports Team</t>
+        </is>
+      </c>
+      <c r="D2262" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="E2262" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1900294657</t>
+        </is>
+      </c>
+    </row>
+    <row r="2263">
+      <c r="A2263" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2263" t="inlineStr">
+        <is>
+          <t>01:22</t>
+        </is>
+      </c>
+      <c r="C2263" t="inlineStr">
+        <is>
+          <t>Ladyhawke</t>
+        </is>
+      </c>
+      <c r="D2263" t="inlineStr">
+        <is>
+          <t>Dusk Till Dawn</t>
+        </is>
+      </c>
+      <c r="E2263" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2203182</t>
+        </is>
+      </c>
+    </row>
+    <row r="2264">
+      <c r="A2264" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2264" t="inlineStr">
+        <is>
+          <t>01:08</t>
+        </is>
+      </c>
+      <c r="C2264" t="inlineStr">
+        <is>
+          <t>Mary Jane Hooper</t>
+        </is>
+      </c>
+      <c r="D2264" t="inlineStr">
+        <is>
+          <t>I've Got Reasons</t>
+        </is>
+      </c>
+      <c r="E2264" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2264" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1858789987</t>
+        </is>
+      </c>
+    </row>
+    <row r="2265">
+      <c r="A2265" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2265" t="inlineStr">
+        <is>
+          <t>00:57</t>
+        </is>
+      </c>
+      <c r="C2265" t="inlineStr">
+        <is>
+          <t>INXS</t>
+        </is>
+      </c>
+      <c r="D2265" t="inlineStr">
+        <is>
+          <t>Never Tear Us Apart</t>
+        </is>
+      </c>
+      <c r="E2265" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/14636764</t>
+        </is>
+      </c>
+    </row>
+    <row r="2266">
+      <c r="A2266" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2266" t="inlineStr">
+        <is>
+          <t>00:51</t>
+        </is>
+      </c>
+      <c r="C2266" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D2266" t="inlineStr">
+        <is>
+          <t>Life In Tokyo</t>
+        </is>
+      </c>
+      <c r="E2266" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/71510573</t>
+        </is>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2267" t="inlineStr">
+        <is>
+          <t>00:46</t>
+        </is>
+      </c>
+      <c r="C2267" t="inlineStr">
+        <is>
+          <t>The Black Keys</t>
+        </is>
+      </c>
+      <c r="D2267" t="inlineStr">
+        <is>
+          <t>You Got To Lose</t>
+        </is>
+      </c>
+      <c r="E2267" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3825790261</t>
+        </is>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="A2268" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2268" t="inlineStr">
+        <is>
+          <t>00:34</t>
+        </is>
+      </c>
+      <c r="C2268" t="inlineStr">
+        <is>
+          <t>The Future Sound of London</t>
+        </is>
+      </c>
+      <c r="D2268" t="inlineStr">
+        <is>
+          <t>Cascade</t>
+        </is>
+      </c>
+      <c r="E2268" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3132775</t>
+        </is>
+      </c>
+    </row>
+    <row r="2269">
+      <c r="A2269" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2269" t="inlineStr">
+        <is>
+          <t>00:25</t>
+        </is>
+      </c>
+      <c r="C2269" t="inlineStr">
+        <is>
+          <t>Ghostpoet</t>
+        </is>
+      </c>
+      <c r="D2269" t="inlineStr">
+        <is>
+          <t>Liiines</t>
+        </is>
+      </c>
+      <c r="E2269" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/106136538</t>
+        </is>
+      </c>
+    </row>
+    <row r="2270">
+      <c r="A2270" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2270" t="inlineStr">
+        <is>
+          <t>00:17</t>
+        </is>
+      </c>
+      <c r="C2270" t="inlineStr">
+        <is>
+          <t>Divorce</t>
+        </is>
+      </c>
+      <c r="D2270" t="inlineStr">
+        <is>
+          <t>Scratch Your Metal</t>
+        </is>
+      </c>
+      <c r="E2270" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2536773521</t>
+        </is>
+      </c>
+    </row>
+    <row r="2271">
+      <c r="A2271" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2271" t="inlineStr">
+        <is>
+          <t>00:12</t>
+        </is>
+      </c>
+      <c r="C2271" t="inlineStr">
+        <is>
+          <t>Florentenes</t>
+        </is>
+      </c>
+      <c r="D2271" t="inlineStr">
+        <is>
+          <t>A Step In The Right Direction</t>
+        </is>
+      </c>
+      <c r="E2271" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3778078032</t>
+        </is>
+      </c>
+    </row>
+    <row r="2272">
+      <c r="A2272" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2272" t="inlineStr">
+        <is>
+          <t>00:08</t>
+        </is>
+      </c>
+      <c r="C2272" t="inlineStr">
+        <is>
+          <t>De La Soul</t>
+        </is>
+      </c>
+      <c r="D2272" t="inlineStr">
+        <is>
+          <t>Eye Know</t>
+        </is>
+      </c>
+      <c r="E2272" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2070202617</t>
+        </is>
+      </c>
+    </row>
+    <row r="2273">
+      <c r="A2273" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2273" t="inlineStr">
+        <is>
+          <t>00:01</t>
+        </is>
+      </c>
+      <c r="C2273" t="inlineStr">
+        <is>
+          <t>Arctic Monkeys</t>
+        </is>
+      </c>
+      <c r="D2273" t="inlineStr">
+        <is>
+          <t>Brianstorm</t>
+        </is>
+      </c>
+      <c r="E2273" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/14633818</t>
         </is>
       </c>
     </row>
@@ -71326,6 +75326,131 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2146" r:id="rId2145"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2147" r:id="rId2146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2148" r:id="rId2147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2149" r:id="rId2148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2150" r:id="rId2149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2151" r:id="rId2150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2152" r:id="rId2151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2153" r:id="rId2152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2154" r:id="rId2153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2155" r:id="rId2154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2156" r:id="rId2155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2157" r:id="rId2156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2158" r:id="rId2157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2159" r:id="rId2158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2160" r:id="rId2159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2161" r:id="rId2160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2162" r:id="rId2161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2163" r:id="rId2162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2164" r:id="rId2163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2165" r:id="rId2164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2166" r:id="rId2165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2167" r:id="rId2166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2168" r:id="rId2167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2169" r:id="rId2168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2170" r:id="rId2169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2171" r:id="rId2170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2172" r:id="rId2171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2173" r:id="rId2172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2174" r:id="rId2173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2175" r:id="rId2174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2176" r:id="rId2175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2177" r:id="rId2176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2178" r:id="rId2177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2179" r:id="rId2178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2180" r:id="rId2179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2181" r:id="rId2180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2182" r:id="rId2181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2183" r:id="rId2182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2184" r:id="rId2183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2185" r:id="rId2184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2186" r:id="rId2185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2187" r:id="rId2186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2188" r:id="rId2187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2189" r:id="rId2188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2190" r:id="rId2189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2191" r:id="rId2190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2192" r:id="rId2191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2193" r:id="rId2192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2194" r:id="rId2193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2195" r:id="rId2194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2196" r:id="rId2195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2197" r:id="rId2196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2198" r:id="rId2197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2199" r:id="rId2198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2200" r:id="rId2199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2201" r:id="rId2200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2202" r:id="rId2201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2203" r:id="rId2202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2204" r:id="rId2203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2205" r:id="rId2204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2206" r:id="rId2205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2207" r:id="rId2206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2208" r:id="rId2207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2209" r:id="rId2208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2210" r:id="rId2209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2211" r:id="rId2210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2212" r:id="rId2211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2213" r:id="rId2212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2214" r:id="rId2213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2215" r:id="rId2214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2216" r:id="rId2215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2217" r:id="rId2216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2218" r:id="rId2217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2219" r:id="rId2218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2220" r:id="rId2219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2221" r:id="rId2220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2222" r:id="rId2221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2223" r:id="rId2222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2224" r:id="rId2223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2225" r:id="rId2224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2226" r:id="rId2225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2227" r:id="rId2226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2228" r:id="rId2227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2229" r:id="rId2228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2230" r:id="rId2229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2231" r:id="rId2230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2232" r:id="rId2231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2233" r:id="rId2232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2234" r:id="rId2233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2235" r:id="rId2234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2236" r:id="rId2235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2237" r:id="rId2236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2238" r:id="rId2237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2239" r:id="rId2238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2240" r:id="rId2239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2241" r:id="rId2240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2242" r:id="rId2241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2243" r:id="rId2242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2244" r:id="rId2243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2245" r:id="rId2244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2246" r:id="rId2245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2247" r:id="rId2246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2248" r:id="rId2247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2249" r:id="rId2248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2250" r:id="rId2249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2251" r:id="rId2250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2252" r:id="rId2251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2253" r:id="rId2252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2254" r:id="rId2253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2255" r:id="rId2254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2256" r:id="rId2255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2257" r:id="rId2256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2258" r:id="rId2257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2259" r:id="rId2258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2260" r:id="rId2259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2261" r:id="rId2260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2262" r:id="rId2261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2263" r:id="rId2262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2264" r:id="rId2263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2265" r:id="rId2264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2266" r:id="rId2265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2267" r:id="rId2266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2268" r:id="rId2267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2269" r:id="rId2268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2270" r:id="rId2269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2271" r:id="rId2270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2272" r:id="rId2271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2273" r:id="rId2272"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/BBC6 Music Log.xlsx
+++ b/output/BBC6 Music Log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2273"/>
+  <dimension ref="A1:F2359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -73174,6 +73174,2758 @@
       <c r="F2273" s="2" t="inlineStr">
         <is>
           <t>https://www.deezer.com/track/14633818</t>
+        </is>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="A2274" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2274" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="C2274" t="inlineStr">
+        <is>
+          <t>Jeshi</t>
+        </is>
+      </c>
+      <c r="D2274" t="inlineStr">
+        <is>
+          <t>girls and boys</t>
+        </is>
+      </c>
+      <c r="E2274" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3975450081</t>
+        </is>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="A2275" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2275" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="C2275" t="inlineStr">
+        <is>
+          <t>Kelsey Lu</t>
+        </is>
+      </c>
+      <c r="D2275" t="inlineStr">
+        <is>
+          <t>Comfort</t>
+        </is>
+      </c>
+      <c r="E2275" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3918841521</t>
+        </is>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="A2276" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2276" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="C2276" t="inlineStr">
+        <is>
+          <t>Vince Staples</t>
+        </is>
+      </c>
+      <c r="D2276" t="inlineStr">
+        <is>
+          <t>White Flag</t>
+        </is>
+      </c>
+      <c r="E2276" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4020784311</t>
+        </is>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2277" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="C2277" t="inlineStr">
+        <is>
+          <t>Arctic Monkeys</t>
+        </is>
+      </c>
+      <c r="D2277" t="inlineStr">
+        <is>
+          <t>Tranquility Base Hotel &amp; Casino</t>
+        </is>
+      </c>
+      <c r="E2277" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/497736972</t>
+        </is>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2278" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="C2278" t="inlineStr">
+        <is>
+          <t>Arctic Monkeys</t>
+        </is>
+      </c>
+      <c r="D2278" t="inlineStr">
+        <is>
+          <t>Do I Wanna Know?</t>
+        </is>
+      </c>
+      <c r="E2278" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/70322130</t>
+        </is>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2279" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="C2279" t="inlineStr">
+        <is>
+          <t>Arctic Monkeys</t>
+        </is>
+      </c>
+      <c r="D2279" t="inlineStr">
+        <is>
+          <t>I Wanna Be Yours</t>
+        </is>
+      </c>
+      <c r="E2279" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2279" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/70322142</t>
+        </is>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2280" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="C2280" t="inlineStr">
+        <is>
+          <t>Arctic Monkeys</t>
+        </is>
+      </c>
+      <c r="D2280" t="inlineStr">
+        <is>
+          <t>Snap Out Of It</t>
+        </is>
+      </c>
+      <c r="E2280" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/70322140</t>
+        </is>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2281" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C2281" t="inlineStr">
+        <is>
+          <t>Arctic Monkeys</t>
+        </is>
+      </c>
+      <c r="D2281" t="inlineStr">
+        <is>
+          <t>Why'd You Only Call Me When You're High?</t>
+        </is>
+      </c>
+      <c r="E2281" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2281" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/70322139</t>
+        </is>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2282" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="C2282" t="inlineStr">
+        <is>
+          <t>Arctic Monkeys</t>
+        </is>
+      </c>
+      <c r="D2282" t="inlineStr">
+        <is>
+          <t>From The Ritz To The Rubble</t>
+        </is>
+      </c>
+      <c r="E2282" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2282" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4315320</t>
+        </is>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2283" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="C2283" t="inlineStr">
+        <is>
+          <t>Mock Tudors</t>
+        </is>
+      </c>
+      <c r="D2283" t="inlineStr">
+        <is>
+          <t>Bin Day</t>
+        </is>
+      </c>
+      <c r="E2283" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2283" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1990120577</t>
+        </is>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2284" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="C2284" t="inlineStr">
+        <is>
+          <t>Kim Weston</t>
+        </is>
+      </c>
+      <c r="D2284" t="inlineStr">
+        <is>
+          <t>Take Me In Your Arms (Rock Me A Little While)</t>
+        </is>
+      </c>
+      <c r="E2284" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/903751192</t>
+        </is>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2285" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="C2285" t="inlineStr">
+        <is>
+          <t>Foxygen</t>
+        </is>
+      </c>
+      <c r="D2285" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E2285" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/64785754</t>
+        </is>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2286" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="C2286" t="inlineStr">
+        <is>
+          <t>Aldous Harding</t>
+        </is>
+      </c>
+      <c r="D2286" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E2286" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3964400841</t>
+        </is>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2287" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="C2287" t="inlineStr">
+        <is>
+          <t>Sufjan Stevens</t>
+        </is>
+      </c>
+      <c r="D2287" t="inlineStr">
+        <is>
+          <t>The Seer's Tower</t>
+        </is>
+      </c>
+      <c r="E2287" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/62743229</t>
+        </is>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2288" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="C2288" t="inlineStr">
+        <is>
+          <t>Cardiacs</t>
+        </is>
+      </c>
+      <c r="D2288" t="inlineStr">
+        <is>
+          <t>Manhoo</t>
+        </is>
+      </c>
+      <c r="E2288" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1226787282</t>
+        </is>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2289" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="C2289" t="inlineStr">
+        <is>
+          <t>Modern Woman</t>
+        </is>
+      </c>
+      <c r="D2289" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="E2289" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2289" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3718048682</t>
+        </is>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2290" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="C2290" t="inlineStr">
+        <is>
+          <t>The Foot &amp; Leg Clinic</t>
+        </is>
+      </c>
+      <c r="D2290" t="inlineStr">
+        <is>
+          <t>Music for Baby Fairy</t>
+        </is>
+      </c>
+      <c r="E2290" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3809347662</t>
+        </is>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2291" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="C2291" t="inlineStr">
+        <is>
+          <t>Cate Le Bon</t>
+        </is>
+      </c>
+      <c r="D2291" t="inlineStr">
+        <is>
+          <t>Are You With Me Now?</t>
+        </is>
+      </c>
+      <c r="E2291" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1925140307</t>
+        </is>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2292" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="C2292" t="inlineStr">
+        <is>
+          <t>Wild Billy Childish &amp; CTMF</t>
+        </is>
+      </c>
+      <c r="D2292" t="inlineStr">
+        <is>
+          <t>House On Fire</t>
+        </is>
+      </c>
+      <c r="E2292" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3840121531</t>
+        </is>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2293" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="C2293" t="inlineStr">
+        <is>
+          <t>Damaged Bug</t>
+        </is>
+      </c>
+      <c r="D2293" t="inlineStr">
+        <is>
+          <t>End of The War</t>
+        </is>
+      </c>
+      <c r="E2293" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3834637691</t>
+        </is>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2294" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C2294" t="inlineStr">
+        <is>
+          <t>The Blind Shake</t>
+        </is>
+      </c>
+      <c r="D2294" t="inlineStr">
+        <is>
+          <t>I Shot All the Birds</t>
+        </is>
+      </c>
+      <c r="E2294" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/131416264</t>
+        </is>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2295" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="C2295" t="inlineStr">
+        <is>
+          <t>Pet Shop Boys</t>
+        </is>
+      </c>
+      <c r="D2295" t="inlineStr">
+        <is>
+          <t>West End Girls</t>
+        </is>
+      </c>
+      <c r="E2295" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2210634367</t>
+        </is>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2296" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="C2296" t="inlineStr">
+        <is>
+          <t>Fanfarlo</t>
+        </is>
+      </c>
+      <c r="D2296" t="inlineStr">
+        <is>
+          <t>You Are One Of The Few Outsiders Who Really Understands Us</t>
+        </is>
+      </c>
+      <c r="E2296" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/87196161</t>
+        </is>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2297" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="C2297" t="inlineStr">
+        <is>
+          <t>Loukeman</t>
+        </is>
+      </c>
+      <c r="D2297" t="inlineStr">
+        <is>
+          <t>All I Could Think Of</t>
+        </is>
+      </c>
+      <c r="E2297" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3839959891</t>
+        </is>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2298" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="C2298" t="inlineStr">
+        <is>
+          <t>Sonic Youth</t>
+        </is>
+      </c>
+      <c r="D2298" t="inlineStr">
+        <is>
+          <t>Bull in the Heather</t>
+        </is>
+      </c>
+      <c r="E2298" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1140377</t>
+        </is>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2299" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="C2299" t="inlineStr">
+        <is>
+          <t>Lena Platonos</t>
+        </is>
+      </c>
+      <c r="D2299" t="inlineStr">
+        <is>
+          <t>Markos</t>
+        </is>
+      </c>
+      <c r="E2299" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/102241236</t>
+        </is>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2300" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="C2300" t="inlineStr">
+        <is>
+          <t>Yottie</t>
+        </is>
+      </c>
+      <c r="D2300" t="inlineStr">
+        <is>
+          <t>little little</t>
+        </is>
+      </c>
+      <c r="E2300" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2356088715</t>
+        </is>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2301" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="C2301" t="inlineStr">
+        <is>
+          <t>Jacques Greene &amp; umru</t>
+        </is>
+      </c>
+      <c r="D2301" t="inlineStr">
+        <is>
+          <t>What You Say</t>
+        </is>
+      </c>
+      <c r="E2301" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4028494331</t>
+        </is>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2302" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="C2302" t="inlineStr">
+        <is>
+          <t>Voka Gentle</t>
+        </is>
+      </c>
+      <c r="D2302" t="inlineStr">
+        <is>
+          <t>K Sees The Deal Go Down (Jonathan Snipes Remix)</t>
+        </is>
+      </c>
+      <c r="E2302" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3995002061</t>
+        </is>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2303" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="C2303" t="inlineStr">
+        <is>
+          <t>Spike</t>
+        </is>
+      </c>
+      <c r="D2303" t="inlineStr">
+        <is>
+          <t>Disappear</t>
+        </is>
+      </c>
+      <c r="E2303" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4021372081</t>
+        </is>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="A2304" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2304" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="C2304" t="inlineStr">
+        <is>
+          <t>Sunday Mourners</t>
+        </is>
+      </c>
+      <c r="D2304" t="inlineStr">
+        <is>
+          <t>In The Shadow Of Your Ego</t>
+        </is>
+      </c>
+      <c r="E2304" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4015264201</t>
+        </is>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2305" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="C2305" t="inlineStr">
+        <is>
+          <t>synecdoche new york</t>
+        </is>
+      </c>
+      <c r="D2305" t="inlineStr">
+        <is>
+          <t>to make you so</t>
+        </is>
+      </c>
+      <c r="E2305" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3995350921</t>
+        </is>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2306" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="C2306" t="inlineStr">
+        <is>
+          <t>Digging for Kanky</t>
+        </is>
+      </c>
+      <c r="D2306" t="inlineStr">
+        <is>
+          <t>Wide Open</t>
+        </is>
+      </c>
+      <c r="E2306" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3868974981</t>
+        </is>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2307" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="C2307" t="inlineStr">
+        <is>
+          <t>TURNSPIT</t>
+        </is>
+      </c>
+      <c r="D2307" t="inlineStr">
+        <is>
+          <t>DO I KNOW YOU?</t>
+        </is>
+      </c>
+      <c r="E2307" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3918127291</t>
+        </is>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2308" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="C2308" t="inlineStr">
+        <is>
+          <t>Warmduscher</t>
+        </is>
+      </c>
+      <c r="D2308" t="inlineStr">
+        <is>
+          <t>Twitchin In The Kitchen</t>
+        </is>
+      </c>
+      <c r="E2308" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1541639482</t>
+        </is>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2309" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="C2309" t="inlineStr">
+        <is>
+          <t>Ibibio Sound Machine</t>
+        </is>
+      </c>
+      <c r="D2309" t="inlineStr">
+        <is>
+          <t>Wanna Come Down</t>
+        </is>
+      </c>
+      <c r="E2309" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3551166961</t>
+        </is>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2310" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="C2310" t="inlineStr">
+        <is>
+          <t>Ash</t>
+        </is>
+      </c>
+      <c r="D2310" t="inlineStr">
+        <is>
+          <t>Burn Baby Burn</t>
+        </is>
+      </c>
+      <c r="E2310" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3801373002</t>
+        </is>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2311" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="C2311" t="inlineStr">
+        <is>
+          <t>A Tribe Called Quest</t>
+        </is>
+      </c>
+      <c r="D2311" t="inlineStr">
+        <is>
+          <t>Bonita Applebum</t>
+        </is>
+      </c>
+      <c r="E2311" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2311" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/14878499</t>
+        </is>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2312" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="C2312" t="inlineStr">
+        <is>
+          <t>New Order</t>
+        </is>
+      </c>
+      <c r="D2312" t="inlineStr">
+        <is>
+          <t>Blue Monday</t>
+        </is>
+      </c>
+      <c r="E2312" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2312" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/131744046</t>
+        </is>
+      </c>
+    </row>
+    <row r="2313">
+      <c r="A2313" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2313" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="C2313" t="inlineStr">
+        <is>
+          <t>The Notorious B.I.G.</t>
+        </is>
+      </c>
+      <c r="D2313" t="inlineStr">
+        <is>
+          <t>Unbelievable</t>
+        </is>
+      </c>
+      <c r="E2313" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2793759</t>
+        </is>
+      </c>
+    </row>
+    <row r="2314">
+      <c r="A2314" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2314" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="C2314" t="inlineStr">
+        <is>
+          <t>The Velvelettes</t>
+        </is>
+      </c>
+      <c r="D2314" t="inlineStr">
+        <is>
+          <t>He Was Really Saying Something</t>
+        </is>
+      </c>
+      <c r="E2314" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1887296</t>
+        </is>
+      </c>
+    </row>
+    <row r="2315">
+      <c r="A2315" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2315" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="C2315" t="inlineStr">
+        <is>
+          <t>Mandy, Indiana</t>
+        </is>
+      </c>
+      <c r="D2315" t="inlineStr">
+        <is>
+          <t>Magazine</t>
+        </is>
+      </c>
+      <c r="E2315" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2315" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3604345092</t>
+        </is>
+      </c>
+    </row>
+    <row r="2316">
+      <c r="A2316" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2316" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="C2316" t="inlineStr">
+        <is>
+          <t>Pharrell Williams</t>
+        </is>
+      </c>
+      <c r="D2316" t="inlineStr">
+        <is>
+          <t>Gust Of Wind</t>
+        </is>
+      </c>
+      <c r="E2316" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/701326582</t>
+        </is>
+      </c>
+    </row>
+    <row r="2317">
+      <c r="A2317" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2317" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="C2317" t="inlineStr">
+        <is>
+          <t>Sky Ferreira</t>
+        </is>
+      </c>
+      <c r="D2317" t="inlineStr">
+        <is>
+          <t>Leash</t>
+        </is>
+      </c>
+      <c r="E2317" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3045345111</t>
+        </is>
+      </c>
+    </row>
+    <row r="2318">
+      <c r="A2318" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2318" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C2318" t="inlineStr">
+        <is>
+          <t>Nirvana</t>
+        </is>
+      </c>
+      <c r="D2318" t="inlineStr">
+        <is>
+          <t>Smells Like Teen Spirit</t>
+        </is>
+      </c>
+      <c r="E2318" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13693497</t>
+        </is>
+      </c>
+    </row>
+    <row r="2319">
+      <c r="A2319" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2319" t="inlineStr">
+        <is>
+          <t>07:56</t>
+        </is>
+      </c>
+      <c r="C2319" t="inlineStr">
+        <is>
+          <t>Pigs Pigs Pigs Pigs Pigs Pigs Pigs</t>
+        </is>
+      </c>
+      <c r="D2319" t="inlineStr">
+        <is>
+          <t>Rubbernecker</t>
+        </is>
+      </c>
+      <c r="E2319" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2319" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/830103802</t>
+        </is>
+      </c>
+    </row>
+    <row r="2320">
+      <c r="A2320" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2320" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="C2320" t="inlineStr">
+        <is>
+          <t>Wu-Lu</t>
+        </is>
+      </c>
+      <c r="D2320" t="inlineStr">
+        <is>
+          <t>Blunted Strings</t>
+        </is>
+      </c>
+      <c r="E2320" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2700756092</t>
+        </is>
+      </c>
+    </row>
+    <row r="2321">
+      <c r="A2321" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2321" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="C2321" t="inlineStr">
+        <is>
+          <t>Nia Archives</t>
+        </is>
+      </c>
+      <c r="D2321" t="inlineStr">
+        <is>
+          <t>Baianá</t>
+        </is>
+      </c>
+      <c r="E2321" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1926908957</t>
+        </is>
+      </c>
+    </row>
+    <row r="2322">
+      <c r="A2322" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2322" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="C2322" t="inlineStr">
+        <is>
+          <t>Belle and Sebastian</t>
+        </is>
+      </c>
+      <c r="D2322" t="inlineStr">
+        <is>
+          <t>Legal Man</t>
+        </is>
+      </c>
+      <c r="E2322" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2502814511</t>
+        </is>
+      </c>
+    </row>
+    <row r="2323">
+      <c r="A2323" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2323" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="C2323" t="inlineStr">
+        <is>
+          <t>Deep Purple</t>
+        </is>
+      </c>
+      <c r="D2323" t="inlineStr">
+        <is>
+          <t>The Painter</t>
+        </is>
+      </c>
+      <c r="E2323" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1762583327</t>
+        </is>
+      </c>
+    </row>
+    <row r="2324">
+      <c r="A2324" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2324" t="inlineStr">
+        <is>
+          <t>07:16</t>
+        </is>
+      </c>
+      <c r="C2324" t="inlineStr">
+        <is>
+          <t>Pink Floyd</t>
+        </is>
+      </c>
+      <c r="D2324" t="inlineStr">
+        <is>
+          <t>The Nile Song</t>
+        </is>
+      </c>
+      <c r="E2324" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/116913918</t>
+        </is>
+      </c>
+    </row>
+    <row r="2325">
+      <c r="A2325" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2325" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="C2325" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="D2325" t="inlineStr">
+        <is>
+          <t>All Right Now</t>
+        </is>
+      </c>
+      <c r="E2325" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/929222</t>
+        </is>
+      </c>
+    </row>
+    <row r="2326">
+      <c r="A2326" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2326" t="inlineStr">
+        <is>
+          <t>06:33</t>
+        </is>
+      </c>
+      <c r="C2326" t="inlineStr">
+        <is>
+          <t>Adventures of Stevie V</t>
+        </is>
+      </c>
+      <c r="D2326" t="inlineStr">
+        <is>
+          <t>Dirty Cash (Money Talks)</t>
+        </is>
+      </c>
+      <c r="E2326" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/78304375</t>
+        </is>
+      </c>
+    </row>
+    <row r="2327">
+      <c r="A2327" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2327" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="C2327" t="inlineStr">
+        <is>
+          <t>EELS</t>
+        </is>
+      </c>
+      <c r="D2327" t="inlineStr">
+        <is>
+          <t>Mr. E's Beautiful Blues</t>
+        </is>
+      </c>
+      <c r="E2327" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2075697127</t>
+        </is>
+      </c>
+    </row>
+    <row r="2328">
+      <c r="A2328" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2328" t="inlineStr">
+        <is>
+          <t>05:56</t>
+        </is>
+      </c>
+      <c r="C2328" t="inlineStr">
+        <is>
+          <t>The Beta Band</t>
+        </is>
+      </c>
+      <c r="D2328" t="inlineStr">
+        <is>
+          <t>Squares</t>
+        </is>
+      </c>
+      <c r="E2328" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/453208372</t>
+        </is>
+      </c>
+    </row>
+    <row r="2329">
+      <c r="A2329" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2329" t="inlineStr">
+        <is>
+          <t>05:33</t>
+        </is>
+      </c>
+      <c r="C2329" t="inlineStr">
+        <is>
+          <t>Jungle</t>
+        </is>
+      </c>
+      <c r="D2329" t="inlineStr">
+        <is>
+          <t>Happy Man</t>
+        </is>
+      </c>
+      <c r="E2329" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/489775242</t>
+        </is>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="A2330" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2330" t="inlineStr">
+        <is>
+          <t>05:26</t>
+        </is>
+      </c>
+      <c r="C2330" t="inlineStr">
+        <is>
+          <t>Goat</t>
+        </is>
+      </c>
+      <c r="D2330" t="inlineStr">
+        <is>
+          <t>Do the Dance</t>
+        </is>
+      </c>
+      <c r="E2330" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1851014557</t>
+        </is>
+      </c>
+    </row>
+    <row r="2331">
+      <c r="A2331" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2331" t="inlineStr">
+        <is>
+          <t>05:16</t>
+        </is>
+      </c>
+      <c r="C2331" t="inlineStr">
+        <is>
+          <t>Saint Etienne</t>
+        </is>
+      </c>
+      <c r="D2331" t="inlineStr">
+        <is>
+          <t>He's On The Phone</t>
+        </is>
+      </c>
+      <c r="E2331" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/362797451</t>
+        </is>
+      </c>
+    </row>
+    <row r="2332">
+      <c r="A2332" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2332" t="inlineStr">
+        <is>
+          <t>04:33</t>
+        </is>
+      </c>
+      <c r="C2332" t="inlineStr">
+        <is>
+          <t>Cat Power</t>
+        </is>
+      </c>
+      <c r="D2332" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="E2332" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/58202301</t>
+        </is>
+      </c>
+    </row>
+    <row r="2333">
+      <c r="A2333" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2333" t="inlineStr">
+        <is>
+          <t>04:26</t>
+        </is>
+      </c>
+      <c r="C2333" t="inlineStr">
+        <is>
+          <t>The Kinks</t>
+        </is>
+      </c>
+      <c r="D2333" t="inlineStr">
+        <is>
+          <t>The Village Green Preservation Society</t>
+        </is>
+      </c>
+      <c r="E2333" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3783329692</t>
+        </is>
+      </c>
+    </row>
+    <row r="2334">
+      <c r="A2334" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2334" t="inlineStr">
+        <is>
+          <t>04:18</t>
+        </is>
+      </c>
+      <c r="C2334" t="inlineStr">
+        <is>
+          <t>Talking Heads</t>
+        </is>
+      </c>
+      <c r="D2334" t="inlineStr">
+        <is>
+          <t>(Nothing But) Flowers</t>
+        </is>
+      </c>
+      <c r="E2334" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/747647</t>
+        </is>
+      </c>
+    </row>
+    <row r="2335">
+      <c r="A2335" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2335" t="inlineStr">
+        <is>
+          <t>04:13</t>
+        </is>
+      </c>
+      <c r="C2335" t="inlineStr">
+        <is>
+          <t>Radiohead</t>
+        </is>
+      </c>
+      <c r="D2335" t="inlineStr">
+        <is>
+          <t>Lotus Flower</t>
+        </is>
+      </c>
+      <c r="E2335" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/138544249</t>
+        </is>
+      </c>
+    </row>
+    <row r="2336">
+      <c r="A2336" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2336" t="inlineStr">
+        <is>
+          <t>04:09</t>
+        </is>
+      </c>
+      <c r="C2336" t="inlineStr">
+        <is>
+          <t>Durand Jones &amp; The Indications</t>
+        </is>
+      </c>
+      <c r="D2336" t="inlineStr">
+        <is>
+          <t>Flower Moon</t>
+        </is>
+      </c>
+      <c r="E2336" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3243621061</t>
+        </is>
+      </c>
+    </row>
+    <row r="2337">
+      <c r="A2337" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2337" t="inlineStr">
+        <is>
+          <t>04:06</t>
+        </is>
+      </c>
+      <c r="C2337" t="inlineStr">
+        <is>
+          <t>Minnie Riperton</t>
+        </is>
+      </c>
+      <c r="D2337" t="inlineStr">
+        <is>
+          <t>Les Fleurs</t>
+        </is>
+      </c>
+      <c r="E2337" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3332223</t>
+        </is>
+      </c>
+    </row>
+    <row r="2338">
+      <c r="A2338" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2338" t="inlineStr">
+        <is>
+          <t>03:54</t>
+        </is>
+      </c>
+      <c r="C2338" t="inlineStr">
+        <is>
+          <t>Angelo De Augustine</t>
+        </is>
+      </c>
+      <c r="D2338" t="inlineStr">
+        <is>
+          <t>Goodbye Baby Blue</t>
+        </is>
+      </c>
+      <c r="E2338" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3776433392</t>
+        </is>
+      </c>
+    </row>
+    <row r="2339">
+      <c r="A2339" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2339" t="inlineStr">
+        <is>
+          <t>03:34</t>
+        </is>
+      </c>
+      <c r="C2339" t="inlineStr">
+        <is>
+          <t>Jessica Winter</t>
+        </is>
+      </c>
+      <c r="D2339" t="inlineStr">
+        <is>
+          <t>L.O.V.E.</t>
+        </is>
+      </c>
+      <c r="E2339" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3266860871</t>
+        </is>
+      </c>
+    </row>
+    <row r="2340">
+      <c r="A2340" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2340" t="inlineStr">
+        <is>
+          <t>03:26</t>
+        </is>
+      </c>
+      <c r="C2340" t="inlineStr">
+        <is>
+          <t>Joy Anonymous</t>
+        </is>
+      </c>
+      <c r="D2340" t="inlineStr">
+        <is>
+          <t>JOY (Light In The Dark)</t>
+        </is>
+      </c>
+      <c r="E2340" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4013862131</t>
+        </is>
+      </c>
+    </row>
+    <row r="2341">
+      <c r="A2341" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2341" t="inlineStr">
+        <is>
+          <t>03:10</t>
+        </is>
+      </c>
+      <c r="C2341" t="inlineStr">
+        <is>
+          <t>Jayda G</t>
+        </is>
+      </c>
+      <c r="D2341" t="inlineStr">
+        <is>
+          <t>All I Need</t>
+        </is>
+      </c>
+      <c r="E2341" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1277103392</t>
+        </is>
+      </c>
+    </row>
+    <row r="2342">
+      <c r="A2342" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2342" t="inlineStr">
+        <is>
+          <t>03:03</t>
+        </is>
+      </c>
+      <c r="C2342" t="inlineStr">
+        <is>
+          <t>Chapterhouse</t>
+        </is>
+      </c>
+      <c r="D2342" t="inlineStr">
+        <is>
+          <t>Pearl</t>
+        </is>
+      </c>
+      <c r="E2342" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/7583408</t>
+        </is>
+      </c>
+    </row>
+    <row r="2343">
+      <c r="A2343" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2343" t="inlineStr">
+        <is>
+          <t>02:59</t>
+        </is>
+      </c>
+      <c r="C2343" t="inlineStr">
+        <is>
+          <t>Slowdive</t>
+        </is>
+      </c>
+      <c r="D2343" t="inlineStr">
+        <is>
+          <t>Souvlaki Space Station</t>
+        </is>
+      </c>
+      <c r="E2343" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/7599574</t>
+        </is>
+      </c>
+    </row>
+    <row r="2344">
+      <c r="A2344" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2344" t="inlineStr">
+        <is>
+          <t>02:51</t>
+        </is>
+      </c>
+      <c r="C2344" t="inlineStr">
+        <is>
+          <t>Ride</t>
+        </is>
+      </c>
+      <c r="D2344" t="inlineStr">
+        <is>
+          <t>Vapour Trail</t>
+        </is>
+      </c>
+      <c r="E2344" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/65088090</t>
+        </is>
+      </c>
+    </row>
+    <row r="2345">
+      <c r="A2345" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2345" t="inlineStr">
+        <is>
+          <t>02:20</t>
+        </is>
+      </c>
+      <c r="C2345" t="inlineStr">
+        <is>
+          <t>TSHA</t>
+        </is>
+      </c>
+      <c r="D2345" t="inlineStr">
+        <is>
+          <t>Dancing In The Shadows</t>
+        </is>
+      </c>
+      <c r="E2345" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1854469517</t>
+        </is>
+      </c>
+    </row>
+    <row r="2346">
+      <c r="A2346" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2346" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="C2346" t="inlineStr">
+        <is>
+          <t>Yeah Yeah Yeahs</t>
+        </is>
+      </c>
+      <c r="D2346" t="inlineStr">
+        <is>
+          <t>Burning</t>
+        </is>
+      </c>
+      <c r="E2346" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1745402837</t>
+        </is>
+      </c>
+    </row>
+    <row r="2347">
+      <c r="A2347" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2347" t="inlineStr">
+        <is>
+          <t>01:57</t>
+        </is>
+      </c>
+      <c r="C2347" t="inlineStr">
+        <is>
+          <t>Unknown Mortal Orchestra</t>
+        </is>
+      </c>
+      <c r="D2347" t="inlineStr">
+        <is>
+          <t>American Guilt</t>
+        </is>
+      </c>
+      <c r="E2347" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/468638872</t>
+        </is>
+      </c>
+    </row>
+    <row r="2348">
+      <c r="A2348" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2348" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="C2348" t="inlineStr">
+        <is>
+          <t>Ritchie</t>
+        </is>
+      </c>
+      <c r="D2348" t="inlineStr">
+        <is>
+          <t>Pelo Interfone</t>
+        </is>
+      </c>
+      <c r="E2348" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/14924895</t>
+        </is>
+      </c>
+    </row>
+    <row r="2349">
+      <c r="A2349" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2349" t="inlineStr">
+        <is>
+          <t>01:34</t>
+        </is>
+      </c>
+      <c r="C2349" t="inlineStr">
+        <is>
+          <t>Everything but the Girl</t>
+        </is>
+      </c>
+      <c r="D2349" t="inlineStr">
+        <is>
+          <t>Tracey In My Room</t>
+        </is>
+      </c>
+      <c r="E2349" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1787742967</t>
+        </is>
+      </c>
+    </row>
+    <row r="2350">
+      <c r="A2350" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2350" t="inlineStr">
+        <is>
+          <t>01:16</t>
+        </is>
+      </c>
+      <c r="C2350" t="inlineStr">
+        <is>
+          <t>The Strokes</t>
+        </is>
+      </c>
+      <c r="D2350" t="inlineStr">
+        <is>
+          <t>Last Nite</t>
+        </is>
+      </c>
+      <c r="E2350" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/15615270</t>
+        </is>
+      </c>
+    </row>
+    <row r="2351">
+      <c r="A2351" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2351" t="inlineStr">
+        <is>
+          <t>01:02</t>
+        </is>
+      </c>
+      <c r="C2351" t="inlineStr">
+        <is>
+          <t>Sudan Archives</t>
+        </is>
+      </c>
+      <c r="D2351" t="inlineStr">
+        <is>
+          <t>Glorious</t>
+        </is>
+      </c>
+      <c r="E2351" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/739390162</t>
+        </is>
+      </c>
+    </row>
+    <row r="2352">
+      <c r="A2352" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2352" t="inlineStr">
+        <is>
+          <t>00:57</t>
+        </is>
+      </c>
+      <c r="C2352" t="inlineStr">
+        <is>
+          <t>Nick Hakim</t>
+        </is>
+      </c>
+      <c r="D2352" t="inlineStr">
+        <is>
+          <t>Real Here Now</t>
+        </is>
+      </c>
+      <c r="E2352" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3965143221</t>
+        </is>
+      </c>
+    </row>
+    <row r="2353">
+      <c r="A2353" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2353" t="inlineStr">
+        <is>
+          <t>00:53</t>
+        </is>
+      </c>
+      <c r="C2353" t="inlineStr">
+        <is>
+          <t>Rufus Wainwright</t>
+        </is>
+      </c>
+      <c r="D2353" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="E2353" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/24271621</t>
+        </is>
+      </c>
+    </row>
+    <row r="2354">
+      <c r="A2354" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2354" t="inlineStr">
+        <is>
+          <t>00:46</t>
+        </is>
+      </c>
+      <c r="C2354" t="inlineStr">
+        <is>
+          <t>Origin Unknown</t>
+        </is>
+      </c>
+      <c r="D2354" t="inlineStr">
+        <is>
+          <t>Valley Of The Shadows</t>
+        </is>
+      </c>
+      <c r="E2354" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2354" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3782897352</t>
+        </is>
+      </c>
+    </row>
+    <row r="2355">
+      <c r="A2355" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2355" t="inlineStr">
+        <is>
+          <t>00:35</t>
+        </is>
+      </c>
+      <c r="C2355" t="inlineStr">
+        <is>
+          <t>David Byrne</t>
+        </is>
+      </c>
+      <c r="D2355" t="inlineStr">
+        <is>
+          <t>Everybody's Coming To My House</t>
+        </is>
+      </c>
+      <c r="E2355" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/466342532</t>
+        </is>
+      </c>
+    </row>
+    <row r="2356">
+      <c r="A2356" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2356" t="inlineStr">
+        <is>
+          <t>00:24</t>
+        </is>
+      </c>
+      <c r="C2356" t="inlineStr">
+        <is>
+          <t>Depeche Mode</t>
+        </is>
+      </c>
+      <c r="D2356" t="inlineStr">
+        <is>
+          <t>New Life</t>
+        </is>
+      </c>
+      <c r="E2356" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2356" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/68511189</t>
+        </is>
+      </c>
+    </row>
+    <row r="2357">
+      <c r="A2357" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2357" t="inlineStr">
+        <is>
+          <t>00:19</t>
+        </is>
+      </c>
+      <c r="C2357" t="inlineStr">
+        <is>
+          <t>Primal Scream</t>
+        </is>
+      </c>
+      <c r="D2357" t="inlineStr">
+        <is>
+          <t>Come Together (7" Mix)</t>
+        </is>
+      </c>
+      <c r="E2357" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2357" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/12711121</t>
+        </is>
+      </c>
+    </row>
+    <row r="2358">
+      <c r="A2358" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2358" t="inlineStr">
+        <is>
+          <t>00:14</t>
+        </is>
+      </c>
+      <c r="C2358" t="inlineStr">
+        <is>
+          <t>Marcos Valle</t>
+        </is>
+      </c>
+      <c r="D2358" t="inlineStr">
+        <is>
+          <t>Estrelar</t>
+        </is>
+      </c>
+      <c r="E2358" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/11085336</t>
+        </is>
+      </c>
+    </row>
+    <row r="2359">
+      <c r="A2359" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B2359" t="inlineStr">
+        <is>
+          <t>00:09</t>
+        </is>
+      </c>
+      <c r="C2359" t="inlineStr">
+        <is>
+          <t>The Comet Is Coming</t>
+        </is>
+      </c>
+      <c r="D2359" t="inlineStr">
+        <is>
+          <t>Summon The Fire</t>
+        </is>
+      </c>
+      <c r="E2359" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/646330872</t>
         </is>
       </c>
     </row>
@@ -75451,6 +78203,92 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2271" r:id="rId2270"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2272" r:id="rId2271"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2273" r:id="rId2272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2274" r:id="rId2273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2275" r:id="rId2274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2276" r:id="rId2275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2277" r:id="rId2276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2278" r:id="rId2277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2279" r:id="rId2278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2280" r:id="rId2279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2281" r:id="rId2280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2282" r:id="rId2281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2283" r:id="rId2282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2284" r:id="rId2283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2285" r:id="rId2284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2286" r:id="rId2285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2287" r:id="rId2286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2288" r:id="rId2287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2289" r:id="rId2288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2290" r:id="rId2289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2291" r:id="rId2290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2292" r:id="rId2291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2293" r:id="rId2292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2294" r:id="rId2293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2295" r:id="rId2294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2296" r:id="rId2295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2297" r:id="rId2296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2298" r:id="rId2297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2299" r:id="rId2298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2300" r:id="rId2299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2301" r:id="rId2300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2302" r:id="rId2301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2303" r:id="rId2302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2304" r:id="rId2303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2305" r:id="rId2304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2306" r:id="rId2305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2307" r:id="rId2306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2308" r:id="rId2307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2309" r:id="rId2308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2310" r:id="rId2309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2311" r:id="rId2310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2312" r:id="rId2311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2313" r:id="rId2312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2314" r:id="rId2313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2315" r:id="rId2314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2316" r:id="rId2315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2317" r:id="rId2316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2318" r:id="rId2317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2319" r:id="rId2318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2320" r:id="rId2319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2321" r:id="rId2320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2322" r:id="rId2321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2323" r:id="rId2322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2324" r:id="rId2323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2325" r:id="rId2324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2326" r:id="rId2325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2327" r:id="rId2326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2328" r:id="rId2327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2329" r:id="rId2328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2330" r:id="rId2329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2331" r:id="rId2330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2332" r:id="rId2331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2333" r:id="rId2332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2334" r:id="rId2333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2335" r:id="rId2334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2336" r:id="rId2335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2337" r:id="rId2336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2338" r:id="rId2337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2339" r:id="rId2338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2340" r:id="rId2339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2341" r:id="rId2340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2342" r:id="rId2341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2343" r:id="rId2342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2344" r:id="rId2343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2345" r:id="rId2344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2346" r:id="rId2345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2347" r:id="rId2346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2348" r:id="rId2347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2349" r:id="rId2348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2350" r:id="rId2349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2351" r:id="rId2350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2352" r:id="rId2351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2353" r:id="rId2352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2354" r:id="rId2353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2355" r:id="rId2354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2356" r:id="rId2355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2357" r:id="rId2356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2358" r:id="rId2357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2359" r:id="rId2358"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/BBC6 Music Log.xlsx
+++ b/output/BBC6 Music Log.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2359"/>
+  <dimension ref="A1:F2488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -75926,6 +75926,4134 @@
       <c r="F2359" s="2" t="inlineStr">
         <is>
           <t>https://www.deezer.com/track/646330872</t>
+        </is>
+      </c>
+    </row>
+    <row r="2360">
+      <c r="A2360" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2360" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="C2360" t="inlineStr">
+        <is>
+          <t>Folamour</t>
+        </is>
+      </c>
+      <c r="D2360" t="inlineStr">
+        <is>
+          <t>These Are Just Places to Me Now</t>
+        </is>
+      </c>
+      <c r="E2360" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/701017372</t>
+        </is>
+      </c>
+    </row>
+    <row r="2361">
+      <c r="A2361" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2361" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="C2361" t="inlineStr">
+        <is>
+          <t>Black Coffee &amp; Thiwe</t>
+        </is>
+      </c>
+      <c r="D2361" t="inlineStr">
+        <is>
+          <t>Crazy (Quentin Harris remix)</t>
+        </is>
+      </c>
+      <c r="E2361" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1898412577</t>
+        </is>
+      </c>
+    </row>
+    <row r="2362">
+      <c r="A2362" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2362" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="C2362" t="inlineStr">
+        <is>
+          <t>DJ Kent</t>
+        </is>
+      </c>
+      <c r="D2362" t="inlineStr">
+        <is>
+          <t>Falling</t>
+        </is>
+      </c>
+      <c r="E2362" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13000194</t>
+        </is>
+      </c>
+    </row>
+    <row r="2363">
+      <c r="A2363" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2363" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="C2363" t="inlineStr">
+        <is>
+          <t>Black Coffee</t>
+        </is>
+      </c>
+      <c r="D2363" t="inlineStr">
+        <is>
+          <t>Superman (feat. Bucie)</t>
+        </is>
+      </c>
+      <c r="E2363" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3153673451</t>
+        </is>
+      </c>
+    </row>
+    <row r="2364">
+      <c r="A2364" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2364" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="C2364" t="inlineStr">
+        <is>
+          <t>Dennis Ferrer</t>
+        </is>
+      </c>
+      <c r="D2364" t="inlineStr">
+        <is>
+          <t>How Do I Let Go</t>
+        </is>
+      </c>
+      <c r="E2364" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2389970525</t>
+        </is>
+      </c>
+    </row>
+    <row r="2365">
+      <c r="A2365" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2365" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="C2365" t="inlineStr">
+        <is>
+          <t>Fish Go Deep &amp; Tracey K</t>
+        </is>
+      </c>
+      <c r="D2365" t="inlineStr">
+        <is>
+          <t>The Cure &amp; The Cause (Dennis Ferrer Remix)</t>
+        </is>
+      </c>
+      <c r="E2365" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3155427641</t>
+        </is>
+      </c>
+    </row>
+    <row r="2366">
+      <c r="A2366" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2366" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="C2366" t="inlineStr">
+        <is>
+          <t>Shaun Escoffery</t>
+        </is>
+      </c>
+      <c r="D2366" t="inlineStr">
+        <is>
+          <t>Days Like This</t>
+        </is>
+      </c>
+      <c r="E2366" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2366" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/92294902</t>
+        </is>
+      </c>
+    </row>
+    <row r="2367">
+      <c r="A2367" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2367" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="C2367" t="inlineStr">
+        <is>
+          <t>Fudge</t>
+        </is>
+      </c>
+      <c r="D2367" t="inlineStr">
+        <is>
+          <t>The Heat Of Your Body</t>
+        </is>
+      </c>
+      <c r="E2367" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3690269322</t>
+        </is>
+      </c>
+    </row>
+    <row r="2368">
+      <c r="A2368" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2368" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="C2368" t="inlineStr">
+        <is>
+          <t>upsammy &amp; Valentina Magaletti</t>
+        </is>
+      </c>
+      <c r="D2368" t="inlineStr">
+        <is>
+          <t>Collide</t>
+        </is>
+      </c>
+      <c r="E2368" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3809247172</t>
+        </is>
+      </c>
+    </row>
+    <row r="2369">
+      <c r="A2369" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2369" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="C2369" t="inlineStr">
+        <is>
+          <t>Tolouse Low Trax</t>
+        </is>
+      </c>
+      <c r="D2369" t="inlineStr">
+        <is>
+          <t>Geo Scan</t>
+        </is>
+      </c>
+      <c r="E2369" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/17189024</t>
+        </is>
+      </c>
+    </row>
+    <row r="2370">
+      <c r="A2370" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2370" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="C2370" t="inlineStr">
+        <is>
+          <t>Tzusing</t>
+        </is>
+      </c>
+      <c r="D2370" t="inlineStr">
+        <is>
+          <t>Exascale</t>
+        </is>
+      </c>
+      <c r="E2370" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2131757297</t>
+        </is>
+      </c>
+    </row>
+    <row r="2371">
+      <c r="A2371" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2371" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="C2371" t="inlineStr">
+        <is>
+          <t>Entrañas</t>
+        </is>
+      </c>
+      <c r="D2371" t="inlineStr">
+        <is>
+          <t>Sapo</t>
+        </is>
+      </c>
+      <c r="E2371" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3459079241</t>
+        </is>
+      </c>
+    </row>
+    <row r="2372">
+      <c r="A2372" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2372" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="C2372" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="D2372" t="inlineStr">
+        <is>
+          <t>Belly (Passing Squall Edit)</t>
+        </is>
+      </c>
+      <c r="E2372" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3317483781</t>
+        </is>
+      </c>
+    </row>
+    <row r="2373">
+      <c r="A2373" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2373" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="C2373" t="inlineStr">
+        <is>
+          <t>Deetron presents Soulmate</t>
+        </is>
+      </c>
+      <c r="D2373" t="inlineStr">
+        <is>
+          <t>Madness</t>
+        </is>
+      </c>
+      <c r="E2373" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4005463541</t>
+        </is>
+      </c>
+    </row>
+    <row r="2374">
+      <c r="A2374" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2374" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="C2374" t="inlineStr">
+        <is>
+          <t>Maōh</t>
+        </is>
+      </c>
+      <c r="D2374" t="inlineStr">
+        <is>
+          <t>Sacrifice</t>
+        </is>
+      </c>
+      <c r="E2374" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2163122647</t>
+        </is>
+      </c>
+    </row>
+    <row r="2375">
+      <c r="A2375" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2375" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="C2375" t="inlineStr">
+        <is>
+          <t>British Murder Boys</t>
+        </is>
+      </c>
+      <c r="D2375" t="inlineStr">
+        <is>
+          <t>It's What You Hide</t>
+        </is>
+      </c>
+      <c r="E2375" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2717435842</t>
+        </is>
+      </c>
+    </row>
+    <row r="2376">
+      <c r="A2376" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2376" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="C2376" t="inlineStr">
+        <is>
+          <t>Jasmín</t>
+        </is>
+      </c>
+      <c r="D2376" t="inlineStr">
+        <is>
+          <t>It's Girls Night</t>
+        </is>
+      </c>
+      <c r="E2376" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3919779071</t>
+        </is>
+      </c>
+    </row>
+    <row r="2377">
+      <c r="A2377" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2377" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="C2377" t="inlineStr">
+        <is>
+          <t>Talismann</t>
+        </is>
+      </c>
+      <c r="D2377" t="inlineStr">
+        <is>
+          <t>ANCHORYST</t>
+        </is>
+      </c>
+      <c r="E2377" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1134700082</t>
+        </is>
+      </c>
+    </row>
+    <row r="2378">
+      <c r="A2378" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2378" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="C2378" t="inlineStr">
+        <is>
+          <t>Nazar</t>
+        </is>
+      </c>
+      <c r="D2378" t="inlineStr">
+        <is>
+          <t>Anticipate</t>
+        </is>
+      </c>
+      <c r="E2378" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3231029111</t>
+        </is>
+      </c>
+    </row>
+    <row r="2379">
+      <c r="A2379" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2379" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="C2379" t="inlineStr">
+        <is>
+          <t>Ween</t>
+        </is>
+      </c>
+      <c r="D2379" t="inlineStr">
+        <is>
+          <t>Freedom Of '76</t>
+        </is>
+      </c>
+      <c r="E2379" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/744609</t>
+        </is>
+      </c>
+    </row>
+    <row r="2380">
+      <c r="A2380" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2380" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C2380" t="inlineStr">
+        <is>
+          <t>Spacemen 3</t>
+        </is>
+      </c>
+      <c r="D2380" t="inlineStr">
+        <is>
+          <t>Big City</t>
+        </is>
+      </c>
+      <c r="E2380" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1054527002</t>
+        </is>
+      </c>
+    </row>
+    <row r="2381">
+      <c r="A2381" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2381" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="C2381" t="inlineStr">
+        <is>
+          <t>Go-Kart Mozart</t>
+        </is>
+      </c>
+      <c r="D2381" t="inlineStr">
+        <is>
+          <t>The Sun</t>
+        </is>
+      </c>
+      <c r="E2381" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1551853952</t>
+        </is>
+      </c>
+    </row>
+    <row r="2382">
+      <c r="A2382" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2382" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="C2382" t="inlineStr">
+        <is>
+          <t>Disgusting Sisters</t>
+        </is>
+      </c>
+      <c r="D2382" t="inlineStr">
+        <is>
+          <t>TGIF (Hot Chip remix)</t>
+        </is>
+      </c>
+      <c r="E2382" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3578563951</t>
+        </is>
+      </c>
+    </row>
+    <row r="2383">
+      <c r="A2383" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2383" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="C2383" t="inlineStr">
+        <is>
+          <t>Lissy Trullie</t>
+        </is>
+      </c>
+      <c r="D2383" t="inlineStr">
+        <is>
+          <t>Ready for the Floor</t>
+        </is>
+      </c>
+      <c r="E2383" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/90727563</t>
+        </is>
+      </c>
+    </row>
+    <row r="2384">
+      <c r="A2384" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2384" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="C2384" t="inlineStr">
+        <is>
+          <t>The Lemonheads</t>
+        </is>
+      </c>
+      <c r="D2384" t="inlineStr">
+        <is>
+          <t>It's A Shame About Ray</t>
+        </is>
+      </c>
+      <c r="E2384" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2122479477</t>
+        </is>
+      </c>
+    </row>
+    <row r="2385">
+      <c r="A2385" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2385" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="C2385" t="inlineStr">
+        <is>
+          <t>DEVO</t>
+        </is>
+      </c>
+      <c r="D2385" t="inlineStr">
+        <is>
+          <t>(I Can't Get No) Satisfaction</t>
+        </is>
+      </c>
+      <c r="E2385" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4382967</t>
+        </is>
+      </c>
+    </row>
+    <row r="2386">
+      <c r="A2386" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2386" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="C2386" t="inlineStr">
+        <is>
+          <t>Nirvana</t>
+        </is>
+      </c>
+      <c r="D2386" t="inlineStr">
+        <is>
+          <t>Heart-Shaped Box</t>
+        </is>
+      </c>
+      <c r="E2386" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/70466227</t>
+        </is>
+      </c>
+    </row>
+    <row r="2387">
+      <c r="A2387" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2387" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="C2387" t="inlineStr">
+        <is>
+          <t>Royal Trux</t>
+        </is>
+      </c>
+      <c r="D2387" t="inlineStr">
+        <is>
+          <t>Waterpark</t>
+        </is>
+      </c>
+      <c r="E2387" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2295693925</t>
+        </is>
+      </c>
+    </row>
+    <row r="2388">
+      <c r="A2388" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2388" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="C2388" t="inlineStr">
+        <is>
+          <t>Pulp</t>
+        </is>
+      </c>
+      <c r="D2388" t="inlineStr">
+        <is>
+          <t>Disco 2000</t>
+        </is>
+      </c>
+      <c r="E2388" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/910079</t>
+        </is>
+      </c>
+    </row>
+    <row r="2389">
+      <c r="A2389" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2389" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="C2389" t="inlineStr">
+        <is>
+          <t>Animal Collective</t>
+        </is>
+      </c>
+      <c r="D2389" t="inlineStr">
+        <is>
+          <t>My Girls</t>
+        </is>
+      </c>
+      <c r="E2389" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2389" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4315555</t>
+        </is>
+      </c>
+    </row>
+    <row r="2390">
+      <c r="A2390" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2390" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="C2390" t="inlineStr">
+        <is>
+          <t>Hot Chip</t>
+        </is>
+      </c>
+      <c r="D2390" t="inlineStr">
+        <is>
+          <t>One Life Stand</t>
+        </is>
+      </c>
+      <c r="E2390" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/376023261</t>
+        </is>
+      </c>
+    </row>
+    <row r="2391">
+      <c r="A2391" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2391" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="C2391" t="inlineStr">
+        <is>
+          <t>Primal Scream</t>
+        </is>
+      </c>
+      <c r="D2391" t="inlineStr">
+        <is>
+          <t>Slip Inside This House</t>
+        </is>
+      </c>
+      <c r="E2391" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/85527676</t>
+        </is>
+      </c>
+    </row>
+    <row r="2392">
+      <c r="A2392" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2392" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="C2392" t="inlineStr">
+        <is>
+          <t>Tom Tom Club</t>
+        </is>
+      </c>
+      <c r="D2392" t="inlineStr">
+        <is>
+          <t>Genius Of Love</t>
+        </is>
+      </c>
+      <c r="E2392" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/14618035</t>
+        </is>
+      </c>
+    </row>
+    <row r="2393">
+      <c r="A2393" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2393" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="C2393" t="inlineStr">
+        <is>
+          <t>Car Seat Headrest</t>
+        </is>
+      </c>
+      <c r="D2393" t="inlineStr">
+        <is>
+          <t>Fill In The Blank</t>
+        </is>
+      </c>
+      <c r="E2393" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/138541009</t>
+        </is>
+      </c>
+    </row>
+    <row r="2394">
+      <c r="A2394" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2394" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="C2394" t="inlineStr">
+        <is>
+          <t>congratulations</t>
+        </is>
+      </c>
+      <c r="D2394" t="inlineStr">
+        <is>
+          <t>Fought 4 Love</t>
+        </is>
+      </c>
+      <c r="E2394" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3505223701</t>
+        </is>
+      </c>
+    </row>
+    <row r="2395">
+      <c r="A2395" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2395" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="C2395" t="inlineStr">
+        <is>
+          <t>The Little Flames</t>
+        </is>
+      </c>
+      <c r="D2395" t="inlineStr">
+        <is>
+          <t>Put Your Dukes Up John</t>
+        </is>
+      </c>
+      <c r="E2395" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/116894706</t>
+        </is>
+      </c>
+    </row>
+    <row r="2396">
+      <c r="A2396" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2396" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="C2396" t="inlineStr">
+        <is>
+          <t>Badly Drawn Boy</t>
+        </is>
+      </c>
+      <c r="D2396" t="inlineStr">
+        <is>
+          <t>Disillusion</t>
+        </is>
+      </c>
+      <c r="E2396" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/950315</t>
+        </is>
+      </c>
+    </row>
+    <row r="2397">
+      <c r="A2397" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2397" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="C2397" t="inlineStr">
+        <is>
+          <t>Telehealth</t>
+        </is>
+      </c>
+      <c r="D2397" t="inlineStr">
+        <is>
+          <t>Yassify Me</t>
+        </is>
+      </c>
+      <c r="E2397" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3807145072</t>
+        </is>
+      </c>
+    </row>
+    <row r="2398">
+      <c r="A2398" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2398" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="C2398" t="inlineStr">
+        <is>
+          <t>Placebo</t>
+        </is>
+      </c>
+      <c r="D2398" t="inlineStr">
+        <is>
+          <t>Nancy Boy</t>
+        </is>
+      </c>
+      <c r="E2398" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1895558227</t>
+        </is>
+      </c>
+    </row>
+    <row r="2399">
+      <c r="A2399" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2399" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="C2399" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="D2399" t="inlineStr">
+        <is>
+          <t>Gold Guns Girls</t>
+        </is>
+      </c>
+      <c r="E2399" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2399" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1758502967</t>
+        </is>
+      </c>
+    </row>
+    <row r="2400">
+      <c r="A2400" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2400" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="C2400" t="inlineStr">
+        <is>
+          <t>Reverend and the Makers</t>
+        </is>
+      </c>
+      <c r="D2400" t="inlineStr">
+        <is>
+          <t>Heavyweight Champion Of The World</t>
+        </is>
+      </c>
+      <c r="E2400" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2400" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/695973632</t>
+        </is>
+      </c>
+    </row>
+    <row r="2401">
+      <c r="A2401" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2401" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="C2401" t="inlineStr">
+        <is>
+          <t>The Strokes</t>
+        </is>
+      </c>
+      <c r="D2401" t="inlineStr">
+        <is>
+          <t>You Only Live Once</t>
+        </is>
+      </c>
+      <c r="E2401" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/15529734</t>
+        </is>
+      </c>
+    </row>
+    <row r="2402">
+      <c r="A2402" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2402" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="C2402" t="inlineStr">
+        <is>
+          <t>Nina Simone</t>
+        </is>
+      </c>
+      <c r="D2402" t="inlineStr">
+        <is>
+          <t>My Baby Just Cares For Me</t>
+        </is>
+      </c>
+      <c r="E2402" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/10218921</t>
+        </is>
+      </c>
+    </row>
+    <row r="2403">
+      <c r="A2403" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2403" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="C2403" t="inlineStr">
+        <is>
+          <t>Perry Como</t>
+        </is>
+      </c>
+      <c r="D2403" t="inlineStr">
+        <is>
+          <t>Papa Loves Mambo</t>
+        </is>
+      </c>
+      <c r="E2403" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/965346</t>
+        </is>
+      </c>
+    </row>
+    <row r="2404">
+      <c r="A2404" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2404" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="C2404" t="inlineStr">
+        <is>
+          <t>Willie Wright</t>
+        </is>
+      </c>
+      <c r="D2404" t="inlineStr">
+        <is>
+          <t>I'm So Happy Now</t>
+        </is>
+      </c>
+      <c r="E2404" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2404" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/71567417</t>
+        </is>
+      </c>
+    </row>
+    <row r="2405">
+      <c r="A2405" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2405" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="C2405" t="inlineStr">
+        <is>
+          <t>Idris Muhammad</t>
+        </is>
+      </c>
+      <c r="D2405" t="inlineStr">
+        <is>
+          <t>Could Heaven Ever Be Like This</t>
+        </is>
+      </c>
+      <c r="E2405" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/138124931</t>
+        </is>
+      </c>
+    </row>
+    <row r="2406">
+      <c r="A2406" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2406" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="C2406" t="inlineStr">
+        <is>
+          <t>D’Angelo</t>
+        </is>
+      </c>
+      <c r="D2406" t="inlineStr">
+        <is>
+          <t>I Found My Smile Again</t>
+        </is>
+      </c>
+      <c r="E2406" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2406" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/10871689</t>
+        </is>
+      </c>
+    </row>
+    <row r="2407">
+      <c r="A2407" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2407" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="C2407" t="inlineStr">
+        <is>
+          <t>Tems</t>
+        </is>
+      </c>
+      <c r="D2407" t="inlineStr">
+        <is>
+          <t>Love Me JeJe</t>
+        </is>
+      </c>
+      <c r="E2407" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2407" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2762250081</t>
+        </is>
+      </c>
+    </row>
+    <row r="2408">
+      <c r="A2408" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2408" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="C2408" t="inlineStr">
+        <is>
+          <t>Patrice Rushen</t>
+        </is>
+      </c>
+      <c r="D2408" t="inlineStr">
+        <is>
+          <t>Haven't You Heard</t>
+        </is>
+      </c>
+      <c r="E2408" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2408" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/434634702</t>
+        </is>
+      </c>
+    </row>
+    <row r="2409">
+      <c r="A2409" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2409" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="C2409" t="inlineStr">
+        <is>
+          <t>Tweet</t>
+        </is>
+      </c>
+      <c r="D2409" t="inlineStr">
+        <is>
+          <t>Boogie 2Nite</t>
+        </is>
+      </c>
+      <c r="E2409" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2409" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/5611639</t>
+        </is>
+      </c>
+    </row>
+    <row r="2410">
+      <c r="A2410" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2410" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="C2410" t="inlineStr">
+        <is>
+          <t>Black Uhuru</t>
+        </is>
+      </c>
+      <c r="D2410" t="inlineStr">
+        <is>
+          <t>Sun Is Shining</t>
+        </is>
+      </c>
+      <c r="E2410" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2410" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/11562563</t>
+        </is>
+      </c>
+    </row>
+    <row r="2411">
+      <c r="A2411" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2411" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="C2411" t="inlineStr">
+        <is>
+          <t>Fred Hammond</t>
+        </is>
+      </c>
+      <c r="D2411" t="inlineStr">
+        <is>
+          <t>This Is The Day</t>
+        </is>
+      </c>
+      <c r="E2411" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2411" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/82486282</t>
+        </is>
+      </c>
+    </row>
+    <row r="2412">
+      <c r="A2412" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2412" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="C2412" t="inlineStr">
+        <is>
+          <t>Sérgio Mendes &amp; Brasil '66</t>
+        </is>
+      </c>
+      <c r="D2412" t="inlineStr">
+        <is>
+          <t>Mas Que Nada</t>
+        </is>
+      </c>
+      <c r="E2412" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/10263253</t>
+        </is>
+      </c>
+    </row>
+    <row r="2413">
+      <c r="A2413" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2413" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="C2413" t="inlineStr">
+        <is>
+          <t>Airto Moreira</t>
+        </is>
+      </c>
+      <c r="D2413" t="inlineStr">
+        <is>
+          <t>Celebration Suite</t>
+        </is>
+      </c>
+      <c r="E2413" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2413" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/15931158</t>
+        </is>
+      </c>
+    </row>
+    <row r="2414">
+      <c r="A2414" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2414" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="C2414" t="inlineStr">
+        <is>
+          <t>Zed Bias &amp; MC Rumpus</t>
+        </is>
+      </c>
+      <c r="D2414" t="inlineStr">
+        <is>
+          <t>Neighbourhood</t>
+        </is>
+      </c>
+      <c r="E2414" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2414" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2501378031</t>
+        </is>
+      </c>
+    </row>
+    <row r="2415">
+      <c r="A2415" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2415" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="C2415" t="inlineStr">
+        <is>
+          <t>Womack &amp; Womack</t>
+        </is>
+      </c>
+      <c r="D2415" t="inlineStr">
+        <is>
+          <t>Teardrops</t>
+        </is>
+      </c>
+      <c r="E2415" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2415" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2516432551</t>
+        </is>
+      </c>
+    </row>
+    <row r="2416">
+      <c r="A2416" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2416" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="C2416" t="inlineStr">
+        <is>
+          <t>Donae’o</t>
+        </is>
+      </c>
+      <c r="D2416" t="inlineStr">
+        <is>
+          <t>Party Hard</t>
+        </is>
+      </c>
+      <c r="E2416" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2416" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/63908199</t>
+        </is>
+      </c>
+    </row>
+    <row r="2417">
+      <c r="A2417" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2417" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="C2417" t="inlineStr">
+        <is>
+          <t>Buju Banton</t>
+        </is>
+      </c>
+      <c r="D2417" t="inlineStr">
+        <is>
+          <t>Champion</t>
+        </is>
+      </c>
+      <c r="E2417" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2417" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1173600382</t>
+        </is>
+      </c>
+    </row>
+    <row r="2418">
+      <c r="A2418" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2418" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="C2418" t="inlineStr">
+        <is>
+          <t>Sampha</t>
+        </is>
+      </c>
+      <c r="D2418" t="inlineStr">
+        <is>
+          <t>Indecision</t>
+        </is>
+      </c>
+      <c r="E2418" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2418" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/85258764</t>
+        </is>
+      </c>
+    </row>
+    <row r="2419">
+      <c r="A2419" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2419" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="C2419" t="inlineStr">
+        <is>
+          <t>The Stranglers</t>
+        </is>
+      </c>
+      <c r="D2419" t="inlineStr">
+        <is>
+          <t>Always The Sun</t>
+        </is>
+      </c>
+      <c r="E2419" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2419" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/869491</t>
+        </is>
+      </c>
+    </row>
+    <row r="2420">
+      <c r="A2420" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2420" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="C2420" t="inlineStr">
+        <is>
+          <t>Hyper Go Go</t>
+        </is>
+      </c>
+      <c r="D2420" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E2420" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1125669872</t>
+        </is>
+      </c>
+    </row>
+    <row r="2421">
+      <c r="A2421" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2421" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="C2421" t="inlineStr">
+        <is>
+          <t>Foals</t>
+        </is>
+      </c>
+      <c r="D2421" t="inlineStr">
+        <is>
+          <t>Mountain At My Gates</t>
+        </is>
+      </c>
+      <c r="E2421" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2421" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1232931732</t>
+        </is>
+      </c>
+    </row>
+    <row r="2422">
+      <c r="A2422" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2422" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="C2422" t="inlineStr">
+        <is>
+          <t>My Bloody Valentine</t>
+        </is>
+      </c>
+      <c r="D2422" t="inlineStr">
+        <is>
+          <t>Only Shallow</t>
+        </is>
+      </c>
+      <c r="E2422" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2422" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/949559</t>
+        </is>
+      </c>
+    </row>
+    <row r="2423">
+      <c r="A2423" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2423" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="C2423" t="inlineStr">
+        <is>
+          <t>The Divine Comedy</t>
+        </is>
+      </c>
+      <c r="D2423" t="inlineStr">
+        <is>
+          <t>Songs Of Love</t>
+        </is>
+      </c>
+      <c r="E2423" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2423" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1546745912</t>
+        </is>
+      </c>
+    </row>
+    <row r="2424">
+      <c r="A2424" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2424" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="C2424" t="inlineStr">
+        <is>
+          <t>The Chemical Brothers</t>
+        </is>
+      </c>
+      <c r="D2424" t="inlineStr">
+        <is>
+          <t>Goodbye</t>
+        </is>
+      </c>
+      <c r="E2424" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2424" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2435127715</t>
+        </is>
+      </c>
+    </row>
+    <row r="2425">
+      <c r="A2425" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2425" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="C2425" t="inlineStr">
+        <is>
+          <t>Peggy Gou</t>
+        </is>
+      </c>
+      <c r="D2425" t="inlineStr">
+        <is>
+          <t>Starry Night</t>
+        </is>
+      </c>
+      <c r="E2425" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2425" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2199719437</t>
+        </is>
+      </c>
+    </row>
+    <row r="2426">
+      <c r="A2426" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2426" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="C2426" t="inlineStr">
+        <is>
+          <t>Divorce</t>
+        </is>
+      </c>
+      <c r="D2426" t="inlineStr">
+        <is>
+          <t>Birds</t>
+        </is>
+      </c>
+      <c r="E2426" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2426" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2536773491</t>
+        </is>
+      </c>
+    </row>
+    <row r="2427">
+      <c r="A2427" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2427" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="C2427" t="inlineStr">
+        <is>
+          <t>Orange Juice</t>
+        </is>
+      </c>
+      <c r="D2427" t="inlineStr">
+        <is>
+          <t>Rip It Up</t>
+        </is>
+      </c>
+      <c r="E2427" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2427" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1861023807</t>
+        </is>
+      </c>
+    </row>
+    <row r="2428">
+      <c r="A2428" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2428" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="C2428" t="inlineStr">
+        <is>
+          <t>Massive Attack</t>
+        </is>
+      </c>
+      <c r="D2428" t="inlineStr">
+        <is>
+          <t>Unfinished Sympathy</t>
+        </is>
+      </c>
+      <c r="E2428" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2428" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/61381707</t>
+        </is>
+      </c>
+    </row>
+    <row r="2429">
+      <c r="A2429" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2429" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="C2429" t="inlineStr">
+        <is>
+          <t>Grandmaster Flash</t>
+        </is>
+      </c>
+      <c r="D2429" t="inlineStr">
+        <is>
+          <t>White Lines (Don't Don't Do It)</t>
+        </is>
+      </c>
+      <c r="E2429" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2429" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3853107</t>
+        </is>
+      </c>
+    </row>
+    <row r="2430">
+      <c r="A2430" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2430" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="C2430" t="inlineStr">
+        <is>
+          <t>Yeah Yeah Yeahs</t>
+        </is>
+      </c>
+      <c r="D2430" t="inlineStr">
+        <is>
+          <t>Maps</t>
+        </is>
+      </c>
+      <c r="E2430" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2430" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/417368992</t>
+        </is>
+      </c>
+    </row>
+    <row r="2431">
+      <c r="A2431" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2431" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="C2431" t="inlineStr">
+        <is>
+          <t>Empire of the Sun</t>
+        </is>
+      </c>
+      <c r="D2431" t="inlineStr">
+        <is>
+          <t>We Are The People</t>
+        </is>
+      </c>
+      <c r="E2431" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2431" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/4286053</t>
+        </is>
+      </c>
+    </row>
+    <row r="2432">
+      <c r="A2432" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2432" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="C2432" t="inlineStr">
+        <is>
+          <t>Cults</t>
+        </is>
+      </c>
+      <c r="D2432" t="inlineStr">
+        <is>
+          <t>Go Outside</t>
+        </is>
+      </c>
+      <c r="E2432" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/12000297</t>
+        </is>
+      </c>
+    </row>
+    <row r="2433">
+      <c r="A2433" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2433" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="C2433" t="inlineStr">
+        <is>
+          <t>The Cult</t>
+        </is>
+      </c>
+      <c r="D2433" t="inlineStr">
+        <is>
+          <t>She Sells Sanctuary</t>
+        </is>
+      </c>
+      <c r="E2433" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2433" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/105426372</t>
+        </is>
+      </c>
+    </row>
+    <row r="2434">
+      <c r="A2434" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2434" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="C2434" t="inlineStr">
+        <is>
+          <t>Parliament</t>
+        </is>
+      </c>
+      <c r="D2434" t="inlineStr">
+        <is>
+          <t>Give Up The Funk (Tear The Roof Off The Sucker)</t>
+        </is>
+      </c>
+      <c r="E2434" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2434" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/118993820</t>
+        </is>
+      </c>
+    </row>
+    <row r="2435">
+      <c r="A2435" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2435" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="C2435" t="inlineStr">
+        <is>
+          <t>Jungle</t>
+        </is>
+      </c>
+      <c r="D2435" t="inlineStr">
+        <is>
+          <t>Keep Moving</t>
+        </is>
+      </c>
+      <c r="E2435" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2435" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1875518177</t>
+        </is>
+      </c>
+    </row>
+    <row r="2436">
+      <c r="A2436" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2436" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="C2436" t="inlineStr">
+        <is>
+          <t>Cate Le Bon</t>
+        </is>
+      </c>
+      <c r="D2436" t="inlineStr">
+        <is>
+          <t>I Can't Help You</t>
+        </is>
+      </c>
+      <c r="E2436" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2436" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1925140297</t>
+        </is>
+      </c>
+    </row>
+    <row r="2437">
+      <c r="A2437" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2437" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="C2437" t="inlineStr">
+        <is>
+          <t>The Smashing Pumpkins</t>
+        </is>
+      </c>
+      <c r="D2437" t="inlineStr">
+        <is>
+          <t>Cherub Rock</t>
+        </is>
+      </c>
+      <c r="E2437" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2437" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/15715632</t>
+        </is>
+      </c>
+    </row>
+    <row r="2438">
+      <c r="A2438" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2438" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="C2438" t="inlineStr">
+        <is>
+          <t>Röyksopp</t>
+        </is>
+      </c>
+      <c r="D2438" t="inlineStr">
+        <is>
+          <t>Poor Leno</t>
+        </is>
+      </c>
+      <c r="E2438" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2438" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/109713890</t>
+        </is>
+      </c>
+    </row>
+    <row r="2439">
+      <c r="A2439" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2439" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="C2439" t="inlineStr">
+        <is>
+          <t>The Sundays</t>
+        </is>
+      </c>
+      <c r="D2439" t="inlineStr">
+        <is>
+          <t>Here's Where The Story Ends</t>
+        </is>
+      </c>
+      <c r="E2439" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2439" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2476993561</t>
+        </is>
+      </c>
+    </row>
+    <row r="2440">
+      <c r="A2440" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2440" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="C2440" t="inlineStr">
+        <is>
+          <t>tUnE-yArDs</t>
+        </is>
+      </c>
+      <c r="D2440" t="inlineStr">
+        <is>
+          <t>Water Fountain</t>
+        </is>
+      </c>
+      <c r="E2440" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2440" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2895688981</t>
+        </is>
+      </c>
+    </row>
+    <row r="2441">
+      <c r="A2441" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2441" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="C2441" t="inlineStr">
+        <is>
+          <t>Ray Charles</t>
+        </is>
+      </c>
+      <c r="D2441" t="inlineStr">
+        <is>
+          <t>Rainy Night In Georgia</t>
+        </is>
+      </c>
+      <c r="E2441" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2441" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/6426850</t>
+        </is>
+      </c>
+    </row>
+    <row r="2442">
+      <c r="A2442" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2442" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="C2442" t="inlineStr">
+        <is>
+          <t>Rocket From the Crypt</t>
+        </is>
+      </c>
+      <c r="D2442" t="inlineStr">
+        <is>
+          <t>On A Rope</t>
+        </is>
+      </c>
+      <c r="E2442" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2442" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/7375677</t>
+        </is>
+      </c>
+    </row>
+    <row r="2443">
+      <c r="A2443" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2443" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="C2443" t="inlineStr">
+        <is>
+          <t>Sufjan Stevens</t>
+        </is>
+      </c>
+      <c r="D2443" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="E2443" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2443" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/62743219</t>
+        </is>
+      </c>
+    </row>
+    <row r="2444">
+      <c r="A2444" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2444" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="C2444" t="inlineStr">
+        <is>
+          <t>Basement Jaxx</t>
+        </is>
+      </c>
+      <c r="D2444" t="inlineStr">
+        <is>
+          <t>Good Luck (feat. Lisa Kekaula)</t>
+        </is>
+      </c>
+      <c r="E2444" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2444" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2204674137</t>
+        </is>
+      </c>
+    </row>
+    <row r="2445">
+      <c r="A2445" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2445" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="C2445" t="inlineStr">
+        <is>
+          <t>DJ Jazzy Jeff &amp; the Fresh Prince</t>
+        </is>
+      </c>
+      <c r="D2445" t="inlineStr">
+        <is>
+          <t>Summertime</t>
+        </is>
+      </c>
+      <c r="E2445" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2445" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/831351</t>
+        </is>
+      </c>
+    </row>
+    <row r="2446">
+      <c r="A2446" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2446" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C2446" t="inlineStr">
+        <is>
+          <t>KAYTRANADA &amp; Charlotte Day Wilson</t>
+        </is>
+      </c>
+      <c r="D2446" t="inlineStr">
+        <is>
+          <t>What You Need</t>
+        </is>
+      </c>
+      <c r="E2446" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2446" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/829306272</t>
+        </is>
+      </c>
+    </row>
+    <row r="2447">
+      <c r="A2447" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2447" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="C2447" t="inlineStr">
+        <is>
+          <t>The Velvelettes</t>
+        </is>
+      </c>
+      <c r="D2447" t="inlineStr">
+        <is>
+          <t>Needle In A Haystack</t>
+        </is>
+      </c>
+      <c r="E2447" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2447" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2604040</t>
+        </is>
+      </c>
+    </row>
+    <row r="2448">
+      <c r="A2448" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2448" t="inlineStr">
+        <is>
+          <t>07:23</t>
+        </is>
+      </c>
+      <c r="C2448" t="inlineStr">
+        <is>
+          <t>The Libertines</t>
+        </is>
+      </c>
+      <c r="D2448" t="inlineStr">
+        <is>
+          <t>Time for Heroes</t>
+        </is>
+      </c>
+      <c r="E2448" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2448" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/951290</t>
+        </is>
+      </c>
+    </row>
+    <row r="2449">
+      <c r="A2449" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2449" t="inlineStr">
+        <is>
+          <t>07:08</t>
+        </is>
+      </c>
+      <c r="C2449" t="inlineStr">
+        <is>
+          <t>Tony Joe White &amp; Flying Mojito Bros</t>
+        </is>
+      </c>
+      <c r="D2449" t="inlineStr">
+        <is>
+          <t>Woman</t>
+        </is>
+      </c>
+      <c r="E2449" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2449" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3852169081</t>
+        </is>
+      </c>
+    </row>
+    <row r="2450">
+      <c r="A2450" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2450" t="inlineStr">
+        <is>
+          <t>06:34</t>
+        </is>
+      </c>
+      <c r="C2450" t="inlineStr">
+        <is>
+          <t>Warpaint</t>
+        </is>
+      </c>
+      <c r="D2450" t="inlineStr">
+        <is>
+          <t>Disco//Very</t>
+        </is>
+      </c>
+      <c r="E2450" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2450" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/73998682</t>
+        </is>
+      </c>
+    </row>
+    <row r="2451">
+      <c r="A2451" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2451" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="C2451" t="inlineStr">
+        <is>
+          <t>Loose Ends</t>
+        </is>
+      </c>
+      <c r="D2451" t="inlineStr">
+        <is>
+          <t>Hangin' On A String</t>
+        </is>
+      </c>
+      <c r="E2451" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2451" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3536744</t>
+        </is>
+      </c>
+    </row>
+    <row r="2452">
+      <c r="A2452" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2452" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="C2452" t="inlineStr">
+        <is>
+          <t>Feist</t>
+        </is>
+      </c>
+      <c r="D2452" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="E2452" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2452" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2226981277</t>
+        </is>
+      </c>
+    </row>
+    <row r="2453">
+      <c r="A2453" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2453" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="C2453" t="inlineStr">
+        <is>
+          <t>Calvin Harris</t>
+        </is>
+      </c>
+      <c r="D2453" t="inlineStr">
+        <is>
+          <t>Acceptable In The 80s</t>
+        </is>
+      </c>
+      <c r="E2453" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2453" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/13132580</t>
+        </is>
+      </c>
+    </row>
+    <row r="2454">
+      <c r="A2454" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2454" t="inlineStr">
+        <is>
+          <t>06:08</t>
+        </is>
+      </c>
+      <c r="C2454" t="inlineStr">
+        <is>
+          <t>Klaxons</t>
+        </is>
+      </c>
+      <c r="D2454" t="inlineStr">
+        <is>
+          <t>Golden Skans</t>
+        </is>
+      </c>
+      <c r="E2454" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2454" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1157378</t>
+        </is>
+      </c>
+    </row>
+    <row r="2455">
+      <c r="A2455" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2455" t="inlineStr">
+        <is>
+          <t>05:34</t>
+        </is>
+      </c>
+      <c r="C2455" t="inlineStr">
+        <is>
+          <t>Jon Hopkins &amp; Kelly Lee Owens</t>
+        </is>
+      </c>
+      <c r="D2455" t="inlineStr">
+        <is>
+          <t>Luminous Spaces</t>
+        </is>
+      </c>
+      <c r="E2455" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2455" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/792989112</t>
+        </is>
+      </c>
+    </row>
+    <row r="2456">
+      <c r="A2456" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2456" t="inlineStr">
+        <is>
+          <t>05:27</t>
+        </is>
+      </c>
+      <c r="C2456" t="inlineStr">
+        <is>
+          <t>Mylo</t>
+        </is>
+      </c>
+      <c r="D2456" t="inlineStr">
+        <is>
+          <t>Drop The Pressure</t>
+        </is>
+      </c>
+      <c r="E2456" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2456" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1895191437</t>
+        </is>
+      </c>
+    </row>
+    <row r="2457">
+      <c r="A2457" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2457" t="inlineStr">
+        <is>
+          <t>05:14</t>
+        </is>
+      </c>
+      <c r="C2457" t="inlineStr">
+        <is>
+          <t>Suzy Q</t>
+        </is>
+      </c>
+      <c r="D2457" t="inlineStr">
+        <is>
+          <t>Tonight</t>
+        </is>
+      </c>
+      <c r="E2457" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2457" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/635832502</t>
+        </is>
+      </c>
+    </row>
+    <row r="2458">
+      <c r="A2458" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2458" t="inlineStr">
+        <is>
+          <t>04:54</t>
+        </is>
+      </c>
+      <c r="C2458" t="inlineStr">
+        <is>
+          <t>Seu Jorge &amp; Beck</t>
+        </is>
+      </c>
+      <c r="D2458" t="inlineStr">
+        <is>
+          <t>River Man</t>
+        </is>
+      </c>
+      <c r="E2458" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2458" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3958774391</t>
+        </is>
+      </c>
+    </row>
+    <row r="2459">
+      <c r="A2459" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2459" t="inlineStr">
+        <is>
+          <t>04:49</t>
+        </is>
+      </c>
+      <c r="C2459" t="inlineStr">
+        <is>
+          <t>Cabaret Voltaire</t>
+        </is>
+      </c>
+      <c r="D2459" t="inlineStr">
+        <is>
+          <t>Just Fascination</t>
+        </is>
+      </c>
+      <c r="E2459" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2459" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/78660817</t>
+        </is>
+      </c>
+    </row>
+    <row r="2460">
+      <c r="A2460" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2460" t="inlineStr">
+        <is>
+          <t>04:41</t>
+        </is>
+      </c>
+      <c r="C2460" t="inlineStr">
+        <is>
+          <t>Dexys Midnight Runners</t>
+        </is>
+      </c>
+      <c r="D2460" t="inlineStr">
+        <is>
+          <t>My Life In England</t>
+        </is>
+      </c>
+      <c r="E2460" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2460" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3968477371</t>
+        </is>
+      </c>
+    </row>
+    <row r="2461">
+      <c r="A2461" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2461" t="inlineStr">
+        <is>
+          <t>04:34</t>
+        </is>
+      </c>
+      <c r="C2461" t="inlineStr">
+        <is>
+          <t>Vampire Weekend</t>
+        </is>
+      </c>
+      <c r="D2461" t="inlineStr">
+        <is>
+          <t>Sunflower</t>
+        </is>
+      </c>
+      <c r="E2461" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2461" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/672770962</t>
+        </is>
+      </c>
+    </row>
+    <row r="2462">
+      <c r="A2462" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2462" t="inlineStr">
+        <is>
+          <t>04:26</t>
+        </is>
+      </c>
+      <c r="C2462" t="inlineStr">
+        <is>
+          <t>Sampha</t>
+        </is>
+      </c>
+      <c r="D2462" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="E2462" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/140875599</t>
+        </is>
+      </c>
+    </row>
+    <row r="2463">
+      <c r="A2463" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2463" t="inlineStr">
+        <is>
+          <t>04:18</t>
+        </is>
+      </c>
+      <c r="C2463" t="inlineStr">
+        <is>
+          <t>1-800 GIRLS</t>
+        </is>
+      </c>
+      <c r="D2463" t="inlineStr">
+        <is>
+          <t>eye contact (feat. Council)</t>
+        </is>
+      </c>
+      <c r="E2463" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2463" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3971497241</t>
+        </is>
+      </c>
+    </row>
+    <row r="2464">
+      <c r="A2464" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2464" t="inlineStr">
+        <is>
+          <t>04:14</t>
+        </is>
+      </c>
+      <c r="C2464" t="inlineStr">
+        <is>
+          <t>Arlo Parks</t>
+        </is>
+      </c>
+      <c r="D2464" t="inlineStr">
+        <is>
+          <t>Caroline</t>
+        </is>
+      </c>
+      <c r="E2464" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2464" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1129199372</t>
+        </is>
+      </c>
+    </row>
+    <row r="2465">
+      <c r="A2465" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2465" t="inlineStr">
+        <is>
+          <t>03:59</t>
+        </is>
+      </c>
+      <c r="C2465" t="inlineStr">
+        <is>
+          <t>Janet Kay</t>
+        </is>
+      </c>
+      <c r="D2465" t="inlineStr">
+        <is>
+          <t>Silly Games</t>
+        </is>
+      </c>
+      <c r="E2465" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2465" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3786368052</t>
+        </is>
+      </c>
+    </row>
+    <row r="2466">
+      <c r="A2466" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2466" t="inlineStr">
+        <is>
+          <t>03:56</t>
+        </is>
+      </c>
+      <c r="C2466" t="inlineStr">
+        <is>
+          <t>Matumbi</t>
+        </is>
+      </c>
+      <c r="D2466" t="inlineStr">
+        <is>
+          <t>Empire Road</t>
+        </is>
+      </c>
+      <c r="E2466" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2466" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2887768902</t>
+        </is>
+      </c>
+    </row>
+    <row r="2467">
+      <c r="A2467" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2467" t="inlineStr">
+        <is>
+          <t>03:51</t>
+        </is>
+      </c>
+      <c r="C2467" t="inlineStr">
+        <is>
+          <t>Dennis Bovell</t>
+        </is>
+      </c>
+      <c r="D2467" t="inlineStr">
+        <is>
+          <t>Rowing</t>
+        </is>
+      </c>
+      <c r="E2467" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2467" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3783186272</t>
+        </is>
+      </c>
+    </row>
+    <row r="2468">
+      <c r="A2468" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2468" t="inlineStr">
+        <is>
+          <t>03:47</t>
+        </is>
+      </c>
+      <c r="C2468" t="inlineStr">
+        <is>
+          <t>Linton Kwesi Johnson</t>
+        </is>
+      </c>
+      <c r="D2468" t="inlineStr">
+        <is>
+          <t>Want Fi Goh Rave</t>
+        </is>
+      </c>
+      <c r="E2468" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2285021</t>
+        </is>
+      </c>
+    </row>
+    <row r="2469">
+      <c r="A2469" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2469" t="inlineStr">
+        <is>
+          <t>03:43</t>
+        </is>
+      </c>
+      <c r="C2469" t="inlineStr">
+        <is>
+          <t>Orange Juice</t>
+        </is>
+      </c>
+      <c r="D2469" t="inlineStr">
+        <is>
+          <t>Flesh of My Flesh (12" Version)</t>
+        </is>
+      </c>
+      <c r="E2469" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2469" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1899499617</t>
+        </is>
+      </c>
+    </row>
+    <row r="2470">
+      <c r="A2470" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2470" t="inlineStr">
+        <is>
+          <t>03:39</t>
+        </is>
+      </c>
+      <c r="C2470" t="inlineStr">
+        <is>
+          <t>The Slits</t>
+        </is>
+      </c>
+      <c r="D2470" t="inlineStr">
+        <is>
+          <t>Typical Girls</t>
+        </is>
+      </c>
+      <c r="E2470" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1140837</t>
+        </is>
+      </c>
+    </row>
+    <row r="2471">
+      <c r="A2471" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2471" t="inlineStr">
+        <is>
+          <t>03:27</t>
+        </is>
+      </c>
+      <c r="C2471" t="inlineStr">
+        <is>
+          <t>MGMT</t>
+        </is>
+      </c>
+      <c r="D2471" t="inlineStr">
+        <is>
+          <t>Little Dark Age</t>
+        </is>
+      </c>
+      <c r="E2471" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2471" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/457602422</t>
+        </is>
+      </c>
+    </row>
+    <row r="2472">
+      <c r="A2472" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2472" t="inlineStr">
+        <is>
+          <t>03:24</t>
+        </is>
+      </c>
+      <c r="C2472" t="inlineStr">
+        <is>
+          <t>Lava La Rue &amp; Foster the People</t>
+        </is>
+      </c>
+      <c r="D2472" t="inlineStr">
+        <is>
+          <t>JET LAGGED</t>
+        </is>
+      </c>
+      <c r="E2472" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2472" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3911906741</t>
+        </is>
+      </c>
+    </row>
+    <row r="2473">
+      <c r="A2473" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2473" t="inlineStr">
+        <is>
+          <t>03:01</t>
+        </is>
+      </c>
+      <c r="C2473" t="inlineStr">
+        <is>
+          <t>Laura Marling</t>
+        </is>
+      </c>
+      <c r="D2473" t="inlineStr">
+        <is>
+          <t>Master Hunter</t>
+        </is>
+      </c>
+      <c r="E2473" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2473" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/67317642</t>
+        </is>
+      </c>
+    </row>
+    <row r="2474">
+      <c r="A2474" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2474" t="inlineStr">
+        <is>
+          <t>02:57</t>
+        </is>
+      </c>
+      <c r="C2474" t="inlineStr">
+        <is>
+          <t>Maribou State</t>
+        </is>
+      </c>
+      <c r="D2474" t="inlineStr">
+        <is>
+          <t>Nervous Tics (feat. Holly Walker)</t>
+        </is>
+      </c>
+      <c r="E2474" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2474" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/510203452</t>
+        </is>
+      </c>
+    </row>
+    <row r="2475">
+      <c r="A2475" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2475" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C2475" t="inlineStr">
+        <is>
+          <t>St. Panther</t>
+        </is>
+      </c>
+      <c r="D2475" t="inlineStr">
+        <is>
+          <t>Highway</t>
+        </is>
+      </c>
+      <c r="E2475" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2475" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2275344937</t>
+        </is>
+      </c>
+    </row>
+    <row r="2476">
+      <c r="A2476" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2476" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="C2476" t="inlineStr">
+        <is>
+          <t>BURNS</t>
+        </is>
+      </c>
+      <c r="D2476" t="inlineStr">
+        <is>
+          <t>Talamanca</t>
+        </is>
+      </c>
+      <c r="E2476" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2476" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1502313592</t>
+        </is>
+      </c>
+    </row>
+    <row r="2477">
+      <c r="A2477" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2477" t="inlineStr">
+        <is>
+          <t>01:55</t>
+        </is>
+      </c>
+      <c r="C2477" t="inlineStr">
+        <is>
+          <t>Loose Joints</t>
+        </is>
+      </c>
+      <c r="D2477" t="inlineStr">
+        <is>
+          <t>Is It All over My Face?</t>
+        </is>
+      </c>
+      <c r="E2477" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2477" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3726665172</t>
+        </is>
+      </c>
+    </row>
+    <row r="2478">
+      <c r="A2478" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2478" t="inlineStr">
+        <is>
+          <t>01:34</t>
+        </is>
+      </c>
+      <c r="C2478" t="inlineStr">
+        <is>
+          <t>Neil Young</t>
+        </is>
+      </c>
+      <c r="D2478" t="inlineStr">
+        <is>
+          <t>Heart Of Gold</t>
+        </is>
+      </c>
+      <c r="E2478" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3826694</t>
+        </is>
+      </c>
+    </row>
+    <row r="2479">
+      <c r="A2479" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2479" t="inlineStr">
+        <is>
+          <t>01:21</t>
+        </is>
+      </c>
+      <c r="C2479" t="inlineStr">
+        <is>
+          <t>Altern 8</t>
+        </is>
+      </c>
+      <c r="D2479" t="inlineStr">
+        <is>
+          <t>E-Vapor-8</t>
+        </is>
+      </c>
+      <c r="E2479" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2479" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/109665816</t>
+        </is>
+      </c>
+    </row>
+    <row r="2480">
+      <c r="A2480" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2480" t="inlineStr">
+        <is>
+          <t>01:16</t>
+        </is>
+      </c>
+      <c r="C2480" t="inlineStr">
+        <is>
+          <t>David Bowie</t>
+        </is>
+      </c>
+      <c r="D2480" t="inlineStr">
+        <is>
+          <t>Modern Love</t>
+        </is>
+      </c>
+      <c r="E2480" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2480" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/730342582</t>
+        </is>
+      </c>
+    </row>
+    <row r="2481">
+      <c r="A2481" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2481" t="inlineStr">
+        <is>
+          <t>01:13</t>
+        </is>
+      </c>
+      <c r="C2481" t="inlineStr">
+        <is>
+          <t>Fontaines D.C.</t>
+        </is>
+      </c>
+      <c r="D2481" t="inlineStr">
+        <is>
+          <t>Big</t>
+        </is>
+      </c>
+      <c r="E2481" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2481" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3124676251</t>
+        </is>
+      </c>
+    </row>
+    <row r="2482">
+      <c r="A2482" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2482" t="inlineStr">
+        <is>
+          <t>01:09</t>
+        </is>
+      </c>
+      <c r="C2482" t="inlineStr">
+        <is>
+          <t>High Contrast</t>
+        </is>
+      </c>
+      <c r="D2482" t="inlineStr">
+        <is>
+          <t>Racing Green</t>
+        </is>
+      </c>
+      <c r="E2482" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2482" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3050389831</t>
+        </is>
+      </c>
+    </row>
+    <row r="2483">
+      <c r="A2483" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2483" t="inlineStr">
+        <is>
+          <t>01:03</t>
+        </is>
+      </c>
+      <c r="C2483" t="inlineStr">
+        <is>
+          <t>Tame Impala</t>
+        </is>
+      </c>
+      <c r="D2483" t="inlineStr">
+        <is>
+          <t>Dracula</t>
+        </is>
+      </c>
+      <c r="E2483" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2483" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3818963601</t>
+        </is>
+      </c>
+    </row>
+    <row r="2484">
+      <c r="A2484" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2484" t="inlineStr">
+        <is>
+          <t>00:52</t>
+        </is>
+      </c>
+      <c r="C2484" t="inlineStr">
+        <is>
+          <t>The Postal Service</t>
+        </is>
+      </c>
+      <c r="D2484" t="inlineStr">
+        <is>
+          <t>Such Great Heights</t>
+        </is>
+      </c>
+      <c r="E2484" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2484" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/1137149682</t>
+        </is>
+      </c>
+    </row>
+    <row r="2485">
+      <c r="A2485" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2485" t="inlineStr">
+        <is>
+          <t>00:50</t>
+        </is>
+      </c>
+      <c r="C2485" t="inlineStr">
+        <is>
+          <t>Two Door Cinema Club</t>
+        </is>
+      </c>
+      <c r="D2485" t="inlineStr">
+        <is>
+          <t>Something Good Can Work</t>
+        </is>
+      </c>
+      <c r="E2485" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2485" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3026050191</t>
+        </is>
+      </c>
+    </row>
+    <row r="2486">
+      <c r="A2486" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2486" t="inlineStr">
+        <is>
+          <t>00:47</t>
+        </is>
+      </c>
+      <c r="C2486" t="inlineStr">
+        <is>
+          <t>Inner City</t>
+        </is>
+      </c>
+      <c r="D2486" t="inlineStr">
+        <is>
+          <t>Big Fun</t>
+        </is>
+      </c>
+      <c r="E2486" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2486" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3133682</t>
+        </is>
+      </c>
+    </row>
+    <row r="2487">
+      <c r="A2487" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2487" t="inlineStr">
+        <is>
+          <t>00:35</t>
+        </is>
+      </c>
+      <c r="C2487" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="D2487" t="inlineStr">
+        <is>
+          <t>1901</t>
+        </is>
+      </c>
+      <c r="E2487" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2487" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/3026048721</t>
+        </is>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B2488" t="inlineStr">
+        <is>
+          <t>00:20</t>
+        </is>
+      </c>
+      <c r="C2488" t="inlineStr">
+        <is>
+          <t>Mk.gee</t>
+        </is>
+      </c>
+      <c r="D2488" t="inlineStr">
+        <is>
+          <t>Lonely Fight</t>
+        </is>
+      </c>
+      <c r="E2488" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F2488" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deezer.com/track/2935002371</t>
         </is>
       </c>
     </row>
@@ -78289,6 +82417,135 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2357" r:id="rId2356"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2358" r:id="rId2357"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2359" r:id="rId2358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2360" r:id="rId2359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2361" r:id="rId2360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2362" r:id="rId2361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2363" r:id="rId2362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2364" r:id="rId2363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2365" r:id="rId2364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2366" r:id="rId2365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2367" r:id="rId2366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2368" r:id="rId2367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2369" r:id="rId2368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2370" r:id="rId2369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2371" r:id="rId2370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2372" r:id="rId2371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2373" r:id="rId2372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2374" r:id="rId2373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2375" r:id="rId2374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2376" r:id="rId2375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2377" r:id="rId2376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2378" r:id="rId2377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2379" r:id="rId2378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2380" r:id="rId2379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2381" r:id="rId2380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2382" r:id="rId2381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2383" r:id="rId2382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2384" r:id="rId2383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2385" r:id="rId2384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2386" r:id="rId2385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2387" r:id="rId2386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2388" r:id="rId2387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2389" r:id="rId2388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2390" r:id="rId2389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2391" r:id="rId2390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2392" r:id="rId2391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2393" r:id="rId2392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2394" r:id="rId2393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2395" r:id="rId2394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2396" r:id="rId2395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2397" r:id="rId2396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2398" r:id="rId2397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2399" r:id="rId2398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2400" r:id="rId2399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2401" r:id="rId2400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2402" r:id="rId2401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2403" r:id="rId2402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2404" r:id="rId2403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2405" r:id="rId2404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2406" r:id="rId2405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2407" r:id="rId2406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2408" r:id="rId2407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2409" r:id="rId2408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2410" r:id="rId2409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2411" r:id="rId2410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2412" r:id="rId2411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2413" r:id="rId2412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2414" r:id="rId2413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2415" r:id="rId2414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2416" r:id="rId2415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2417" r:id="rId2416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2418" r:id="rId2417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2419" r:id="rId2418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2420" r:id="rId2419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2421" r:id="rId2420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2422" r:id="rId2421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2423" r:id="rId2422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2424" r:id="rId2423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2425" r:id="rId2424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2426" r:id="rId2425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2427" r:id="rId2426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2428" r:id="rId2427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2429" r:id="rId2428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2430" r:id="rId2429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2431" r:id="rId2430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2432" r:id="rId2431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2433" r:id="rId2432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2434" r:id="rId2433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2435" r:id="rId2434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2436" r:id="rId2435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2437" r:id="rId2436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2438" r:id="rId2437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2439" r:id="rId2438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2440" r:id="rId2439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2441" r:id="rId2440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2442" r:id="rId2441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2443" r:id="rId2442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2444" r:id="rId2443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2445" r:id="rId2444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2446" r:id="rId2445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2447" r:id="rId2446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2448" r:id="rId2447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2449" r:id="rId2448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2450" r:id="rId2449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2451" r:id="rId2450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2452" r:id="rId2451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2453" r:id="rId2452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2454" r:id="rId2453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2455" r:id="rId2454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2456" r:id="rId2455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2457" r:id="rId2456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2458" r:id="rId2457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2459" r:id="rId2458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2460" r:id="rId2459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2461" r:id="rId2460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2462" r:id="rId2461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2463" r:id="rId2462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2464" r:id="rId2463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2465" r:id="rId2464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2466" r:id="rId2465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2467" r:id="rId2466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2468" r:id="rId2467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2469" r:id="rId2468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2470" r:id="rId2469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2471" r:id="rId2470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2472" r:id="rId2471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2473" r:id="rId2472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2474" r:id="rId2473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2475" r:id="rId2474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2476" r:id="rId2475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2477" r:id="rId2476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2478" r:id="rId2477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2479" r:id="rId2478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2480" r:id="rId2479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2481" r:id="rId2480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2482" r:id="rId2481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2483" r:id="rId2482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2484" r:id="rId2483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2485" r:id="rId2484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2486" r:id="rId2485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2487" r:id="rId2486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2488" r:id="rId2487"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
